--- a/주52시간_3개월_현황_요약_0902.xlsx
+++ b/주52시간_3개월_현황_요약_0902.xlsx
@@ -11,6 +11,7 @@
     <sheet name="아모레 생산" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'0.요약'!$A$1:$R$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
   </definedNames>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -155,62 +156,56 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
       <color rgb="007F7F7F"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
@@ -218,12 +213,23 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00C00000"/>
-      <sz val="9"/>
+      <sz val="7.5"/>
     </font>
   </fonts>
   <fills count="11">
@@ -281,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -830,6 +836,50 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -839,7 +889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1232,103 +1282,111 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="23" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="24" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="23" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="28" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="29" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1873,2724 +1931,1853 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="130" min="1" max="1"/>
-    <col width="20" customWidth="1" style="130" min="2" max="2"/>
-    <col width="18" customWidth="1" style="130" min="3" max="3"/>
-    <col width="13" customWidth="1" style="130" min="4" max="4"/>
-    <col width="11" customWidth="1" style="130" min="5" max="5"/>
-    <col width="11" customWidth="1" style="130" min="6" max="6"/>
-    <col width="15" customWidth="1" style="130" min="7" max="7"/>
-    <col width="14" customWidth="1" style="130" min="8" max="8"/>
-    <col width="16" customWidth="1" style="130" min="9" max="9"/>
+    <col width="10" customWidth="1" style="130" min="1" max="1"/>
+    <col width="6.5" customWidth="1" style="130" min="2" max="2"/>
+    <col width="7.5" customWidth="1" style="130" min="3" max="3"/>
+    <col width="6.5" customWidth="1" style="130" min="4" max="4"/>
+    <col width="7.5" customWidth="1" style="130" min="5" max="5"/>
+    <col width="6.5" customWidth="1" style="130" min="6" max="6"/>
+    <col width="10" customWidth="1" style="130" min="7" max="7"/>
+    <col width="6.5" customWidth="1" style="130" min="8" max="8"/>
+    <col width="7.5" customWidth="1" style="130" min="9" max="9"/>
+    <col width="6.5" customWidth="1" style="130" min="10" max="10"/>
+    <col width="7.5" customWidth="1" style="130" min="11" max="11"/>
+    <col width="6.5" customWidth="1" style="130" min="12" max="12"/>
+    <col width="10" customWidth="1" style="130" min="13" max="13"/>
+    <col width="6.5" customWidth="1" style="130" min="14" max="14"/>
+    <col width="7.5" customWidth="1" style="130" min="15" max="15"/>
+    <col width="6.5" customWidth="1" style="130" min="16" max="16"/>
+    <col width="7.5" customWidth="1" style="130" min="17" max="17"/>
+    <col width="6.5" customWidth="1" style="130" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="130">
+    <row r="1" ht="22" customHeight="1" s="130">
       <c r="A1" s="131" t="inlineStr">
         <is>
           <t>주 52시간 3개월(6~8월) 시간외근무 현황 — 요약</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="132" t="inlineStr">
-        <is>
-          <t>기준: 연장근로 한도 주 12시간 × 13주 = 156시간 / 월 환산 51.4H(30일) · 53.1H(31일). 원본 2개 시트는 수정하지 않았음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="130">
-      <c r="A4" s="133" t="inlineStr">
+      <c r="B1" s="132" t="n"/>
+      <c r="C1" s="132" t="n"/>
+      <c r="D1" s="132" t="n"/>
+      <c r="E1" s="132" t="n"/>
+      <c r="F1" s="132" t="n"/>
+      <c r="G1" s="132" t="n"/>
+      <c r="H1" s="132" t="n"/>
+      <c r="I1" s="132" t="n"/>
+      <c r="J1" s="132" t="n"/>
+      <c r="K1" s="132" t="n"/>
+      <c r="L1" s="132" t="n"/>
+      <c r="M1" s="132" t="n"/>
+      <c r="N1" s="132" t="n"/>
+      <c r="O1" s="132" t="n"/>
+      <c r="P1" s="132" t="n"/>
+      <c r="Q1" s="132" t="n"/>
+      <c r="R1" s="132" t="n"/>
+    </row>
+    <row r="2" ht="12" customHeight="1" s="130">
+      <c r="A2" s="133" t="inlineStr">
+        <is>
+          <t>기준: 연장 한도 주 12H × 13주 = 156H  ·  9월 가용 = min(156 − 7·8월 실적, 51.4H)  |  원본 2개 시트 미수정  |  2026.09.02</t>
+        </is>
+      </c>
+      <c r="B2" s="134" t="n"/>
+      <c r="C2" s="134" t="n"/>
+      <c r="D2" s="134" t="n"/>
+      <c r="E2" s="134" t="n"/>
+      <c r="F2" s="134" t="n"/>
+      <c r="G2" s="134" t="n"/>
+      <c r="H2" s="134" t="n"/>
+      <c r="I2" s="134" t="n"/>
+      <c r="J2" s="134" t="n"/>
+      <c r="K2" s="134" t="n"/>
+      <c r="L2" s="134" t="n"/>
+      <c r="M2" s="134" t="n"/>
+      <c r="N2" s="134" t="n"/>
+      <c r="O2" s="134" t="n"/>
+      <c r="P2" s="134" t="n"/>
+      <c r="Q2" s="134" t="n"/>
+      <c r="R2" s="134" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1" s="130">
+      <c r="A3" s="135" t="inlineStr">
         <is>
           <t>① 전체 현황</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="130">
-      <c r="A5" s="134" t="inlineStr">
+      <c r="B3" s="136" t="n"/>
+      <c r="C3" s="136" t="n"/>
+      <c r="D3" s="136" t="n"/>
+      <c r="E3" s="136" t="n"/>
+      <c r="F3" s="136" t="n"/>
+      <c r="G3" s="136" t="n"/>
+      <c r="H3" s="136" t="n"/>
+      <c r="I3" s="136" t="n"/>
+      <c r="J3" s="136" t="n"/>
+      <c r="K3" s="136" t="n"/>
+      <c r="L3" s="136" t="n"/>
+      <c r="M3" s="136" t="n"/>
+      <c r="N3" s="136" t="n"/>
+      <c r="O3" s="136" t="n"/>
+      <c r="P3" s="136" t="n"/>
+      <c r="Q3" s="136" t="n"/>
+      <c r="R3" s="136" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" s="130">
+      <c r="A4" s="137" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B5" s="134" t="inlineStr">
+      <c r="B4" s="137" t="inlineStr">
         <is>
           <t>인원</t>
         </is>
       </c>
-      <c r="C5" s="134" t="inlineStr">
-        <is>
-          <t>3개월 합계(H)</t>
-        </is>
-      </c>
-      <c r="D5" s="134" t="inlineStr">
-        <is>
-          <t>인당 평균(H)</t>
-        </is>
-      </c>
-      <c r="E5" s="134" t="inlineStr">
-        <is>
-          <t>156H 초과 인원</t>
-        </is>
-      </c>
-      <c r="F5" s="134" t="inlineStr">
-        <is>
-          <t>초과분 합계(H)</t>
-        </is>
-      </c>
-      <c r="G5" s="134" t="inlineStr">
-        <is>
-          <t>9월 가용 연장(H)</t>
-        </is>
-      </c>
-      <c r="H5" s="134" t="inlineStr">
+      <c r="C4" s="137" t="inlineStr">
+        <is>
+          <t>3개월 계(H)</t>
+        </is>
+      </c>
+      <c r="D4" s="137" t="inlineStr">
+        <is>
+          <t>인당(H)</t>
+        </is>
+      </c>
+      <c r="E4" s="137" t="inlineStr">
+        <is>
+          <t>156H 초과</t>
+        </is>
+      </c>
+      <c r="F4" s="137" t="inlineStr">
+        <is>
+          <t>초과분(H)</t>
+        </is>
+      </c>
+      <c r="G4" s="137" t="inlineStr">
+        <is>
+          <t>9월 가용(H)</t>
+        </is>
+      </c>
+      <c r="H4" s="137" t="inlineStr">
         <is>
           <t>인당 가용(H)</t>
         </is>
       </c>
-      <c r="I5" s="134" t="inlineStr">
-        <is>
-          <t>9월 잔업 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="135" t="inlineStr">
-        <is>
-          <t>아모레 업무</t>
-        </is>
-      </c>
-      <c r="B6" s="136" t="n">
+      <c r="I4" s="137" t="inlineStr">
+        <is>
+          <t>9월 편성 불가</t>
+        </is>
+      </c>
+      <c r="J4" s="138" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="K4" s="139" t="n"/>
+      <c r="L4" s="139" t="n"/>
+      <c r="M4" s="139" t="n"/>
+      <c r="N4" s="139" t="n"/>
+      <c r="O4" s="139" t="n"/>
+      <c r="P4" s="139" t="n"/>
+      <c r="Q4" s="139" t="n"/>
+      <c r="R4" s="139" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1" s="130">
+      <c r="A5" s="140" t="inlineStr">
+        <is>
+          <t>업무도급</t>
+        </is>
+      </c>
+      <c r="B5" s="141" t="n">
         <v>88</v>
       </c>
-      <c r="C6" s="136" t="n">
+      <c r="C5" s="141" t="n">
         <v>7680</v>
       </c>
-      <c r="D6" s="137" t="n">
+      <c r="D5" s="142" t="n">
         <v>87.27272727272727</v>
       </c>
-      <c r="E6" s="138" t="n">
+      <c r="E5" s="143" t="n">
         <v>16</v>
       </c>
-      <c r="F6" s="139" t="n">
+      <c r="F5" s="144" t="n">
         <v>744</v>
       </c>
-      <c r="G6" s="140" t="n">
+      <c r="G5" s="145" t="n">
         <v>4068.800000000004</v>
       </c>
-      <c r="H6" s="137" t="n">
+      <c r="H5" s="142" t="n">
         <v>46.23636363636368</v>
       </c>
-      <c r="I6" s="139" t="n">
+      <c r="I5" s="144" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="135" t="inlineStr">
-        <is>
-          <t>아모레 생산</t>
-        </is>
-      </c>
-      <c r="B7" s="136" t="n">
+      <c r="J5" s="146" t="inlineStr">
+        <is>
+          <t>239명 중 34명이 이미 3개월 156H 초과 (초과분 1,219H)</t>
+        </is>
+      </c>
+      <c r="K5" s="147" t="n"/>
+      <c r="L5" s="147" t="n"/>
+      <c r="M5" s="147" t="n"/>
+      <c r="N5" s="147" t="n"/>
+      <c r="O5" s="147" t="n"/>
+      <c r="P5" s="147" t="n"/>
+      <c r="Q5" s="147" t="n"/>
+      <c r="R5" s="147" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1" s="130">
+      <c r="A6" s="140" t="inlineStr">
+        <is>
+          <t>생산도급</t>
+        </is>
+      </c>
+      <c r="B6" s="141" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="136" t="n">
+      <c r="C6" s="141" t="n">
         <v>13825</v>
       </c>
-      <c r="D7" s="137" t="n">
+      <c r="D6" s="142" t="n">
         <v>91.55629139072848</v>
       </c>
-      <c r="E7" s="138" t="n">
+      <c r="E6" s="143" t="n">
         <v>18</v>
       </c>
-      <c r="F7" s="139" t="n">
+      <c r="F6" s="144" t="n">
         <v>475</v>
       </c>
-      <c r="G7" s="140" t="n">
+      <c r="G6" s="145" t="n">
         <v>7334.099999999984</v>
       </c>
-      <c r="H7" s="137" t="n">
+      <c r="H6" s="142" t="n">
         <v>48.57019867549658</v>
       </c>
-      <c r="I7" s="139" t="n">
+      <c r="I6" s="144" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="J6" s="146" t="inlineStr">
+        <is>
+          <t>9월 추가 편성 가능 연장 전사 11,403H — 38주 대응의 상한</t>
+        </is>
+      </c>
+      <c r="K6" s="147" t="n"/>
+      <c r="L6" s="147" t="n"/>
+      <c r="M6" s="147" t="n"/>
+      <c r="N6" s="147" t="n"/>
+      <c r="O6" s="147" t="n"/>
+      <c r="P6" s="147" t="n"/>
+      <c r="Q6" s="147" t="n"/>
+      <c r="R6" s="147" t="n"/>
+    </row>
+    <row r="7" ht="13" customHeight="1" s="130">
+      <c r="A7" s="140" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B7" s="148" t="n">
+        <v>239</v>
+      </c>
+      <c r="C7" s="148" t="n">
+        <v>21505</v>
+      </c>
+      <c r="D7" s="149" t="n">
+        <v>89.97907949790795</v>
+      </c>
+      <c r="E7" s="143" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" s="150" t="n">
+        <v>1219</v>
+      </c>
+      <c r="G7" s="148" t="n">
+        <v>11402.89999999999</v>
+      </c>
+      <c r="H7" s="149" t="n">
+        <v>47.71087866108782</v>
+      </c>
+      <c r="I7" s="150" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="151" t="inlineStr">
+        <is>
+          <t>7·8월만으로 156H 초과 → 9월 편성 불가 4명 (세척실 3 · PM 1)</t>
+        </is>
+      </c>
+      <c r="K7" s="147" t="n"/>
+      <c r="L7" s="147" t="n"/>
+      <c r="M7" s="147" t="n"/>
+      <c r="N7" s="147" t="n"/>
+      <c r="O7" s="147" t="n"/>
+      <c r="P7" s="147" t="n"/>
+      <c r="Q7" s="147" t="n"/>
+      <c r="R7" s="147" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1" s="130">
       <c r="A8" s="135" t="inlineStr">
         <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B8" s="141" t="n">
-        <v>239</v>
-      </c>
-      <c r="C8" s="141" t="n">
-        <v>21505</v>
-      </c>
-      <c r="D8" s="142" t="n">
-        <v>89.97907949790795</v>
-      </c>
-      <c r="E8" s="138" t="n">
-        <v>34</v>
-      </c>
-      <c r="F8" s="143" t="n">
-        <v>1219</v>
-      </c>
-      <c r="G8" s="141" t="n">
-        <v>11402.89999999999</v>
-      </c>
-      <c r="H8" s="142" t="n">
-        <v>47.71087866108782</v>
-      </c>
-      <c r="I8" s="143" t="n">
+          <t>② 공정 · 라인별 현황 및 9월 여력</t>
+        </is>
+      </c>
+      <c r="B8" s="136" t="n"/>
+      <c r="C8" s="136" t="n"/>
+      <c r="D8" s="136" t="n"/>
+      <c r="E8" s="136" t="n"/>
+      <c r="F8" s="136" t="n"/>
+      <c r="G8" s="136" t="n"/>
+      <c r="H8" s="136" t="n"/>
+      <c r="I8" s="136" t="n"/>
+      <c r="J8" s="136" t="n"/>
+      <c r="K8" s="136" t="n"/>
+      <c r="L8" s="136" t="n"/>
+      <c r="M8" s="136" t="n"/>
+      <c r="N8" s="136" t="n"/>
+      <c r="O8" s="136" t="n"/>
+      <c r="P8" s="136" t="n"/>
+      <c r="Q8" s="136" t="n"/>
+      <c r="R8" s="136" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="130">
+      <c r="A9" s="137" t="inlineStr">
+        <is>
+          <t>공정 / 라인</t>
+        </is>
+      </c>
+      <c r="B9" s="137" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="C9" s="137" t="inlineStr">
+        <is>
+          <t>3개월
+평균(H)</t>
+        </is>
+      </c>
+      <c r="D9" s="137" t="inlineStr">
+        <is>
+          <t>156H
+초과</t>
+        </is>
+      </c>
+      <c r="E9" s="137" t="inlineStr">
+        <is>
+          <t>9월 가용
+(H)</t>
+        </is>
+      </c>
+      <c r="F9" s="137" t="inlineStr">
+        <is>
+          <t>여력</t>
+        </is>
+      </c>
+      <c r="G9" s="137" t="inlineStr">
+        <is>
+          <t>공정 / 라인</t>
+        </is>
+      </c>
+      <c r="H9" s="137" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="I9" s="137" t="inlineStr">
+        <is>
+          <t>3개월
+평균(H)</t>
+        </is>
+      </c>
+      <c r="J9" s="137" t="inlineStr">
+        <is>
+          <t>156H
+초과</t>
+        </is>
+      </c>
+      <c r="K9" s="137" t="inlineStr">
+        <is>
+          <t>9월 가용
+(H)</t>
+        </is>
+      </c>
+      <c r="L9" s="137" t="inlineStr">
+        <is>
+          <t>여력</t>
+        </is>
+      </c>
+      <c r="M9" s="137" t="inlineStr">
+        <is>
+          <t>공정 / 라인</t>
+        </is>
+      </c>
+      <c r="N9" s="137" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="O9" s="137" t="inlineStr">
+        <is>
+          <t>3개월
+평균(H)</t>
+        </is>
+      </c>
+      <c r="P9" s="137" t="inlineStr">
+        <is>
+          <t>156H
+초과</t>
+        </is>
+      </c>
+      <c r="Q9" s="137" t="inlineStr">
+        <is>
+          <t>9월 가용
+(H)</t>
+        </is>
+      </c>
+      <c r="R9" s="137" t="inlineStr">
+        <is>
+          <t>여력</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="12" customHeight="1" s="130">
+      <c r="A10" s="152" t="inlineStr">
+        <is>
+          <t>주임 (생)</t>
+        </is>
+      </c>
+      <c r="B10" s="141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="153" t="n">
+        <v>189.8333333333333</v>
+      </c>
+      <c r="D10" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="145" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F10" s="155" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="G10" s="156" t="inlineStr">
+        <is>
+          <t>튜브 (생)</t>
+        </is>
+      </c>
+      <c r="H10" s="141" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" s="142" t="n">
+        <v>110.6176470588235</v>
+      </c>
+      <c r="J10" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="145" t="n">
+        <v>813.5999999999998</v>
+      </c>
+      <c r="L10" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M10" s="156" t="inlineStr">
+        <is>
+          <t>PM장 (생)</t>
+        </is>
+      </c>
+      <c r="N10" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="142" t="n">
+        <v>56</v>
+      </c>
+      <c r="P10" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="145" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="R10" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="12" customHeight="1" s="130">
+      <c r="A11" s="152" t="inlineStr">
+        <is>
+          <t>HnB (생)</t>
+        </is>
+      </c>
+      <c r="B11" s="141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="153" t="n">
+        <v>167.7</v>
+      </c>
+      <c r="D11" s="154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="145" t="n">
+        <v>191.8</v>
+      </c>
+      <c r="F11" s="158" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G11" s="156" t="inlineStr">
+        <is>
+          <t>직선 (생)</t>
+        </is>
+      </c>
+      <c r="H11" s="141" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" s="142" t="n">
+        <v>109.7083333333333</v>
+      </c>
+      <c r="J11" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="145" t="n">
+        <v>1178</v>
+      </c>
+      <c r="L11" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M11" s="156" t="inlineStr">
+        <is>
+          <t>염모 (생)</t>
+        </is>
+      </c>
+      <c r="N11" s="141" t="n">
+        <v>27</v>
+      </c>
+      <c r="O11" s="142" t="n">
+        <v>41.53703703703704</v>
+      </c>
+      <c r="P11" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="145" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="R11" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="12" customHeight="1" s="130">
+      <c r="A12" s="152" t="inlineStr">
+        <is>
+          <t>세척실 (업)</t>
+        </is>
+      </c>
+      <c r="B12" s="141" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="153" t="n">
+        <v>150.7142857142857</v>
+      </c>
+      <c r="D12" s="154" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="145" t="n">
+        <v>470.6999999999999</v>
+      </c>
+      <c r="F12" s="158" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G12" s="156" t="inlineStr">
+        <is>
+          <t>행정 (생)</t>
+        </is>
+      </c>
+      <c r="H12" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="142" t="n">
+        <v>101</v>
+      </c>
+      <c r="J12" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="145" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="L12" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M12" s="156" t="inlineStr">
+        <is>
+          <t>(미기재) (업)</t>
+        </is>
+      </c>
+      <c r="N12" s="141" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" s="130">
-      <c r="A10" s="144" t="inlineStr">
-        <is>
-          <t>▶ 239명 중 34명이 이미 3개월 156시간을 초과했다(초과분 1,219H). 9월에 추가로 편성 가능한 연장시간은 전사 11,403H이며, 이 범위를 넘는 잔업·특근은 법 위반이 된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="130">
-      <c r="A12" s="133" t="inlineStr">
-        <is>
-          <t>② 공정 · 라인별 현황 및 9월 여력</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="130">
-      <c r="A13" s="134" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B13" s="134" t="inlineStr">
-        <is>
-          <t>공정 / 라인</t>
-        </is>
-      </c>
-      <c r="C13" s="134" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-      <c r="D13" s="134" t="inlineStr">
-        <is>
-          <t>3개월 평균(H)</t>
-        </is>
-      </c>
-      <c r="E13" s="134" t="inlineStr">
-        <is>
-          <t>156H 초과</t>
-        </is>
-      </c>
-      <c r="F13" s="134" t="inlineStr">
-        <is>
-          <t>7+8월 평균(H)</t>
-        </is>
-      </c>
-      <c r="G13" s="134" t="inlineStr">
-        <is>
-          <t>9월 가용 계(H)</t>
-        </is>
-      </c>
-      <c r="H13" s="134" t="inlineStr">
-        <is>
-          <t>인당 가용(H)</t>
-        </is>
-      </c>
-      <c r="I13" s="134" t="inlineStr">
-        <is>
-          <t>여력 판정</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B14" s="146" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C14" s="136" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" s="147" t="n">
-        <v>150.7142857142857</v>
-      </c>
-      <c r="E14" s="139" t="n">
+      <c r="O12" s="142" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="P12" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="145" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="R12" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1" s="130">
+      <c r="A13" s="152" t="inlineStr">
+        <is>
+          <t>내용물 관리 (업)</t>
+        </is>
+      </c>
+      <c r="B13" s="141" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="153" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="D13" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="145" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="F13" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G13" s="156" t="inlineStr">
+        <is>
+          <t>실적/순회 (생)</t>
+        </is>
+      </c>
+      <c r="H13" s="141" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="142" t="n">
+        <v>92.875</v>
+      </c>
+      <c r="J13" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="145" t="n">
+        <v>197.2</v>
+      </c>
+      <c r="L13" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M13" s="156" t="inlineStr">
+        <is>
+          <t>공작/미화 (업)</t>
+        </is>
+      </c>
+      <c r="N13" s="141" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" s="142" t="n">
+        <v>38.36666666666667</v>
+      </c>
+      <c r="P13" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="145" t="n">
+        <v>746.0999999999998</v>
+      </c>
+      <c r="R13" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="12" customHeight="1" s="130">
+      <c r="A14" s="156" t="inlineStr">
+        <is>
+          <t>PM (생)</t>
+        </is>
+      </c>
+      <c r="B14" s="141" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="142" t="n">
+        <v>119.8888888888889</v>
+      </c>
+      <c r="D14" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="145" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="F14" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G14" s="156" t="inlineStr">
+        <is>
+          <t>포장재 창고 (업)</t>
+        </is>
+      </c>
+      <c r="H14" s="141" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="142" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="J14" s="154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="145" t="n">
+        <v>1216.3</v>
+      </c>
+      <c r="L14" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M14" s="156" t="inlineStr">
+        <is>
+          <t>(미기재) (생)</t>
+        </is>
+      </c>
+      <c r="N14" s="141" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="137" t="n">
-        <v>102.8571428571429</v>
-      </c>
-      <c r="G14" s="140" t="n">
-        <v>470.6999999999999</v>
-      </c>
-      <c r="H14" s="137" t="n">
-        <v>33.62142857142857</v>
-      </c>
-      <c r="I14" s="148" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B15" s="146" t="inlineStr">
-        <is>
-          <t>내용물 관리</t>
-        </is>
-      </c>
-      <c r="C15" s="136" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="147" t="n">
-        <v>137.3</v>
-      </c>
-      <c r="E15" s="139" t="n">
+      <c r="O14" s="142" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="145" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="R14" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1" s="130">
+      <c r="A15" s="156" t="inlineStr">
+        <is>
+          <t>원료 창고 (업)</t>
+        </is>
+      </c>
+      <c r="B15" s="141" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="142" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="D15" s="154" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="137" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="G15" s="140" t="n">
-        <v>215.2</v>
-      </c>
-      <c r="H15" s="137" t="n">
-        <v>43.04000000000001</v>
-      </c>
-      <c r="I15" s="149" t="inlineStr">
+      <c r="E15" s="145" t="n">
+        <v>287</v>
+      </c>
+      <c r="F15" s="157" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B16" s="146" t="inlineStr">
-        <is>
-          <t>원료 창고</t>
-        </is>
-      </c>
-      <c r="C16" s="136" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="137" t="n">
-        <v>118.75</v>
-      </c>
-      <c r="E16" s="139" t="n">
+      <c r="G15" s="156" t="inlineStr">
+        <is>
+          <t>초격차 (생)</t>
+        </is>
+      </c>
+      <c r="H15" s="141" t="n">
+        <v>19</v>
+      </c>
+      <c r="I15" s="142" t="n">
+        <v>80.15789473684211</v>
+      </c>
+      <c r="J15" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="145" t="n">
+        <v>954.1999999999997</v>
+      </c>
+      <c r="L15" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M15" s="156" t="inlineStr">
+        <is>
+          <t>관리자 (업)</t>
+        </is>
+      </c>
+      <c r="N15" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="142" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P15" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="145" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="R15" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1" s="130">
+      <c r="A16" s="156" t="inlineStr">
+        <is>
+          <t>계획자 (생)</t>
+        </is>
+      </c>
+      <c r="B16" s="141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="142" t="n">
+        <v>115.1666666666667</v>
+      </c>
+      <c r="D16" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="145" t="n">
+        <v>133.3</v>
+      </c>
+      <c r="F16" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G16" s="156" t="inlineStr">
+        <is>
+          <t>O/C (생)</t>
+        </is>
+      </c>
+      <c r="H16" s="141" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="142" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="J16" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="145" t="n">
+        <v>616.7999999999998</v>
+      </c>
+      <c r="L16" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M16" s="156" t="inlineStr">
+        <is>
+          <t>작업지휘자 (업)</t>
+        </is>
+      </c>
+      <c r="N16" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="145" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="R16" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="12" customHeight="1" s="130">
+      <c r="A17" s="156" t="inlineStr">
+        <is>
+          <t>멀티 (생)</t>
+        </is>
+      </c>
+      <c r="B17" s="141" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="142" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="D17" s="154" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="145" t="n">
+        <v>976.3999999999997</v>
+      </c>
+      <c r="F17" s="157" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G17" s="156" t="inlineStr">
+        <is>
+          <t>적재실 (업)</t>
+        </is>
+      </c>
+      <c r="H17" s="141" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" s="142" t="n">
+        <v>78.20588235294117</v>
+      </c>
+      <c r="J17" s="154" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="137" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="G16" s="140" t="n">
-        <v>287</v>
-      </c>
-      <c r="H16" s="137" t="n">
-        <v>47.83333333333334</v>
-      </c>
-      <c r="I16" s="149" t="inlineStr">
+      <c r="K17" s="145" t="n">
+        <v>825.0999999999998</v>
+      </c>
+      <c r="L17" s="157" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B17" s="146" t="inlineStr">
-        <is>
-          <t>포장재 창고</t>
-        </is>
-      </c>
-      <c r="C17" s="136" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" s="137" t="n">
-        <v>83.86</v>
-      </c>
-      <c r="E17" s="139" t="n">
+      <c r="M17" s="134" t="n"/>
+      <c r="N17" s="134" t="n"/>
+      <c r="O17" s="134" t="n"/>
+      <c r="P17" s="134" t="n"/>
+      <c r="Q17" s="134" t="n"/>
+      <c r="R17" s="134" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1" s="130">
+      <c r="A18" s="135" t="inlineStr">
+        <is>
+          <t>③ 3개월 156H 초과자 34명 — 9월 편성 배제 대상 (음영 = 9월 편성 불가)</t>
+        </is>
+      </c>
+      <c r="B18" s="136" t="n"/>
+      <c r="C18" s="136" t="n"/>
+      <c r="D18" s="136" t="n"/>
+      <c r="E18" s="136" t="n"/>
+      <c r="F18" s="136" t="n"/>
+      <c r="G18" s="136" t="n"/>
+      <c r="H18" s="136" t="n"/>
+      <c r="I18" s="136" t="n"/>
+      <c r="J18" s="136" t="n"/>
+      <c r="K18" s="136" t="n"/>
+      <c r="L18" s="136" t="n"/>
+      <c r="M18" s="136" t="n"/>
+      <c r="N18" s="136" t="n"/>
+      <c r="O18" s="136" t="n"/>
+      <c r="P18" s="136" t="n"/>
+      <c r="Q18" s="136" t="n"/>
+      <c r="R18" s="136" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1" s="130">
+      <c r="A19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="B19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="C19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+      <c r="D19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="E19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="F19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+      <c r="G19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="H19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="I19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+      <c r="J19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="K19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="L19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+      <c r="M19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="N19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="O19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+      <c r="P19" s="137" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="Q19" s="137" t="inlineStr">
+        <is>
+          <t>3개월</t>
+        </is>
+      </c>
+      <c r="R19" s="137" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="11.5" customHeight="1" s="130">
+      <c r="A20" s="159" t="inlineStr">
+        <is>
+          <t>박태근</t>
+        </is>
+      </c>
+      <c r="B20" s="160" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="C20" s="161" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D20" s="162" t="inlineStr">
+        <is>
+          <t>전완철</t>
+        </is>
+      </c>
+      <c r="E20" s="163" t="n">
+        <v>217</v>
+      </c>
+      <c r="F20" s="164" t="n">
+        <v>61</v>
+      </c>
+      <c r="G20" s="162" t="inlineStr">
+        <is>
+          <t>정혜숙</t>
+        </is>
+      </c>
+      <c r="H20" s="163" t="n">
+        <v>191</v>
+      </c>
+      <c r="I20" s="164" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" s="162" t="inlineStr">
+        <is>
+          <t>김진만</t>
+        </is>
+      </c>
+      <c r="K20" s="163" t="n">
+        <v>178</v>
+      </c>
+      <c r="L20" s="164" t="n">
+        <v>22</v>
+      </c>
+      <c r="M20" s="162" t="inlineStr">
+        <is>
+          <t>김희빈</t>
+        </is>
+      </c>
+      <c r="N20" s="163" t="n">
+        <v>169</v>
+      </c>
+      <c r="O20" s="164" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" s="162" t="inlineStr">
+        <is>
+          <t>성은경</t>
+        </is>
+      </c>
+      <c r="Q20" s="163" t="n">
+        <v>160</v>
+      </c>
+      <c r="R20" s="164" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" ht="11.5" customHeight="1" s="130">
+      <c r="A21" s="159" t="inlineStr">
+        <is>
+          <t>문석</t>
+        </is>
+      </c>
+      <c r="B21" s="160" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="C21" s="161" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="D21" s="162" t="inlineStr">
+        <is>
+          <t>선우찬</t>
+        </is>
+      </c>
+      <c r="E21" s="163" t="n">
+        <v>206</v>
+      </c>
+      <c r="F21" s="164" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" s="162" t="inlineStr">
+        <is>
+          <t>이준구</t>
+        </is>
+      </c>
+      <c r="H21" s="163" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="I21" s="164" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J21" s="162" t="inlineStr">
+        <is>
+          <t>박효</t>
+        </is>
+      </c>
+      <c r="K21" s="163" t="n">
+        <v>177</v>
+      </c>
+      <c r="L21" s="164" t="n">
+        <v>21</v>
+      </c>
+      <c r="M21" s="162" t="inlineStr">
+        <is>
+          <t>이은하</t>
+        </is>
+      </c>
+      <c r="N21" s="163" t="n">
+        <v>169</v>
+      </c>
+      <c r="O21" s="164" t="n">
+        <v>13</v>
+      </c>
+      <c r="P21" s="162" t="inlineStr">
+        <is>
+          <t>곽옥연</t>
+        </is>
+      </c>
+      <c r="Q21" s="163" t="n">
+        <v>159</v>
+      </c>
+      <c r="R21" s="164" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="137" t="n">
-        <v>55.68</v>
-      </c>
-      <c r="G17" s="140" t="n">
-        <v>1216.3</v>
-      </c>
-      <c r="H17" s="137" t="n">
-        <v>48.652</v>
-      </c>
-      <c r="I17" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B18" s="146" t="inlineStr">
-        <is>
-          <t>적재실</t>
-        </is>
-      </c>
-      <c r="C18" s="136" t="n">
+    </row>
+    <row r="22" ht="11.5" customHeight="1" s="130">
+      <c r="A22" s="159" t="inlineStr">
+        <is>
+          <t>김영두</t>
+        </is>
+      </c>
+      <c r="B22" s="160" t="n">
+        <v>263</v>
+      </c>
+      <c r="C22" s="161" t="n">
+        <v>107</v>
+      </c>
+      <c r="D22" s="162" t="inlineStr">
+        <is>
+          <t>서재권</t>
+        </is>
+      </c>
+      <c r="E22" s="163" t="n">
+        <v>204</v>
+      </c>
+      <c r="F22" s="164" t="n">
+        <v>48</v>
+      </c>
+      <c r="G22" s="162" t="inlineStr">
+        <is>
+          <t>김순리</t>
+        </is>
+      </c>
+      <c r="H22" s="163" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="I22" s="164" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J22" s="162" t="inlineStr">
+        <is>
+          <t>이준엽</t>
+        </is>
+      </c>
+      <c r="K22" s="163" t="n">
+        <v>173</v>
+      </c>
+      <c r="L22" s="164" t="n">
         <v>17</v>
       </c>
-      <c r="D18" s="137" t="n">
-        <v>78.20588235294117</v>
-      </c>
-      <c r="E18" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="137" t="n">
-        <v>54.6764705882353</v>
-      </c>
-      <c r="G18" s="140" t="n">
-        <v>825.0999999999998</v>
-      </c>
-      <c r="H18" s="137" t="n">
-        <v>48.53529411764705</v>
-      </c>
-      <c r="I18" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B19" s="146" t="inlineStr">
-        <is>
-          <t>(미기재)</t>
-        </is>
-      </c>
-      <c r="C19" s="136" t="n">
+      <c r="M22" s="162" t="inlineStr">
+        <is>
+          <t>이차영</t>
+        </is>
+      </c>
+      <c r="N22" s="163" t="n">
+        <v>168</v>
+      </c>
+      <c r="O22" s="164" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" s="162" t="inlineStr">
+        <is>
+          <t>정현수</t>
+        </is>
+      </c>
+      <c r="Q22" s="163" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="R22" s="164" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23" ht="11.5" customHeight="1" s="130">
+      <c r="A23" s="159" t="inlineStr">
+        <is>
+          <t>이세호</t>
+        </is>
+      </c>
+      <c r="B23" s="160" t="n">
+        <v>249</v>
+      </c>
+      <c r="C23" s="161" t="n">
+        <v>93</v>
+      </c>
+      <c r="D23" s="162" t="inlineStr">
+        <is>
+          <t>김예순</t>
+        </is>
+      </c>
+      <c r="E23" s="163" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" s="164" t="n">
+        <v>44</v>
+      </c>
+      <c r="G23" s="162" t="inlineStr">
+        <is>
+          <t>신성수</t>
+        </is>
+      </c>
+      <c r="H23" s="163" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="I23" s="164" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="J23" s="162" t="inlineStr">
+        <is>
+          <t>김해경</t>
+        </is>
+      </c>
+      <c r="K23" s="163" t="n">
+        <v>172</v>
+      </c>
+      <c r="L23" s="164" t="n">
+        <v>16</v>
+      </c>
+      <c r="M23" s="162" t="inlineStr">
+        <is>
+          <t>김선희</t>
+        </is>
+      </c>
+      <c r="N23" s="163" t="n">
+        <v>163</v>
+      </c>
+      <c r="O23" s="164" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="162" t="inlineStr">
+        <is>
+          <t>이동기</t>
+        </is>
+      </c>
+      <c r="Q23" s="163" t="n">
+        <v>157</v>
+      </c>
+      <c r="R23" s="164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="11.5" customHeight="1" s="130">
+      <c r="A24" s="162" t="inlineStr">
+        <is>
+          <t>한인수</t>
+        </is>
+      </c>
+      <c r="B24" s="163" t="n">
+        <v>225</v>
+      </c>
+      <c r="C24" s="164" t="n">
+        <v>69</v>
+      </c>
+      <c r="D24" s="162" t="inlineStr">
+        <is>
+          <t>김영준</t>
+        </is>
+      </c>
+      <c r="E24" s="163" t="n">
+        <v>192</v>
+      </c>
+      <c r="F24" s="164" t="n">
+        <v>36</v>
+      </c>
+      <c r="G24" s="162" t="inlineStr">
+        <is>
+          <t>김필수</t>
+        </is>
+      </c>
+      <c r="H24" s="163" t="n">
+        <v>187</v>
+      </c>
+      <c r="I24" s="164" t="n">
+        <v>31</v>
+      </c>
+      <c r="J24" s="162" t="inlineStr">
+        <is>
+          <t>김명희</t>
+        </is>
+      </c>
+      <c r="K24" s="163" t="n">
+        <v>171</v>
+      </c>
+      <c r="L24" s="164" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" s="162" t="inlineStr">
+        <is>
+          <t>전경수</t>
+        </is>
+      </c>
+      <c r="N24" s="163" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="O24" s="164" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" s="134" t="n"/>
+      <c r="Q24" s="134" t="n"/>
+      <c r="R24" s="134" t="n"/>
+    </row>
+    <row r="25" ht="11.5" customHeight="1" s="130">
+      <c r="A25" s="162" t="inlineStr">
+        <is>
+          <t>조영순</t>
+        </is>
+      </c>
+      <c r="B25" s="163" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="C25" s="164" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="D25" s="162" t="inlineStr">
+        <is>
+          <t>최명필</t>
+        </is>
+      </c>
+      <c r="E25" s="163" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="F25" s="164" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="G25" s="162" t="inlineStr">
+        <is>
+          <t>최광일</t>
+        </is>
+      </c>
+      <c r="H25" s="163" t="n">
+        <v>185</v>
+      </c>
+      <c r="I25" s="164" t="n">
+        <v>29</v>
+      </c>
+      <c r="J25" s="162" t="inlineStr">
+        <is>
+          <t>김태환</t>
+        </is>
+      </c>
+      <c r="K25" s="163" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="L25" s="164" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M25" s="162" t="inlineStr">
+        <is>
+          <t>박미춘</t>
+        </is>
+      </c>
+      <c r="N25" s="163" t="n">
+        <v>160</v>
+      </c>
+      <c r="O25" s="164" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="137" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="E19" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="137" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="G19" s="140" t="n">
-        <v>205.6</v>
-      </c>
-      <c r="H19" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I19" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B20" s="146" t="inlineStr">
-        <is>
-          <t>공작/미화</t>
-        </is>
-      </c>
-      <c r="C20" s="136" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="137" t="n">
-        <v>38.36666666666667</v>
-      </c>
-      <c r="E20" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="137" t="n">
-        <v>28.56666666666667</v>
-      </c>
-      <c r="G20" s="140" t="n">
-        <v>746.0999999999998</v>
-      </c>
-      <c r="H20" s="137" t="n">
-        <v>49.73999999999999</v>
-      </c>
-      <c r="I20" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B21" s="146" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="C21" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="137" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E21" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="137" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G21" s="140" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H21" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I21" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B22" s="146" t="inlineStr">
-        <is>
-          <t>작업지휘자</t>
-        </is>
-      </c>
-      <c r="C22" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="140" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H22" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I22" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B23" s="146" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="C23" s="136" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="147" t="n">
-        <v>189.8333333333333</v>
-      </c>
-      <c r="E23" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="137" t="n">
-        <v>131.1666666666667</v>
-      </c>
-      <c r="G23" s="140" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="H23" s="137" t="n">
-        <v>24.83333333333333</v>
-      </c>
-      <c r="I23" s="150" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B24" s="146" t="inlineStr">
-        <is>
-          <t>HnB</t>
-        </is>
-      </c>
-      <c r="C24" s="136" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="147" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="E24" s="139" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="137" t="n">
-        <v>114</v>
-      </c>
-      <c r="G24" s="140" t="n">
-        <v>191.8</v>
-      </c>
-      <c r="H24" s="137" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="I24" s="148" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B25" s="146" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C25" s="136" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" s="137" t="n">
-        <v>119.8888888888889</v>
-      </c>
-      <c r="E25" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="137" t="n">
-        <v>82.55555555555556</v>
-      </c>
-      <c r="G25" s="140" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="H25" s="137" t="n">
-        <v>44.36666666666666</v>
-      </c>
-      <c r="I25" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B26" s="146" t="inlineStr">
-        <is>
-          <t>계획자</t>
-        </is>
-      </c>
-      <c r="C26" s="136" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="137" t="n">
-        <v>115.1666666666667</v>
-      </c>
-      <c r="E26" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="137" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="G26" s="140" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="H26" s="137" t="n">
-        <v>44.43333333333334</v>
-      </c>
-      <c r="I26" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B27" s="146" t="inlineStr">
-        <is>
-          <t>멀티</t>
-        </is>
-      </c>
-      <c r="C27" s="136" t="n">
-        <v>20</v>
-      </c>
-      <c r="D27" s="137" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="E27" s="139" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="137" t="n">
-        <v>74.45</v>
-      </c>
-      <c r="G27" s="140" t="n">
-        <v>976.3999999999997</v>
-      </c>
-      <c r="H27" s="137" t="n">
-        <v>48.81999999999999</v>
-      </c>
-      <c r="I27" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B28" s="146" t="inlineStr">
-        <is>
-          <t>튜브</t>
-        </is>
-      </c>
-      <c r="C28" s="136" t="n">
-        <v>17</v>
-      </c>
-      <c r="D28" s="137" t="n">
-        <v>110.6176470588235</v>
-      </c>
-      <c r="E28" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="137" t="n">
-        <v>80.29411764705883</v>
-      </c>
-      <c r="G28" s="140" t="n">
-        <v>813.5999999999998</v>
-      </c>
-      <c r="H28" s="137" t="n">
-        <v>47.85882352941175</v>
-      </c>
-      <c r="I28" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B29" s="146" t="inlineStr">
-        <is>
-          <t>직선</t>
-        </is>
-      </c>
-      <c r="C29" s="136" t="n">
-        <v>24</v>
-      </c>
-      <c r="D29" s="137" t="n">
-        <v>109.7083333333333</v>
-      </c>
-      <c r="E29" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="137" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="G29" s="140" t="n">
-        <v>1178</v>
-      </c>
-      <c r="H29" s="137" t="n">
-        <v>49.08333333333334</v>
-      </c>
-      <c r="I29" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B30" s="146" t="inlineStr">
-        <is>
-          <t>행정</t>
-        </is>
-      </c>
-      <c r="C30" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="137" t="n">
-        <v>101</v>
-      </c>
-      <c r="E30" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="137" t="n">
-        <v>74</v>
-      </c>
-      <c r="G30" s="140" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H30" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I30" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B31" s="146" t="inlineStr">
-        <is>
-          <t>실적/순회</t>
-        </is>
-      </c>
-      <c r="C31" s="136" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="137" t="n">
-        <v>92.875</v>
-      </c>
-      <c r="E31" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="137" t="n">
-        <v>55.875</v>
-      </c>
-      <c r="G31" s="140" t="n">
-        <v>197.2</v>
-      </c>
-      <c r="H31" s="137" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="I31" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B32" s="146" t="inlineStr">
-        <is>
-          <t>초격차</t>
-        </is>
-      </c>
-      <c r="C32" s="136" t="n">
-        <v>19</v>
-      </c>
-      <c r="D32" s="137" t="n">
-        <v>80.15789473684211</v>
-      </c>
-      <c r="E32" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="137" t="n">
-        <v>56.21052631578947</v>
-      </c>
-      <c r="G32" s="140" t="n">
-        <v>954.1999999999997</v>
-      </c>
-      <c r="H32" s="137" t="n">
-        <v>50.22105263157894</v>
-      </c>
-      <c r="I32" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B33" s="146" t="inlineStr">
-        <is>
-          <t>O/C</t>
-        </is>
-      </c>
-      <c r="C33" s="136" t="n">
-        <v>12</v>
-      </c>
-      <c r="D33" s="137" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="E33" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="137" t="n">
-        <v>41.08333333333334</v>
-      </c>
-      <c r="G33" s="140" t="n">
-        <v>616.7999999999998</v>
-      </c>
-      <c r="H33" s="137" t="n">
-        <v>51.39999999999998</v>
-      </c>
-      <c r="I33" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B34" s="146" t="inlineStr">
-        <is>
-          <t>PM장</t>
-        </is>
-      </c>
-      <c r="C34" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="137" t="n">
-        <v>56</v>
-      </c>
-      <c r="E34" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="137" t="n">
-        <v>41</v>
-      </c>
-      <c r="G34" s="140" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H34" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I34" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B35" s="146" t="inlineStr">
-        <is>
-          <t>염모</t>
-        </is>
-      </c>
-      <c r="C35" s="136" t="n">
-        <v>27</v>
-      </c>
-      <c r="D35" s="137" t="n">
-        <v>41.53703703703704</v>
-      </c>
-      <c r="E35" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="137" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G35" s="140" t="n">
-        <v>1387.8</v>
-      </c>
-      <c r="H35" s="137" t="n">
-        <v>51.40000000000001</v>
-      </c>
-      <c r="I35" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B36" s="146" t="inlineStr">
-        <is>
-          <t>(미기재)</t>
-        </is>
-      </c>
-      <c r="C36" s="136" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="137" t="n">
-        <v>17</v>
-      </c>
-      <c r="E36" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="137" t="n">
-        <v>17</v>
-      </c>
-      <c r="G36" s="140" t="n">
-        <v>308.4</v>
-      </c>
-      <c r="H36" s="137" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="I36" s="149" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" s="130">
-      <c r="A38" s="133" t="inlineStr">
-        <is>
-          <t>③ 3개월 156시간 초과자 명단 — 9월 편성 시 최우선 배제 대상</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1" s="130">
-      <c r="A39" s="134" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B39" s="134" t="inlineStr">
-        <is>
-          <t>공정</t>
-        </is>
-      </c>
-      <c r="C39" s="134" t="inlineStr">
-        <is>
-          <t>세부 / 직책</t>
-        </is>
-      </c>
-      <c r="D39" s="134" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="E39" s="134" t="inlineStr">
-        <is>
-          <t>6월</t>
-        </is>
-      </c>
-      <c r="F39" s="134" t="inlineStr">
-        <is>
-          <t>7월</t>
-        </is>
-      </c>
-      <c r="G39" s="134" t="inlineStr">
-        <is>
-          <t>8월</t>
-        </is>
-      </c>
-      <c r="H39" s="134" t="inlineStr">
-        <is>
-          <t>3개월 계</t>
-        </is>
-      </c>
-      <c r="I39" s="134" t="inlineStr">
-        <is>
-          <t>초과분</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B40" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C40" s="152" t="inlineStr">
-        <is>
-          <t>포터블</t>
-        </is>
-      </c>
-      <c r="D40" s="150" t="inlineStr">
-        <is>
-          <t>박태근</t>
-        </is>
-      </c>
-      <c r="E40" s="137" t="n">
-        <v>91</v>
-      </c>
-      <c r="F40" s="137" t="n">
-        <v>90</v>
-      </c>
-      <c r="G40" s="137" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="H40" s="153" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="I40" s="154" t="n">
-        <v>133.5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B41" s="151" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C41" s="152" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D41" s="150" t="inlineStr">
-        <is>
-          <t>문석</t>
-        </is>
-      </c>
-      <c r="E41" s="137" t="n">
-        <v>87</v>
-      </c>
-      <c r="F41" s="137" t="n">
-        <v>85</v>
-      </c>
-      <c r="G41" s="137" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="H41" s="153" t="n">
-        <v>264.5</v>
-      </c>
-      <c r="I41" s="154" t="n">
-        <v>108.5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B42" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C42" s="152" t="inlineStr">
-        <is>
-          <t>염모제</t>
-        </is>
-      </c>
-      <c r="D42" s="150" t="inlineStr">
-        <is>
-          <t>김영두</t>
-        </is>
-      </c>
-      <c r="E42" s="137" t="n">
-        <v>85</v>
-      </c>
-      <c r="F42" s="137" t="n">
-        <v>84</v>
-      </c>
-      <c r="G42" s="137" t="n">
-        <v>94</v>
-      </c>
-      <c r="H42" s="153" t="n">
-        <v>263</v>
-      </c>
-      <c r="I42" s="154" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B43" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C43" s="152" t="inlineStr">
-        <is>
-          <t>2층설비세척(멀티)</t>
-        </is>
-      </c>
-      <c r="D43" s="150" t="inlineStr">
-        <is>
-          <t>이세호</t>
-        </is>
-      </c>
-      <c r="E43" s="137" t="n">
-        <v>76</v>
-      </c>
-      <c r="F43" s="137" t="n">
-        <v>81</v>
-      </c>
-      <c r="G43" s="137" t="n">
-        <v>92</v>
-      </c>
-      <c r="H43" s="153" t="n">
-        <v>249</v>
-      </c>
-      <c r="I43" s="154" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B44" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C44" s="152" t="inlineStr">
-        <is>
-          <t>폼가압통</t>
-        </is>
-      </c>
-      <c r="D44" s="155" t="inlineStr">
-        <is>
-          <t>한인수</t>
-        </is>
-      </c>
-      <c r="E44" s="137" t="n">
-        <v>70</v>
-      </c>
-      <c r="F44" s="137" t="n">
-        <v>75</v>
-      </c>
-      <c r="G44" s="137" t="n">
-        <v>80</v>
-      </c>
-      <c r="H44" s="156" t="n">
-        <v>225</v>
-      </c>
-      <c r="I44" s="154" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B45" s="151" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="C45" s="152" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="D45" s="155" t="inlineStr">
-        <is>
-          <t>조영순</t>
-        </is>
-      </c>
-      <c r="E45" s="137" t="n">
-        <v>75</v>
-      </c>
-      <c r="F45" s="137" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="G45" s="137" t="n">
-        <v>77</v>
-      </c>
-      <c r="H45" s="156" t="n">
-        <v>224.5</v>
-      </c>
-      <c r="I45" s="154" t="n">
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B46" s="151" t="inlineStr">
-        <is>
-          <t>내용물 관리</t>
-        </is>
-      </c>
-      <c r="C46" s="152" t="inlineStr">
-        <is>
-          <t>사원</t>
-        </is>
-      </c>
-      <c r="D46" s="155" t="inlineStr">
-        <is>
-          <t>전완철</t>
-        </is>
-      </c>
-      <c r="E46" s="137" t="n">
-        <v>87</v>
-      </c>
-      <c r="F46" s="137" t="n">
-        <v>69</v>
-      </c>
-      <c r="G46" s="137" t="n">
-        <v>61</v>
-      </c>
-      <c r="H46" s="156" t="n">
-        <v>217</v>
-      </c>
-      <c r="I46" s="154" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B47" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C47" s="152" t="inlineStr">
-        <is>
-          <t>포터블</t>
-        </is>
-      </c>
-      <c r="D47" s="155" t="inlineStr">
-        <is>
-          <t>선우찬</t>
-        </is>
-      </c>
-      <c r="E47" s="137" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="F47" s="137" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="G47" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H47" s="156" t="n">
-        <v>206</v>
-      </c>
-      <c r="I47" s="154" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B48" s="151" t="inlineStr">
-        <is>
-          <t>포장재 창고</t>
-        </is>
-      </c>
-      <c r="C48" s="152" t="inlineStr">
-        <is>
-          <t>H&amp;B사원</t>
-        </is>
-      </c>
-      <c r="D48" s="155" t="inlineStr">
-        <is>
-          <t>서재권</t>
-        </is>
-      </c>
-      <c r="E48" s="137" t="n">
-        <v>64</v>
-      </c>
-      <c r="F48" s="137" t="n">
-        <v>68</v>
-      </c>
-      <c r="G48" s="137" t="n">
-        <v>72</v>
-      </c>
-      <c r="H48" s="156" t="n">
-        <v>204</v>
-      </c>
-      <c r="I48" s="154" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B49" s="151" t="inlineStr">
-        <is>
-          <t>HnB</t>
-        </is>
-      </c>
-      <c r="C49" s="152" t="inlineStr">
-        <is>
-          <t>도우미</t>
-        </is>
-      </c>
-      <c r="D49" s="155" t="inlineStr">
-        <is>
-          <t>김예순</t>
-        </is>
-      </c>
-      <c r="E49" s="137" t="n">
-        <v>70</v>
-      </c>
-      <c r="F49" s="137" t="n">
-        <v>72</v>
-      </c>
-      <c r="G49" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="H49" s="156" t="n">
-        <v>200</v>
-      </c>
-      <c r="I49" s="154" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B50" s="151" t="inlineStr">
-        <is>
-          <t>적재실</t>
-        </is>
-      </c>
-      <c r="C50" s="152" t="inlineStr">
-        <is>
-          <t>F&amp;C사원(로봇)</t>
-        </is>
-      </c>
-      <c r="D50" s="155" t="inlineStr">
-        <is>
-          <t>김영준</t>
-        </is>
-      </c>
-      <c r="E50" s="137" t="n">
-        <v>51</v>
-      </c>
-      <c r="F50" s="137" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="G50" s="137" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H50" s="156" t="n">
-        <v>192</v>
-      </c>
-      <c r="I50" s="154" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B51" s="151" t="inlineStr">
-        <is>
-          <t>튜브</t>
-        </is>
-      </c>
-      <c r="C51" s="152" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="D51" s="155" t="inlineStr">
-        <is>
-          <t>최명필</t>
-        </is>
-      </c>
-      <c r="E51" s="137" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="F51" s="137" t="n">
-        <v>69</v>
-      </c>
-      <c r="G51" s="137" t="n">
-        <v>66</v>
-      </c>
-      <c r="H51" s="156" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="I51" s="154" t="n">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B52" s="151" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="C52" s="152" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="D52" s="155" t="inlineStr">
-        <is>
-          <t>정혜숙</t>
-        </is>
-      </c>
-      <c r="E52" s="137" t="n">
-        <v>62</v>
-      </c>
-      <c r="F52" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="G52" s="137" t="n">
-        <v>71</v>
-      </c>
-      <c r="H52" s="156" t="n">
-        <v>191</v>
-      </c>
-      <c r="I52" s="154" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B53" s="151" t="inlineStr">
-        <is>
-          <t>원료 창고</t>
-        </is>
-      </c>
-      <c r="C53" s="152" t="inlineStr">
-        <is>
-          <t>지방산</t>
-        </is>
-      </c>
-      <c r="D53" s="155" t="inlineStr">
-        <is>
-          <t>이준구</t>
-        </is>
-      </c>
-      <c r="E53" s="137" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="F53" s="137" t="n">
-        <v>55</v>
-      </c>
-      <c r="G53" s="137" t="n">
-        <v>71</v>
-      </c>
-      <c r="H53" s="156" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="I53" s="154" t="n">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B54" s="151" t="inlineStr">
-        <is>
-          <t>계획자</t>
-        </is>
-      </c>
-      <c r="C54" s="152" t="inlineStr">
-        <is>
-          <t>계획자</t>
-        </is>
-      </c>
-      <c r="D54" s="155" t="inlineStr">
-        <is>
-          <t>김순리</t>
-        </is>
-      </c>
-      <c r="E54" s="137" t="n">
-        <v>65</v>
-      </c>
-      <c r="F54" s="137" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="G54" s="137" t="n">
-        <v>54</v>
-      </c>
-      <c r="H54" s="156" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="I54" s="154" t="n">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B55" s="151" t="inlineStr">
-        <is>
-          <t>공작/미화</t>
-        </is>
-      </c>
-      <c r="C55" s="152" t="inlineStr">
-        <is>
-          <t>전기시설관리</t>
-        </is>
-      </c>
-      <c r="D55" s="155" t="inlineStr">
-        <is>
-          <t>신성수</t>
-        </is>
-      </c>
-      <c r="E55" s="137" t="n">
-        <v>60</v>
-      </c>
-      <c r="F55" s="137" t="n">
-        <v>73</v>
-      </c>
-      <c r="G55" s="137" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="H55" s="156" t="n">
-        <v>189.5</v>
-      </c>
-      <c r="I55" s="154" t="n">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B56" s="151" t="inlineStr">
-        <is>
-          <t>세척실</t>
-        </is>
-      </c>
-      <c r="C56" s="152" t="inlineStr">
-        <is>
-          <t>염모제</t>
-        </is>
-      </c>
-      <c r="D56" s="155" t="inlineStr">
-        <is>
-          <t>김필수</t>
-        </is>
-      </c>
-      <c r="E56" s="137" t="n">
-        <v>66</v>
-      </c>
-      <c r="F56" s="137" t="n">
-        <v>62</v>
-      </c>
-      <c r="G56" s="137" t="n">
-        <v>59</v>
-      </c>
-      <c r="H56" s="156" t="n">
-        <v>187</v>
-      </c>
-      <c r="I56" s="154" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B57" s="151" t="inlineStr">
-        <is>
-          <t>HnB</t>
-        </is>
-      </c>
-      <c r="C57" s="152" t="inlineStr">
-        <is>
-          <t>도우미</t>
-        </is>
-      </c>
-      <c r="D57" s="155" t="inlineStr">
-        <is>
-          <t>최광일</t>
-        </is>
-      </c>
-      <c r="E57" s="137" t="n">
-        <v>56</v>
-      </c>
-      <c r="F57" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="G57" s="137" t="n">
-        <v>71</v>
-      </c>
-      <c r="H57" s="156" t="n">
-        <v>185</v>
-      </c>
-      <c r="I57" s="154" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B58" s="151" t="inlineStr">
-        <is>
-          <t>튜브</t>
-        </is>
-      </c>
-      <c r="C58" s="152" t="inlineStr">
-        <is>
-          <t>도우미</t>
-        </is>
-      </c>
-      <c r="D58" s="155" t="inlineStr">
-        <is>
-          <t>김진만</t>
-        </is>
-      </c>
-      <c r="E58" s="137" t="n">
-        <v>46</v>
-      </c>
-      <c r="F58" s="137" t="n">
-        <v>69</v>
-      </c>
-      <c r="G58" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H58" s="156" t="n">
-        <v>178</v>
-      </c>
-      <c r="I58" s="154" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B59" s="151" t="inlineStr">
-        <is>
-          <t>내용물 관리</t>
-        </is>
-      </c>
-      <c r="C59" s="152" t="inlineStr">
-        <is>
-          <t>H&amp;B사원</t>
-        </is>
-      </c>
-      <c r="D59" s="155" t="inlineStr">
-        <is>
-          <t>박효</t>
-        </is>
-      </c>
-      <c r="E59" s="137" t="n">
-        <v>56</v>
-      </c>
-      <c r="F59" s="137" t="n">
-        <v>60</v>
-      </c>
-      <c r="G59" s="137" t="n">
-        <v>61</v>
-      </c>
-      <c r="H59" s="156" t="n">
-        <v>177</v>
-      </c>
-      <c r="I59" s="154" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B60" s="151" t="inlineStr">
-        <is>
-          <t>포장재 창고</t>
-        </is>
-      </c>
-      <c r="C60" s="152" t="inlineStr">
-        <is>
-          <t>1층</t>
-        </is>
-      </c>
-      <c r="D60" s="155" t="inlineStr">
-        <is>
-          <t>이준엽</t>
-        </is>
-      </c>
-      <c r="E60" s="137" t="n">
-        <v>43</v>
-      </c>
-      <c r="F60" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="G60" s="137" t="n">
-        <v>72</v>
-      </c>
-      <c r="H60" s="156" t="n">
-        <v>173</v>
-      </c>
-      <c r="I60" s="154" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B61" s="151" t="inlineStr">
-        <is>
-          <t>멀티</t>
-        </is>
-      </c>
-      <c r="C61" s="152" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="D61" s="155" t="inlineStr">
-        <is>
-          <t>김해경</t>
-        </is>
-      </c>
-      <c r="E61" s="137" t="n">
-        <v>39</v>
-      </c>
-      <c r="F61" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="G61" s="137" t="n">
-        <v>75</v>
-      </c>
-      <c r="H61" s="156" t="n">
-        <v>172</v>
-      </c>
-      <c r="I61" s="154" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B62" s="151" t="inlineStr">
-        <is>
-          <t>직선</t>
-        </is>
-      </c>
-      <c r="C62" s="152" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="D62" s="155" t="inlineStr">
-        <is>
-          <t>김명희</t>
-        </is>
-      </c>
-      <c r="E62" s="137" t="n">
-        <v>45</v>
-      </c>
-      <c r="F62" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="G62" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H62" s="156" t="n">
-        <v>171</v>
-      </c>
-      <c r="I62" s="154" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B63" s="151" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C63" s="152" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="D63" s="155" t="inlineStr">
-        <is>
-          <t>김태환</t>
-        </is>
-      </c>
-      <c r="E63" s="137" t="n">
-        <v>53</v>
-      </c>
-      <c r="F63" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="G63" s="137" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H63" s="156" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="I63" s="154" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B64" s="151" t="inlineStr">
-        <is>
-          <t>초격차</t>
-        </is>
-      </c>
-      <c r="C64" s="152" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="D64" s="155" t="inlineStr">
-        <is>
-          <t>김희빈</t>
-        </is>
-      </c>
-      <c r="E64" s="137" t="n">
-        <v>42</v>
-      </c>
-      <c r="F64" s="137" t="n">
-        <v>66</v>
-      </c>
-      <c r="G64" s="137" t="n">
-        <v>61</v>
-      </c>
-      <c r="H64" s="156" t="n">
-        <v>169</v>
-      </c>
-      <c r="I64" s="154" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B65" s="151" t="inlineStr">
-        <is>
-          <t>직선</t>
-        </is>
-      </c>
-      <c r="C65" s="152" t="inlineStr">
-        <is>
-          <t>작업자</t>
-        </is>
-      </c>
-      <c r="D65" s="155" t="inlineStr">
-        <is>
-          <t>이은하</t>
-        </is>
-      </c>
-      <c r="E65" s="137" t="n">
-        <v>47</v>
-      </c>
-      <c r="F65" s="137" t="n">
-        <v>64</v>
-      </c>
-      <c r="G65" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="H65" s="156" t="n">
-        <v>169</v>
-      </c>
-      <c r="I65" s="154" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B66" s="151" t="inlineStr">
-        <is>
-          <t>멀티</t>
-        </is>
-      </c>
-      <c r="C66" s="152" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="D66" s="155" t="inlineStr">
-        <is>
-          <t>이차영</t>
-        </is>
-      </c>
-      <c r="E66" s="137" t="n">
-        <v>53</v>
-      </c>
-      <c r="F66" s="137" t="n">
-        <v>52</v>
-      </c>
-      <c r="G66" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H66" s="156" t="n">
-        <v>168</v>
-      </c>
-      <c r="I66" s="154" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B67" s="151" t="inlineStr">
-        <is>
-          <t>멀티</t>
-        </is>
-      </c>
-      <c r="C67" s="152" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="D67" s="155" t="inlineStr">
-        <is>
-          <t>김선희</t>
-        </is>
-      </c>
-      <c r="E67" s="137" t="n">
-        <v>53</v>
-      </c>
-      <c r="F67" s="137" t="n">
-        <v>47</v>
-      </c>
-      <c r="G67" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H67" s="156" t="n">
-        <v>163</v>
-      </c>
-      <c r="I67" s="154" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B68" s="151" t="inlineStr">
-        <is>
-          <t>포장재 창고</t>
-        </is>
-      </c>
-      <c r="C68" s="152" t="inlineStr">
-        <is>
-          <t>H&amp;B사원</t>
-        </is>
-      </c>
-      <c r="D68" s="155" t="inlineStr">
-        <is>
-          <t>전경수</t>
-        </is>
-      </c>
-      <c r="E68" s="137" t="n">
-        <v>48</v>
-      </c>
-      <c r="F68" s="137" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="G68" s="137" t="n">
-        <v>58</v>
-      </c>
-      <c r="H68" s="156" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="I68" s="154" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B69" s="151" t="inlineStr">
-        <is>
-          <t>적재실</t>
-        </is>
-      </c>
-      <c r="C69" s="152" t="inlineStr">
-        <is>
-          <t>현장관리(로봇)</t>
-        </is>
-      </c>
-      <c r="D69" s="155" t="inlineStr">
-        <is>
-          <t>박미춘</t>
-        </is>
-      </c>
-      <c r="E69" s="137" t="n">
-        <v>49</v>
-      </c>
-      <c r="F69" s="137" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="G69" s="137" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H69" s="156" t="n">
-        <v>160</v>
-      </c>
-      <c r="I69" s="154" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B70" s="151" t="inlineStr">
-        <is>
-          <t>실적/순회</t>
-        </is>
-      </c>
-      <c r="C70" s="152" t="inlineStr">
-        <is>
-          <t>실직/순회</t>
-        </is>
-      </c>
-      <c r="D70" s="155" t="inlineStr">
-        <is>
-          <t>성은경</t>
-        </is>
-      </c>
-      <c r="E70" s="137" t="n">
-        <v>47</v>
-      </c>
-      <c r="F70" s="137" t="n">
-        <v>50</v>
-      </c>
-      <c r="G70" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="H70" s="156" t="n">
-        <v>160</v>
-      </c>
-      <c r="I70" s="154" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B71" s="151" t="inlineStr">
-        <is>
-          <t>멀티</t>
-        </is>
-      </c>
-      <c r="C71" s="152" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="D71" s="155" t="inlineStr">
-        <is>
-          <t>곽옥연</t>
-        </is>
-      </c>
-      <c r="E71" s="137" t="n">
-        <v>47</v>
-      </c>
-      <c r="F71" s="137" t="n">
-        <v>63</v>
-      </c>
-      <c r="G71" s="137" t="n">
-        <v>49</v>
-      </c>
-      <c r="H71" s="156" t="n">
-        <v>159</v>
-      </c>
-      <c r="I71" s="154" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="145" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="B72" s="151" t="inlineStr">
-        <is>
-          <t>HnB</t>
-        </is>
-      </c>
-      <c r="C72" s="152" t="inlineStr">
-        <is>
-          <t>도우미</t>
-        </is>
-      </c>
-      <c r="D72" s="155" t="inlineStr">
-        <is>
-          <t>정현수</t>
-        </is>
-      </c>
-      <c r="E72" s="137" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="F72" s="137" t="n">
-        <v>55</v>
-      </c>
-      <c r="G72" s="137" t="n">
-        <v>47</v>
-      </c>
-      <c r="H72" s="156" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="I72" s="154" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="145" t="inlineStr">
-        <is>
-          <t>업무</t>
-        </is>
-      </c>
-      <c r="B73" s="151" t="inlineStr">
-        <is>
-          <t>원료 창고</t>
-        </is>
-      </c>
-      <c r="C73" s="152" t="inlineStr">
-        <is>
-          <t>현장관리</t>
-        </is>
-      </c>
-      <c r="D73" s="155" t="inlineStr">
-        <is>
-          <t>이동기</t>
-        </is>
-      </c>
-      <c r="E73" s="137" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F73" s="137" t="n">
-        <v>42</v>
-      </c>
-      <c r="G73" s="137" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H73" s="156" t="n">
-        <v>157</v>
-      </c>
-      <c r="I73" s="154" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="157" t="inlineStr">
-        <is>
-          <t>※ 성명 음영 = 7·8월 실적만으로 이미 156H를 넘어 9월 잔업 편성이 불가한 인원</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1" s="130">
-      <c r="A76" s="133" t="inlineStr">
+      <c r="P25" s="134" t="n"/>
+      <c r="Q25" s="134" t="n"/>
+      <c r="R25" s="134" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1" s="130">
+      <c r="A26" s="135" t="inlineStr">
         <is>
           <t>④ 38주 대응전략 연계 판정</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="30" customHeight="1" s="130">
-      <c r="A77" s="134" t="inlineStr">
+      <c r="B26" s="136" t="n"/>
+      <c r="C26" s="136" t="n"/>
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="136" t="n"/>
+      <c r="F26" s="136" t="n"/>
+      <c r="G26" s="136" t="n"/>
+      <c r="H26" s="136" t="n"/>
+      <c r="I26" s="136" t="n"/>
+      <c r="J26" s="136" t="n"/>
+      <c r="K26" s="136" t="n"/>
+      <c r="L26" s="136" t="n"/>
+      <c r="M26" s="136" t="n"/>
+      <c r="N26" s="136" t="n"/>
+      <c r="O26" s="136" t="n"/>
+      <c r="P26" s="136" t="n"/>
+      <c r="Q26" s="136" t="n"/>
+      <c r="R26" s="136" t="n"/>
+    </row>
+    <row r="27" ht="16" customHeight="1" s="130">
+      <c r="A27" s="138" t="inlineStr">
         <is>
           <t>38주 대안</t>
         </is>
       </c>
-      <c r="B77" s="134" t="inlineStr">
-        <is>
-          <t>대상</t>
-        </is>
-      </c>
-      <c r="C77" s="134" t="inlineStr">
-        <is>
-          <t>근로시간 현황</t>
-        </is>
-      </c>
-      <c r="D77" s="134" t="inlineStr">
+      <c r="B27" s="139" t="n"/>
+      <c r="C27" s="139" t="n"/>
+      <c r="D27" s="139" t="n"/>
+      <c r="E27" s="138" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="40" customHeight="1" s="130">
-      <c r="A78" s="158" t="inlineStr">
+      <c r="F27" s="139" t="n"/>
+      <c r="G27" s="138" t="inlineStr">
+        <is>
+          <t>근거 (근로시간)</t>
+        </is>
+      </c>
+      <c r="H27" s="139" t="n"/>
+      <c r="I27" s="139" t="n"/>
+      <c r="J27" s="139" t="n"/>
+      <c r="K27" s="139" t="n"/>
+      <c r="L27" s="139" t="n"/>
+      <c r="M27" s="139" t="n"/>
+      <c r="N27" s="139" t="n"/>
+      <c r="O27" s="139" t="n"/>
+      <c r="P27" s="139" t="n"/>
+      <c r="Q27" s="139" t="n"/>
+      <c r="R27" s="139" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1" s="130">
+      <c r="A28" s="165" t="inlineStr">
         <is>
           <t>세정 1안) 2대 주야 맞교대</t>
         </is>
       </c>
-      <c r="B78" s="159" t="inlineStr">
-        <is>
-          <t>세척실 지원 업무도급 7명 등</t>
-        </is>
-      </c>
-      <c r="C78" s="159" t="inlineStr">
-        <is>
-          <t>세척실 14명 평균 150.7H로 전 공정 최고. 6명이 156H 초과, 3명(박태근·김영두·이세호)은 9월 잔업 편성 불가. 9월 가용은 14명 합계 471H</t>
-        </is>
-      </c>
-      <c r="D78" s="160" t="n"/>
-      <c r="E78" s="160" t="n"/>
-      <c r="F78" s="160" t="n"/>
-      <c r="G78" s="160" t="n"/>
-      <c r="H78" s="161" t="inlineStr">
-        <is>
-          <t>야간 추가 시 위반 임박 — 인원 교체 편성 필수</t>
-        </is>
-      </c>
-      <c r="I78" s="160" t="n"/>
-    </row>
-    <row r="79" ht="40" customHeight="1" s="130">
-      <c r="A79" s="158" t="inlineStr">
+      <c r="B28" s="166" t="n"/>
+      <c r="C28" s="166" t="n"/>
+      <c r="D28" s="166" t="n"/>
+      <c r="E28" s="155" t="inlineStr">
+        <is>
+          <t>위반 임박</t>
+        </is>
+      </c>
+      <c r="F28" s="147" t="n"/>
+      <c r="G28" s="167" t="inlineStr">
+        <is>
+          <t>세척실 14명 평균 150.7H 전 공정 최고 · 6명 초과 · 3명(박태근·김영두·이세호) 9월 편성 불가 · 9월 가용 471H</t>
+        </is>
+      </c>
+      <c r="H28" s="134" t="n"/>
+      <c r="I28" s="134" t="n"/>
+      <c r="J28" s="134" t="n"/>
+      <c r="K28" s="134" t="n"/>
+      <c r="L28" s="134" t="n"/>
+      <c r="M28" s="134" t="n"/>
+      <c r="N28" s="134" t="n"/>
+      <c r="O28" s="134" t="n"/>
+      <c r="P28" s="134" t="n"/>
+      <c r="Q28" s="134" t="n"/>
+      <c r="R28" s="134" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1" s="130">
+      <c r="A29" s="165" t="inlineStr">
         <is>
           <t>세정 2안) 직선 1대 Full 잔특</t>
         </is>
       </c>
-      <c r="B79" s="159" t="inlineStr">
-        <is>
-          <t>직선 24명 / 염모 전용 6명</t>
-        </is>
-      </c>
-      <c r="C79" s="159" t="inlineStr">
-        <is>
-          <t>직선 24명 9월 가용 1,178H, 염모 27명 1,388H로 여력 최대(염모 3개월 평균 18.5H)</t>
-        </is>
-      </c>
-      <c r="D79" s="160" t="n"/>
-      <c r="E79" s="160" t="n"/>
-      <c r="F79" s="160" t="n"/>
-      <c r="G79" s="160" t="n"/>
-      <c r="H79" s="162" t="inlineStr">
-        <is>
-          <t>가능 — 염모 전용 인력 활용이 근로시간 관점에서도 유리</t>
-        </is>
-      </c>
-      <c r="I79" s="160" t="n"/>
-    </row>
-    <row r="80" ht="40" customHeight="1" s="130">
-      <c r="A80" s="158" t="inlineStr">
+      <c r="B29" s="166" t="n"/>
+      <c r="C29" s="166" t="n"/>
+      <c r="D29" s="166" t="n"/>
+      <c r="E29" s="157" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F29" s="168" t="n"/>
+      <c r="G29" s="167" t="inlineStr">
+        <is>
+          <t>직선 24명 1,178H · 염모 27명 1,388H (염모 평균 18.5H, 초과 0명) — 여력 최대</t>
+        </is>
+      </c>
+      <c r="H29" s="134" t="n"/>
+      <c r="I29" s="134" t="n"/>
+      <c r="J29" s="134" t="n"/>
+      <c r="K29" s="134" t="n"/>
+      <c r="L29" s="134" t="n"/>
+      <c r="M29" s="134" t="n"/>
+      <c r="N29" s="134" t="n"/>
+      <c r="O29" s="134" t="n"/>
+      <c r="P29" s="134" t="n"/>
+      <c r="Q29" s="134" t="n"/>
+      <c r="R29" s="134" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" s="130">
+      <c r="A30" s="165" t="inlineStr">
         <is>
           <t>멀티 2안) 7·8호기 주야</t>
         </is>
       </c>
-      <c r="B80" s="159" t="inlineStr">
-        <is>
-          <t>멀티 20명</t>
-        </is>
-      </c>
-      <c r="C80" s="159" t="inlineStr">
-        <is>
-          <t>멀티 20명 평균 113.1H, OP 4명(김해경 172 · 이차영 168 · 김선희 163 · 곽옥연 159)이 이미 초과. 9월 가용 976H</t>
-        </is>
-      </c>
-      <c r="D80" s="160" t="n"/>
-      <c r="E80" s="160" t="n"/>
-      <c r="F80" s="160" t="n"/>
-      <c r="G80" s="160" t="n"/>
-      <c r="H80" s="163" t="inlineStr">
-        <is>
-          <t>조건부 — 초과 4명 제외 편성 시 가능</t>
-        </is>
-      </c>
-      <c r="I80" s="160" t="n"/>
-    </row>
-    <row r="81" ht="40" customHeight="1" s="130">
-      <c r="A81" s="158" t="inlineStr">
+      <c r="B30" s="166" t="n"/>
+      <c r="C30" s="166" t="n"/>
+      <c r="D30" s="166" t="n"/>
+      <c r="E30" s="158" t="inlineStr">
+        <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="F30" s="169" t="n"/>
+      <c r="G30" s="167" t="inlineStr">
+        <is>
+          <t>멀티 20명 평균 113.1H · OP 4명(김해경 172·이차영 168·김선희 163·곽옥연 159) 초과 → 제외 편성 시 가능</t>
+        </is>
+      </c>
+      <c r="H30" s="134" t="n"/>
+      <c r="I30" s="134" t="n"/>
+      <c r="J30" s="134" t="n"/>
+      <c r="K30" s="134" t="n"/>
+      <c r="L30" s="134" t="n"/>
+      <c r="M30" s="134" t="n"/>
+      <c r="N30" s="134" t="n"/>
+      <c r="O30" s="134" t="n"/>
+      <c r="P30" s="134" t="n"/>
+      <c r="Q30" s="134" t="n"/>
+      <c r="R30" s="134" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1" s="130">
+      <c r="A31" s="165" t="inlineStr">
         <is>
           <t>튜브) 9/14 2Shift 1대 추가</t>
         </is>
       </c>
-      <c r="B81" s="159" t="inlineStr">
-        <is>
-          <t>튜브 17명</t>
-        </is>
-      </c>
-      <c r="C81" s="159" t="inlineStr">
-        <is>
-          <t>튜브 17명 평균 110.6H, 9월 가용 814H. 초과자는 주임 1명·도우미 1명</t>
-        </is>
-      </c>
-      <c r="D81" s="160" t="n"/>
-      <c r="E81" s="160" t="n"/>
-      <c r="F81" s="160" t="n"/>
-      <c r="G81" s="160" t="n"/>
-      <c r="H81" s="162" t="inlineStr">
-        <is>
-          <t>가능 — OP 편성 여력 있음</t>
-        </is>
-      </c>
-      <c r="I81" s="160" t="n"/>
-    </row>
-    <row r="82" ht="40" customHeight="1" s="130">
-      <c r="A82" s="158" t="inlineStr">
+      <c r="B31" s="166" t="n"/>
+      <c r="C31" s="166" t="n"/>
+      <c r="D31" s="166" t="n"/>
+      <c r="E31" s="157" t="inlineStr">
+        <is>
+          <t>가능</t>
+        </is>
+      </c>
+      <c r="F31" s="168" t="n"/>
+      <c r="G31" s="167" t="inlineStr">
+        <is>
+          <t>튜브 17명 평균 110.6H · 9월 가용 814H · 초과 2명(주임·도우미) 제외 시 OP 편성 여력 있음</t>
+        </is>
+      </c>
+      <c r="H31" s="134" t="n"/>
+      <c r="I31" s="134" t="n"/>
+      <c r="J31" s="134" t="n"/>
+      <c r="K31" s="134" t="n"/>
+      <c r="L31" s="134" t="n"/>
+      <c r="M31" s="134" t="n"/>
+      <c r="N31" s="134" t="n"/>
+      <c r="O31" s="134" t="n"/>
+      <c r="P31" s="134" t="n"/>
+      <c r="Q31" s="134" t="n"/>
+      <c r="R31" s="134" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1" s="130">
+      <c r="A32" s="165" t="inlineStr">
         <is>
           <t>튜브) 간접(주임) → 직접화</t>
         </is>
       </c>
-      <c r="B82" s="159" t="inlineStr">
-        <is>
-          <t>주임 3명</t>
-        </is>
-      </c>
-      <c r="C82" s="159" t="inlineStr">
-        <is>
-          <t>주임 3명 평균 189.8H로 전 직책 최고. 2명 초과(조영순 224.5 · 최명필 191.5). 9월 가용 3명 합계 74H</t>
-        </is>
-      </c>
-      <c r="D82" s="160" t="n"/>
-      <c r="E82" s="160" t="n"/>
-      <c r="F82" s="160" t="n"/>
-      <c r="G82" s="160" t="n"/>
-      <c r="H82" s="161" t="inlineStr">
-        <is>
-          <t>불가 — 근로시간상 추가 투입 여력 없음</t>
-        </is>
-      </c>
-      <c r="I82" s="160" t="n"/>
-    </row>
-    <row r="83" ht="40" customHeight="1" s="130">
-      <c r="A83" s="158" t="inlineStr">
+      <c r="B32" s="166" t="n"/>
+      <c r="C32" s="166" t="n"/>
+      <c r="D32" s="166" t="n"/>
+      <c r="E32" s="155" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F32" s="147" t="n"/>
+      <c r="G32" s="167" t="inlineStr">
+        <is>
+          <t>주임 3명 평균 189.8H 전 직책 최고 · 2명 초과(조영순 224.5·최명필 191.5) · 9월 가용 3명 합 74H</t>
+        </is>
+      </c>
+      <c r="H32" s="134" t="n"/>
+      <c r="I32" s="134" t="n"/>
+      <c r="J32" s="134" t="n"/>
+      <c r="K32" s="134" t="n"/>
+      <c r="L32" s="134" t="n"/>
+      <c r="M32" s="134" t="n"/>
+      <c r="N32" s="134" t="n"/>
+      <c r="O32" s="134" t="n"/>
+      <c r="P32" s="134" t="n"/>
+      <c r="Q32" s="134" t="n"/>
+      <c r="R32" s="134" t="n"/>
+    </row>
+    <row r="33" ht="14" customHeight="1" s="130">
+      <c r="A33" s="165" t="inlineStr">
         <is>
           <t>10월 1·2주 연속 특근</t>
         </is>
       </c>
-      <c r="B83" s="159" t="inlineStr">
-        <is>
-          <t>전 공정</t>
-        </is>
-      </c>
-      <c r="C83" s="159" t="inlineStr">
-        <is>
-          <t>9월 가용을 소진하면 10월 3개월 구간(8·9·10월)에서 즉시 한도 도달</t>
-        </is>
-      </c>
-      <c r="D83" s="160" t="n"/>
-      <c r="E83" s="160" t="n"/>
-      <c r="F83" s="160" t="n"/>
-      <c r="G83" s="160" t="n"/>
-      <c r="H83" s="162" t="inlineStr">
-        <is>
-          <t>9월 편성량과 연동 관리 필요 — 3안(9/23) 권고</t>
-        </is>
-      </c>
-      <c r="I83" s="160" t="n"/>
-    </row>
-    <row r="85" ht="20" customHeight="1" s="130">
-      <c r="A85" s="133" t="inlineStr">
+      <c r="B33" s="166" t="n"/>
+      <c r="C33" s="166" t="n"/>
+      <c r="D33" s="166" t="n"/>
+      <c r="E33" s="158" t="inlineStr">
+        <is>
+          <t>연동 관리</t>
+        </is>
+      </c>
+      <c r="F33" s="169" t="n"/>
+      <c r="G33" s="167" t="inlineStr">
+        <is>
+          <t>9월 가용 소진 시 10월 구간(8·9·10월) 즉시 한도 도달 → 9월 편성량과 연동. 3안(9/23) 권고</t>
+        </is>
+      </c>
+      <c r="H33" s="134" t="n"/>
+      <c r="I33" s="134" t="n"/>
+      <c r="J33" s="134" t="n"/>
+      <c r="K33" s="134" t="n"/>
+      <c r="L33" s="134" t="n"/>
+      <c r="M33" s="134" t="n"/>
+      <c r="N33" s="134" t="n"/>
+      <c r="O33" s="134" t="n"/>
+      <c r="P33" s="134" t="n"/>
+      <c r="Q33" s="134" t="n"/>
+      <c r="R33" s="134" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1" s="130">
+      <c r="A34" s="135" t="inlineStr">
         <is>
           <t>⑤ 원본 수식 확인 필요</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="30" customHeight="1" s="130">
-      <c r="A86" s="134" t="inlineStr">
-        <is>
-          <t>시트</t>
-        </is>
-      </c>
-      <c r="B86" s="134" t="inlineStr">
-        <is>
-          <t>셀</t>
-        </is>
-      </c>
-      <c r="C86" s="134" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="D86" s="134" t="inlineStr">
-        <is>
-          <t>확인 사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="34" customHeight="1" s="130">
-      <c r="A87" s="164" t="inlineStr">
-        <is>
-          <t>아모레 업무</t>
-        </is>
-      </c>
-      <c r="B87" s="155" t="inlineStr">
-        <is>
-          <t>I91</t>
-        </is>
-      </c>
-      <c r="C87" s="159" t="inlineStr">
-        <is>
-          <t>8월 합계 = 2,578 (수식이 아닌 값으로 입력됨)</t>
-        </is>
-      </c>
-      <c r="D87" s="160" t="n"/>
-      <c r="E87" s="165" t="inlineStr">
-        <is>
-          <t>실제 I3:I90 합계는 2,569H로 9H 차이. G91·H91은 SUM 수식인데 I91만 하드코딩되어 있고, J91(3개월 합계 7,680 = 2,446.5+2,664.5+2,569)과도 어긋남. =SUM(I3:I90)으로 수정 필요</t>
-        </is>
-      </c>
-      <c r="F87" s="160" t="n"/>
-      <c r="G87" s="160" t="n"/>
-      <c r="H87" s="160" t="n"/>
-      <c r="I87" s="160" t="n"/>
-    </row>
-    <row r="88" ht="34" customHeight="1" s="130">
-      <c r="A88" s="164" t="inlineStr">
-        <is>
-          <t>아모레 업무</t>
-        </is>
-      </c>
-      <c r="B88" s="155" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C88" s="159">
-        <f>COUNTIF(J3:J153,"&gt;156") → 17</f>
-        <v/>
-      </c>
-      <c r="D88" s="160" t="n"/>
-      <c r="E88" s="165" t="inlineStr">
-        <is>
-          <t>범위 J3:J153에 합계행 J91(7,680)이 포함되어 1명 과다 계산. 실제 초과자는 16명. 범위를 J3:J90으로 수정 필요</t>
-        </is>
-      </c>
-      <c r="F88" s="160" t="n"/>
-      <c r="G88" s="160" t="n"/>
-      <c r="H88" s="160" t="n"/>
-      <c r="I88" s="160" t="n"/>
-    </row>
-    <row r="89" ht="34" customHeight="1" s="130">
-      <c r="A89" s="164" t="inlineStr">
-        <is>
-          <t>아모레 업무</t>
-        </is>
-      </c>
-      <c r="B89" s="155" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="C89" s="159">
-        <f>52*3 → 156</f>
-        <v/>
-      </c>
-      <c r="D89" s="160" t="n"/>
-      <c r="E89" s="165" t="inlineStr">
-        <is>
-          <t>값 156은 맞으나 산출 근거가 다름. 연장근로 한도는 주 12시간이므로 12H × 13주 = 156H가 정확한 산식. '주 52시간 × 3'은 근거로 제시할 수 없음</t>
-        </is>
-      </c>
-      <c r="F89" s="160" t="n"/>
-      <c r="G89" s="160" t="n"/>
-      <c r="H89" s="160" t="n"/>
-      <c r="I89" s="160" t="n"/>
-    </row>
-    <row r="90" ht="34" customHeight="1" s="130">
-      <c r="A90" s="164" t="inlineStr">
-        <is>
-          <t>아모레 생산</t>
-        </is>
-      </c>
-      <c r="B90" s="155" t="inlineStr">
-        <is>
-          <t>Q3 / R3</t>
-        </is>
-      </c>
-      <c r="C90" s="159">
-        <f>52*3 / =COUNTIF(O3:O153,"&gt;156") → 18</f>
-        <v/>
-      </c>
-      <c r="D90" s="160" t="n"/>
-      <c r="E90" s="165" t="inlineStr">
-        <is>
-          <t>COUNTIF 범위는 합계행(154)을 제외하여 18명으로 정확. 산식 근거는 위와 동일하게 정정 권장</t>
-        </is>
-      </c>
-      <c r="F90" s="160" t="n"/>
-      <c r="G90" s="160" t="n"/>
-      <c r="H90" s="160" t="n"/>
-      <c r="I90" s="160" t="n"/>
+      <c r="B34" s="136" t="n"/>
+      <c r="C34" s="136" t="n"/>
+      <c r="D34" s="136" t="n"/>
+      <c r="E34" s="136" t="n"/>
+      <c r="F34" s="136" t="n"/>
+      <c r="G34" s="136" t="n"/>
+      <c r="H34" s="136" t="n"/>
+      <c r="I34" s="136" t="n"/>
+      <c r="J34" s="136" t="n"/>
+      <c r="K34" s="136" t="n"/>
+      <c r="L34" s="136" t="n"/>
+      <c r="M34" s="136" t="n"/>
+      <c r="N34" s="136" t="n"/>
+      <c r="O34" s="136" t="n"/>
+      <c r="P34" s="136" t="n"/>
+      <c r="Q34" s="136" t="n"/>
+      <c r="R34" s="136" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1" s="130">
+      <c r="A35" s="170" t="inlineStr">
+        <is>
+          <t>업무 I91</t>
+        </is>
+      </c>
+      <c r="B35" s="166" t="n"/>
+      <c r="C35" s="166" t="n"/>
+      <c r="D35" s="171" t="inlineStr">
+        <is>
+          <t>8월 합계가 수식이 아닌 값 2,578. 실제 합 2,569 (9H 차이) · J91(7,680)과 불일치 → =SUM(I3:I90)</t>
+        </is>
+      </c>
+      <c r="E35" s="134" t="n"/>
+      <c r="F35" s="134" t="n"/>
+      <c r="G35" s="134" t="n"/>
+      <c r="H35" s="134" t="n"/>
+      <c r="I35" s="134" t="n"/>
+      <c r="J35" s="134" t="n"/>
+      <c r="K35" s="134" t="n"/>
+      <c r="L35" s="134" t="n"/>
+      <c r="M35" s="134" t="n"/>
+      <c r="N35" s="134" t="n"/>
+      <c r="O35" s="134" t="n"/>
+      <c r="P35" s="134" t="n"/>
+      <c r="Q35" s="134" t="n"/>
+      <c r="R35" s="134" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1" s="130">
+      <c r="A36" s="170" t="inlineStr">
+        <is>
+          <t>업무 M3</t>
+        </is>
+      </c>
+      <c r="B36" s="166" t="n"/>
+      <c r="C36" s="166" t="n"/>
+      <c r="D36" s="171">
+        <f>COUNTIF(J3:J153,"&gt;156") 범위에 합계행 J91(7,680) 포함되어 17명. 실제 16명 → 범위 J3:J90</f>
+        <v/>
+      </c>
+      <c r="E36" s="134" t="n"/>
+      <c r="F36" s="134" t="n"/>
+      <c r="G36" s="134" t="n"/>
+      <c r="H36" s="134" t="n"/>
+      <c r="I36" s="134" t="n"/>
+      <c r="J36" s="134" t="n"/>
+      <c r="K36" s="134" t="n"/>
+      <c r="L36" s="134" t="n"/>
+      <c r="M36" s="134" t="n"/>
+      <c r="N36" s="134" t="n"/>
+      <c r="O36" s="134" t="n"/>
+      <c r="P36" s="134" t="n"/>
+      <c r="Q36" s="134" t="n"/>
+      <c r="R36" s="134" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1" s="130">
+      <c r="A37" s="170" t="inlineStr">
+        <is>
+          <t>업무 L3 / 생산 Q3</t>
+        </is>
+      </c>
+      <c r="B37" s="166" t="n"/>
+      <c r="C37" s="166" t="n"/>
+      <c r="D37" s="171">
+        <f>52*3. 값 156은 맞으나 연장 한도는 주 12H → =12*13이 정확한 근거 (생산 R3 COUNTIF는 정상)</f>
+        <v/>
+      </c>
+      <c r="E37" s="134" t="n"/>
+      <c r="F37" s="134" t="n"/>
+      <c r="G37" s="134" t="n"/>
+      <c r="H37" s="134" t="n"/>
+      <c r="I37" s="134" t="n"/>
+      <c r="J37" s="134" t="n"/>
+      <c r="K37" s="134" t="n"/>
+      <c r="L37" s="134" t="n"/>
+      <c r="M37" s="134" t="n"/>
+      <c r="N37" s="134" t="n"/>
+      <c r="O37" s="134" t="n"/>
+      <c r="P37" s="134" t="n"/>
+      <c r="Q37" s="134" t="n"/>
+      <c r="R37" s="134" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="E88:I88"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="E87:I87"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="E90:I90"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="E89:I89"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C78:G78"/>
+  <mergeCells count="38">
+    <mergeCell ref="J6:R6"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="G28:R28"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J4:R4"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="G30:R30"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A26:R26"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="J7:R7"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="G33:R33"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="D37:R37"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G29:R29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G32:R32"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G31:R31"/>
+    <mergeCell ref="D35:R35"/>
+    <mergeCell ref="A34:R34"/>
+    <mergeCell ref="J5:R5"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G27:R27"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="D36:R36"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4698,16 +3885,16 @@
       <c r="F3" s="58" t="n">
         <v>45901</v>
       </c>
-      <c r="G3" s="166" t="n">
+      <c r="G3" s="172" t="n">
         <v>38</v>
       </c>
-      <c r="H3" s="167" t="n">
+      <c r="H3" s="173" t="n">
         <v>40</v>
       </c>
-      <c r="I3" s="168" t="n">
+      <c r="I3" s="174" t="n">
         <v>31.5</v>
       </c>
-      <c r="J3" s="169">
+      <c r="J3" s="175">
         <f>SUM(G3:I3)</f>
         <v/>
       </c>
@@ -4747,16 +3934,16 @@
       <c r="F4" s="21" t="n">
         <v>44348</v>
       </c>
-      <c r="G4" s="170" t="n">
+      <c r="G4" s="176" t="n">
         <v>21.5</v>
       </c>
-      <c r="H4" s="171" t="n">
+      <c r="H4" s="177" t="n">
         <v>32</v>
       </c>
-      <c r="I4" s="172" t="n">
+      <c r="I4" s="178" t="n">
         <v>13</v>
       </c>
-      <c r="J4" s="173">
+      <c r="J4" s="179">
         <f>SUM(G4:I4)</f>
         <v/>
       </c>
@@ -4788,16 +3975,16 @@
       <c r="F5" s="23" t="n">
         <v>44417</v>
       </c>
-      <c r="G5" s="170" t="n">
+      <c r="G5" s="176" t="n">
         <v>62</v>
       </c>
-      <c r="H5" s="171" t="n">
+      <c r="H5" s="177" t="n">
         <v>43.5</v>
       </c>
-      <c r="I5" s="172" t="n">
+      <c r="I5" s="178" t="n">
         <v>21</v>
       </c>
-      <c r="J5" s="173">
+      <c r="J5" s="179">
         <f>SUM(G5:I5)</f>
         <v/>
       </c>
@@ -4829,16 +4016,16 @@
       <c r="F6" s="23" t="n">
         <v>45264</v>
       </c>
-      <c r="G6" s="170" t="n">
+      <c r="G6" s="176" t="n">
         <v>28</v>
       </c>
-      <c r="H6" s="171" t="n">
+      <c r="H6" s="177" t="n">
         <v>26</v>
       </c>
-      <c r="I6" s="172" t="n">
+      <c r="I6" s="178" t="n">
         <v>17</v>
       </c>
-      <c r="J6" s="173">
+      <c r="J6" s="179">
         <f>SUM(G6:I6)</f>
         <v/>
       </c>
@@ -4870,16 +4057,16 @@
       <c r="F7" s="24" t="n">
         <v>45887</v>
       </c>
-      <c r="G7" s="170" t="n">
+      <c r="G7" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="171" t="n">
+      <c r="H7" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="172" t="n">
+      <c r="I7" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="173">
+      <c r="J7" s="179">
         <f>SUM(G7:I7)</f>
         <v/>
       </c>
@@ -4911,16 +4098,16 @@
       <c r="F8" s="23" t="n">
         <v>45635</v>
       </c>
-      <c r="G8" s="170" t="n">
+      <c r="G8" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="171" t="n">
+      <c r="H8" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="172" t="n">
+      <c r="I8" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="173">
+      <c r="J8" s="179">
         <f>SUM(G8:I8)</f>
         <v/>
       </c>
@@ -4952,16 +4139,16 @@
       <c r="F9" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G9" s="174" t="n">
+      <c r="G9" s="180" t="n">
         <v>19.5</v>
       </c>
-      <c r="H9" s="175" t="n">
+      <c r="H9" s="181" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="172" t="n">
+      <c r="I9" s="178" t="n">
         <v>1.5</v>
       </c>
-      <c r="J9" s="173">
+      <c r="J9" s="179">
         <f>SUM(G9:I9)</f>
         <v/>
       </c>
@@ -4993,16 +4180,16 @@
       <c r="F10" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G10" s="176" t="n">
+      <c r="G10" s="182" t="n">
         <v>49.5</v>
       </c>
-      <c r="H10" s="177" t="n">
+      <c r="H10" s="183" t="n">
         <v>51</v>
       </c>
-      <c r="I10" s="172" t="n">
+      <c r="I10" s="178" t="n">
         <v>52</v>
       </c>
-      <c r="J10" s="173">
+      <c r="J10" s="179">
         <f>SUM(G10:I10)</f>
         <v/>
       </c>
@@ -5034,16 +4221,16 @@
       <c r="F11" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G11" s="174" t="n">
+      <c r="G11" s="180" t="n">
         <v>41.5</v>
       </c>
-      <c r="H11" s="175" t="n">
+      <c r="H11" s="181" t="n">
         <v>41</v>
       </c>
-      <c r="I11" s="172" t="n">
+      <c r="I11" s="178" t="n">
         <v>38</v>
       </c>
-      <c r="J11" s="173">
+      <c r="J11" s="179">
         <f>SUM(G11:I11)</f>
         <v/>
       </c>
@@ -5075,16 +4262,16 @@
       <c r="F12" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G12" s="174" t="n">
+      <c r="G12" s="180" t="n">
         <v>18</v>
       </c>
-      <c r="H12" s="175" t="n">
+      <c r="H12" s="181" t="n">
         <v>32</v>
       </c>
-      <c r="I12" s="172" t="n">
+      <c r="I12" s="178" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="173">
+      <c r="J12" s="179">
         <f>SUM(G12:I12)</f>
         <v/>
       </c>
@@ -5116,20 +4303,20 @@
       <c r="F13" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G13" s="174" t="n">
+      <c r="G13" s="180" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="175" t="n">
+      <c r="H13" s="181" t="n">
         <v>84</v>
       </c>
-      <c r="I13" s="172" t="n">
+      <c r="I13" s="178" t="n">
         <v>94</v>
       </c>
-      <c r="J13" s="173">
+      <c r="J13" s="179">
         <f>SUM(G13:I13)</f>
         <v/>
       </c>
-      <c r="K13" s="178">
+      <c r="K13" s="184">
         <f>J13-$L$3</f>
         <v/>
       </c>
@@ -5160,20 +4347,20 @@
       <c r="F14" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G14" s="174" t="n">
+      <c r="G14" s="180" t="n">
         <v>51</v>
       </c>
-      <c r="H14" s="175" t="n">
+      <c r="H14" s="181" t="n">
         <v>67.5</v>
       </c>
-      <c r="I14" s="172" t="n">
+      <c r="I14" s="178" t="n">
         <v>73.5</v>
       </c>
-      <c r="J14" s="173">
+      <c r="J14" s="179">
         <f>SUM(G14:I14)</f>
         <v/>
       </c>
-      <c r="K14" s="178">
+      <c r="K14" s="184">
         <f>J14-$L$3</f>
         <v/>
       </c>
@@ -5204,16 +4391,16 @@
       <c r="F15" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G15" s="174" t="n">
+      <c r="G15" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="175" t="n">
+      <c r="H15" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="172" t="n">
+      <c r="I15" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="173">
+      <c r="J15" s="179">
         <f>SUM(G15:I15)</f>
         <v/>
       </c>
@@ -5242,16 +4429,16 @@
       <c r="F16" s="26" t="n">
         <v>46143</v>
       </c>
-      <c r="G16" s="174" t="n">
+      <c r="G16" s="180" t="n">
         <v>44</v>
       </c>
-      <c r="H16" s="175" t="n">
+      <c r="H16" s="181" t="n">
         <v>38</v>
       </c>
-      <c r="I16" s="172" t="n">
+      <c r="I16" s="178" t="n">
         <v>23</v>
       </c>
-      <c r="J16" s="173">
+      <c r="J16" s="179">
         <f>SUM(G16:I16)</f>
         <v/>
       </c>
@@ -5283,16 +4470,16 @@
       <c r="F17" s="23" t="n">
         <v>44805</v>
       </c>
-      <c r="G17" s="170" t="n">
+      <c r="G17" s="176" t="n">
         <v>36</v>
       </c>
-      <c r="H17" s="171" t="n">
+      <c r="H17" s="177" t="n">
         <v>39</v>
       </c>
-      <c r="I17" s="172" t="n">
+      <c r="I17" s="178" t="n">
         <v>41</v>
       </c>
-      <c r="J17" s="173">
+      <c r="J17" s="179">
         <f>SUM(G17:I17)</f>
         <v/>
       </c>
@@ -5324,16 +4511,16 @@
       <c r="F18" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G18" s="174" t="n">
+      <c r="G18" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="175" t="n">
+      <c r="H18" s="181" t="n">
         <v>16</v>
       </c>
-      <c r="I18" s="172" t="n">
+      <c r="I18" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="173">
+      <c r="J18" s="179">
         <f>SUM(G18:I18)</f>
         <v/>
       </c>
@@ -5365,16 +4552,16 @@
       <c r="F19" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G19" s="174" t="n">
+      <c r="G19" s="180" t="n">
         <v>46.5</v>
       </c>
-      <c r="H19" s="175" t="n">
+      <c r="H19" s="181" t="n">
         <v>33</v>
       </c>
-      <c r="I19" s="172" t="n">
+      <c r="I19" s="178" t="n">
         <v>38.5</v>
       </c>
-      <c r="J19" s="173">
+      <c r="J19" s="179">
         <f>SUM(G19:I19)</f>
         <v/>
       </c>
@@ -5408,16 +4595,16 @@
       <c r="F20" s="23" t="n">
         <v>44652</v>
       </c>
-      <c r="G20" s="170" t="n">
+      <c r="G20" s="176" t="n">
         <v>9.5</v>
       </c>
-      <c r="H20" s="171" t="n">
+      <c r="H20" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I20" s="172" t="n">
+      <c r="I20" s="178" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="173">
+      <c r="J20" s="179">
         <f>SUM(G20:I20)</f>
         <v/>
       </c>
@@ -5449,16 +4636,16 @@
       <c r="F21" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G21" s="174" t="n">
+      <c r="G21" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="H21" s="175" t="n">
+      <c r="H21" s="181" t="n">
         <v>9</v>
       </c>
-      <c r="I21" s="172" t="n">
+      <c r="I21" s="178" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="173">
+      <c r="J21" s="179">
         <f>SUM(G21:I21)</f>
         <v/>
       </c>
@@ -5490,20 +4677,20 @@
       <c r="F22" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G22" s="176" t="n">
+      <c r="G22" s="182" t="n">
         <v>66</v>
       </c>
-      <c r="H22" s="177" t="n">
+      <c r="H22" s="183" t="n">
         <v>62</v>
       </c>
-      <c r="I22" s="172" t="n">
+      <c r="I22" s="178" t="n">
         <v>59</v>
       </c>
-      <c r="J22" s="173">
+      <c r="J22" s="179">
         <f>SUM(G22:I22)</f>
         <v/>
       </c>
-      <c r="K22" s="178">
+      <c r="K22" s="184">
         <f>J22-$L$3</f>
         <v/>
       </c>
@@ -5534,16 +4721,16 @@
       <c r="F23" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G23" s="176" t="n">
+      <c r="G23" s="182" t="n">
         <v>30.5</v>
       </c>
-      <c r="H23" s="177" t="n">
+      <c r="H23" s="183" t="n">
         <v>32.5</v>
       </c>
-      <c r="I23" s="172" t="n">
+      <c r="I23" s="178" t="n">
         <v>22.5</v>
       </c>
-      <c r="J23" s="173">
+      <c r="J23" s="179">
         <f>SUM(G23:I23)</f>
         <v/>
       </c>
@@ -5575,16 +4762,16 @@
       <c r="F24" s="23" t="n">
         <v>45383</v>
       </c>
-      <c r="G24" s="176" t="n">
+      <c r="G24" s="182" t="n">
         <v>21.5</v>
       </c>
-      <c r="H24" s="177" t="n">
+      <c r="H24" s="183" t="n">
         <v>30.5</v>
       </c>
-      <c r="I24" s="172" t="n">
+      <c r="I24" s="178" t="n">
         <v>18</v>
       </c>
-      <c r="J24" s="173">
+      <c r="J24" s="179">
         <f>SUM(G24:I24)</f>
         <v/>
       </c>
@@ -5616,16 +4803,16 @@
       <c r="F25" s="23" t="n">
         <v>45068</v>
       </c>
-      <c r="G25" s="176" t="n">
+      <c r="G25" s="182" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="177" t="n">
+      <c r="H25" s="183" t="n">
         <v>27</v>
       </c>
-      <c r="I25" s="172" t="n">
+      <c r="I25" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="173">
+      <c r="J25" s="179">
         <f>SUM(G25:I25)</f>
         <v/>
       </c>
@@ -5657,16 +4844,16 @@
       <c r="F26" s="23" t="n">
         <v>44562</v>
       </c>
-      <c r="G26" s="176" t="n">
+      <c r="G26" s="182" t="n">
         <v>21</v>
       </c>
-      <c r="H26" s="177" t="n">
+      <c r="H26" s="183" t="n">
         <v>20.5</v>
       </c>
-      <c r="I26" s="172" t="n">
+      <c r="I26" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="173">
+      <c r="J26" s="179">
         <f>SUM(G26:I26)</f>
         <v/>
       </c>
@@ -5700,16 +4887,16 @@
       <c r="F27" s="23" t="n">
         <v>44896</v>
       </c>
-      <c r="G27" s="176" t="n">
+      <c r="G27" s="182" t="n">
         <v>18.5</v>
       </c>
-      <c r="H27" s="177" t="n">
+      <c r="H27" s="183" t="n">
         <v>23.5</v>
       </c>
-      <c r="I27" s="172" t="n">
+      <c r="I27" s="178" t="n">
         <v>16</v>
       </c>
-      <c r="J27" s="173">
+      <c r="J27" s="179">
         <f>SUM(G27:I27)</f>
         <v/>
       </c>
@@ -5741,20 +4928,20 @@
       <c r="F28" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G28" s="170" t="n">
+      <c r="G28" s="176" t="n">
         <v>49</v>
       </c>
-      <c r="H28" s="171" t="n">
+      <c r="H28" s="177" t="n">
         <v>71.5</v>
       </c>
-      <c r="I28" s="172" t="n">
+      <c r="I28" s="178" t="n">
         <v>39.5</v>
       </c>
-      <c r="J28" s="173">
+      <c r="J28" s="179">
         <f>SUM(G28:I28)</f>
         <v/>
       </c>
-      <c r="K28" s="178">
+      <c r="K28" s="184">
         <f>J28-$L$3</f>
         <v/>
       </c>
@@ -5785,16 +4972,16 @@
       <c r="F29" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G29" s="174" t="n">
+      <c r="G29" s="180" t="n">
         <v>25</v>
       </c>
-      <c r="H29" s="175" t="n">
+      <c r="H29" s="181" t="n">
         <v>18</v>
       </c>
-      <c r="I29" s="172" t="n">
+      <c r="I29" s="178" t="n">
         <v>26</v>
       </c>
-      <c r="J29" s="173">
+      <c r="J29" s="179">
         <f>SUM(G29:I29)</f>
         <v/>
       </c>
@@ -5826,16 +5013,16 @@
       <c r="F30" s="24" t="n">
         <v>45754</v>
       </c>
-      <c r="G30" s="174" t="n">
+      <c r="G30" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="H30" s="175" t="n">
+      <c r="H30" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="172" t="n">
+      <c r="I30" s="178" t="n">
         <v>2.5</v>
       </c>
-      <c r="J30" s="173">
+      <c r="J30" s="179">
         <f>SUM(G30:I30)</f>
         <v/>
       </c>
@@ -5867,16 +5054,16 @@
       <c r="F31" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G31" s="174" t="n">
+      <c r="G31" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="H31" s="175" t="n">
+      <c r="H31" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="172" t="n">
+      <c r="I31" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="173">
+      <c r="J31" s="179">
         <f>SUM(G31:I31)</f>
         <v/>
       </c>
@@ -5910,16 +5097,16 @@
       <c r="F32" s="24" t="n">
         <v>45200</v>
       </c>
-      <c r="G32" s="174" t="n">
+      <c r="G32" s="180" t="n">
         <v>42</v>
       </c>
-      <c r="H32" s="175" t="n">
+      <c r="H32" s="181" t="n">
         <v>32</v>
       </c>
-      <c r="I32" s="172" t="n">
+      <c r="I32" s="178" t="n">
         <v>38</v>
       </c>
-      <c r="J32" s="173">
+      <c r="J32" s="179">
         <f>SUM(G32:I32)</f>
         <v/>
       </c>
@@ -5951,20 +5138,20 @@
       <c r="F33" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G33" s="174" t="n">
+      <c r="G33" s="180" t="n">
         <v>91</v>
       </c>
-      <c r="H33" s="175" t="n">
+      <c r="H33" s="181" t="n">
         <v>90</v>
       </c>
-      <c r="I33" s="172" t="n">
+      <c r="I33" s="178" t="n">
         <v>108.5</v>
       </c>
-      <c r="J33" s="173">
+      <c r="J33" s="179">
         <f>SUM(G33:I33)</f>
         <v/>
       </c>
-      <c r="K33" s="178">
+      <c r="K33" s="184">
         <f>J33-$L$3</f>
         <v/>
       </c>
@@ -5995,20 +5182,20 @@
       <c r="F34" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G34" s="174" t="n">
+      <c r="G34" s="180" t="n">
         <v>56</v>
       </c>
-      <c r="H34" s="175" t="n">
+      <c r="H34" s="181" t="n">
         <v>60</v>
       </c>
-      <c r="I34" s="172" t="n">
+      <c r="I34" s="178" t="n">
         <v>61</v>
       </c>
-      <c r="J34" s="173">
+      <c r="J34" s="179">
         <f>SUM(G34:I34)</f>
         <v/>
       </c>
-      <c r="K34" s="178">
+      <c r="K34" s="184">
         <f>J34-$L$3</f>
         <v/>
       </c>
@@ -6037,16 +5224,16 @@
       <c r="F35" s="23" t="n">
         <v>45748</v>
       </c>
-      <c r="G35" s="174" t="n">
+      <c r="G35" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="175" t="n">
+      <c r="H35" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="172" t="n">
+      <c r="I35" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="173">
+      <c r="J35" s="179">
         <f>SUM(G35:I35)</f>
         <v/>
       </c>
@@ -6078,16 +5265,16 @@
       <c r="F36" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G36" s="174" t="n">
+      <c r="G36" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="175" t="n">
+      <c r="H36" s="181" t="n">
         <v>37</v>
       </c>
-      <c r="I36" s="172" t="n">
+      <c r="I36" s="178" t="n">
         <v>45</v>
       </c>
-      <c r="J36" s="173">
+      <c r="J36" s="179">
         <f>SUM(G36:I36)</f>
         <v/>
       </c>
@@ -6119,20 +5306,20 @@
       <c r="F37" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G37" s="174" t="n">
+      <c r="G37" s="180" t="n">
         <v>64</v>
       </c>
-      <c r="H37" s="175" t="n">
+      <c r="H37" s="181" t="n">
         <v>68</v>
       </c>
-      <c r="I37" s="172" t="n">
+      <c r="I37" s="178" t="n">
         <v>72</v>
       </c>
-      <c r="J37" s="173">
+      <c r="J37" s="179">
         <f>SUM(G37:I37)</f>
         <v/>
       </c>
-      <c r="K37" s="178">
+      <c r="K37" s="184">
         <f>J37-$L$3</f>
         <v/>
       </c>
@@ -6163,20 +5350,20 @@
       <c r="F38" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G38" s="174" t="n">
+      <c r="G38" s="180" t="n">
         <v>73.5</v>
       </c>
-      <c r="H38" s="175" t="n">
+      <c r="H38" s="181" t="n">
         <v>69.5</v>
       </c>
-      <c r="I38" s="172" t="n">
+      <c r="I38" s="178" t="n">
         <v>63</v>
       </c>
-      <c r="J38" s="173">
+      <c r="J38" s="179">
         <f>SUM(G38:I38)</f>
         <v/>
       </c>
-      <c r="K38" s="178">
+      <c r="K38" s="184">
         <f>J38-$L$3</f>
         <v/>
       </c>
@@ -6207,16 +5394,16 @@
       <c r="F39" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G39" s="174" t="n">
+      <c r="G39" s="180" t="n">
         <v>61</v>
       </c>
-      <c r="H39" s="175" t="n">
+      <c r="H39" s="181" t="n">
         <v>53</v>
       </c>
-      <c r="I39" s="172" t="n">
+      <c r="I39" s="178" t="n">
         <v>40</v>
       </c>
-      <c r="J39" s="173">
+      <c r="J39" s="179">
         <f>SUM(G39:I39)</f>
         <v/>
       </c>
@@ -6248,20 +5435,20 @@
       <c r="F40" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G40" s="174" t="n">
+      <c r="G40" s="180" t="n">
         <v>60</v>
       </c>
-      <c r="H40" s="175" t="n">
+      <c r="H40" s="181" t="n">
         <v>73</v>
       </c>
-      <c r="I40" s="172" t="n">
+      <c r="I40" s="178" t="n">
         <v>56.5</v>
       </c>
-      <c r="J40" s="173">
+      <c r="J40" s="179">
         <f>SUM(G40:I40)</f>
         <v/>
       </c>
-      <c r="K40" s="178">
+      <c r="K40" s="184">
         <f>J40-$L$3</f>
         <v/>
       </c>
@@ -6294,16 +5481,16 @@
       <c r="F41" s="23" t="n">
         <v>45962</v>
       </c>
-      <c r="G41" s="174" t="n">
+      <c r="G41" s="180" t="n">
         <v>25</v>
       </c>
-      <c r="H41" s="175" t="n">
+      <c r="H41" s="181" t="n">
         <v>36</v>
       </c>
-      <c r="I41" s="172" t="n">
+      <c r="I41" s="178" t="n">
         <v>25</v>
       </c>
-      <c r="J41" s="173">
+      <c r="J41" s="179">
         <f>SUM(G41:I41)</f>
         <v/>
       </c>
@@ -6335,16 +5522,16 @@
       <c r="F42" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G42" s="174" t="n">
+      <c r="G42" s="180" t="n">
         <v>46.5</v>
       </c>
-      <c r="H42" s="175" t="n">
+      <c r="H42" s="181" t="n">
         <v>40.5</v>
       </c>
-      <c r="I42" s="172" t="n">
+      <c r="I42" s="178" t="n">
         <v>42</v>
       </c>
-      <c r="J42" s="173">
+      <c r="J42" s="179">
         <f>SUM(G42:I42)</f>
         <v/>
       </c>
@@ -6376,16 +5563,16 @@
       <c r="F43" s="23" t="n">
         <v>44991</v>
       </c>
-      <c r="G43" s="174" t="n">
+      <c r="G43" s="180" t="n">
         <v>0.5</v>
       </c>
-      <c r="H43" s="175" t="n">
+      <c r="H43" s="181" t="n">
         <v>25.5</v>
       </c>
-      <c r="I43" s="172" t="n">
+      <c r="I43" s="178" t="n">
         <v>14.5</v>
       </c>
-      <c r="J43" s="173">
+      <c r="J43" s="179">
         <f>SUM(G43:I43)</f>
         <v/>
       </c>
@@ -6417,16 +5604,16 @@
       <c r="F44" s="23" t="n">
         <v>44229</v>
       </c>
-      <c r="G44" s="170" t="n">
+      <c r="G44" s="176" t="n">
         <v>9.5</v>
       </c>
-      <c r="H44" s="171" t="n">
+      <c r="H44" s="177" t="n">
         <v>15.5</v>
       </c>
-      <c r="I44" s="172" t="n">
+      <c r="I44" s="178" t="n">
         <v>6.5</v>
       </c>
-      <c r="J44" s="173">
+      <c r="J44" s="179">
         <f>SUM(G44:I44)</f>
         <v/>
       </c>
@@ -6458,16 +5645,16 @@
       <c r="F45" s="21" t="n">
         <v>44621</v>
       </c>
-      <c r="G45" s="170" t="n">
+      <c r="G45" s="176" t="n">
         <v>8</v>
       </c>
-      <c r="H45" s="171" t="n">
+      <c r="H45" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="172" t="n">
+      <c r="I45" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="173">
+      <c r="J45" s="179">
         <f>SUM(G45:I45)</f>
         <v/>
       </c>
@@ -6488,16 +5675,16 @@
       <c r="F46" s="21" t="n">
         <v>46235</v>
       </c>
-      <c r="G46" s="170" t="n">
+      <c r="G46" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="171" t="n">
+      <c r="H46" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="172" t="n">
+      <c r="I46" s="178" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="173">
+      <c r="J46" s="179">
         <f>SUM(G46:I46)</f>
         <v/>
       </c>
@@ -6529,16 +5716,16 @@
       <c r="F47" s="21" t="n">
         <v>44348</v>
       </c>
-      <c r="G47" s="170" t="n">
+      <c r="G47" s="176" t="n">
         <v>36</v>
       </c>
-      <c r="H47" s="171" t="n">
+      <c r="H47" s="177" t="n">
         <v>39</v>
       </c>
-      <c r="I47" s="172" t="n">
+      <c r="I47" s="178" t="n">
         <v>41</v>
       </c>
-      <c r="J47" s="173">
+      <c r="J47" s="179">
         <f>SUM(G47:I47)</f>
         <v/>
       </c>
@@ -6570,16 +5757,16 @@
       <c r="F48" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G48" s="174" t="n">
+      <c r="G48" s="180" t="n">
         <v>16.5</v>
       </c>
-      <c r="H48" s="175" t="n">
+      <c r="H48" s="181" t="n">
         <v>16</v>
       </c>
-      <c r="I48" s="172" t="n">
+      <c r="I48" s="178" t="n">
         <v>24</v>
       </c>
-      <c r="J48" s="173">
+      <c r="J48" s="179">
         <f>SUM(G48:I48)</f>
         <v/>
       </c>
@@ -6613,16 +5800,16 @@
       <c r="F49" s="21" t="n">
         <v>44927</v>
       </c>
-      <c r="G49" s="170" t="n">
+      <c r="G49" s="176" t="n">
         <v>20.5</v>
       </c>
-      <c r="H49" s="171" t="n">
+      <c r="H49" s="177" t="n">
         <v>33</v>
       </c>
-      <c r="I49" s="172" t="n">
+      <c r="I49" s="178" t="n">
         <v>20</v>
       </c>
-      <c r="J49" s="173">
+      <c r="J49" s="179">
         <f>SUM(G49:I49)</f>
         <v/>
       </c>
@@ -6652,16 +5839,16 @@
       <c r="F50" s="21" t="n">
         <v>45677</v>
       </c>
-      <c r="G50" s="170" t="n">
+      <c r="G50" s="176" t="n">
         <v>36</v>
       </c>
-      <c r="H50" s="171" t="n">
+      <c r="H50" s="177" t="n">
         <v>29</v>
       </c>
-      <c r="I50" s="172" t="n">
+      <c r="I50" s="178" t="n">
         <v>40</v>
       </c>
-      <c r="J50" s="173">
+      <c r="J50" s="179">
         <f>SUM(G50:I50)</f>
         <v/>
       </c>
@@ -6693,16 +5880,16 @@
       <c r="F51" s="21" t="n">
         <v>46214</v>
       </c>
-      <c r="G51" s="170" t="n">
+      <c r="G51" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="171" t="n">
+      <c r="H51" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="172" t="n">
+      <c r="I51" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="173">
+      <c r="J51" s="179">
         <f>SUM(G51:I51)</f>
         <v/>
       </c>
@@ -6734,20 +5921,20 @@
       <c r="F52" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G52" s="174" t="n">
+      <c r="G52" s="180" t="n">
         <v>61.5</v>
       </c>
-      <c r="H52" s="175" t="n">
+      <c r="H52" s="181" t="n">
         <v>42</v>
       </c>
-      <c r="I52" s="172" t="n">
+      <c r="I52" s="178" t="n">
         <v>53.5</v>
       </c>
-      <c r="J52" s="173">
+      <c r="J52" s="179">
         <f>SUM(G52:I52)</f>
         <v/>
       </c>
-      <c r="K52" s="178">
+      <c r="K52" s="184">
         <f>J52-$L$3</f>
         <v/>
       </c>
@@ -6778,16 +5965,16 @@
       <c r="F53" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G53" s="174" t="n">
+      <c r="G53" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="175" t="n">
+      <c r="H53" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="172" t="n">
+      <c r="I53" s="178" t="n">
         <v>17</v>
       </c>
-      <c r="J53" s="173">
+      <c r="J53" s="179">
         <f>SUM(G53:I53)</f>
         <v/>
       </c>
@@ -6815,16 +6002,16 @@
       <c r="F54" s="21" t="n">
         <v>46062</v>
       </c>
-      <c r="G54" s="174" t="n">
+      <c r="G54" s="180" t="n">
         <v>39.5</v>
       </c>
-      <c r="H54" s="175" t="n">
+      <c r="H54" s="181" t="n">
         <v>32</v>
       </c>
-      <c r="I54" s="172" t="n">
+      <c r="I54" s="178" t="n">
         <v>33</v>
       </c>
-      <c r="J54" s="173">
+      <c r="J54" s="179">
         <f>SUM(G54:I54)</f>
         <v/>
       </c>
@@ -6858,20 +6045,20 @@
       <c r="F55" s="24" t="n">
         <v>45139</v>
       </c>
-      <c r="G55" s="174" t="n">
+      <c r="G55" s="180" t="n">
         <v>76</v>
       </c>
-      <c r="H55" s="175" t="n">
+      <c r="H55" s="181" t="n">
         <v>81</v>
       </c>
-      <c r="I55" s="172" t="n">
+      <c r="I55" s="178" t="n">
         <v>92</v>
       </c>
-      <c r="J55" s="173">
+      <c r="J55" s="179">
         <f>SUM(G55:I55)</f>
         <v/>
       </c>
-      <c r="K55" s="178">
+      <c r="K55" s="184">
         <f>J55-$L$3</f>
         <v/>
       </c>
@@ -6902,16 +6089,16 @@
       <c r="F56" s="24" t="n">
         <v>45817</v>
       </c>
-      <c r="G56" s="174" t="n">
+      <c r="G56" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="175" t="n">
+      <c r="H56" s="181" t="n">
         <v>8</v>
       </c>
-      <c r="I56" s="172" t="n">
+      <c r="I56" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J56" s="173">
+      <c r="J56" s="179">
         <f>SUM(G56:I56)</f>
         <v/>
       </c>
@@ -6943,16 +6130,16 @@
       <c r="F57" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G57" s="174" t="n">
+      <c r="G57" s="180" t="n">
         <v>42</v>
       </c>
-      <c r="H57" s="175" t="n">
+      <c r="H57" s="181" t="n">
         <v>47</v>
       </c>
-      <c r="I57" s="172" t="n">
+      <c r="I57" s="178" t="n">
         <v>43</v>
       </c>
-      <c r="J57" s="173">
+      <c r="J57" s="179">
         <f>SUM(G57:I57)</f>
         <v/>
       </c>
@@ -6986,16 +6173,16 @@
       <c r="F58" s="24" t="n">
         <v>46023</v>
       </c>
-      <c r="G58" s="170" t="n">
+      <c r="G58" s="176" t="n">
         <v>33</v>
       </c>
-      <c r="H58" s="171" t="n">
+      <c r="H58" s="177" t="n">
         <v>37</v>
       </c>
-      <c r="I58" s="172" t="n">
+      <c r="I58" s="178" t="n">
         <v>41</v>
       </c>
-      <c r="J58" s="173">
+      <c r="J58" s="179">
         <f>SUM(G58:I58)</f>
         <v/>
       </c>
@@ -7029,16 +6216,16 @@
       <c r="F59" s="23" t="n">
         <v>44562</v>
       </c>
-      <c r="G59" s="170" t="n">
+      <c r="G59" s="176" t="n">
         <v>19</v>
       </c>
-      <c r="H59" s="171" t="n">
+      <c r="H59" s="177" t="n">
         <v>12</v>
       </c>
-      <c r="I59" s="172" t="n">
+      <c r="I59" s="178" t="n">
         <v>11</v>
       </c>
-      <c r="J59" s="173">
+      <c r="J59" s="179">
         <f>SUM(G59:I59)</f>
         <v/>
       </c>
@@ -7072,16 +6259,16 @@
       <c r="F60" s="23" t="n">
         <v>45231</v>
       </c>
-      <c r="G60" s="174" t="n">
+      <c r="G60" s="180" t="n">
         <v>57.5</v>
       </c>
-      <c r="H60" s="175" t="n">
+      <c r="H60" s="181" t="n">
         <v>36</v>
       </c>
-      <c r="I60" s="172" t="n">
+      <c r="I60" s="178" t="n">
         <v>44.5</v>
       </c>
-      <c r="J60" s="173">
+      <c r="J60" s="179">
         <f>SUM(G60:I60)</f>
         <v/>
       </c>
@@ -7113,20 +6300,20 @@
       <c r="F61" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G61" s="174" t="n">
+      <c r="G61" s="180" t="n">
         <v>64.5</v>
       </c>
-      <c r="H61" s="175" t="n">
+      <c r="H61" s="181" t="n">
         <v>55</v>
       </c>
-      <c r="I61" s="172" t="n">
+      <c r="I61" s="178" t="n">
         <v>71</v>
       </c>
-      <c r="J61" s="173">
+      <c r="J61" s="179">
         <f>SUM(G61:I61)</f>
         <v/>
       </c>
-      <c r="K61" s="178">
+      <c r="K61" s="184">
         <f>J61-$L$3</f>
         <v/>
       </c>
@@ -7159,20 +6346,20 @@
       <c r="F62" s="23" t="n">
         <v>45992</v>
       </c>
-      <c r="G62" s="174" t="n">
+      <c r="G62" s="180" t="n">
         <v>43</v>
       </c>
-      <c r="H62" s="175" t="n">
+      <c r="H62" s="181" t="n">
         <v>58</v>
       </c>
-      <c r="I62" s="172" t="n">
+      <c r="I62" s="178" t="n">
         <v>72</v>
       </c>
-      <c r="J62" s="173">
+      <c r="J62" s="179">
         <f>SUM(G62:I62)</f>
         <v/>
       </c>
-      <c r="K62" s="178">
+      <c r="K62" s="184">
         <f>J62-$L$3</f>
         <v/>
       </c>
@@ -7199,16 +6386,16 @@
       <c r="F63" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G63" s="174" t="n">
+      <c r="G63" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="175" t="n">
+      <c r="H63" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="172" t="n">
+      <c r="I63" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="173">
+      <c r="J63" s="179">
         <f>SUM(G63:I63)</f>
         <v/>
       </c>
@@ -7240,16 +6427,16 @@
       <c r="F64" s="23" t="n">
         <v>44879</v>
       </c>
-      <c r="G64" s="174" t="n">
+      <c r="G64" s="180" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="175" t="n">
+      <c r="H64" s="181" t="n">
         <v>8</v>
       </c>
-      <c r="I64" s="172" t="n">
+      <c r="I64" s="178" t="n">
         <v>8</v>
       </c>
-      <c r="J64" s="173">
+      <c r="J64" s="179">
         <f>SUM(G64:I64)</f>
         <v/>
       </c>
@@ -7281,16 +6468,16 @@
       <c r="F65" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G65" s="174" t="n">
+      <c r="G65" s="180" t="n">
         <v>18.5</v>
       </c>
-      <c r="H65" s="175" t="n">
+      <c r="H65" s="181" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="172" t="n">
+      <c r="I65" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="173">
+      <c r="J65" s="179">
         <f>SUM(G65:I65)</f>
         <v/>
       </c>
@@ -7324,16 +6511,16 @@
       <c r="F66" s="24" t="n">
         <v>44652</v>
       </c>
-      <c r="G66" s="174" t="n">
+      <c r="G66" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="175" t="n">
+      <c r="H66" s="181" t="n">
         <v>26</v>
       </c>
-      <c r="I66" s="172" t="n">
+      <c r="I66" s="178" t="n">
         <v>14</v>
       </c>
-      <c r="J66" s="173">
+      <c r="J66" s="179">
         <f>SUM(G66:I66)</f>
         <v/>
       </c>
@@ -7365,20 +6552,20 @@
       <c r="F67" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G67" s="174" t="n">
+      <c r="G67" s="180" t="n">
         <v>48</v>
       </c>
-      <c r="H67" s="175" t="n">
+      <c r="H67" s="181" t="n">
         <v>54.5</v>
       </c>
-      <c r="I67" s="172" t="n">
+      <c r="I67" s="178" t="n">
         <v>58</v>
       </c>
-      <c r="J67" s="173">
+      <c r="J67" s="179">
         <f>SUM(G67:I67)</f>
         <v/>
       </c>
-      <c r="K67" s="178">
+      <c r="K67" s="184">
         <f>J67-$L$3</f>
         <v/>
       </c>
@@ -7400,16 +6587,16 @@
           <t>2026-07-0</t>
         </is>
       </c>
-      <c r="G68" s="170" t="n">
+      <c r="G68" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="175" t="n">
+      <c r="H68" s="181" t="n">
         <v>11</v>
       </c>
-      <c r="I68" s="172" t="n">
+      <c r="I68" s="178" t="n">
         <v>9</v>
       </c>
-      <c r="J68" s="173">
+      <c r="J68" s="179">
         <f>SUM(G68:I68)</f>
         <v/>
       </c>
@@ -7441,16 +6628,16 @@
       <c r="F69" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G69" s="174" t="n">
+      <c r="G69" s="180" t="n">
         <v>44.5</v>
       </c>
-      <c r="H69" s="175" t="n">
+      <c r="H69" s="181" t="n">
         <v>51</v>
       </c>
-      <c r="I69" s="172" t="n">
+      <c r="I69" s="178" t="n">
         <v>59.5</v>
       </c>
-      <c r="J69" s="173">
+      <c r="J69" s="179">
         <f>SUM(G69:I69)</f>
         <v/>
       </c>
@@ -7484,20 +6671,20 @@
       <c r="F70" s="24" t="n">
         <v>45047</v>
       </c>
-      <c r="G70" s="174" t="n">
+      <c r="G70" s="180" t="n">
         <v>87</v>
       </c>
-      <c r="H70" s="175" t="n">
+      <c r="H70" s="181" t="n">
         <v>69</v>
       </c>
-      <c r="I70" s="172" t="n">
+      <c r="I70" s="178" t="n">
         <v>61</v>
       </c>
-      <c r="J70" s="173">
+      <c r="J70" s="179">
         <f>SUM(G70:I70)</f>
         <v/>
       </c>
-      <c r="K70" s="178">
+      <c r="K70" s="184">
         <f>J70-$L$3</f>
         <v/>
       </c>
@@ -7528,16 +6715,16 @@
       <c r="F71" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G71" s="174" t="n">
+      <c r="G71" s="180" t="n">
         <v>10.5</v>
       </c>
-      <c r="H71" s="175" t="n">
+      <c r="H71" s="181" t="n">
         <v>16.5</v>
       </c>
-      <c r="I71" s="172" t="n">
+      <c r="I71" s="178" t="n">
         <v>15.5</v>
       </c>
-      <c r="J71" s="173">
+      <c r="J71" s="179">
         <f>SUM(G71:I71)</f>
         <v/>
       </c>
@@ -7569,16 +6756,16 @@
       <c r="F72" s="21" t="n">
         <v>44200</v>
       </c>
-      <c r="G72" s="170" t="n">
+      <c r="G72" s="176" t="n">
         <v>47</v>
       </c>
-      <c r="H72" s="171" t="n">
+      <c r="H72" s="177" t="n">
         <v>37.5</v>
       </c>
-      <c r="I72" s="172" t="n">
+      <c r="I72" s="178" t="n">
         <v>7</v>
       </c>
-      <c r="J72" s="173">
+      <c r="J72" s="179">
         <f>SUM(G72:I72)</f>
         <v/>
       </c>
@@ -7610,16 +6797,16 @@
       <c r="F73" s="29" t="n">
         <v>44197</v>
       </c>
-      <c r="G73" s="170" t="n">
+      <c r="G73" s="176" t="n">
         <v>18.5</v>
       </c>
-      <c r="H73" s="171" t="n">
+      <c r="H73" s="177" t="n">
         <v>25</v>
       </c>
-      <c r="I73" s="179" t="n">
+      <c r="I73" s="185" t="n">
         <v>25</v>
       </c>
-      <c r="J73" s="173">
+      <c r="J73" s="179">
         <f>SUM(G73:I73)</f>
         <v/>
       </c>
@@ -7640,16 +6827,16 @@
       <c r="F74" s="29" t="n">
         <v>46204</v>
       </c>
-      <c r="G74" s="170" t="n">
+      <c r="G74" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="171" t="n">
+      <c r="H74" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I74" s="172" t="n">
+      <c r="I74" s="178" t="n">
         <v>28</v>
       </c>
-      <c r="J74" s="173">
+      <c r="J74" s="179">
         <f>SUM(G74:I74)</f>
         <v/>
       </c>
@@ -7670,16 +6857,16 @@
       <c r="F75" s="29" t="n">
         <v>46204</v>
       </c>
-      <c r="G75" s="170" t="n">
+      <c r="G75" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="171" t="n">
+      <c r="H75" s="177" t="n">
         <v>47</v>
       </c>
-      <c r="I75" s="172" t="n">
+      <c r="I75" s="178" t="n">
         <v>53</v>
       </c>
-      <c r="J75" s="173">
+      <c r="J75" s="179">
         <f>SUM(G75:I75)</f>
         <v/>
       </c>
@@ -7711,16 +6898,16 @@
       <c r="F76" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G76" s="170" t="n">
+      <c r="G76" s="176" t="n">
         <v>34.5</v>
       </c>
-      <c r="H76" s="171" t="n">
+      <c r="H76" s="177" t="n">
         <v>41.5</v>
       </c>
-      <c r="I76" s="172" t="n">
+      <c r="I76" s="178" t="n">
         <v>47.5</v>
       </c>
-      <c r="J76" s="173">
+      <c r="J76" s="179">
         <f>SUM(G76:I76)</f>
         <v/>
       </c>
@@ -7752,16 +6939,16 @@
       <c r="F77" s="31" t="n">
         <v>44621</v>
       </c>
-      <c r="G77" s="170" t="n">
+      <c r="G77" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="171" t="n">
+      <c r="H77" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I77" s="168" t="n">
+      <c r="I77" s="174" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="173">
+      <c r="J77" s="179">
         <f>SUM(G77:I77)</f>
         <v/>
       </c>
@@ -7793,16 +6980,16 @@
       <c r="F78" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G78" s="170" t="n">
+      <c r="G78" s="176" t="n">
         <v>8.5</v>
       </c>
-      <c r="H78" s="171" t="n">
+      <c r="H78" s="177" t="n">
         <v>8</v>
       </c>
-      <c r="I78" s="172" t="n">
+      <c r="I78" s="178" t="n">
         <v>24</v>
       </c>
-      <c r="J78" s="173">
+      <c r="J78" s="179">
         <f>SUM(G78:I78)</f>
         <v/>
       </c>
@@ -7836,16 +7023,16 @@
       <c r="F79" s="23" t="n">
         <v>45292</v>
       </c>
-      <c r="G79" s="170" t="n">
+      <c r="G79" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="171" t="n">
+      <c r="H79" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="172" t="n">
+      <c r="I79" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="173">
+      <c r="J79" s="179">
         <f>SUM(G79:I79)</f>
         <v/>
       </c>
@@ -7877,16 +7064,16 @@
       <c r="F80" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G80" s="170" t="n">
+      <c r="G80" s="176" t="n">
         <v>9</v>
       </c>
-      <c r="H80" s="171" t="n">
+      <c r="H80" s="177" t="n">
         <v>26</v>
       </c>
-      <c r="I80" s="172" t="n">
+      <c r="I80" s="178" t="n">
         <v>39</v>
       </c>
-      <c r="J80" s="173">
+      <c r="J80" s="179">
         <f>SUM(G80:I80)</f>
         <v/>
       </c>
@@ -7918,16 +7105,16 @@
       <c r="F81" s="23" t="n">
         <v>45450</v>
       </c>
-      <c r="G81" s="170" t="n">
+      <c r="G81" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="171" t="n">
+      <c r="H81" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="172" t="n">
+      <c r="I81" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="173">
+      <c r="J81" s="179">
         <f>SUM(G81:I81)</f>
         <v/>
       </c>
@@ -7959,16 +7146,16 @@
       <c r="F82" s="23" t="n">
         <v>45536</v>
       </c>
-      <c r="G82" s="170" t="n">
+      <c r="G82" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="171" t="n">
+      <c r="H82" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="172" t="n">
+      <c r="I82" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="173">
+      <c r="J82" s="179">
         <f>SUM(G82:I82)</f>
         <v/>
       </c>
@@ -7997,16 +7184,16 @@
       <c r="F83" s="24" t="n">
         <v>46143</v>
       </c>
-      <c r="G83" s="170" t="n">
+      <c r="G83" s="176" t="n">
         <v>42</v>
       </c>
-      <c r="H83" s="171" t="n">
+      <c r="H83" s="177" t="n">
         <v>50</v>
       </c>
-      <c r="I83" s="172" t="n">
+      <c r="I83" s="178" t="n">
         <v>45</v>
       </c>
-      <c r="J83" s="173">
+      <c r="J83" s="179">
         <f>SUM(G83:I83)</f>
         <v/>
       </c>
@@ -8038,16 +7225,16 @@
       <c r="F84" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G84" s="170" t="n">
+      <c r="G84" s="176" t="n">
         <v>3</v>
       </c>
-      <c r="H84" s="171" t="n">
+      <c r="H84" s="177" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="172" t="n">
+      <c r="I84" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="173">
+      <c r="J84" s="179">
         <f>SUM(G84:I84)</f>
         <v/>
       </c>
@@ -8081,16 +7268,16 @@
       <c r="F85" s="24" t="n">
         <v>45108</v>
       </c>
-      <c r="G85" s="170" t="n">
+      <c r="G85" s="176" t="n">
         <v>20</v>
       </c>
-      <c r="H85" s="171" t="n">
+      <c r="H85" s="177" t="n">
         <v>16</v>
       </c>
-      <c r="I85" s="172" t="n">
+      <c r="I85" s="178" t="n">
         <v>25.5</v>
       </c>
-      <c r="J85" s="173">
+      <c r="J85" s="179">
         <f>SUM(G85:I85)</f>
         <v/>
       </c>
@@ -8122,16 +7309,16 @@
       <c r="F86" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G86" s="170" t="n">
+      <c r="G86" s="176" t="n">
         <v>36</v>
       </c>
-      <c r="H86" s="171" t="n">
+      <c r="H86" s="177" t="n">
         <v>39</v>
       </c>
-      <c r="I86" s="172" t="n">
+      <c r="I86" s="178" t="n">
         <v>41</v>
       </c>
-      <c r="J86" s="173">
+      <c r="J86" s="179">
         <f>SUM(G86:I86)</f>
         <v/>
       </c>
@@ -8163,16 +7350,16 @@
       <c r="F87" s="23" t="n">
         <v>45793</v>
       </c>
-      <c r="G87" s="170" t="n">
+      <c r="G87" s="176" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="171" t="n">
+      <c r="H87" s="177" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="172" t="n">
+      <c r="I87" s="178" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="173">
+      <c r="J87" s="179">
         <f>SUM(G87:I87)</f>
         <v/>
       </c>
@@ -8204,20 +7391,20 @@
       <c r="F88" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G88" s="170" t="n">
+      <c r="G88" s="176" t="n">
         <v>70</v>
       </c>
-      <c r="H88" s="171" t="n">
+      <c r="H88" s="177" t="n">
         <v>75</v>
       </c>
-      <c r="I88" s="172" t="n">
+      <c r="I88" s="178" t="n">
         <v>80</v>
       </c>
-      <c r="J88" s="173">
+      <c r="J88" s="179">
         <f>SUM(G88:I88)</f>
         <v/>
       </c>
-      <c r="K88" s="178">
+      <c r="K88" s="184">
         <f>J88-$L$3</f>
         <v/>
       </c>
@@ -8248,16 +7435,16 @@
       <c r="F89" s="23" t="n">
         <v>45261</v>
       </c>
-      <c r="G89" s="170" t="n">
+      <c r="G89" s="176" t="n">
         <v>18</v>
       </c>
-      <c r="H89" s="171" t="n">
+      <c r="H89" s="177" t="n">
         <v>14</v>
       </c>
-      <c r="I89" s="172" t="n">
+      <c r="I89" s="178" t="n">
         <v>21.5</v>
       </c>
-      <c r="J89" s="173">
+      <c r="J89" s="179">
         <f>SUM(G89:I89)</f>
         <v/>
       </c>
@@ -8289,16 +7476,16 @@
       <c r="F90" s="33" t="n">
         <v>45261</v>
       </c>
-      <c r="G90" s="180" t="n">
+      <c r="G90" s="186" t="n">
         <v>21</v>
       </c>
-      <c r="H90" s="181" t="n">
+      <c r="H90" s="187" t="n">
         <v>28</v>
       </c>
-      <c r="I90" s="179" t="n">
+      <c r="I90" s="185" t="n">
         <v>29</v>
       </c>
-      <c r="J90" s="182">
+      <c r="J90" s="188">
         <f>SUM(G90:I90)</f>
         <v/>
       </c>
@@ -8323,10 +7510,10 @@
         <f>SUM(H3:H90)</f>
         <v/>
       </c>
-      <c r="I91" s="183" t="n">
+      <c r="I91" s="189" t="n">
         <v>2578</v>
       </c>
-      <c r="J91" s="184">
+      <c r="J91" s="190">
         <f>SUM(J3:J90)</f>
         <v/>
       </c>
@@ -8369,7 +7556,7 @@
     <col width="12.625" customWidth="1" style="71" min="9" max="9"/>
     <col width="11.375" customWidth="1" style="71" min="10" max="10"/>
     <col width="11.125" customWidth="1" style="70" min="11" max="14"/>
-    <col width="9.25" customWidth="1" style="185" min="15" max="16"/>
+    <col width="9.25" customWidth="1" style="191" min="15" max="16"/>
     <col width="8.75" customWidth="1" style="70" min="17" max="16384"/>
   </cols>
   <sheetData>
@@ -9415,13 +8602,13 @@
         <v>45887</v>
       </c>
       <c r="K19" s="81" t="n"/>
-      <c r="L19" s="186" t="n">
+      <c r="L19" s="192" t="n">
         <v>44</v>
       </c>
-      <c r="M19" s="187" t="n">
+      <c r="M19" s="193" t="n">
         <v>42</v>
       </c>
-      <c r="N19" s="186" t="n">
+      <c r="N19" s="192" t="n">
         <v>51</v>
       </c>
       <c r="O19" s="107">
@@ -9473,13 +8660,13 @@
         <v>45536</v>
       </c>
       <c r="K20" s="81" t="n"/>
-      <c r="L20" s="186" t="n">
+      <c r="L20" s="192" t="n">
         <v>28.5</v>
       </c>
-      <c r="M20" s="187" t="n">
+      <c r="M20" s="193" t="n">
         <v>20.5</v>
       </c>
-      <c r="N20" s="186" t="n">
+      <c r="N20" s="192" t="n">
         <v>41</v>
       </c>
       <c r="O20" s="107">
@@ -9531,13 +8718,13 @@
         <v>45536</v>
       </c>
       <c r="K21" s="81" t="n"/>
-      <c r="L21" s="186" t="n">
+      <c r="L21" s="192" t="n">
         <v>45</v>
       </c>
-      <c r="M21" s="187" t="n">
+      <c r="M21" s="193" t="n">
         <v>63</v>
       </c>
-      <c r="N21" s="186" t="n">
+      <c r="N21" s="192" t="n">
         <v>63</v>
       </c>
       <c r="O21" s="107">
@@ -9592,13 +8779,13 @@
         <v>45536</v>
       </c>
       <c r="K22" s="81" t="n"/>
-      <c r="L22" s="186" t="n">
+      <c r="L22" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M22" s="187" t="n">
+      <c r="M22" s="193" t="n">
         <v>47</v>
       </c>
-      <c r="N22" s="186" t="n">
+      <c r="N22" s="192" t="n">
         <v>63</v>
       </c>
       <c r="O22" s="107">
@@ -9653,13 +8840,13 @@
         <v>45536</v>
       </c>
       <c r="K23" s="81" t="n"/>
-      <c r="L23" s="186" t="n">
+      <c r="L23" s="192" t="n">
         <v>43</v>
       </c>
-      <c r="M23" s="187" t="n">
+      <c r="M23" s="193" t="n">
         <v>58</v>
       </c>
-      <c r="N23" s="186" t="n">
+      <c r="N23" s="192" t="n">
         <v>44</v>
       </c>
       <c r="O23" s="107">
@@ -9704,13 +8891,13 @@
         <v>44571</v>
       </c>
       <c r="K24" s="81" t="n"/>
-      <c r="L24" s="186" t="n">
+      <c r="L24" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="187" t="n">
+      <c r="M24" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="186" t="n">
+      <c r="N24" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="107">
@@ -9762,13 +8949,13 @@
         <v>45536</v>
       </c>
       <c r="K25" s="81" t="n"/>
-      <c r="L25" s="186" t="n">
+      <c r="L25" s="192" t="n">
         <v>32</v>
       </c>
-      <c r="M25" s="187" t="n">
+      <c r="M25" s="193" t="n">
         <v>10.5</v>
       </c>
-      <c r="N25" s="186" t="n">
+      <c r="N25" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="107">
@@ -9820,13 +9007,13 @@
         <v>45536</v>
       </c>
       <c r="K26" s="81" t="n"/>
-      <c r="L26" s="186" t="n">
+      <c r="L26" s="192" t="n">
         <v>65</v>
       </c>
-      <c r="M26" s="187" t="n">
+      <c r="M26" s="193" t="n">
         <v>71.5</v>
       </c>
-      <c r="N26" s="186" t="n">
+      <c r="N26" s="192" t="n">
         <v>54</v>
       </c>
       <c r="O26" s="107">
@@ -9881,13 +9068,13 @@
         <v>45536</v>
       </c>
       <c r="K27" s="81" t="n"/>
-      <c r="L27" s="186" t="n">
+      <c r="L27" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M27" s="187" t="n">
+      <c r="M27" s="193" t="n">
         <v>53</v>
       </c>
-      <c r="N27" s="186" t="n">
+      <c r="N27" s="192" t="n">
         <v>54</v>
       </c>
       <c r="O27" s="107">
@@ -9939,13 +9126,13 @@
         <v>45536</v>
       </c>
       <c r="K28" s="81" t="n"/>
-      <c r="L28" s="186" t="n">
+      <c r="L28" s="192" t="n">
         <v>44</v>
       </c>
-      <c r="M28" s="187" t="n">
+      <c r="M28" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="N28" s="186" t="n">
+      <c r="N28" s="192" t="n">
         <v>41</v>
       </c>
       <c r="O28" s="107">
@@ -9997,13 +9184,13 @@
         <v>45536</v>
       </c>
       <c r="K29" s="81" t="n"/>
-      <c r="L29" s="186" t="n">
+      <c r="L29" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M29" s="187" t="n">
+      <c r="M29" s="193" t="n">
         <v>39</v>
       </c>
-      <c r="N29" s="186" t="n">
+      <c r="N29" s="192" t="n">
         <v>38</v>
       </c>
       <c r="O29" s="107">
@@ -10055,13 +9242,13 @@
         <v>45536</v>
       </c>
       <c r="K30" s="81" t="n"/>
-      <c r="L30" s="186" t="n">
+      <c r="L30" s="192" t="n">
         <v>44</v>
       </c>
-      <c r="M30" s="187" t="n">
+      <c r="M30" s="193" t="n">
         <v>44</v>
       </c>
-      <c r="N30" s="186" t="n">
+      <c r="N30" s="192" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="107">
@@ -10113,13 +9300,13 @@
         <v>45536</v>
       </c>
       <c r="K31" s="81" t="n"/>
-      <c r="L31" s="186" t="n">
+      <c r="L31" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M31" s="187" t="n">
+      <c r="M31" s="193" t="n">
         <v>38</v>
       </c>
-      <c r="N31" s="186" t="n">
+      <c r="N31" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O31" s="107">
@@ -10171,13 +9358,13 @@
         <v>45900</v>
       </c>
       <c r="K32" s="81" t="n"/>
-      <c r="L32" s="186" t="n">
+      <c r="L32" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M32" s="187" t="n">
+      <c r="M32" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N32" s="186" t="n">
+      <c r="N32" s="192" t="n">
         <v>36</v>
       </c>
       <c r="O32" s="107">
@@ -10229,13 +9416,13 @@
         <v>46030</v>
       </c>
       <c r="K33" s="81" t="n"/>
-      <c r="L33" s="186" t="n">
+      <c r="L33" s="192" t="n">
         <v>70</v>
       </c>
-      <c r="M33" s="187" t="n">
+      <c r="M33" s="193" t="n">
         <v>72</v>
       </c>
-      <c r="N33" s="186" t="n">
+      <c r="N33" s="192" t="n">
         <v>58</v>
       </c>
       <c r="O33" s="107">
@@ -10290,13 +9477,13 @@
         <v>46032</v>
       </c>
       <c r="K34" s="81" t="n"/>
-      <c r="L34" s="186" t="n">
+      <c r="L34" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="187" t="n">
+      <c r="M34" s="193" t="n">
         <v>25</v>
       </c>
-      <c r="N34" s="186" t="n">
+      <c r="N34" s="192" t="n">
         <v>28</v>
       </c>
       <c r="O34" s="107">
@@ -10348,13 +9535,13 @@
         <v>45536</v>
       </c>
       <c r="K35" s="81" t="n"/>
-      <c r="L35" s="186" t="n">
+      <c r="L35" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M35" s="187" t="n">
+      <c r="M35" s="193" t="n">
         <v>31</v>
       </c>
-      <c r="N35" s="186" t="n">
+      <c r="N35" s="192" t="n">
         <v>40</v>
       </c>
       <c r="O35" s="107">
@@ -10406,13 +9593,13 @@
         <v>45536</v>
       </c>
       <c r="K36" s="81" t="n"/>
-      <c r="L36" s="186" t="n">
+      <c r="L36" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M36" s="187" t="n">
+      <c r="M36" s="193" t="n">
         <v>63</v>
       </c>
-      <c r="N36" s="186" t="n">
+      <c r="N36" s="192" t="n">
         <v>57</v>
       </c>
       <c r="O36" s="107">
@@ -10464,13 +9651,13 @@
         <v>45536</v>
       </c>
       <c r="K37" s="81" t="n"/>
-      <c r="L37" s="186" t="n">
+      <c r="L37" s="192" t="n">
         <v>55</v>
       </c>
-      <c r="M37" s="187" t="n">
+      <c r="M37" s="193" t="n">
         <v>33</v>
       </c>
-      <c r="N37" s="186" t="n">
+      <c r="N37" s="192" t="n">
         <v>36</v>
       </c>
       <c r="O37" s="107">
@@ -10522,13 +9709,13 @@
         <v>45536</v>
       </c>
       <c r="K38" s="81" t="n"/>
-      <c r="L38" s="186" t="n">
+      <c r="L38" s="192" t="n">
         <v>30</v>
       </c>
-      <c r="M38" s="187" t="n">
+      <c r="M38" s="193" t="n">
         <v>17</v>
       </c>
-      <c r="N38" s="186" t="n">
+      <c r="N38" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O38" s="107">
@@ -10580,13 +9767,13 @@
         <v>45536</v>
       </c>
       <c r="K39" s="81" t="n"/>
-      <c r="L39" s="186" t="n">
+      <c r="L39" s="192" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="187" t="n">
+      <c r="M39" s="193" t="n">
         <v>32</v>
       </c>
-      <c r="N39" s="186" t="n">
+      <c r="N39" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O39" s="107">
@@ -10638,13 +9825,13 @@
         <v>45536</v>
       </c>
       <c r="K40" s="81" t="n"/>
-      <c r="L40" s="186" t="n">
+      <c r="L40" s="192" t="n">
         <v>25</v>
       </c>
-      <c r="M40" s="187" t="n">
+      <c r="M40" s="193" t="n">
         <v>22</v>
       </c>
-      <c r="N40" s="186" t="n">
+      <c r="N40" s="192" t="n">
         <v>22</v>
       </c>
       <c r="O40" s="107">
@@ -10696,13 +9883,13 @@
         <v>44197</v>
       </c>
       <c r="K41" s="81" t="n"/>
-      <c r="L41" s="186" t="n">
+      <c r="L41" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="187" t="n">
+      <c r="M41" s="193" t="n">
         <v>38</v>
       </c>
-      <c r="N41" s="186" t="n">
+      <c r="N41" s="192" t="n">
         <v>9</v>
       </c>
       <c r="O41" s="107">
@@ -10754,13 +9941,13 @@
         <v>45536</v>
       </c>
       <c r="K42" s="81" t="n"/>
-      <c r="L42" s="186" t="n">
+      <c r="L42" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M42" s="187" t="n">
+      <c r="M42" s="193" t="n">
         <v>47</v>
       </c>
-      <c r="N42" s="186" t="n">
+      <c r="N42" s="192" t="n">
         <v>33</v>
       </c>
       <c r="O42" s="107">
@@ -10812,13 +9999,13 @@
         <v>45536</v>
       </c>
       <c r="K43" s="81" t="n"/>
-      <c r="L43" s="186" t="n">
+      <c r="L43" s="192" t="n">
         <v>18</v>
       </c>
-      <c r="M43" s="187" t="n">
+      <c r="M43" s="193" t="n">
         <v>61</v>
       </c>
-      <c r="N43" s="186" t="n">
+      <c r="N43" s="192" t="n">
         <v>29</v>
       </c>
       <c r="O43" s="107">
@@ -10870,13 +10057,13 @@
         <v>45536</v>
       </c>
       <c r="K44" s="81" t="n"/>
-      <c r="L44" s="186" t="n">
+      <c r="L44" s="192" t="n">
         <v>46</v>
       </c>
-      <c r="M44" s="187" t="n">
+      <c r="M44" s="193" t="n">
         <v>69</v>
       </c>
-      <c r="N44" s="186" t="n">
+      <c r="N44" s="192" t="n">
         <v>63</v>
       </c>
       <c r="O44" s="107">
@@ -10931,13 +10118,13 @@
         <v>45536</v>
       </c>
       <c r="K45" s="81" t="n"/>
-      <c r="L45" s="186" t="n">
+      <c r="L45" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M45" s="187" t="n">
+      <c r="M45" s="193" t="n">
         <v>58</v>
       </c>
-      <c r="N45" s="186" t="n">
+      <c r="N45" s="192" t="n">
         <v>58.5</v>
       </c>
       <c r="O45" s="107">
@@ -10992,13 +10179,13 @@
         <v>45536</v>
       </c>
       <c r="K46" s="81" t="n"/>
-      <c r="L46" s="186" t="n">
+      <c r="L46" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M46" s="187" t="n">
+      <c r="M46" s="193" t="n">
         <v>58</v>
       </c>
-      <c r="N46" s="186" t="n">
+      <c r="N46" s="192" t="n">
         <v>75</v>
       </c>
       <c r="O46" s="107">
@@ -11053,13 +10240,13 @@
         <v>45536</v>
       </c>
       <c r="K47" s="81" t="n"/>
-      <c r="L47" s="186" t="n">
+      <c r="L47" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M47" s="187" t="n">
+      <c r="M47" s="193" t="n">
         <v>37</v>
       </c>
-      <c r="N47" s="186" t="n">
+      <c r="N47" s="192" t="n">
         <v>41</v>
       </c>
       <c r="O47" s="107">
@@ -11111,13 +10298,13 @@
         <v>45536</v>
       </c>
       <c r="K48" s="81" t="n"/>
-      <c r="L48" s="186" t="n">
+      <c r="L48" s="192" t="n">
         <v>42</v>
       </c>
-      <c r="M48" s="187" t="n">
+      <c r="M48" s="193" t="n">
         <v>66</v>
       </c>
-      <c r="N48" s="186" t="n">
+      <c r="N48" s="192" t="n">
         <v>61</v>
       </c>
       <c r="O48" s="107">
@@ -11172,13 +10359,13 @@
         <v>45809</v>
       </c>
       <c r="K49" s="81" t="n"/>
-      <c r="L49" s="186" t="n">
+      <c r="L49" s="192" t="n">
         <v>21</v>
       </c>
-      <c r="M49" s="187" t="n">
+      <c r="M49" s="193" t="n">
         <v>32</v>
       </c>
-      <c r="N49" s="186" t="n">
+      <c r="N49" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O49" s="107">
@@ -11230,13 +10417,13 @@
         <v>45536</v>
       </c>
       <c r="K50" s="81" t="n"/>
-      <c r="L50" s="186" t="n">
+      <c r="L50" s="192" t="n">
         <v>51</v>
       </c>
-      <c r="M50" s="187" t="n">
+      <c r="M50" s="193" t="n">
         <v>47</v>
       </c>
-      <c r="N50" s="186" t="n">
+      <c r="N50" s="192" t="n">
         <v>42</v>
       </c>
       <c r="O50" s="107">
@@ -11288,13 +10475,13 @@
         <v>45536</v>
       </c>
       <c r="K51" s="81" t="n"/>
-      <c r="L51" s="186" t="n">
+      <c r="L51" s="192" t="n">
         <v>87</v>
       </c>
-      <c r="M51" s="187" t="n">
+      <c r="M51" s="193" t="n">
         <v>85</v>
       </c>
-      <c r="N51" s="186" t="n">
+      <c r="N51" s="192" t="n">
         <v>92.5</v>
       </c>
       <c r="O51" s="107">
@@ -11349,13 +10536,13 @@
         <v>45536</v>
       </c>
       <c r="K52" s="81" t="n"/>
-      <c r="L52" s="186" t="n">
+      <c r="L52" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M52" s="187" t="n">
+      <c r="M52" s="193" t="n">
         <v>23</v>
       </c>
-      <c r="N52" s="186" t="n">
+      <c r="N52" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="107">
@@ -11407,13 +10594,13 @@
         <v>45536</v>
       </c>
       <c r="K53" s="81" t="n"/>
-      <c r="L53" s="186" t="n">
+      <c r="L53" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M53" s="187" t="n">
+      <c r="M53" s="193" t="n">
         <v>17</v>
       </c>
-      <c r="N53" s="186" t="n">
+      <c r="N53" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O53" s="107">
@@ -11465,13 +10652,13 @@
         <v>45536</v>
       </c>
       <c r="K54" s="81" t="n"/>
-      <c r="L54" s="186" t="n">
+      <c r="L54" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M54" s="187" t="n">
+      <c r="M54" s="193" t="n">
         <v>6</v>
       </c>
-      <c r="N54" s="186" t="n">
+      <c r="N54" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="107">
@@ -11523,13 +10710,13 @@
         <v>45536</v>
       </c>
       <c r="K55" s="81" t="n"/>
-      <c r="L55" s="186" t="n">
+      <c r="L55" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M55" s="187" t="n">
+      <c r="M55" s="193" t="n">
         <v>29</v>
       </c>
-      <c r="N55" s="186" t="n">
+      <c r="N55" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O55" s="107">
@@ -11562,13 +10749,13 @@
         <v>46143</v>
       </c>
       <c r="K56" s="81" t="n"/>
-      <c r="L56" s="186" t="n">
+      <c r="L56" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M56" s="187" t="n">
+      <c r="M56" s="193" t="n">
         <v>46</v>
       </c>
-      <c r="N56" s="186" t="n">
+      <c r="N56" s="192" t="n">
         <v>32</v>
       </c>
       <c r="O56" s="107">
@@ -11620,13 +10807,13 @@
         <v>45536</v>
       </c>
       <c r="K57" s="81" t="n"/>
-      <c r="L57" s="186" t="n">
+      <c r="L57" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M57" s="187" t="n">
+      <c r="M57" s="193" t="n">
         <v>50</v>
       </c>
-      <c r="N57" s="186" t="n">
+      <c r="N57" s="192" t="n">
         <v>49</v>
       </c>
       <c r="O57" s="107">
@@ -11678,13 +10865,13 @@
         <v>45775</v>
       </c>
       <c r="K58" s="81" t="n"/>
-      <c r="L58" s="186" t="n">
+      <c r="L58" s="192" t="n">
         <v>23.5</v>
       </c>
-      <c r="M58" s="187" t="n">
+      <c r="M58" s="193" t="n">
         <v>5</v>
       </c>
-      <c r="N58" s="186" t="n">
+      <c r="N58" s="192" t="n">
         <v>9</v>
       </c>
       <c r="O58" s="107">
@@ -11736,13 +10923,13 @@
         <v>45536</v>
       </c>
       <c r="K59" s="81" t="n"/>
-      <c r="L59" s="186" t="n">
+      <c r="L59" s="192" t="n">
         <v>30</v>
       </c>
-      <c r="M59" s="187" t="n">
+      <c r="M59" s="193" t="n">
         <v>6</v>
       </c>
-      <c r="N59" s="186" t="n">
+      <c r="N59" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O59" s="107">
@@ -11794,13 +10981,13 @@
         <v>45536</v>
       </c>
       <c r="K60" s="81" t="n"/>
-      <c r="L60" s="186" t="n">
+      <c r="L60" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M60" s="187" t="n">
+      <c r="M60" s="193" t="n">
         <v>31</v>
       </c>
-      <c r="N60" s="186" t="n">
+      <c r="N60" s="192" t="n">
         <v>32</v>
       </c>
       <c r="O60" s="107">
@@ -11852,13 +11039,13 @@
         <v>45536</v>
       </c>
       <c r="K61" s="81" t="n"/>
-      <c r="L61" s="186" t="n">
+      <c r="L61" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M61" s="187" t="n">
+      <c r="M61" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N61" s="186" t="n">
+      <c r="N61" s="192" t="n">
         <v>27</v>
       </c>
       <c r="O61" s="107">
@@ -11910,13 +11097,13 @@
         <v>45536</v>
       </c>
       <c r="K62" s="81" t="n"/>
-      <c r="L62" s="186" t="n">
+      <c r="L62" s="192" t="n">
         <v>29</v>
       </c>
-      <c r="M62" s="187" t="n">
+      <c r="M62" s="193" t="n">
         <v>16.5</v>
       </c>
-      <c r="N62" s="186" t="n">
+      <c r="N62" s="192" t="n">
         <v>12</v>
       </c>
       <c r="O62" s="107">
@@ -11968,13 +11155,13 @@
         <v>45536</v>
       </c>
       <c r="K63" s="81" t="n"/>
-      <c r="L63" s="186" t="n">
+      <c r="L63" s="192" t="n">
         <v>26</v>
       </c>
-      <c r="M63" s="187" t="n">
+      <c r="M63" s="193" t="n">
         <v>20</v>
       </c>
-      <c r="N63" s="186" t="n">
+      <c r="N63" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O63" s="107">
@@ -12026,13 +11213,13 @@
         <v>45536</v>
       </c>
       <c r="K64" s="81" t="n"/>
-      <c r="L64" s="186" t="n">
+      <c r="L64" s="192" t="n">
         <v>18</v>
       </c>
-      <c r="M64" s="187" t="n">
+      <c r="M64" s="193" t="n">
         <v>16</v>
       </c>
-      <c r="N64" s="186" t="n">
+      <c r="N64" s="192" t="n">
         <v>16</v>
       </c>
       <c r="O64" s="107">
@@ -12084,13 +11271,13 @@
         <v>45536</v>
       </c>
       <c r="K65" s="81" t="n"/>
-      <c r="L65" s="186" t="n">
+      <c r="L65" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M65" s="187" t="n">
+      <c r="M65" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N65" s="186" t="n">
+      <c r="N65" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O65" s="107">
@@ -12142,13 +11329,13 @@
         <v>45839</v>
       </c>
       <c r="K66" s="81" t="n"/>
-      <c r="L66" s="186" t="n">
+      <c r="L66" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M66" s="187" t="n">
+      <c r="M66" s="193" t="n">
         <v>32</v>
       </c>
-      <c r="N66" s="186" t="n">
+      <c r="N66" s="192" t="n">
         <v>32</v>
       </c>
       <c r="O66" s="107">
@@ -12200,13 +11387,13 @@
         <v>45536</v>
       </c>
       <c r="K67" s="81" t="n"/>
-      <c r="L67" s="186" t="n">
+      <c r="L67" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M67" s="187" t="n">
+      <c r="M67" s="193" t="n">
         <v>26</v>
       </c>
-      <c r="N67" s="186" t="n">
+      <c r="N67" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O67" s="107">
@@ -12235,13 +11422,13 @@
         <v>46226</v>
       </c>
       <c r="K68" s="81" t="n"/>
-      <c r="L68" s="186" t="n">
+      <c r="L68" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M68" s="187" t="n">
+      <c r="M68" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="186" t="n">
+      <c r="N68" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O68" s="107">
@@ -12293,13 +11480,13 @@
         <v>45536</v>
       </c>
       <c r="K69" s="81" t="n"/>
-      <c r="L69" s="186" t="n">
+      <c r="L69" s="192" t="n">
         <v>10</v>
       </c>
-      <c r="M69" s="187" t="n">
+      <c r="M69" s="193" t="n">
         <v>8</v>
       </c>
-      <c r="N69" s="186" t="n">
+      <c r="N69" s="192" t="n">
         <v>10</v>
       </c>
       <c r="O69" s="107">
@@ -12351,13 +11538,13 @@
         <v>45536</v>
       </c>
       <c r="K70" s="81" t="n"/>
-      <c r="L70" s="186" t="n">
+      <c r="L70" s="192" t="n">
         <v>45</v>
       </c>
-      <c r="M70" s="187" t="n">
+      <c r="M70" s="193" t="n">
         <v>49</v>
       </c>
-      <c r="N70" s="186" t="n">
+      <c r="N70" s="192" t="n">
         <v>33</v>
       </c>
       <c r="O70" s="107">
@@ -12409,13 +11596,13 @@
         <v>45536</v>
       </c>
       <c r="K71" s="81" t="n"/>
-      <c r="L71" s="186" t="n">
+      <c r="L71" s="192" t="n">
         <v>30</v>
       </c>
-      <c r="M71" s="187" t="n">
+      <c r="M71" s="193" t="n">
         <v>38</v>
       </c>
-      <c r="N71" s="186" t="n">
+      <c r="N71" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O71" s="107">
@@ -12467,13 +11654,13 @@
         <v>45536</v>
       </c>
       <c r="K72" s="81" t="n"/>
-      <c r="L72" s="186" t="n">
+      <c r="L72" s="192" t="n">
         <v>47</v>
       </c>
-      <c r="M72" s="187" t="n">
+      <c r="M72" s="193" t="n">
         <v>50</v>
       </c>
-      <c r="N72" s="186" t="n">
+      <c r="N72" s="192" t="n">
         <v>63</v>
       </c>
       <c r="O72" s="107">
@@ -12505,13 +11692,13 @@
         <v>46204</v>
       </c>
       <c r="K73" s="81" t="n"/>
-      <c r="L73" s="186" t="n">
+      <c r="L73" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="187" t="n">
+      <c r="M73" s="193" t="n">
         <v>18</v>
       </c>
-      <c r="N73" s="186" t="n">
+      <c r="N73" s="192" t="n">
         <v>27</v>
       </c>
       <c r="O73" s="107">
@@ -12563,13 +11750,13 @@
         <v>45536</v>
       </c>
       <c r="K74" s="81" t="n"/>
-      <c r="L74" s="186" t="n">
+      <c r="L74" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M74" s="187" t="n">
+      <c r="M74" s="193" t="n">
         <v>41</v>
       </c>
-      <c r="N74" s="186" t="n">
+      <c r="N74" s="192" t="n">
         <v>45</v>
       </c>
       <c r="O74" s="107">
@@ -12614,13 +11801,13 @@
         <v>44652</v>
       </c>
       <c r="K75" s="81" t="n"/>
-      <c r="L75" s="186" t="n">
+      <c r="L75" s="192" t="n">
         <v>32</v>
       </c>
-      <c r="M75" s="187" t="n">
+      <c r="M75" s="193" t="n">
         <v>54</v>
       </c>
-      <c r="N75" s="186" t="n">
+      <c r="N75" s="192" t="n">
         <v>21</v>
       </c>
       <c r="O75" s="107">
@@ -12653,13 +11840,13 @@
         <v>46143</v>
       </c>
       <c r="K76" s="81" t="n"/>
-      <c r="L76" s="186" t="n">
+      <c r="L76" s="192" t="n">
         <v>34</v>
       </c>
-      <c r="M76" s="187" t="n">
+      <c r="M76" s="193" t="n">
         <v>39</v>
       </c>
-      <c r="N76" s="186" t="n">
+      <c r="N76" s="192" t="n">
         <v>39</v>
       </c>
       <c r="O76" s="107">
@@ -12711,13 +11898,13 @@
         <v>46206</v>
       </c>
       <c r="K77" s="81" t="n"/>
-      <c r="L77" s="186" t="n">
+      <c r="L77" s="192" t="n">
         <v>63</v>
       </c>
-      <c r="M77" s="187" t="n">
+      <c r="M77" s="193" t="n">
         <v>3</v>
       </c>
-      <c r="N77" s="186" t="n">
+      <c r="N77" s="192" t="n">
         <v>42</v>
       </c>
       <c r="O77" s="107">
@@ -12769,13 +11956,13 @@
         <v>45536</v>
       </c>
       <c r="K78" s="81" t="n"/>
-      <c r="L78" s="186" t="n">
+      <c r="L78" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M78" s="187" t="n">
+      <c r="M78" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N78" s="186" t="n">
+      <c r="N78" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="107">
@@ -12827,13 +12014,13 @@
         <v>45536</v>
       </c>
       <c r="K79" s="81" t="n"/>
-      <c r="L79" s="186" t="n">
+      <c r="L79" s="192" t="n">
         <v>34</v>
       </c>
-      <c r="M79" s="187" t="n">
+      <c r="M79" s="193" t="n">
         <v>42</v>
       </c>
-      <c r="N79" s="186" t="n">
+      <c r="N79" s="192" t="n">
         <v>34</v>
       </c>
       <c r="O79" s="107">
@@ -12885,13 +12072,13 @@
         <v>45809</v>
       </c>
       <c r="K80" s="81" t="n"/>
-      <c r="L80" s="186" t="n">
+      <c r="L80" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M80" s="187" t="n">
+      <c r="M80" s="193" t="n">
         <v>38</v>
       </c>
-      <c r="N80" s="186" t="n">
+      <c r="N80" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O80" s="107">
@@ -12943,13 +12130,13 @@
         <v>45536</v>
       </c>
       <c r="K81" s="81" t="n"/>
-      <c r="L81" s="186" t="n">
+      <c r="L81" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="187" t="n">
+      <c r="M81" s="193" t="n">
         <v>8</v>
       </c>
-      <c r="N81" s="186" t="n">
+      <c r="N81" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="107">
@@ -13001,13 +12188,13 @@
         <v>45536</v>
       </c>
       <c r="K82" s="81" t="n"/>
-      <c r="L82" s="186" t="n">
+      <c r="L82" s="192" t="n">
         <v>31</v>
       </c>
-      <c r="M82" s="187" t="n">
+      <c r="M82" s="193" t="n">
         <v>57</v>
       </c>
-      <c r="N82" s="186" t="n">
+      <c r="N82" s="192" t="n">
         <v>28</v>
       </c>
       <c r="O82" s="107">
@@ -13059,13 +12246,13 @@
         <v>45536</v>
       </c>
       <c r="K83" s="81" t="n"/>
-      <c r="L83" s="186" t="n">
+      <c r="L83" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M83" s="187" t="n">
+      <c r="M83" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="N83" s="186" t="n">
+      <c r="N83" s="192" t="n">
         <v>28</v>
       </c>
       <c r="O83" s="107">
@@ -13117,13 +12304,13 @@
         <v>45536</v>
       </c>
       <c r="K84" s="81" t="n"/>
-      <c r="L84" s="186" t="n">
+      <c r="L84" s="192" t="n">
         <v>40</v>
       </c>
-      <c r="M84" s="187" t="n">
+      <c r="M84" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="N84" s="186" t="n">
+      <c r="N84" s="192" t="n">
         <v>20</v>
       </c>
       <c r="O84" s="107">
@@ -13175,13 +12362,13 @@
         <v>45536</v>
       </c>
       <c r="K85" s="81" t="n"/>
-      <c r="L85" s="186" t="n">
+      <c r="L85" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M85" s="187" t="n">
+      <c r="M85" s="193" t="n">
         <v>41</v>
       </c>
-      <c r="N85" s="186" t="n">
+      <c r="N85" s="192" t="n">
         <v>26</v>
       </c>
       <c r="O85" s="107">
@@ -13233,13 +12420,13 @@
         <v>45536</v>
       </c>
       <c r="K86" s="81" t="n"/>
-      <c r="L86" s="186" t="n">
+      <c r="L86" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M86" s="187" t="n">
+      <c r="M86" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="N86" s="186" t="n">
+      <c r="N86" s="192" t="n">
         <v>20</v>
       </c>
       <c r="O86" s="107">
@@ -13291,13 +12478,13 @@
         <v>45536</v>
       </c>
       <c r="K87" s="81" t="n"/>
-      <c r="L87" s="186" t="n">
+      <c r="L87" s="192" t="n">
         <v>42</v>
       </c>
-      <c r="M87" s="187" t="n">
+      <c r="M87" s="193" t="n">
         <v>30</v>
       </c>
-      <c r="N87" s="186" t="n">
+      <c r="N87" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O87" s="107">
@@ -13349,13 +12536,13 @@
         <v>45536</v>
       </c>
       <c r="K88" s="81" t="n"/>
-      <c r="L88" s="186" t="n">
+      <c r="L88" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M88" s="187" t="n">
+      <c r="M88" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N88" s="186" t="n">
+      <c r="N88" s="192" t="n">
         <v>9</v>
       </c>
       <c r="O88" s="107">
@@ -13407,13 +12594,13 @@
         <v>45536</v>
       </c>
       <c r="K89" s="81" t="n"/>
-      <c r="L89" s="186" t="n">
+      <c r="L89" s="192" t="n">
         <v>21</v>
       </c>
-      <c r="M89" s="187" t="n">
+      <c r="M89" s="193" t="n">
         <v>34</v>
       </c>
-      <c r="N89" s="186" t="n">
+      <c r="N89" s="192" t="n">
         <v>18</v>
       </c>
       <c r="O89" s="107">
@@ -13465,13 +12652,13 @@
         <v>45139</v>
       </c>
       <c r="K90" s="81" t="n"/>
-      <c r="L90" s="186" t="n">
+      <c r="L90" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M90" s="187" t="n">
+      <c r="M90" s="193" t="n">
         <v>50</v>
       </c>
-      <c r="N90" s="186" t="n">
+      <c r="N90" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O90" s="107">
@@ -13523,13 +12710,13 @@
         <v>45536</v>
       </c>
       <c r="K91" s="81" t="n"/>
-      <c r="L91" s="186" t="n">
+      <c r="L91" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M91" s="187" t="n">
+      <c r="M91" s="193" t="n">
         <v>40</v>
       </c>
-      <c r="N91" s="186" t="n">
+      <c r="N91" s="192" t="n">
         <v>29</v>
       </c>
       <c r="O91" s="107">
@@ -13562,13 +12749,13 @@
         <v>46168</v>
       </c>
       <c r="K92" s="81" t="n"/>
-      <c r="L92" s="186" t="n">
+      <c r="L92" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M92" s="187" t="n">
+      <c r="M92" s="193" t="n">
         <v>33</v>
       </c>
-      <c r="N92" s="186" t="n">
+      <c r="N92" s="192" t="n">
         <v>30</v>
       </c>
       <c r="O92" s="107">
@@ -13601,13 +12788,13 @@
         <v>46143</v>
       </c>
       <c r="K93" s="81" t="n"/>
-      <c r="L93" s="186" t="n">
+      <c r="L93" s="192" t="n">
         <v>10</v>
       </c>
-      <c r="M93" s="187" t="n">
+      <c r="M93" s="193" t="n">
         <v>24</v>
       </c>
-      <c r="N93" s="186" t="n">
+      <c r="N93" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O93" s="107">
@@ -13659,13 +12846,13 @@
         <v>45536</v>
       </c>
       <c r="K94" s="81" t="n"/>
-      <c r="L94" s="186" t="n">
+      <c r="L94" s="192" t="n">
         <v>38</v>
       </c>
-      <c r="M94" s="187" t="n">
+      <c r="M94" s="193" t="n">
         <v>38</v>
       </c>
-      <c r="N94" s="186" t="n">
+      <c r="N94" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O94" s="107">
@@ -13717,13 +12904,13 @@
         <v>45778</v>
       </c>
       <c r="K95" s="81" t="n"/>
-      <c r="L95" s="186" t="n">
+      <c r="L95" s="192" t="n">
         <v>15</v>
       </c>
-      <c r="M95" s="187" t="n">
+      <c r="M95" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N95" s="186" t="n">
+      <c r="N95" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O95" s="107">
@@ -13775,13 +12962,13 @@
         <v>45536</v>
       </c>
       <c r="K96" s="81" t="n"/>
-      <c r="L96" s="186" t="n">
+      <c r="L96" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M96" s="187" t="n">
+      <c r="M96" s="193" t="n">
         <v>60</v>
       </c>
-      <c r="N96" s="186" t="n">
+      <c r="N96" s="192" t="n">
         <v>50</v>
       </c>
       <c r="O96" s="107">
@@ -13833,13 +13020,13 @@
         <v>45536</v>
       </c>
       <c r="K97" s="81" t="n"/>
-      <c r="L97" s="186" t="n">
+      <c r="L97" s="192" t="n">
         <v>24</v>
       </c>
-      <c r="M97" s="187" t="n">
+      <c r="M97" s="193" t="n">
         <v>6</v>
       </c>
-      <c r="N97" s="186" t="n">
+      <c r="N97" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O97" s="107">
@@ -13891,13 +13078,13 @@
         <v>45536</v>
       </c>
       <c r="K98" s="81" t="n"/>
-      <c r="L98" s="186" t="n">
+      <c r="L98" s="192" t="n">
         <v>12</v>
       </c>
-      <c r="M98" s="187" t="n">
+      <c r="M98" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="186" t="n">
+      <c r="N98" s="192" t="n">
         <v>9</v>
       </c>
       <c r="O98" s="107">
@@ -13949,13 +13136,13 @@
         <v>45536</v>
       </c>
       <c r="K99" s="81" t="n"/>
-      <c r="L99" s="186" t="n">
+      <c r="L99" s="192" t="n">
         <v>15</v>
       </c>
-      <c r="M99" s="187" t="n">
+      <c r="M99" s="193" t="n">
         <v>28</v>
       </c>
-      <c r="N99" s="186" t="n">
+      <c r="N99" s="192" t="n">
         <v>13</v>
       </c>
       <c r="O99" s="107">
@@ -14007,13 +13194,13 @@
         <v>45536</v>
       </c>
       <c r="K100" s="81" t="n"/>
-      <c r="L100" s="186" t="n">
+      <c r="L100" s="192" t="n">
         <v>32</v>
       </c>
-      <c r="M100" s="187" t="n">
+      <c r="M100" s="193" t="n">
         <v>28</v>
       </c>
-      <c r="N100" s="186" t="n">
+      <c r="N100" s="192" t="n">
         <v>12</v>
       </c>
       <c r="O100" s="107">
@@ -14046,13 +13233,13 @@
         <v>46143</v>
       </c>
       <c r="K101" s="81" t="n"/>
-      <c r="L101" s="186" t="n">
+      <c r="L101" s="192" t="n">
         <v>9</v>
       </c>
-      <c r="M101" s="187" t="n">
+      <c r="M101" s="193" t="n">
         <v>23</v>
       </c>
-      <c r="N101" s="186" t="n">
+      <c r="N101" s="192" t="n">
         <v>22</v>
       </c>
       <c r="O101" s="107">
@@ -14104,13 +13291,13 @@
         <v>45536</v>
       </c>
       <c r="K102" s="81" t="n"/>
-      <c r="L102" s="186" t="n">
+      <c r="L102" s="192" t="n">
         <v>50</v>
       </c>
-      <c r="M102" s="187" t="n">
+      <c r="M102" s="193" t="n">
         <v>63</v>
       </c>
-      <c r="N102" s="186" t="n">
+      <c r="N102" s="192" t="n">
         <v>29</v>
       </c>
       <c r="O102" s="107">
@@ -14162,13 +13349,13 @@
         <v>45536</v>
       </c>
       <c r="K103" s="81" t="n"/>
-      <c r="L103" s="186" t="n">
+      <c r="L103" s="192" t="n">
         <v>24</v>
       </c>
-      <c r="M103" s="187" t="n">
+      <c r="M103" s="193" t="n">
         <v>35.5</v>
       </c>
-      <c r="N103" s="186" t="n">
+      <c r="N103" s="192" t="n">
         <v>23</v>
       </c>
       <c r="O103" s="107">
@@ -14220,13 +13407,13 @@
         <v>45536</v>
       </c>
       <c r="K104" s="81" t="n"/>
-      <c r="L104" s="186" t="n">
+      <c r="L104" s="192" t="n">
         <v>10</v>
       </c>
-      <c r="M104" s="187" t="n">
+      <c r="M104" s="193" t="n">
         <v>24</v>
       </c>
-      <c r="N104" s="186" t="n">
+      <c r="N104" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O104" s="107">
@@ -14278,13 +13465,13 @@
         <v>45536</v>
       </c>
       <c r="K105" s="81" t="n"/>
-      <c r="L105" s="186" t="n">
+      <c r="L105" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M105" s="187" t="n">
+      <c r="M105" s="193" t="n">
         <v>49</v>
       </c>
-      <c r="N105" s="186" t="n">
+      <c r="N105" s="192" t="n">
         <v>44</v>
       </c>
       <c r="O105" s="107">
@@ -14336,13 +13523,13 @@
         <v>45536</v>
       </c>
       <c r="K106" s="81" t="n"/>
-      <c r="L106" s="186" t="n">
+      <c r="L106" s="192" t="n">
         <v>18</v>
       </c>
-      <c r="M106" s="187" t="n">
+      <c r="M106" s="193" t="n">
         <v>16</v>
       </c>
-      <c r="N106" s="186" t="n">
+      <c r="N106" s="192" t="n">
         <v>16</v>
       </c>
       <c r="O106" s="107">
@@ -14394,13 +13581,13 @@
         <v>45536</v>
       </c>
       <c r="K107" s="81" t="n"/>
-      <c r="L107" s="186" t="n">
+      <c r="L107" s="192" t="n">
         <v>47</v>
       </c>
-      <c r="M107" s="187" t="n">
+      <c r="M107" s="193" t="n">
         <v>64</v>
       </c>
-      <c r="N107" s="186" t="n">
+      <c r="N107" s="192" t="n">
         <v>58</v>
       </c>
       <c r="O107" s="107">
@@ -14455,13 +13642,13 @@
         <v>45536</v>
       </c>
       <c r="K108" s="81" t="n"/>
-      <c r="L108" s="186" t="n">
+      <c r="L108" s="192" t="n">
         <v>47</v>
       </c>
-      <c r="M108" s="187" t="n">
+      <c r="M108" s="193" t="n">
         <v>32</v>
       </c>
-      <c r="N108" s="186" t="n">
+      <c r="N108" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O108" s="107">
@@ -14513,13 +13700,13 @@
         <v>45536</v>
       </c>
       <c r="K109" s="81" t="n"/>
-      <c r="L109" s="186" t="n">
+      <c r="L109" s="192" t="n">
         <v>24</v>
       </c>
-      <c r="M109" s="187" t="n">
+      <c r="M109" s="193" t="n">
         <v>6</v>
       </c>
-      <c r="N109" s="186" t="n">
+      <c r="N109" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O109" s="107">
@@ -14571,13 +13758,13 @@
         <v>45536</v>
       </c>
       <c r="K110" s="81" t="n"/>
-      <c r="L110" s="186" t="n">
+      <c r="L110" s="192" t="n">
         <v>3</v>
       </c>
-      <c r="M110" s="187" t="n">
+      <c r="M110" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N110" s="186" t="n">
+      <c r="N110" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="107">
@@ -14629,13 +13816,13 @@
         <v>45536</v>
       </c>
       <c r="K111" s="81" t="n"/>
-      <c r="L111" s="186" t="n">
+      <c r="L111" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M111" s="187" t="n">
+      <c r="M111" s="193" t="n">
         <v>18</v>
       </c>
-      <c r="N111" s="186" t="n">
+      <c r="N111" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O111" s="107">
@@ -14687,13 +13874,13 @@
         <v>45536</v>
       </c>
       <c r="K112" s="81" t="n"/>
-      <c r="L112" s="186" t="n">
+      <c r="L112" s="192" t="n">
         <v>36</v>
       </c>
-      <c r="M112" s="187" t="n">
+      <c r="M112" s="193" t="n">
         <v>56</v>
       </c>
-      <c r="N112" s="186" t="n">
+      <c r="N112" s="192" t="n">
         <v>60</v>
       </c>
       <c r="O112" s="107">
@@ -14745,13 +13932,13 @@
         <v>45536</v>
       </c>
       <c r="K113" s="81" t="n"/>
-      <c r="L113" s="186" t="n">
+      <c r="L113" s="192" t="n">
         <v>53</v>
       </c>
-      <c r="M113" s="187" t="n">
+      <c r="M113" s="193" t="n">
         <v>52</v>
       </c>
-      <c r="N113" s="186" t="n">
+      <c r="N113" s="192" t="n">
         <v>63</v>
       </c>
       <c r="O113" s="107">
@@ -14806,13 +13993,13 @@
         <v>45536</v>
       </c>
       <c r="K114" s="81" t="n"/>
-      <c r="L114" s="186" t="n">
+      <c r="L114" s="192" t="n">
         <v>18</v>
       </c>
-      <c r="M114" s="187" t="n">
+      <c r="M114" s="193" t="n">
         <v>24</v>
       </c>
-      <c r="N114" s="186" t="n">
+      <c r="N114" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O114" s="107">
@@ -14864,13 +14051,13 @@
         <v>45536</v>
       </c>
       <c r="K115" s="81" t="n"/>
-      <c r="L115" s="186" t="n">
+      <c r="L115" s="192" t="n">
         <v>26</v>
       </c>
-      <c r="M115" s="187" t="n">
+      <c r="M115" s="193" t="n">
         <v>39</v>
       </c>
-      <c r="N115" s="186" t="n">
+      <c r="N115" s="192" t="n">
         <v>22</v>
       </c>
       <c r="O115" s="107">
@@ -14903,13 +14090,13 @@
         <v>46143</v>
       </c>
       <c r="K116" s="81" t="n"/>
-      <c r="L116" s="186" t="n">
+      <c r="L116" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M116" s="187" t="n">
+      <c r="M116" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N116" s="186" t="n">
+      <c r="N116" s="192" t="n">
         <v>32</v>
       </c>
       <c r="O116" s="107">
@@ -14961,13 +14148,13 @@
         <v>45536</v>
       </c>
       <c r="K117" s="81" t="n"/>
-      <c r="L117" s="186" t="n">
+      <c r="L117" s="192" t="n">
         <v>39</v>
       </c>
-      <c r="M117" s="187" t="n">
+      <c r="M117" s="193" t="n">
         <v>66</v>
       </c>
-      <c r="N117" s="186" t="n">
+      <c r="N117" s="192" t="n">
         <v>49</v>
       </c>
       <c r="O117" s="107">
@@ -15021,13 +14208,13 @@
         <v>45870</v>
       </c>
       <c r="K118" s="81" t="n"/>
-      <c r="L118" s="186" t="n">
+      <c r="L118" s="192" t="n">
         <v>32</v>
       </c>
-      <c r="M118" s="187" t="n">
+      <c r="M118" s="193" t="n">
         <v>20.5</v>
       </c>
-      <c r="N118" s="186" t="n">
+      <c r="N118" s="192" t="n">
         <v>33</v>
       </c>
       <c r="O118" s="107">
@@ -15079,13 +14266,13 @@
         <v>45536</v>
       </c>
       <c r="K119" s="81" t="n"/>
-      <c r="L119" s="186" t="n">
+      <c r="L119" s="192" t="n">
         <v>3</v>
       </c>
-      <c r="M119" s="187" t="n">
+      <c r="M119" s="193" t="n">
         <v>33</v>
       </c>
-      <c r="N119" s="186" t="n">
+      <c r="N119" s="192" t="n">
         <v>12</v>
       </c>
       <c r="O119" s="107">
@@ -15137,13 +14324,13 @@
         <v>45536</v>
       </c>
       <c r="K120" s="81" t="n"/>
-      <c r="L120" s="186" t="n">
+      <c r="L120" s="192" t="n">
         <v>56</v>
       </c>
-      <c r="M120" s="187" t="n">
+      <c r="M120" s="193" t="n">
         <v>41</v>
       </c>
-      <c r="N120" s="186" t="n">
+      <c r="N120" s="192" t="n">
         <v>49</v>
       </c>
       <c r="O120" s="107">
@@ -15172,13 +14359,13 @@
         <v>46235</v>
       </c>
       <c r="K121" s="81" t="n"/>
-      <c r="L121" s="186" t="n">
+      <c r="L121" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M121" s="187" t="n">
+      <c r="M121" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N121" s="186" t="n">
+      <c r="N121" s="192" t="n">
         <v>21</v>
       </c>
       <c r="O121" s="107">
@@ -15230,13 +14417,13 @@
         <v>45536</v>
       </c>
       <c r="K122" s="81" t="n"/>
-      <c r="L122" s="186" t="n">
+      <c r="L122" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M122" s="187" t="n">
+      <c r="M122" s="193" t="n">
         <v>41</v>
       </c>
-      <c r="N122" s="186" t="n">
+      <c r="N122" s="192" t="n">
         <v>13</v>
       </c>
       <c r="O122" s="107">
@@ -15288,13 +14475,13 @@
         <v>45536</v>
       </c>
       <c r="K123" s="81" t="n"/>
-      <c r="L123" s="186" t="n">
+      <c r="L123" s="192" t="n">
         <v>30</v>
       </c>
-      <c r="M123" s="187" t="n">
+      <c r="M123" s="193" t="n">
         <v>17</v>
       </c>
-      <c r="N123" s="186" t="n">
+      <c r="N123" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O123" s="107">
@@ -15323,13 +14510,13 @@
         <v>46235</v>
       </c>
       <c r="K124" s="81" t="n"/>
-      <c r="L124" s="186" t="n">
+      <c r="L124" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M124" s="187" t="n">
+      <c r="M124" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N124" s="186" t="n">
+      <c r="N124" s="192" t="n">
         <v>15</v>
       </c>
       <c r="O124" s="107">
@@ -15381,13 +14568,13 @@
         <v>45809</v>
       </c>
       <c r="K125" s="81" t="n"/>
-      <c r="L125" s="186" t="n">
+      <c r="L125" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M125" s="187" t="n">
+      <c r="M125" s="193" t="n">
         <v>33</v>
       </c>
-      <c r="N125" s="186" t="n">
+      <c r="N125" s="192" t="n">
         <v>32</v>
       </c>
       <c r="O125" s="107">
@@ -15439,13 +14626,13 @@
         <v>45536</v>
       </c>
       <c r="K126" s="81" t="n"/>
-      <c r="L126" s="186" t="n">
+      <c r="L126" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M126" s="187" t="n">
+      <c r="M126" s="193" t="n">
         <v>40</v>
       </c>
-      <c r="N126" s="186" t="n">
+      <c r="N126" s="192" t="n">
         <v>45</v>
       </c>
       <c r="O126" s="107">
@@ -15497,13 +14684,13 @@
         <v>45536</v>
       </c>
       <c r="K127" s="81" t="n"/>
-      <c r="L127" s="186" t="n">
+      <c r="L127" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M127" s="187" t="n">
+      <c r="M127" s="193" t="n">
         <v>32</v>
       </c>
-      <c r="N127" s="186" t="n">
+      <c r="N127" s="192" t="n">
         <v>6</v>
       </c>
       <c r="O127" s="107">
@@ -15555,13 +14742,13 @@
         <v>46222</v>
       </c>
       <c r="K128" s="81" t="n"/>
-      <c r="L128" s="186" t="n">
+      <c r="L128" s="192" t="n">
         <v>15</v>
       </c>
-      <c r="M128" s="187" t="n">
+      <c r="M128" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N128" s="186" t="n">
+      <c r="N128" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="107">
@@ -15613,13 +14800,13 @@
         <v>45536</v>
       </c>
       <c r="K129" s="81" t="n"/>
-      <c r="L129" s="186" t="n">
+      <c r="L129" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M129" s="187" t="n">
+      <c r="M129" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N129" s="186" t="n">
+      <c r="N129" s="192" t="n">
         <v>9</v>
       </c>
       <c r="O129" s="107">
@@ -15648,13 +14835,13 @@
         <v>46235</v>
       </c>
       <c r="K130" s="81" t="n"/>
-      <c r="L130" s="186" t="n">
+      <c r="L130" s="192" t="n">
         <v>0</v>
       </c>
-      <c r="M130" s="187" t="n">
+      <c r="M130" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N130" s="186" t="n">
+      <c r="N130" s="192" t="n">
         <v>18</v>
       </c>
       <c r="O130" s="107">
@@ -15706,13 +14893,13 @@
         <v>45536</v>
       </c>
       <c r="K131" s="81" t="n"/>
-      <c r="L131" s="186" t="n">
+      <c r="L131" s="192" t="n">
         <v>35</v>
       </c>
-      <c r="M131" s="187" t="n">
+      <c r="M131" s="193" t="n">
         <v>23</v>
       </c>
-      <c r="N131" s="186" t="n">
+      <c r="N131" s="192" t="n">
         <v>24</v>
       </c>
       <c r="O131" s="107">
@@ -15764,13 +14951,13 @@
         <v>45959</v>
       </c>
       <c r="K132" s="81" t="n"/>
-      <c r="L132" s="186" t="n">
+      <c r="L132" s="192" t="n">
         <v>55.5</v>
       </c>
-      <c r="M132" s="187" t="n">
+      <c r="M132" s="193" t="n">
         <v>55</v>
       </c>
-      <c r="N132" s="186" t="n">
+      <c r="N132" s="192" t="n">
         <v>47</v>
       </c>
       <c r="O132" s="107">
@@ -15825,13 +15012,13 @@
         <v>45536</v>
       </c>
       <c r="K133" s="81" t="n"/>
-      <c r="L133" s="186" t="n">
+      <c r="L133" s="192" t="n">
         <v>62</v>
       </c>
-      <c r="M133" s="187" t="n">
+      <c r="M133" s="193" t="n">
         <v>58</v>
       </c>
-      <c r="N133" s="186" t="n">
+      <c r="N133" s="192" t="n">
         <v>71</v>
       </c>
       <c r="O133" s="107">
@@ -15886,13 +15073,13 @@
         <v>45536</v>
       </c>
       <c r="K134" s="81" t="n"/>
-      <c r="L134" s="186" t="n">
+      <c r="L134" s="192" t="n">
         <v>17</v>
       </c>
-      <c r="M134" s="187" t="n">
+      <c r="M134" s="193" t="n">
         <v>24</v>
       </c>
-      <c r="N134" s="186" t="n">
+      <c r="N134" s="192" t="n">
         <v>8</v>
       </c>
       <c r="O134" s="107">
@@ -15944,13 +15131,13 @@
         <v>45536</v>
       </c>
       <c r="K135" s="81" t="n"/>
-      <c r="L135" s="186" t="n">
+      <c r="L135" s="192" t="n">
         <v>25</v>
       </c>
-      <c r="M135" s="187" t="n">
+      <c r="M135" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N135" s="186" t="n">
+      <c r="N135" s="192" t="n">
         <v>18</v>
       </c>
       <c r="O135" s="107">
@@ -16002,13 +15189,13 @@
         <v>45536</v>
       </c>
       <c r="K136" s="81" t="n"/>
-      <c r="L136" s="186" t="n">
+      <c r="L136" s="192" t="n">
         <v>75</v>
       </c>
-      <c r="M136" s="187" t="n">
+      <c r="M136" s="193" t="n">
         <v>72.5</v>
       </c>
-      <c r="N136" s="186" t="n">
+      <c r="N136" s="192" t="n">
         <v>77</v>
       </c>
       <c r="O136" s="107">
@@ -16063,13 +15250,13 @@
         <v>45536</v>
       </c>
       <c r="K137" s="81" t="n"/>
-      <c r="L137" s="186" t="n">
+      <c r="L137" s="192" t="n">
         <v>51</v>
       </c>
-      <c r="M137" s="187" t="n">
+      <c r="M137" s="193" t="n">
         <v>49</v>
       </c>
-      <c r="N137" s="186" t="n">
+      <c r="N137" s="192" t="n">
         <v>50</v>
       </c>
       <c r="O137" s="107">
@@ -16121,13 +15308,13 @@
         <v>45536</v>
       </c>
       <c r="K138" s="81" t="n"/>
-      <c r="L138" s="186" t="n">
+      <c r="L138" s="192" t="n">
         <v>37</v>
       </c>
-      <c r="M138" s="187" t="n">
+      <c r="M138" s="193" t="n">
         <v>60</v>
       </c>
-      <c r="N138" s="186" t="n">
+      <c r="N138" s="192" t="n">
         <v>20</v>
       </c>
       <c r="O138" s="107">
@@ -16179,13 +15366,13 @@
         <v>45536</v>
       </c>
       <c r="K139" s="81" t="n"/>
-      <c r="L139" s="186" t="n">
+      <c r="L139" s="192" t="n">
         <v>34</v>
       </c>
-      <c r="M139" s="187" t="n">
+      <c r="M139" s="193" t="n">
         <v>39</v>
       </c>
-      <c r="N139" s="186" t="n">
+      <c r="N139" s="192" t="n">
         <v>38</v>
       </c>
       <c r="O139" s="107">
@@ -16237,13 +15424,13 @@
         <v>45536</v>
       </c>
       <c r="K140" s="81" t="n"/>
-      <c r="L140" s="186" t="n">
+      <c r="L140" s="192" t="n">
         <v>56</v>
       </c>
-      <c r="M140" s="187" t="n">
+      <c r="M140" s="193" t="n">
         <v>58</v>
       </c>
-      <c r="N140" s="186" t="n">
+      <c r="N140" s="192" t="n">
         <v>71</v>
       </c>
       <c r="O140" s="107">
@@ -16298,13 +15485,13 @@
         <v>45536</v>
       </c>
       <c r="K141" s="81" t="n"/>
-      <c r="L141" s="186" t="n">
+      <c r="L141" s="192" t="n">
         <v>56.5</v>
       </c>
-      <c r="M141" s="187" t="n">
+      <c r="M141" s="193" t="n">
         <v>69</v>
       </c>
-      <c r="N141" s="186" t="n">
+      <c r="N141" s="192" t="n">
         <v>66</v>
       </c>
       <c r="O141" s="107">
@@ -16359,13 +15546,13 @@
         <v>45536</v>
       </c>
       <c r="K142" s="81" t="n"/>
-      <c r="L142" s="186" t="n">
+      <c r="L142" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M142" s="187" t="n">
+      <c r="M142" s="193" t="n">
         <v>17</v>
       </c>
-      <c r="N142" s="186" t="n">
+      <c r="N142" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="107">
@@ -16417,13 +15604,13 @@
         <v>45536</v>
       </c>
       <c r="K143" s="81" t="n"/>
-      <c r="L143" s="186" t="n">
+      <c r="L143" s="192" t="n">
         <v>28</v>
       </c>
-      <c r="M143" s="187" t="n">
+      <c r="M143" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N143" s="186" t="n">
+      <c r="N143" s="192" t="n">
         <v>33</v>
       </c>
       <c r="O143" s="107">
@@ -16475,13 +15662,13 @@
         <v>45536</v>
       </c>
       <c r="K144" s="81" t="n"/>
-      <c r="L144" s="186" t="n">
+      <c r="L144" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M144" s="187" t="n">
+      <c r="M144" s="193" t="n">
         <v>35</v>
       </c>
-      <c r="N144" s="186" t="n">
+      <c r="N144" s="192" t="n">
         <v>12</v>
       </c>
       <c r="O144" s="107">
@@ -16533,13 +15720,13 @@
         <v>45839</v>
       </c>
       <c r="K145" s="81" t="n"/>
-      <c r="L145" s="186" t="n">
+      <c r="L145" s="192" t="n">
         <v>18</v>
       </c>
-      <c r="M145" s="187" t="n">
+      <c r="M145" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N145" s="186" t="n">
+      <c r="N145" s="192" t="n">
         <v>20</v>
       </c>
       <c r="O145" s="107">
@@ -16591,13 +15778,13 @@
         <v>45536</v>
       </c>
       <c r="K146" s="81" t="n"/>
-      <c r="L146" s="186" t="n">
+      <c r="L146" s="192" t="n">
         <v>27</v>
       </c>
-      <c r="M146" s="187" t="n">
+      <c r="M146" s="193" t="n">
         <v>0</v>
       </c>
-      <c r="N146" s="186" t="n">
+      <c r="N146" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O146" s="107">
@@ -16649,13 +15836,13 @@
         <v>45778</v>
       </c>
       <c r="K147" s="81" t="n"/>
-      <c r="L147" s="186" t="n">
+      <c r="L147" s="192" t="n">
         <v>9</v>
       </c>
-      <c r="M147" s="187" t="n">
+      <c r="M147" s="193" t="n">
         <v>1.5</v>
       </c>
-      <c r="N147" s="186" t="n">
+      <c r="N147" s="192" t="n">
         <v>3</v>
       </c>
       <c r="O147" s="107">
@@ -16707,13 +15894,13 @@
         <v>46018</v>
       </c>
       <c r="K148" s="81" t="n"/>
-      <c r="L148" s="186" t="n">
+      <c r="L148" s="192" t="n">
         <v>45</v>
       </c>
-      <c r="M148" s="187" t="n">
+      <c r="M148" s="193" t="n">
         <v>55</v>
       </c>
-      <c r="N148" s="186" t="n">
+      <c r="N148" s="192" t="n">
         <v>47</v>
       </c>
       <c r="O148" s="107">
@@ -16765,13 +15952,13 @@
         <v>45536</v>
       </c>
       <c r="K149" s="81" t="n"/>
-      <c r="L149" s="186" t="n">
+      <c r="L149" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="M149" s="187" t="n">
+      <c r="M149" s="193" t="n">
         <v>39</v>
       </c>
-      <c r="N149" s="186" t="n">
+      <c r="N149" s="192" t="n">
         <v>35</v>
       </c>
       <c r="O149" s="107">
@@ -16823,13 +16010,13 @@
         <v>45536</v>
       </c>
       <c r="K150" s="81" t="n"/>
-      <c r="L150" s="186" t="n">
+      <c r="L150" s="192" t="n">
         <v>10</v>
       </c>
-      <c r="M150" s="187" t="n">
+      <c r="M150" s="193" t="n">
         <v>8</v>
       </c>
-      <c r="N150" s="186" t="n">
+      <c r="N150" s="192" t="n">
         <v>8</v>
       </c>
       <c r="O150" s="107">
@@ -16881,13 +16068,13 @@
         <v>45536</v>
       </c>
       <c r="K151" s="81" t="n"/>
-      <c r="L151" s="186" t="n">
+      <c r="L151" s="192" t="n">
         <v>26</v>
       </c>
-      <c r="M151" s="187" t="n">
+      <c r="M151" s="193" t="n">
         <v>24</v>
       </c>
-      <c r="N151" s="186" t="n">
+      <c r="N151" s="192" t="n">
         <v>18</v>
       </c>
       <c r="O151" s="107">
@@ -16939,13 +16126,13 @@
         <v>45536</v>
       </c>
       <c r="K152" s="99" t="n"/>
-      <c r="L152" s="188" t="n">
+      <c r="L152" s="194" t="n">
         <v>26</v>
       </c>
-      <c r="M152" s="189" t="n">
+      <c r="M152" s="195" t="n">
         <v>0</v>
       </c>
-      <c r="N152" s="186" t="n">
+      <c r="N152" s="192" t="n">
         <v>0</v>
       </c>
       <c r="O152" s="107">
@@ -16997,13 +16184,13 @@
         <v>45536</v>
       </c>
       <c r="K153" s="99" t="n"/>
-      <c r="L153" s="188" t="n">
+      <c r="L153" s="194" t="n">
         <v>36</v>
       </c>
-      <c r="M153" s="189" t="n">
+      <c r="M153" s="195" t="n">
         <v>49</v>
       </c>
-      <c r="N153" s="186" t="n">
+      <c r="N153" s="192" t="n">
         <v>49</v>
       </c>
       <c r="O153" s="107">
@@ -17040,11 +16227,11 @@
         <f>SUM(N3:N153)</f>
         <v/>
       </c>
-      <c r="O154" s="190">
+      <c r="O154" s="196">
         <f>SUM(O3:O153)</f>
         <v/>
       </c>
-      <c r="P154" s="190">
+      <c r="P154" s="196">
         <f>SUM(P3:P153)</f>
         <v/>
       </c>

--- a/주52시간_3개월_현황_요약_0902.xlsx
+++ b/주52시간_3개월_현황_요약_0902.xlsx
@@ -11,7 +11,7 @@
     <sheet name="아모레 생산" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'0.요약'!$A$1:$R$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'0.요약'!$A$1:$R$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
   </definedNames>
@@ -200,8 +200,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00C00000"/>
-      <sz val="8"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -889,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1306,18 +1307,19 @@
     <xf numFmtId="3" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="24" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="25" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1328,9 +1330,6 @@
     <xf numFmtId="164" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="24" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1349,12 +1348,12 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1364,24 +1363,47 @@
     <xf numFmtId="164" fontId="29" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1933,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="130" min="1" max="1"/>
@@ -1959,7 +1981,7 @@
     <row r="1" ht="22" customHeight="1" s="130">
       <c r="A1" s="131" t="inlineStr">
         <is>
-          <t>주 52시간 3개월(6~8월) 시간외근무 현황 — 요약</t>
+          <t>3개월 탄력근로 단위기간(7·8·9월) 연장근로 현황 — 요약</t>
         </is>
       </c>
       <c r="B1" s="132" t="n"/>
@@ -1983,7 +2005,7 @@
     <row r="2" ht="12" customHeight="1" s="130">
       <c r="A2" s="133" t="inlineStr">
         <is>
-          <t>기준: 연장 한도 주 12H × 13주 = 156H  ·  9월 가용 = min(156 − 7·8월 실적, 51.4H)  |  원본 2개 시트 미수정  |  2026.09.02</t>
+          <t>단위기간 4·5·6월 / 7·8·9월 / 10·11·12월  ·  기간 한도 156H(12H/주 × 13주)  ·  9월 잔여 = 156H − (7월+8월)  |  6월은 직전 단위기간이므로 현 구간 계산 제외  |  원본 2개 시트 미수정  ·  2026.09.02</t>
         </is>
       </c>
       <c r="B2" s="134" t="n"/>
@@ -2041,37 +2063,37 @@
       </c>
       <c r="C4" s="137" t="inlineStr">
         <is>
-          <t>3개월 계(H)</t>
+          <t>7월(H)</t>
         </is>
       </c>
       <c r="D4" s="137" t="inlineStr">
         <is>
-          <t>인당(H)</t>
+          <t>8월(H)</t>
         </is>
       </c>
       <c r="E4" s="137" t="inlineStr">
         <is>
-          <t>156H 초과</t>
+          <t>7·8월 계(H)</t>
         </is>
       </c>
       <c r="F4" s="137" t="inlineStr">
         <is>
-          <t>초과분(H)</t>
+          <t>인당 소진(H)</t>
         </is>
       </c>
       <c r="G4" s="137" t="inlineStr">
         <is>
-          <t>9월 가용(H)</t>
+          <t>9월 잔여 계(H)</t>
         </is>
       </c>
       <c r="H4" s="137" t="inlineStr">
         <is>
-          <t>인당 가용(H)</t>
+          <t>인당 잔여(H)</t>
         </is>
       </c>
       <c r="I4" s="137" t="inlineStr">
         <is>
-          <t>9월 편성 불가</t>
+          <t>잔여 0H</t>
         </is>
       </c>
       <c r="J4" s="138" t="inlineStr">
@@ -2098,39 +2120,39 @@
         <v>88</v>
       </c>
       <c r="C5" s="141" t="n">
-        <v>7680</v>
-      </c>
-      <c r="D5" s="142" t="n">
-        <v>87.27272727272727</v>
-      </c>
-      <c r="E5" s="143" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" s="144" t="n">
-        <v>744</v>
-      </c>
-      <c r="G5" s="145" t="n">
-        <v>4068.800000000004</v>
-      </c>
-      <c r="H5" s="142" t="n">
-        <v>46.23636363636368</v>
+        <v>2664.5</v>
+      </c>
+      <c r="D5" s="141" t="n">
+        <v>2569</v>
+      </c>
+      <c r="E5" s="142" t="n">
+        <v>5233.5</v>
+      </c>
+      <c r="F5" s="143" t="n">
+        <v>59.47159090909091</v>
+      </c>
+      <c r="G5" s="142" t="n">
+        <v>8576</v>
+      </c>
+      <c r="H5" s="143" t="n">
+        <v>97.45454545454545</v>
       </c>
       <c r="I5" s="144" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="146" t="inlineStr">
-        <is>
-          <t>239명 중 34명이 이미 3개월 156H 초과 (초과분 1,219H)</t>
-        </is>
-      </c>
-      <c r="K5" s="147" t="n"/>
-      <c r="L5" s="147" t="n"/>
-      <c r="M5" s="147" t="n"/>
-      <c r="N5" s="147" t="n"/>
-      <c r="O5" s="147" t="n"/>
-      <c r="P5" s="147" t="n"/>
-      <c r="Q5" s="147" t="n"/>
-      <c r="R5" s="147" t="n"/>
+      <c r="J5" s="145" t="inlineStr">
+        <is>
+          <t>현 단위기간(7·8·9월) 7·8월 소진 14,354H · 인당 60H (한도 156H의 39%)</t>
+        </is>
+      </c>
+      <c r="K5" s="146" t="n"/>
+      <c r="L5" s="146" t="n"/>
+      <c r="M5" s="146" t="n"/>
+      <c r="N5" s="146" t="n"/>
+      <c r="O5" s="146" t="n"/>
+      <c r="P5" s="146" t="n"/>
+      <c r="Q5" s="146" t="n"/>
+      <c r="R5" s="146" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1" s="130">
       <c r="A6" s="140" t="inlineStr">
@@ -2142,39 +2164,39 @@
         <v>151</v>
       </c>
       <c r="C6" s="141" t="n">
-        <v>13825</v>
-      </c>
-      <c r="D6" s="142" t="n">
-        <v>91.55629139072848</v>
-      </c>
-      <c r="E6" s="143" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="144" t="n">
-        <v>475</v>
-      </c>
-      <c r="G6" s="145" t="n">
-        <v>7334.099999999984</v>
-      </c>
-      <c r="H6" s="142" t="n">
-        <v>48.57019867549658</v>
+        <v>4983</v>
+      </c>
+      <c r="D6" s="141" t="n">
+        <v>4138</v>
+      </c>
+      <c r="E6" s="142" t="n">
+        <v>9121</v>
+      </c>
+      <c r="F6" s="143" t="n">
+        <v>60.40397350993378</v>
+      </c>
+      <c r="G6" s="142" t="n">
+        <v>14456.5</v>
+      </c>
+      <c r="H6" s="143" t="n">
+        <v>95.73841059602648</v>
       </c>
       <c r="I6" s="144" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="146" t="inlineStr">
-        <is>
-          <t>9월 추가 편성 가능 연장 전사 11,403H — 38주 대응의 상한</t>
-        </is>
-      </c>
-      <c r="K6" s="147" t="n"/>
-      <c r="L6" s="147" t="n"/>
-      <c r="M6" s="147" t="n"/>
-      <c r="N6" s="147" t="n"/>
-      <c r="O6" s="147" t="n"/>
-      <c r="P6" s="147" t="n"/>
-      <c r="Q6" s="147" t="n"/>
-      <c r="R6" s="147" t="n"/>
+      <c r="J6" s="147" t="inlineStr">
+        <is>
+          <t>9월 잔여 연장 전사 23,032H · 인당 96H — 9월 잔업·특근의 상한</t>
+        </is>
+      </c>
+      <c r="K6" s="148" t="n"/>
+      <c r="L6" s="148" t="n"/>
+      <c r="M6" s="148" t="n"/>
+      <c r="N6" s="148" t="n"/>
+      <c r="O6" s="148" t="n"/>
+      <c r="P6" s="148" t="n"/>
+      <c r="Q6" s="148" t="n"/>
+      <c r="R6" s="148" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1" s="130">
       <c r="A7" s="140" t="inlineStr">
@@ -2182,43 +2204,43 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="B7" s="148" t="n">
+      <c r="B7" s="149" t="n">
         <v>239</v>
       </c>
-      <c r="C7" s="148" t="n">
-        <v>21505</v>
+      <c r="C7" s="149" t="n">
+        <v>7647.5</v>
       </c>
       <c r="D7" s="149" t="n">
-        <v>89.97907949790795</v>
-      </c>
-      <c r="E7" s="143" t="n">
-        <v>34</v>
+        <v>6707</v>
+      </c>
+      <c r="E7" s="149" t="n">
+        <v>14354.5</v>
       </c>
       <c r="F7" s="150" t="n">
-        <v>1219</v>
-      </c>
-      <c r="G7" s="148" t="n">
-        <v>11402.89999999999</v>
-      </c>
-      <c r="H7" s="149" t="n">
-        <v>47.71087866108782</v>
-      </c>
-      <c r="I7" s="150" t="n">
+        <v>60.06066945606695</v>
+      </c>
+      <c r="G7" s="149" t="n">
+        <v>23032.5</v>
+      </c>
+      <c r="H7" s="150" t="n">
+        <v>96.37029288702929</v>
+      </c>
+      <c r="I7" s="144" t="n">
         <v>4</v>
       </c>
       <c r="J7" s="151" t="inlineStr">
         <is>
-          <t>7·8월만으로 156H 초과 → 9월 편성 불가 4명 (세척실 3 · PM 1)</t>
-        </is>
-      </c>
-      <c r="K7" s="147" t="n"/>
-      <c r="L7" s="147" t="n"/>
-      <c r="M7" s="147" t="n"/>
-      <c r="N7" s="147" t="n"/>
-      <c r="O7" s="147" t="n"/>
-      <c r="P7" s="147" t="n"/>
-      <c r="Q7" s="147" t="n"/>
-      <c r="R7" s="147" t="n"/>
+          <t>잔여 0H 4명 · 30H 미만 19명  |  10월부터 새 단위기간 → 156H 리셋</t>
+        </is>
+      </c>
+      <c r="K7" s="148" t="n"/>
+      <c r="L7" s="148" t="n"/>
+      <c r="M7" s="148" t="n"/>
+      <c r="N7" s="148" t="n"/>
+      <c r="O7" s="148" t="n"/>
+      <c r="P7" s="148" t="n"/>
+      <c r="Q7" s="148" t="n"/>
+      <c r="R7" s="148" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1" s="130">
       <c r="A8" s="135" t="inlineStr">
@@ -2257,20 +2279,20 @@
       </c>
       <c r="C9" s="137" t="inlineStr">
         <is>
-          <t>3개월
-평균(H)</t>
+          <t>7·8월
+인당(H)</t>
         </is>
       </c>
       <c r="D9" s="137" t="inlineStr">
         <is>
-          <t>156H
-초과</t>
+          <t>잔여
+30H미만</t>
         </is>
       </c>
       <c r="E9" s="137" t="inlineStr">
         <is>
-          <t>9월 가용
-(H)</t>
+          <t>9월 잔여
+계(H)</t>
         </is>
       </c>
       <c r="F9" s="137" t="inlineStr">
@@ -2290,20 +2312,20 @@
       </c>
       <c r="I9" s="137" t="inlineStr">
         <is>
-          <t>3개월
-평균(H)</t>
+          <t>7·8월
+인당(H)</t>
         </is>
       </c>
       <c r="J9" s="137" t="inlineStr">
         <is>
-          <t>156H
-초과</t>
+          <t>잔여
+30H미만</t>
         </is>
       </c>
       <c r="K9" s="137" t="inlineStr">
         <is>
-          <t>9월 가용
-(H)</t>
+          <t>9월 잔여
+계(H)</t>
         </is>
       </c>
       <c r="L9" s="137" t="inlineStr">
@@ -2323,20 +2345,20 @@
       </c>
       <c r="O9" s="137" t="inlineStr">
         <is>
-          <t>3개월
-평균(H)</t>
+          <t>7·8월
+인당(H)</t>
         </is>
       </c>
       <c r="P9" s="137" t="inlineStr">
         <is>
-          <t>156H
-초과</t>
+          <t>잔여
+30H미만</t>
         </is>
       </c>
       <c r="Q9" s="137" t="inlineStr">
         <is>
-          <t>9월 가용
-(H)</t>
+          <t>9월 잔여
+계(H)</t>
         </is>
       </c>
       <c r="R9" s="137" t="inlineStr">
@@ -2355,12 +2377,12 @@
         <v>3</v>
       </c>
       <c r="C10" s="153" t="n">
-        <v>189.8333333333333</v>
+        <v>131.1666666666667</v>
       </c>
       <c r="D10" s="154" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="145" t="n">
+      <c r="E10" s="142" t="n">
         <v>74.5</v>
       </c>
       <c r="F10" s="155" t="inlineStr">
@@ -2370,24 +2392,24 @@
       </c>
       <c r="G10" s="156" t="inlineStr">
         <is>
-          <t>튜브 (생)</t>
+          <t>원료 창고 (업)</t>
         </is>
       </c>
       <c r="H10" s="141" t="n">
-        <v>17</v>
-      </c>
-      <c r="I10" s="142" t="n">
-        <v>110.6176470588235</v>
-      </c>
-      <c r="J10" s="154" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="145" t="n">
-        <v>813.5999999999998</v>
+        <v>6</v>
+      </c>
+      <c r="I10" s="143" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="J10" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="142" t="n">
+        <v>490.5</v>
       </c>
       <c r="L10" s="157" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M10" s="156" t="inlineStr">
@@ -2398,16 +2420,16 @@
       <c r="N10" s="141" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="142" t="n">
-        <v>56</v>
+      <c r="O10" s="143" t="n">
+        <v>41</v>
       </c>
       <c r="P10" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="145" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="R10" s="157" t="inlineStr">
+      <c r="Q10" s="142" t="n">
+        <v>115</v>
+      </c>
+      <c r="R10" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2423,59 +2445,59 @@
         <v>5</v>
       </c>
       <c r="C11" s="153" t="n">
-        <v>167.7</v>
+        <v>114</v>
       </c>
       <c r="D11" s="154" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="145" t="n">
-        <v>191.8</v>
-      </c>
-      <c r="F11" s="158" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E11" s="142" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" s="155" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="G11" s="156" t="inlineStr">
+        <is>
+          <t>행정 (생)</t>
+        </is>
+      </c>
+      <c r="H11" s="141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="143" t="n">
+        <v>74</v>
+      </c>
+      <c r="J11" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="142" t="n">
+        <v>82</v>
+      </c>
+      <c r="L11" s="157" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
       </c>
-      <c r="G11" s="156" t="inlineStr">
-        <is>
-          <t>직선 (생)</t>
-        </is>
-      </c>
-      <c r="H11" s="141" t="n">
-        <v>24</v>
-      </c>
-      <c r="I11" s="142" t="n">
-        <v>109.7083333333333</v>
-      </c>
-      <c r="J11" s="154" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="145" t="n">
-        <v>1178</v>
-      </c>
-      <c r="L11" s="157" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
       <c r="M11" s="156" t="inlineStr">
         <is>
-          <t>염모 (생)</t>
+          <t>(미기재) (업)</t>
         </is>
       </c>
       <c r="N11" s="141" t="n">
-        <v>27</v>
-      </c>
-      <c r="O11" s="142" t="n">
-        <v>41.53703703703704</v>
+        <v>4</v>
+      </c>
+      <c r="O11" s="143" t="n">
+        <v>39.75</v>
       </c>
       <c r="P11" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="145" t="n">
-        <v>1387.8</v>
-      </c>
-      <c r="R11" s="157" t="inlineStr">
+      <c r="Q11" s="142" t="n">
+        <v>465</v>
+      </c>
+      <c r="R11" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2491,66 +2513,66 @@
         <v>14</v>
       </c>
       <c r="C12" s="153" t="n">
-        <v>150.7142857142857</v>
+        <v>102.8571428571429</v>
       </c>
       <c r="D12" s="154" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="145" t="n">
-        <v>470.6999999999999</v>
-      </c>
-      <c r="F12" s="158" t="inlineStr">
-        <is>
-          <t>보통</t>
+        <v>5</v>
+      </c>
+      <c r="E12" s="142" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="F12" s="155" t="inlineStr">
+        <is>
+          <t>낮음</t>
         </is>
       </c>
       <c r="G12" s="156" t="inlineStr">
         <is>
-          <t>행정 (생)</t>
+          <t>계획자 (생)</t>
         </is>
       </c>
       <c r="H12" s="141" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="142" t="n">
-        <v>101</v>
+        <v>3</v>
+      </c>
+      <c r="I12" s="143" t="n">
+        <v>72.5</v>
       </c>
       <c r="J12" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="145" t="n">
-        <v>51.4</v>
+      <c r="K12" s="142" t="n">
+        <v>250.5</v>
       </c>
       <c r="L12" s="157" t="inlineStr">
         <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M12" s="156" t="inlineStr">
+        <is>
+          <t>공작/미화 (업)</t>
+        </is>
+      </c>
+      <c r="N12" s="141" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="143" t="n">
+        <v>28.56666666666667</v>
+      </c>
+      <c r="P12" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="142" t="n">
+        <v>1911.5</v>
+      </c>
+      <c r="R12" s="158" t="inlineStr">
+        <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M12" s="156" t="inlineStr">
-        <is>
-          <t>(미기재) (업)</t>
-        </is>
-      </c>
-      <c r="N12" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" s="142" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="P12" s="141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="145" t="n">
-        <v>205.6</v>
-      </c>
-      <c r="R12" s="157" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="130">
-      <c r="A13" s="152" t="inlineStr">
+      <c r="A13" s="156" t="inlineStr">
         <is>
           <t>내용물 관리 (업)</t>
         </is>
@@ -2558,60 +2580,60 @@
       <c r="B13" s="141" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="153" t="n">
-        <v>137.3</v>
+      <c r="C13" s="143" t="n">
+        <v>87.3</v>
       </c>
       <c r="D13" s="154" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="145" t="n">
-        <v>215.2</v>
+        <v>1</v>
+      </c>
+      <c r="E13" s="142" t="n">
+        <v>343.5</v>
       </c>
       <c r="F13" s="157" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G13" s="156" t="inlineStr">
         <is>
-          <t>실적/순회 (생)</t>
+          <t>초격차 (생)</t>
         </is>
       </c>
       <c r="H13" s="141" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="142" t="n">
-        <v>92.875</v>
+        <v>19</v>
+      </c>
+      <c r="I13" s="143" t="n">
+        <v>56.21052631578947</v>
       </c>
       <c r="J13" s="154" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="145" t="n">
-        <v>197.2</v>
+      <c r="K13" s="142" t="n">
+        <v>1896</v>
       </c>
       <c r="L13" s="157" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="M13" s="156" t="inlineStr">
         <is>
-          <t>공작/미화 (업)</t>
+          <t>염모 (생)</t>
         </is>
       </c>
       <c r="N13" s="141" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" s="142" t="n">
-        <v>38.36666666666667</v>
-      </c>
-      <c r="P13" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="145" t="n">
-        <v>746.0999999999998</v>
-      </c>
-      <c r="R13" s="157" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="O13" s="143" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P13" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="142" t="n">
+        <v>3712.5</v>
+      </c>
+      <c r="R13" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2620,44 +2642,44 @@
     <row r="14" ht="12" customHeight="1" s="130">
       <c r="A14" s="156" t="inlineStr">
         <is>
-          <t>PM (생)</t>
+          <t>튜브 (생)</t>
         </is>
       </c>
       <c r="B14" s="141" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="142" t="n">
-        <v>119.8888888888889</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="143" t="n">
+        <v>80.29411764705883</v>
       </c>
       <c r="D14" s="154" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="145" t="n">
-        <v>399.3</v>
+      <c r="E14" s="142" t="n">
+        <v>1287</v>
       </c>
       <c r="F14" s="157" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G14" s="156" t="inlineStr">
         <is>
-          <t>포장재 창고 (업)</t>
+          <t>실적/순회 (생)</t>
         </is>
       </c>
       <c r="H14" s="141" t="n">
-        <v>25</v>
-      </c>
-      <c r="I14" s="142" t="n">
-        <v>83.86</v>
-      </c>
-      <c r="J14" s="154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="145" t="n">
-        <v>1216.3</v>
-      </c>
-      <c r="L14" s="157" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I14" s="143" t="n">
+        <v>55.875</v>
+      </c>
+      <c r="J14" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="142" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="L14" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2670,16 +2692,16 @@
       <c r="N14" s="141" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="142" t="n">
+      <c r="O14" s="143" t="n">
         <v>17</v>
       </c>
       <c r="P14" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="145" t="n">
-        <v>308.4</v>
-      </c>
-      <c r="R14" s="157" t="inlineStr">
+      <c r="Q14" s="142" t="n">
+        <v>834</v>
+      </c>
+      <c r="R14" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2688,44 +2710,44 @@
     <row r="15" ht="12" customHeight="1" s="130">
       <c r="A15" s="156" t="inlineStr">
         <is>
-          <t>원료 창고 (업)</t>
+          <t>PM (생)</t>
         </is>
       </c>
       <c r="B15" s="141" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="142" t="n">
-        <v>118.75</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="143" t="n">
+        <v>82.55555555555556</v>
       </c>
       <c r="D15" s="154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="142" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="F15" s="157" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G15" s="156" t="inlineStr">
+        <is>
+          <t>포장재 창고 (업)</t>
+        </is>
+      </c>
+      <c r="H15" s="141" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="143" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="J15" s="154" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="145" t="n">
-        <v>287</v>
-      </c>
-      <c r="F15" s="157" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G15" s="156" t="inlineStr">
-        <is>
-          <t>초격차 (생)</t>
-        </is>
-      </c>
-      <c r="H15" s="141" t="n">
-        <v>19</v>
-      </c>
-      <c r="I15" s="142" t="n">
-        <v>80.15789473684211</v>
-      </c>
-      <c r="J15" s="154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="145" t="n">
-        <v>954.1999999999997</v>
-      </c>
-      <c r="L15" s="157" t="inlineStr">
+      <c r="K15" s="142" t="n">
+        <v>2508</v>
+      </c>
+      <c r="L15" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2738,16 +2760,16 @@
       <c r="N15" s="141" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="142" t="n">
-        <v>10.5</v>
+      <c r="O15" s="143" t="n">
+        <v>2.5</v>
       </c>
       <c r="P15" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="145" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="R15" s="157" t="inlineStr">
+      <c r="Q15" s="142" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="R15" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2756,44 +2778,44 @@
     <row r="16" ht="12" customHeight="1" s="130">
       <c r="A16" s="156" t="inlineStr">
         <is>
-          <t>계획자 (생)</t>
+          <t>직선 (생)</t>
         </is>
       </c>
       <c r="B16" s="141" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="142" t="n">
-        <v>115.1666666666667</v>
-      </c>
-      <c r="D16" s="154" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" s="143" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="D16" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="142" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F16" s="157" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="G16" s="156" t="inlineStr">
+        <is>
+          <t>적재실 (업)</t>
+        </is>
+      </c>
+      <c r="H16" s="141" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" s="143" t="n">
+        <v>54.6764705882353</v>
+      </c>
+      <c r="J16" s="154" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="145" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="F16" s="157" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="G16" s="156" t="inlineStr">
-        <is>
-          <t>O/C (생)</t>
-        </is>
-      </c>
-      <c r="H16" s="141" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="142" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="J16" s="141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="145" t="n">
-        <v>616.7999999999998</v>
-      </c>
-      <c r="L16" s="157" t="inlineStr">
+      <c r="K16" s="142" t="n">
+        <v>1722.5</v>
+      </c>
+      <c r="L16" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2806,16 +2828,16 @@
       <c r="N16" s="141" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="142" t="n">
+      <c r="O16" s="143" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="141" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="145" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="R16" s="157" t="inlineStr">
+      <c r="Q16" s="142" t="n">
+        <v>156</v>
+      </c>
+      <c r="R16" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2830,38 +2852,38 @@
       <c r="B17" s="141" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="142" t="n">
-        <v>113.1</v>
+      <c r="C17" s="143" t="n">
+        <v>74.45</v>
       </c>
       <c r="D17" s="154" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="145" t="n">
-        <v>976.3999999999997</v>
+        <v>1</v>
+      </c>
+      <c r="E17" s="142" t="n">
+        <v>1631</v>
       </c>
       <c r="F17" s="157" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="G17" s="156" t="inlineStr">
         <is>
-          <t>적재실 (업)</t>
+          <t>O/C (생)</t>
         </is>
       </c>
       <c r="H17" s="141" t="n">
-        <v>17</v>
-      </c>
-      <c r="I17" s="142" t="n">
-        <v>78.20588235294117</v>
-      </c>
-      <c r="J17" s="154" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="145" t="n">
-        <v>825.0999999999998</v>
-      </c>
-      <c r="L17" s="157" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="I17" s="143" t="n">
+        <v>41.08333333333334</v>
+      </c>
+      <c r="J17" s="141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="142" t="n">
+        <v>1379</v>
+      </c>
+      <c r="L17" s="158" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2876,7 +2898,7 @@
     <row r="18" ht="14" customHeight="1" s="130">
       <c r="A18" s="135" t="inlineStr">
         <is>
-          <t>③ 3개월 156H 초과자 34명 — 9월 편성 배제 대상 (음영 = 9월 편성 불가)</t>
+          <t>③ 9월 잔여 연장시간 하위 30명 — 잔업·특근 편성 시 우선 배제 (진한 음영 = 잔여 0H)</t>
         </is>
       </c>
       <c r="B18" s="136" t="n"/>
@@ -2905,12 +2927,12 @@
       </c>
       <c r="B19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="C19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
       <c r="D19" s="137" t="inlineStr">
@@ -2920,12 +2942,12 @@
       </c>
       <c r="E19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="F19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
       <c r="G19" s="137" t="inlineStr">
@@ -2935,12 +2957,12 @@
       </c>
       <c r="H19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="I19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
       <c r="J19" s="137" t="inlineStr">
@@ -2950,12 +2972,12 @@
       </c>
       <c r="K19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="L19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
       <c r="M19" s="137" t="inlineStr">
@@ -2965,12 +2987,12 @@
       </c>
       <c r="N19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="O19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
       <c r="P19" s="137" t="inlineStr">
@@ -2980,162 +3002,162 @@
       </c>
       <c r="Q19" s="137" t="inlineStr">
         <is>
-          <t>3개월</t>
+          <t>7+8월</t>
         </is>
       </c>
       <c r="R19" s="137" t="inlineStr">
         <is>
-          <t>초과</t>
+          <t>9월 잔여</t>
         </is>
       </c>
     </row>
     <row r="20" ht="11.5" customHeight="1" s="130">
       <c r="A20" s="159" t="inlineStr">
         <is>
-          <t>박태근</t>
+          <t>김영두</t>
         </is>
       </c>
       <c r="B20" s="160" t="n">
-        <v>289.5</v>
+        <v>178</v>
       </c>
       <c r="C20" s="161" t="n">
-        <v>133.5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="162" t="inlineStr">
         <is>
-          <t>전완철</t>
+          <t>조영순</t>
         </is>
       </c>
       <c r="E20" s="163" t="n">
-        <v>217</v>
+        <v>149.5</v>
       </c>
       <c r="F20" s="164" t="n">
-        <v>61</v>
+        <v>6.5</v>
       </c>
       <c r="G20" s="162" t="inlineStr">
         <is>
-          <t>정혜숙</t>
+          <t>선우찬</t>
         </is>
       </c>
       <c r="H20" s="163" t="n">
-        <v>191</v>
+        <v>132.5</v>
       </c>
       <c r="I20" s="164" t="n">
-        <v>35</v>
+        <v>23.5</v>
       </c>
       <c r="J20" s="162" t="inlineStr">
         <is>
-          <t>김진만</t>
+          <t>신성수</t>
         </is>
       </c>
       <c r="K20" s="163" t="n">
-        <v>178</v>
+        <v>129.5</v>
       </c>
       <c r="L20" s="164" t="n">
-        <v>22</v>
-      </c>
-      <c r="M20" s="162" t="inlineStr">
-        <is>
-          <t>김희빈</t>
-        </is>
-      </c>
-      <c r="N20" s="163" t="n">
-        <v>169</v>
-      </c>
-      <c r="O20" s="164" t="n">
-        <v>13</v>
-      </c>
-      <c r="P20" s="162" t="inlineStr">
-        <is>
-          <t>성은경</t>
-        </is>
-      </c>
-      <c r="Q20" s="163" t="n">
-        <v>160</v>
-      </c>
-      <c r="R20" s="164" t="n">
-        <v>4</v>
+        <v>26.5</v>
+      </c>
+      <c r="M20" s="165" t="inlineStr">
+        <is>
+          <t>김명희</t>
+        </is>
+      </c>
+      <c r="N20" s="166" t="n">
+        <v>126</v>
+      </c>
+      <c r="O20" s="167" t="n">
+        <v>30</v>
+      </c>
+      <c r="P20" s="165" t="inlineStr">
+        <is>
+          <t>김인규</t>
+        </is>
+      </c>
+      <c r="Q20" s="166" t="n">
+        <v>120</v>
+      </c>
+      <c r="R20" s="167" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="11.5" customHeight="1" s="130">
       <c r="A21" s="159" t="inlineStr">
         <is>
-          <t>문석</t>
+          <t>박태근</t>
         </is>
       </c>
       <c r="B21" s="160" t="n">
-        <v>264.5</v>
+        <v>198.5</v>
       </c>
       <c r="C21" s="161" t="n">
-        <v>108.5</v>
+        <v>0</v>
       </c>
       <c r="D21" s="162" t="inlineStr">
         <is>
-          <t>선우찬</t>
+          <t>김영준</t>
         </is>
       </c>
       <c r="E21" s="163" t="n">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="F21" s="164" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G21" s="162" t="inlineStr">
         <is>
-          <t>이준구</t>
+          <t>김진만</t>
         </is>
       </c>
       <c r="H21" s="163" t="n">
-        <v>190.5</v>
+        <v>132</v>
       </c>
       <c r="I21" s="164" t="n">
-        <v>34.5</v>
+        <v>24</v>
       </c>
       <c r="J21" s="162" t="inlineStr">
         <is>
-          <t>박효</t>
+          <t>정혜숙</t>
         </is>
       </c>
       <c r="K21" s="163" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="L21" s="164" t="n">
-        <v>21</v>
-      </c>
-      <c r="M21" s="162" t="inlineStr">
-        <is>
-          <t>이은하</t>
-        </is>
-      </c>
-      <c r="N21" s="163" t="n">
-        <v>169</v>
-      </c>
-      <c r="O21" s="164" t="n">
-        <v>13</v>
-      </c>
-      <c r="P21" s="162" t="inlineStr">
-        <is>
-          <t>곽옥연</t>
-        </is>
-      </c>
-      <c r="Q21" s="163" t="n">
-        <v>159</v>
-      </c>
-      <c r="R21" s="164" t="n">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="M21" s="165" t="inlineStr">
+        <is>
+          <t>김순리</t>
+        </is>
+      </c>
+      <c r="N21" s="166" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="O21" s="167" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="P21" s="165" t="inlineStr">
+        <is>
+          <t>김태환</t>
+        </is>
+      </c>
+      <c r="Q21" s="166" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="R21" s="167" t="n">
+        <v>39.5</v>
       </c>
     </row>
     <row r="22" ht="11.5" customHeight="1" s="130">
       <c r="A22" s="159" t="inlineStr">
         <is>
-          <t>김영두</t>
+          <t>이세호</t>
         </is>
       </c>
       <c r="B22" s="160" t="n">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="C22" s="161" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D22" s="162" t="inlineStr">
         <is>
@@ -3143,122 +3165,122 @@
         </is>
       </c>
       <c r="E22" s="163" t="n">
-        <v>204</v>
+        <v>140</v>
       </c>
       <c r="F22" s="164" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G22" s="162" t="inlineStr">
         <is>
-          <t>김순리</t>
+          <t>이준엽</t>
         </is>
       </c>
       <c r="H22" s="163" t="n">
-        <v>190.5</v>
+        <v>130</v>
       </c>
       <c r="I22" s="164" t="n">
-        <v>34.5</v>
+        <v>26</v>
       </c>
       <c r="J22" s="162" t="inlineStr">
         <is>
-          <t>이준엽</t>
+          <t>최광일</t>
         </is>
       </c>
       <c r="K22" s="163" t="n">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="L22" s="164" t="n">
-        <v>17</v>
-      </c>
-      <c r="M22" s="162" t="inlineStr">
-        <is>
-          <t>이차영</t>
-        </is>
-      </c>
-      <c r="N22" s="163" t="n">
-        <v>168</v>
-      </c>
-      <c r="O22" s="164" t="n">
-        <v>12</v>
-      </c>
-      <c r="P22" s="162" t="inlineStr">
-        <is>
-          <t>정현수</t>
-        </is>
-      </c>
-      <c r="Q22" s="163" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="R22" s="164" t="n">
-        <v>1.5</v>
+        <v>27</v>
+      </c>
+      <c r="M22" s="165" t="inlineStr">
+        <is>
+          <t>이은하</t>
+        </is>
+      </c>
+      <c r="N22" s="166" t="n">
+        <v>122</v>
+      </c>
+      <c r="O22" s="167" t="n">
+        <v>34</v>
+      </c>
+      <c r="P22" s="165" t="inlineStr">
+        <is>
+          <t>이지연</t>
+        </is>
+      </c>
+      <c r="Q22" s="166" t="n">
+        <v>116</v>
+      </c>
+      <c r="R22" s="167" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="23" ht="11.5" customHeight="1" s="130">
       <c r="A23" s="159" t="inlineStr">
         <is>
-          <t>이세호</t>
+          <t>문석</t>
         </is>
       </c>
       <c r="B23" s="160" t="n">
-        <v>249</v>
+        <v>177.5</v>
       </c>
       <c r="C23" s="161" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D23" s="162" t="inlineStr">
         <is>
-          <t>김예순</t>
+          <t>최명필</t>
         </is>
       </c>
       <c r="E23" s="163" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="F23" s="164" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G23" s="162" t="inlineStr">
         <is>
-          <t>신성수</t>
+          <t>전완철</t>
         </is>
       </c>
       <c r="H23" s="163" t="n">
-        <v>189.5</v>
+        <v>130</v>
       </c>
       <c r="I23" s="164" t="n">
-        <v>33.5</v>
+        <v>26</v>
       </c>
       <c r="J23" s="162" t="inlineStr">
         <is>
-          <t>김해경</t>
+          <t>김희빈</t>
         </is>
       </c>
       <c r="K23" s="163" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="L23" s="164" t="n">
-        <v>16</v>
-      </c>
-      <c r="M23" s="162" t="inlineStr">
-        <is>
-          <t>김선희</t>
-        </is>
-      </c>
-      <c r="N23" s="163" t="n">
-        <v>163</v>
-      </c>
-      <c r="O23" s="164" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="162" t="inlineStr">
-        <is>
-          <t>이동기</t>
-        </is>
-      </c>
-      <c r="Q23" s="163" t="n">
-        <v>157</v>
-      </c>
-      <c r="R23" s="164" t="n">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="M23" s="165" t="inlineStr">
+        <is>
+          <t>김필수</t>
+        </is>
+      </c>
+      <c r="N23" s="166" t="n">
+        <v>121</v>
+      </c>
+      <c r="O23" s="167" t="n">
+        <v>35</v>
+      </c>
+      <c r="P23" s="165" t="inlineStr">
+        <is>
+          <t>이차영</t>
+        </is>
+      </c>
+      <c r="Q23" s="166" t="n">
+        <v>115</v>
+      </c>
+      <c r="R23" s="167" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="11.5" customHeight="1" s="130">
@@ -3268,193 +3290,173 @@
         </is>
       </c>
       <c r="B24" s="163" t="n">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="C24" s="164" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D24" s="162" t="inlineStr">
         <is>
-          <t>김영준</t>
+          <t>김해경</t>
         </is>
       </c>
       <c r="E24" s="163" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
       <c r="F24" s="164" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G24" s="162" t="inlineStr">
         <is>
-          <t>김필수</t>
+          <t>김예순</t>
         </is>
       </c>
       <c r="H24" s="163" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="I24" s="164" t="n">
-        <v>31</v>
-      </c>
-      <c r="J24" s="162" t="inlineStr">
-        <is>
-          <t>김명희</t>
-        </is>
-      </c>
-      <c r="K24" s="163" t="n">
-        <v>171</v>
-      </c>
-      <c r="L24" s="164" t="n">
-        <v>15</v>
-      </c>
-      <c r="M24" s="162" t="inlineStr">
-        <is>
-          <t>전경수</t>
-        </is>
-      </c>
-      <c r="N24" s="163" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="O24" s="164" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="134" t="n"/>
-      <c r="Q24" s="134" t="n"/>
-      <c r="R24" s="134" t="n"/>
-    </row>
-    <row r="25" ht="11.5" customHeight="1" s="130">
-      <c r="A25" s="162" t="inlineStr">
-        <is>
-          <t>조영순</t>
-        </is>
-      </c>
-      <c r="B25" s="163" t="n">
-        <v>224.5</v>
-      </c>
-      <c r="C25" s="164" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="D25" s="162" t="inlineStr">
-        <is>
-          <t>최명필</t>
-        </is>
-      </c>
-      <c r="E25" s="163" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="F25" s="164" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G25" s="162" t="inlineStr">
-        <is>
-          <t>최광일</t>
-        </is>
-      </c>
-      <c r="H25" s="163" t="n">
-        <v>185</v>
-      </c>
-      <c r="I25" s="164" t="n">
-        <v>29</v>
-      </c>
-      <c r="J25" s="162" t="inlineStr">
-        <is>
-          <t>김태환</t>
-        </is>
-      </c>
-      <c r="K25" s="163" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="L25" s="164" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M25" s="162" t="inlineStr">
-        <is>
-          <t>박미춘</t>
-        </is>
-      </c>
-      <c r="N25" s="163" t="n">
-        <v>160</v>
-      </c>
-      <c r="O25" s="164" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" s="134" t="n"/>
-      <c r="Q25" s="134" t="n"/>
-      <c r="R25" s="134" t="n"/>
-    </row>
-    <row r="26" ht="14" customHeight="1" s="130">
-      <c r="A26" s="135" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="J24" s="165" t="inlineStr">
+        <is>
+          <t>이준구</t>
+        </is>
+      </c>
+      <c r="K24" s="166" t="n">
+        <v>126</v>
+      </c>
+      <c r="L24" s="167" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" s="165" t="inlineStr">
+        <is>
+          <t>박효</t>
+        </is>
+      </c>
+      <c r="N24" s="166" t="n">
+        <v>121</v>
+      </c>
+      <c r="O24" s="167" t="n">
+        <v>35</v>
+      </c>
+      <c r="P24" s="165" t="inlineStr">
+        <is>
+          <t>임설희</t>
+        </is>
+      </c>
+      <c r="Q24" s="166" t="n">
+        <v>115</v>
+      </c>
+      <c r="R24" s="167" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1" s="130">
+      <c r="A25" s="135" t="inlineStr">
         <is>
           <t>④ 38주 대응전략 연계 판정</t>
         </is>
       </c>
-      <c r="B26" s="136" t="n"/>
-      <c r="C26" s="136" t="n"/>
-      <c r="D26" s="136" t="n"/>
-      <c r="E26" s="136" t="n"/>
-      <c r="F26" s="136" t="n"/>
-      <c r="G26" s="136" t="n"/>
-      <c r="H26" s="136" t="n"/>
-      <c r="I26" s="136" t="n"/>
-      <c r="J26" s="136" t="n"/>
-      <c r="K26" s="136" t="n"/>
-      <c r="L26" s="136" t="n"/>
-      <c r="M26" s="136" t="n"/>
-      <c r="N26" s="136" t="n"/>
-      <c r="O26" s="136" t="n"/>
-      <c r="P26" s="136" t="n"/>
-      <c r="Q26" s="136" t="n"/>
-      <c r="R26" s="136" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1" s="130">
-      <c r="A27" s="138" t="inlineStr">
+      <c r="B25" s="136" t="n"/>
+      <c r="C25" s="136" t="n"/>
+      <c r="D25" s="136" t="n"/>
+      <c r="E25" s="136" t="n"/>
+      <c r="F25" s="136" t="n"/>
+      <c r="G25" s="136" t="n"/>
+      <c r="H25" s="136" t="n"/>
+      <c r="I25" s="136" t="n"/>
+      <c r="J25" s="136" t="n"/>
+      <c r="K25" s="136" t="n"/>
+      <c r="L25" s="136" t="n"/>
+      <c r="M25" s="136" t="n"/>
+      <c r="N25" s="136" t="n"/>
+      <c r="O25" s="136" t="n"/>
+      <c r="P25" s="136" t="n"/>
+      <c r="Q25" s="136" t="n"/>
+      <c r="R25" s="136" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1" s="130">
+      <c r="A26" s="138" t="inlineStr">
         <is>
           <t>38주 대안</t>
         </is>
       </c>
-      <c r="B27" s="139" t="n"/>
-      <c r="C27" s="139" t="n"/>
-      <c r="D27" s="139" t="n"/>
-      <c r="E27" s="138" t="inlineStr">
+      <c r="B26" s="139" t="n"/>
+      <c r="C26" s="139" t="n"/>
+      <c r="D26" s="139" t="n"/>
+      <c r="E26" s="138" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="F27" s="139" t="n"/>
-      <c r="G27" s="138" t="inlineStr">
+      <c r="F26" s="139" t="n"/>
+      <c r="G26" s="138" t="inlineStr">
         <is>
           <t>근거 (근로시간)</t>
         </is>
       </c>
-      <c r="H27" s="139" t="n"/>
-      <c r="I27" s="139" t="n"/>
-      <c r="J27" s="139" t="n"/>
-      <c r="K27" s="139" t="n"/>
-      <c r="L27" s="139" t="n"/>
-      <c r="M27" s="139" t="n"/>
-      <c r="N27" s="139" t="n"/>
-      <c r="O27" s="139" t="n"/>
-      <c r="P27" s="139" t="n"/>
-      <c r="Q27" s="139" t="n"/>
-      <c r="R27" s="139" t="n"/>
-    </row>
-    <row r="28" ht="14" customHeight="1" s="130">
-      <c r="A28" s="165" t="inlineStr">
+      <c r="H26" s="139" t="n"/>
+      <c r="I26" s="139" t="n"/>
+      <c r="J26" s="139" t="n"/>
+      <c r="K26" s="139" t="n"/>
+      <c r="L26" s="139" t="n"/>
+      <c r="M26" s="139" t="n"/>
+      <c r="N26" s="139" t="n"/>
+      <c r="O26" s="139" t="n"/>
+      <c r="P26" s="139" t="n"/>
+      <c r="Q26" s="139" t="n"/>
+      <c r="R26" s="139" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="130">
+      <c r="A27" s="168" t="inlineStr">
+        <is>
+          <t>[전제] 야간 편성과 근로시간의 관계</t>
+        </is>
+      </c>
+      <c r="B27" s="146" t="n"/>
+      <c r="C27" s="146" t="n"/>
+      <c r="D27" s="146" t="n"/>
+      <c r="E27" s="157" t="inlineStr">
+        <is>
+          <t>구분 필요</t>
+        </is>
+      </c>
+      <c r="F27" s="169" t="n"/>
+      <c r="G27" s="170" t="inlineStr">
+        <is>
+          <t>주야 2조를 각 8H 소정근로로 편성하면 연장근로는 발생하지 않음 — 156H 한도와 무관. 야간은 가산수당 50% · 여성 야간근로 동의(근기법 §70②) · 특수건강진단이 제약. 한도가 걸리는 것은 기존 인원에게 잔업으로 야간을 얹는 경우</t>
+        </is>
+      </c>
+      <c r="H27" s="134" t="n"/>
+      <c r="I27" s="134" t="n"/>
+      <c r="J27" s="134" t="n"/>
+      <c r="K27" s="134" t="n"/>
+      <c r="L27" s="134" t="n"/>
+      <c r="M27" s="134" t="n"/>
+      <c r="N27" s="134" t="n"/>
+      <c r="O27" s="134" t="n"/>
+      <c r="P27" s="134" t="n"/>
+      <c r="Q27" s="134" t="n"/>
+      <c r="R27" s="134" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1" s="130">
+      <c r="A28" s="168" t="inlineStr">
         <is>
           <t>세정 1안) 2대 주야 맞교대</t>
         </is>
       </c>
-      <c r="B28" s="166" t="n"/>
-      <c r="C28" s="166" t="n"/>
-      <c r="D28" s="166" t="n"/>
-      <c r="E28" s="155" t="inlineStr">
-        <is>
-          <t>위반 임박</t>
-        </is>
-      </c>
-      <c r="F28" s="147" t="n"/>
-      <c r="G28" s="167" t="inlineStr">
-        <is>
-          <t>세척실 14명 평균 150.7H 전 공정 최고 · 6명 초과 · 3명(박태근·김영두·이세호) 9월 편성 불가 · 9월 가용 471H</t>
+      <c r="B28" s="146" t="n"/>
+      <c r="C28" s="146" t="n"/>
+      <c r="D28" s="146" t="n"/>
+      <c r="E28" s="157" t="inlineStr">
+        <is>
+          <t>인원 문제</t>
+        </is>
+      </c>
+      <c r="F28" s="169" t="n"/>
+      <c r="G28" s="170" t="inlineStr">
+        <is>
+          <t>별도 조 편성이면 근로시간 한도 아님. 지원 7명 차출 시 원 소속 공백을 잔업으로 메우면 그때 한도가 걸림 — 창고 100H·로봇 101H·내용물 69H는 여유, 세척 59H가 병목</t>
         </is>
       </c>
       <c r="H28" s="134" t="n"/>
@@ -3469,24 +3471,24 @@
       <c r="Q28" s="134" t="n"/>
       <c r="R28" s="134" t="n"/>
     </row>
-    <row r="29" ht="14" customHeight="1" s="130">
-      <c r="A29" s="165" t="inlineStr">
+    <row r="29" ht="17" customHeight="1" s="130">
+      <c r="A29" s="168" t="inlineStr">
         <is>
           <t>세정 2안) 직선 1대 Full 잔특</t>
         </is>
       </c>
-      <c r="B29" s="166" t="n"/>
-      <c r="C29" s="166" t="n"/>
-      <c r="D29" s="166" t="n"/>
-      <c r="E29" s="157" t="inlineStr">
+      <c r="B29" s="146" t="n"/>
+      <c r="C29" s="146" t="n"/>
+      <c r="D29" s="146" t="n"/>
+      <c r="E29" s="158" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
-      <c r="F29" s="168" t="n"/>
-      <c r="G29" s="167" t="inlineStr">
-        <is>
-          <t>직선 24명 1,178H · 염모 27명 1,388H (염모 평균 18.5H, 초과 0명) — 여력 최대</t>
+      <c r="F29" s="171" t="n"/>
+      <c r="G29" s="170" t="inlineStr">
+        <is>
+          <t>순수 잔업·특근이라 잔여 직결. 직선 24명 1,902H(인당 79H) · 염모 27명 3,712H(인당 138H) — 염모 전용이 유리</t>
         </is>
       </c>
       <c r="H29" s="134" t="n"/>
@@ -3501,24 +3503,24 @@
       <c r="Q29" s="134" t="n"/>
       <c r="R29" s="134" t="n"/>
     </row>
-    <row r="30" ht="14" customHeight="1" s="130">
-      <c r="A30" s="165" t="inlineStr">
+    <row r="30" ht="17" customHeight="1" s="130">
+      <c r="A30" s="168" t="inlineStr">
         <is>
           <t>멀티 2안) 7·8호기 주야</t>
         </is>
       </c>
-      <c r="B30" s="166" t="n"/>
-      <c r="C30" s="166" t="n"/>
-      <c r="D30" s="166" t="n"/>
-      <c r="E30" s="158" t="inlineStr">
-        <is>
-          <t>조건부</t>
+      <c r="B30" s="146" t="n"/>
+      <c r="C30" s="146" t="n"/>
+      <c r="D30" s="146" t="n"/>
+      <c r="E30" s="157" t="inlineStr">
+        <is>
+          <t>인원 문제</t>
         </is>
       </c>
       <c r="F30" s="169" t="n"/>
-      <c r="G30" s="167" t="inlineStr">
-        <is>
-          <t>멀티 20명 평균 113.1H · OP 4명(김해경 172·이차영 168·김선희 163·곽옥연 159) 초과 → 제외 편성 시 가능</t>
+      <c r="G30" s="170" t="inlineStr">
+        <is>
+          <t>세정 1안과 동일 구조. 잔업 부가 시 멀티 20명 1,631H(인당 82H), 잔여 50H 미만 4명 제외 편성</t>
         </is>
       </c>
       <c r="H30" s="134" t="n"/>
@@ -3533,24 +3535,24 @@
       <c r="Q30" s="134" t="n"/>
       <c r="R30" s="134" t="n"/>
     </row>
-    <row r="31" ht="14" customHeight="1" s="130">
-      <c r="A31" s="165" t="inlineStr">
+    <row r="31" ht="17" customHeight="1" s="130">
+      <c r="A31" s="168" t="inlineStr">
         <is>
           <t>튜브) 9/14 2Shift 1대 추가</t>
         </is>
       </c>
-      <c r="B31" s="166" t="n"/>
-      <c r="C31" s="166" t="n"/>
-      <c r="D31" s="166" t="n"/>
-      <c r="E31" s="157" t="inlineStr">
+      <c r="B31" s="146" t="n"/>
+      <c r="C31" s="146" t="n"/>
+      <c r="D31" s="146" t="n"/>
+      <c r="E31" s="158" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
-      <c r="F31" s="168" t="n"/>
-      <c r="G31" s="167" t="inlineStr">
-        <is>
-          <t>튜브 17명 평균 110.6H · 9월 가용 814H · 초과 2명(주임·도우미) 제외 시 OP 편성 여력 있음</t>
+      <c r="F31" s="171" t="n"/>
+      <c r="G31" s="170" t="inlineStr">
+        <is>
+          <t>튜브 17명 1,287H(인당 76H) · 잔여 부족 2명(최명필 21H·김진만 24H) 제외 시 여력 있음</t>
         </is>
       </c>
       <c r="H31" s="134" t="n"/>
@@ -3565,24 +3567,24 @@
       <c r="Q31" s="134" t="n"/>
       <c r="R31" s="134" t="n"/>
     </row>
-    <row r="32" ht="14" customHeight="1" s="130">
-      <c r="A32" s="165" t="inlineStr">
+    <row r="32" ht="17" customHeight="1" s="130">
+      <c r="A32" s="168" t="inlineStr">
         <is>
           <t>튜브) 간접(주임) → 직접화</t>
         </is>
       </c>
-      <c r="B32" s="166" t="n"/>
-      <c r="C32" s="166" t="n"/>
-      <c r="D32" s="166" t="n"/>
+      <c r="B32" s="146" t="n"/>
+      <c r="C32" s="146" t="n"/>
+      <c r="D32" s="146" t="n"/>
       <c r="E32" s="155" t="inlineStr">
         <is>
           <t>불가</t>
         </is>
       </c>
-      <c r="F32" s="147" t="n"/>
-      <c r="G32" s="167" t="inlineStr">
-        <is>
-          <t>주임 3명 평균 189.8H 전 직책 최고 · 2명 초과(조영순 224.5·최명필 191.5) · 9월 가용 3명 합 74H</t>
+      <c r="F32" s="148" t="n"/>
+      <c r="G32" s="170" t="inlineStr">
+        <is>
+          <t>관리업무에 직접작업을 더하는 구조라 연장 발생 불가피. 주임 3명 잔여 74H(인당 25H) 전 직책 최저</t>
         </is>
       </c>
       <c r="H32" s="134" t="n"/>
@@ -3597,24 +3599,24 @@
       <c r="Q32" s="134" t="n"/>
       <c r="R32" s="134" t="n"/>
     </row>
-    <row r="33" ht="14" customHeight="1" s="130">
-      <c r="A33" s="165" t="inlineStr">
+    <row r="33" ht="17" customHeight="1" s="130">
+      <c r="A33" s="168" t="inlineStr">
         <is>
           <t>10월 1·2주 연속 특근</t>
         </is>
       </c>
-      <c r="B33" s="166" t="n"/>
-      <c r="C33" s="166" t="n"/>
-      <c r="D33" s="166" t="n"/>
+      <c r="B33" s="146" t="n"/>
+      <c r="C33" s="146" t="n"/>
+      <c r="D33" s="146" t="n"/>
       <c r="E33" s="158" t="inlineStr">
         <is>
-          <t>연동 관리</t>
-        </is>
-      </c>
-      <c r="F33" s="169" t="n"/>
-      <c r="G33" s="167" t="inlineStr">
-        <is>
-          <t>9월 가용 소진 시 10월 구간(8·9·10월) 즉시 한도 도달 → 9월 편성량과 연동. 3안(9/23) 권고</t>
+          <t>한도 여유</t>
+        </is>
+      </c>
+      <c r="F33" s="171" t="n"/>
+      <c r="G33" s="170" t="inlineStr">
+        <is>
+          <t>10월부터 새 단위기간(10·11·12월) → 156H 리셋되어 근로시간 한도로는 막히지 않음. 남는 제약은 휴일근로 동의 · 가산수당 · 추석 직후 3주 연속 무휴 피로도 → 3안(9/23) 권고</t>
         </is>
       </c>
       <c r="H33" s="134" t="n"/>
@@ -3632,7 +3634,7 @@
     <row r="34" ht="14" customHeight="1" s="130">
       <c r="A34" s="135" t="inlineStr">
         <is>
-          <t>⑤ 원본 수식 확인 필요</t>
+          <t>⑤ 9월 토요 특근 시나리오 — 잔여 대비 소요</t>
         </is>
       </c>
       <c r="B34" s="136" t="n"/>
@@ -3653,127 +3655,412 @@
       <c r="Q34" s="136" t="n"/>
       <c r="R34" s="136" t="n"/>
     </row>
-    <row r="35" ht="13" customHeight="1" s="130">
-      <c r="A35" s="170" t="inlineStr">
-        <is>
-          <t>업무 I91</t>
-        </is>
-      </c>
-      <c r="B35" s="166" t="n"/>
-      <c r="C35" s="166" t="n"/>
-      <c r="D35" s="171" t="inlineStr">
-        <is>
-          <t>8월 합계가 수식이 아닌 값 2,578. 실제 합 2,569 (9H 차이) · J91(7,680)과 불일치 → =SUM(I3:I90)</t>
-        </is>
-      </c>
-      <c r="E35" s="134" t="n"/>
-      <c r="F35" s="134" t="n"/>
-      <c r="G35" s="134" t="n"/>
-      <c r="H35" s="134" t="n"/>
-      <c r="I35" s="134" t="n"/>
-      <c r="J35" s="134" t="n"/>
-      <c r="K35" s="134" t="n"/>
-      <c r="L35" s="134" t="n"/>
-      <c r="M35" s="134" t="n"/>
-      <c r="N35" s="134" t="n"/>
-      <c r="O35" s="134" t="n"/>
-      <c r="P35" s="134" t="n"/>
-      <c r="Q35" s="134" t="n"/>
-      <c r="R35" s="134" t="n"/>
+    <row r="35" ht="15" customHeight="1" s="130">
+      <c r="A35" s="138" t="inlineStr">
+        <is>
+          <t>특근 횟수</t>
+        </is>
+      </c>
+      <c r="B35" s="139" t="n"/>
+      <c r="C35" s="139" t="n"/>
+      <c r="D35" s="138" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="E35" s="139" t="n"/>
+      <c r="F35" s="139" t="n"/>
+      <c r="G35" s="138" t="inlineStr">
+        <is>
+          <t>인당 소요</t>
+        </is>
+      </c>
+      <c r="H35" s="138" t="inlineStr">
+        <is>
+          <t>전사 소요(H)</t>
+        </is>
+      </c>
+      <c r="I35" s="139" t="n"/>
+      <c r="J35" s="138" t="inlineStr">
+        <is>
+          <t>잔여 대비</t>
+        </is>
+      </c>
+      <c r="K35" s="138" t="inlineStr">
+        <is>
+          <t>편성 불가</t>
+        </is>
+      </c>
+      <c r="L35" s="139" t="n"/>
+      <c r="M35" s="138" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="N35" s="139" t="n"/>
+      <c r="O35" s="139" t="n"/>
+      <c r="P35" s="139" t="n"/>
+      <c r="Q35" s="139" t="n"/>
+      <c r="R35" s="139" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1" s="130">
-      <c r="A36" s="170" t="inlineStr">
-        <is>
-          <t>업무 M3</t>
-        </is>
-      </c>
-      <c r="B36" s="166" t="n"/>
-      <c r="C36" s="166" t="n"/>
-      <c r="D36" s="171">
-        <f>COUNTIF(J3:J153,"&gt;156") 범위에 합계행 J91(7,680) 포함되어 17명. 실제 16명 → 범위 J3:J90</f>
-        <v/>
+      <c r="A36" s="140" t="inlineStr">
+        <is>
+          <t>1회</t>
+        </is>
+      </c>
+      <c r="B36" s="146" t="n"/>
+      <c r="C36" s="146" t="n"/>
+      <c r="D36" s="172" t="inlineStr">
+        <is>
+          <t>9/5</t>
+        </is>
       </c>
       <c r="E36" s="134" t="n"/>
       <c r="F36" s="134" t="n"/>
-      <c r="G36" s="134" t="n"/>
-      <c r="H36" s="134" t="n"/>
+      <c r="G36" s="172" t="inlineStr">
+        <is>
+          <t>8H</t>
+        </is>
+      </c>
+      <c r="H36" s="141" t="n">
+        <v>1912</v>
+      </c>
       <c r="I36" s="134" t="n"/>
-      <c r="J36" s="134" t="n"/>
-      <c r="K36" s="134" t="n"/>
+      <c r="J36" s="173" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K36" s="174" t="inlineStr">
+        <is>
+          <t>6명</t>
+        </is>
+      </c>
       <c r="L36" s="134" t="n"/>
-      <c r="M36" s="134" t="n"/>
-      <c r="N36" s="134" t="n"/>
-      <c r="O36" s="134" t="n"/>
-      <c r="P36" s="134" t="n"/>
-      <c r="Q36" s="134" t="n"/>
-      <c r="R36" s="134" t="n"/>
+      <c r="M36" s="175" t="inlineStr">
+        <is>
+          <t>여유</t>
+        </is>
+      </c>
+      <c r="N36" s="171" t="n"/>
+      <c r="O36" s="171" t="n"/>
+      <c r="P36" s="171" t="n"/>
+      <c r="Q36" s="171" t="n"/>
+      <c r="R36" s="171" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1" s="130">
-      <c r="A37" s="170" t="inlineStr">
-        <is>
-          <t>업무 L3 / 생산 Q3</t>
-        </is>
-      </c>
-      <c r="B37" s="166" t="n"/>
-      <c r="C37" s="166" t="n"/>
-      <c r="D37" s="171">
-        <f>52*3. 값 156은 맞으나 연장 한도는 주 12H → =12*13이 정확한 근거 (생산 R3 COUNTIF는 정상)</f>
-        <v/>
+      <c r="A37" s="140" t="inlineStr">
+        <is>
+          <t>2회</t>
+        </is>
+      </c>
+      <c r="B37" s="146" t="n"/>
+      <c r="C37" s="146" t="n"/>
+      <c r="D37" s="172" t="inlineStr">
+        <is>
+          <t>9/5 · 12</t>
+        </is>
       </c>
       <c r="E37" s="134" t="n"/>
       <c r="F37" s="134" t="n"/>
-      <c r="G37" s="134" t="n"/>
-      <c r="H37" s="134" t="n"/>
+      <c r="G37" s="172" t="inlineStr">
+        <is>
+          <t>16H</t>
+        </is>
+      </c>
+      <c r="H37" s="141" t="n">
+        <v>3824</v>
+      </c>
       <c r="I37" s="134" t="n"/>
-      <c r="J37" s="134" t="n"/>
-      <c r="K37" s="134" t="n"/>
+      <c r="J37" s="173" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="K37" s="174" t="inlineStr">
+        <is>
+          <t>7명</t>
+        </is>
+      </c>
       <c r="L37" s="134" t="n"/>
-      <c r="M37" s="134" t="n"/>
-      <c r="N37" s="134" t="n"/>
-      <c r="O37" s="134" t="n"/>
-      <c r="P37" s="134" t="n"/>
-      <c r="Q37" s="134" t="n"/>
-      <c r="R37" s="134" t="n"/>
+      <c r="M37" s="175" t="inlineStr">
+        <is>
+          <t>여유</t>
+        </is>
+      </c>
+      <c r="N37" s="171" t="n"/>
+      <c r="O37" s="171" t="n"/>
+      <c r="P37" s="171" t="n"/>
+      <c r="Q37" s="171" t="n"/>
+      <c r="R37" s="171" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1" s="130">
+      <c r="A38" s="140" t="inlineStr">
+        <is>
+          <t>3회</t>
+        </is>
+      </c>
+      <c r="B38" s="146" t="n"/>
+      <c r="C38" s="146" t="n"/>
+      <c r="D38" s="172" t="inlineStr">
+        <is>
+          <t>9/5 · 12 · 19</t>
+        </is>
+      </c>
+      <c r="E38" s="134" t="n"/>
+      <c r="F38" s="134" t="n"/>
+      <c r="G38" s="172" t="inlineStr">
+        <is>
+          <t>24H</t>
+        </is>
+      </c>
+      <c r="H38" s="141" t="n">
+        <v>5736</v>
+      </c>
+      <c r="I38" s="134" t="n"/>
+      <c r="J38" s="173" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K38" s="174" t="inlineStr">
+        <is>
+          <t>11명</t>
+        </is>
+      </c>
+      <c r="L38" s="134" t="n"/>
+      <c r="M38" s="175" t="inlineStr">
+        <is>
+          <t>권장 상한 — 세척실 5명(김영두·박태근·이세호·한인수·선우찬) 제외 편성</t>
+        </is>
+      </c>
+      <c r="N38" s="171" t="n"/>
+      <c r="O38" s="171" t="n"/>
+      <c r="P38" s="171" t="n"/>
+      <c r="Q38" s="171" t="n"/>
+      <c r="R38" s="171" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1" s="130">
+      <c r="A39" s="140" t="inlineStr">
+        <is>
+          <t>4회</t>
+        </is>
+      </c>
+      <c r="B39" s="146" t="n"/>
+      <c r="C39" s="146" t="n"/>
+      <c r="D39" s="172" t="inlineStr">
+        <is>
+          <t>+ 9/26 (추석 연휴)</t>
+        </is>
+      </c>
+      <c r="E39" s="134" t="n"/>
+      <c r="F39" s="134" t="n"/>
+      <c r="G39" s="172" t="inlineStr">
+        <is>
+          <t>32H</t>
+        </is>
+      </c>
+      <c r="H39" s="141" t="n">
+        <v>7648</v>
+      </c>
+      <c r="I39" s="134" t="n"/>
+      <c r="J39" s="173" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="K39" s="174" t="inlineStr">
+        <is>
+          <t>22명</t>
+        </is>
+      </c>
+      <c r="L39" s="134" t="n"/>
+      <c r="M39" s="176" t="inlineStr">
+        <is>
+          <t>9/26은 추석 연휴 중 토요일 — 휴일근로 가산·연휴 근무 동의 별도 필요</t>
+        </is>
+      </c>
+      <c r="N39" s="169" t="n"/>
+      <c r="O39" s="169" t="n"/>
+      <c r="P39" s="169" t="n"/>
+      <c r="Q39" s="169" t="n"/>
+      <c r="R39" s="169" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1" s="130">
+      <c r="A40" s="135" t="inlineStr">
+        <is>
+          <t>⑥ 원본 수식 확인 필요</t>
+        </is>
+      </c>
+      <c r="B40" s="136" t="n"/>
+      <c r="C40" s="136" t="n"/>
+      <c r="D40" s="136" t="n"/>
+      <c r="E40" s="136" t="n"/>
+      <c r="F40" s="136" t="n"/>
+      <c r="G40" s="136" t="n"/>
+      <c r="H40" s="136" t="n"/>
+      <c r="I40" s="136" t="n"/>
+      <c r="J40" s="136" t="n"/>
+      <c r="K40" s="136" t="n"/>
+      <c r="L40" s="136" t="n"/>
+      <c r="M40" s="136" t="n"/>
+      <c r="N40" s="136" t="n"/>
+      <c r="O40" s="136" t="n"/>
+      <c r="P40" s="136" t="n"/>
+      <c r="Q40" s="136" t="n"/>
+      <c r="R40" s="136" t="n"/>
+    </row>
+    <row r="41" ht="12" customHeight="1" s="130">
+      <c r="A41" s="177" t="inlineStr">
+        <is>
+          <t>업무 I91</t>
+        </is>
+      </c>
+      <c r="B41" s="146" t="n"/>
+      <c r="C41" s="146" t="n"/>
+      <c r="D41" s="178" t="inlineStr">
+        <is>
+          <t>8월 합계가 수식이 아닌 값 2,578. 실제 합 2,569 (9H 차이) · J91(7,680)과 불일치 → =SUM(I3:I90)</t>
+        </is>
+      </c>
+      <c r="E41" s="134" t="n"/>
+      <c r="F41" s="134" t="n"/>
+      <c r="G41" s="134" t="n"/>
+      <c r="H41" s="134" t="n"/>
+      <c r="I41" s="134" t="n"/>
+      <c r="J41" s="134" t="n"/>
+      <c r="K41" s="134" t="n"/>
+      <c r="L41" s="134" t="n"/>
+      <c r="M41" s="134" t="n"/>
+      <c r="N41" s="134" t="n"/>
+      <c r="O41" s="134" t="n"/>
+      <c r="P41" s="134" t="n"/>
+      <c r="Q41" s="134" t="n"/>
+      <c r="R41" s="134" t="n"/>
+    </row>
+    <row r="42" ht="12" customHeight="1" s="130">
+      <c r="A42" s="177" t="inlineStr">
+        <is>
+          <t>업무 M3</t>
+        </is>
+      </c>
+      <c r="B42" s="146" t="n"/>
+      <c r="C42" s="146" t="n"/>
+      <c r="D42" s="178">
+        <f>COUNTIF(J3:J153,"&gt;156") 범위에 합계행 J91(7,680) 포함되어 17명. 실제 16명 → 범위 J3:J90</f>
+        <v/>
+      </c>
+      <c r="E42" s="134" t="n"/>
+      <c r="F42" s="134" t="n"/>
+      <c r="G42" s="134" t="n"/>
+      <c r="H42" s="134" t="n"/>
+      <c r="I42" s="134" t="n"/>
+      <c r="J42" s="134" t="n"/>
+      <c r="K42" s="134" t="n"/>
+      <c r="L42" s="134" t="n"/>
+      <c r="M42" s="134" t="n"/>
+      <c r="N42" s="134" t="n"/>
+      <c r="O42" s="134" t="n"/>
+      <c r="P42" s="134" t="n"/>
+      <c r="Q42" s="134" t="n"/>
+      <c r="R42" s="134" t="n"/>
+    </row>
+    <row r="43" ht="12" customHeight="1" s="130">
+      <c r="A43" s="177" t="inlineStr">
+        <is>
+          <t>업무 L3 / 생산 Q3</t>
+        </is>
+      </c>
+      <c r="B43" s="146" t="n"/>
+      <c r="C43" s="146" t="n"/>
+      <c r="D43" s="178">
+        <f>52*3. 값 156은 맞으나 연장 한도는 주 12H → =12*13이 정확한 근거 (생산 R3 COUNTIF는 정상)</f>
+        <v/>
+      </c>
+      <c r="E43" s="134" t="n"/>
+      <c r="F43" s="134" t="n"/>
+      <c r="G43" s="134" t="n"/>
+      <c r="H43" s="134" t="n"/>
+      <c r="I43" s="134" t="n"/>
+      <c r="J43" s="134" t="n"/>
+      <c r="K43" s="134" t="n"/>
+      <c r="L43" s="134" t="n"/>
+      <c r="M43" s="134" t="n"/>
+      <c r="N43" s="134" t="n"/>
+      <c r="O43" s="134" t="n"/>
+      <c r="P43" s="134" t="n"/>
+      <c r="Q43" s="134" t="n"/>
+      <c r="R43" s="134" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="67">
     <mergeCell ref="J6:R6"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A25:R25"/>
+    <mergeCell ref="H38:I38"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="G28:R28"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="D41:R41"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="J4:R4"/>
     <mergeCell ref="A18:R18"/>
     <mergeCell ref="G30:R30"/>
     <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A26:R26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="D43:R43"/>
     <mergeCell ref="J7:R7"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="G33:R33"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="M37:R37"/>
     <mergeCell ref="A30:D30"/>
+    <mergeCell ref="M36:R36"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="D37:R37"/>
+    <mergeCell ref="H36:I36"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A8:R8"/>
+    <mergeCell ref="G26:R26"/>
+    <mergeCell ref="D39:F39"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A38:C38"/>
     <mergeCell ref="G29:R29"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="M38:R38"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="G32:R32"/>
+    <mergeCell ref="D42:R42"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="G31:R31"/>
-    <mergeCell ref="D35:R35"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="K39:L39"/>
     <mergeCell ref="A34:R34"/>
+    <mergeCell ref="A40:R40"/>
     <mergeCell ref="J5:R5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="E32:F32"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="G27:R27"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="K37:L37"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="D36:R36"/>
+    <mergeCell ref="M39:R39"/>
+    <mergeCell ref="M35:R35"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
@@ -3885,16 +4172,16 @@
       <c r="F3" s="58" t="n">
         <v>45901</v>
       </c>
-      <c r="G3" s="172" t="n">
+      <c r="G3" s="179" t="n">
         <v>38</v>
       </c>
-      <c r="H3" s="173" t="n">
+      <c r="H3" s="180" t="n">
         <v>40</v>
       </c>
-      <c r="I3" s="174" t="n">
+      <c r="I3" s="181" t="n">
         <v>31.5</v>
       </c>
-      <c r="J3" s="175">
+      <c r="J3" s="182">
         <f>SUM(G3:I3)</f>
         <v/>
       </c>
@@ -3934,16 +4221,16 @@
       <c r="F4" s="21" t="n">
         <v>44348</v>
       </c>
-      <c r="G4" s="176" t="n">
+      <c r="G4" s="183" t="n">
         <v>21.5</v>
       </c>
-      <c r="H4" s="177" t="n">
+      <c r="H4" s="184" t="n">
         <v>32</v>
       </c>
-      <c r="I4" s="178" t="n">
+      <c r="I4" s="185" t="n">
         <v>13</v>
       </c>
-      <c r="J4" s="179">
+      <c r="J4" s="186">
         <f>SUM(G4:I4)</f>
         <v/>
       </c>
@@ -3975,16 +4262,16 @@
       <c r="F5" s="23" t="n">
         <v>44417</v>
       </c>
-      <c r="G5" s="176" t="n">
+      <c r="G5" s="183" t="n">
         <v>62</v>
       </c>
-      <c r="H5" s="177" t="n">
+      <c r="H5" s="184" t="n">
         <v>43.5</v>
       </c>
-      <c r="I5" s="178" t="n">
+      <c r="I5" s="185" t="n">
         <v>21</v>
       </c>
-      <c r="J5" s="179">
+      <c r="J5" s="186">
         <f>SUM(G5:I5)</f>
         <v/>
       </c>
@@ -4016,16 +4303,16 @@
       <c r="F6" s="23" t="n">
         <v>45264</v>
       </c>
-      <c r="G6" s="176" t="n">
+      <c r="G6" s="183" t="n">
         <v>28</v>
       </c>
-      <c r="H6" s="177" t="n">
+      <c r="H6" s="184" t="n">
         <v>26</v>
       </c>
-      <c r="I6" s="178" t="n">
+      <c r="I6" s="185" t="n">
         <v>17</v>
       </c>
-      <c r="J6" s="179">
+      <c r="J6" s="186">
         <f>SUM(G6:I6)</f>
         <v/>
       </c>
@@ -4057,16 +4344,16 @@
       <c r="F7" s="24" t="n">
         <v>45887</v>
       </c>
-      <c r="G7" s="176" t="n">
+      <c r="G7" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="177" t="n">
+      <c r="H7" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="178" t="n">
+      <c r="I7" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="179">
+      <c r="J7" s="186">
         <f>SUM(G7:I7)</f>
         <v/>
       </c>
@@ -4098,16 +4385,16 @@
       <c r="F8" s="23" t="n">
         <v>45635</v>
       </c>
-      <c r="G8" s="176" t="n">
+      <c r="G8" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="177" t="n">
+      <c r="H8" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="178" t="n">
+      <c r="I8" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="179">
+      <c r="J8" s="186">
         <f>SUM(G8:I8)</f>
         <v/>
       </c>
@@ -4139,16 +4426,16 @@
       <c r="F9" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G9" s="180" t="n">
+      <c r="G9" s="187" t="n">
         <v>19.5</v>
       </c>
-      <c r="H9" s="181" t="n">
+      <c r="H9" s="188" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="178" t="n">
+      <c r="I9" s="185" t="n">
         <v>1.5</v>
       </c>
-      <c r="J9" s="179">
+      <c r="J9" s="186">
         <f>SUM(G9:I9)</f>
         <v/>
       </c>
@@ -4180,16 +4467,16 @@
       <c r="F10" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G10" s="182" t="n">
+      <c r="G10" s="189" t="n">
         <v>49.5</v>
       </c>
-      <c r="H10" s="183" t="n">
+      <c r="H10" s="190" t="n">
         <v>51</v>
       </c>
-      <c r="I10" s="178" t="n">
+      <c r="I10" s="185" t="n">
         <v>52</v>
       </c>
-      <c r="J10" s="179">
+      <c r="J10" s="186">
         <f>SUM(G10:I10)</f>
         <v/>
       </c>
@@ -4221,16 +4508,16 @@
       <c r="F11" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G11" s="180" t="n">
+      <c r="G11" s="187" t="n">
         <v>41.5</v>
       </c>
-      <c r="H11" s="181" t="n">
+      <c r="H11" s="188" t="n">
         <v>41</v>
       </c>
-      <c r="I11" s="178" t="n">
+      <c r="I11" s="185" t="n">
         <v>38</v>
       </c>
-      <c r="J11" s="179">
+      <c r="J11" s="186">
         <f>SUM(G11:I11)</f>
         <v/>
       </c>
@@ -4262,16 +4549,16 @@
       <c r="F12" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G12" s="180" t="n">
+      <c r="G12" s="187" t="n">
         <v>18</v>
       </c>
-      <c r="H12" s="181" t="n">
+      <c r="H12" s="188" t="n">
         <v>32</v>
       </c>
-      <c r="I12" s="178" t="n">
+      <c r="I12" s="185" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="179">
+      <c r="J12" s="186">
         <f>SUM(G12:I12)</f>
         <v/>
       </c>
@@ -4303,20 +4590,20 @@
       <c r="F13" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G13" s="180" t="n">
+      <c r="G13" s="187" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="181" t="n">
+      <c r="H13" s="188" t="n">
         <v>84</v>
       </c>
-      <c r="I13" s="178" t="n">
+      <c r="I13" s="185" t="n">
         <v>94</v>
       </c>
-      <c r="J13" s="179">
+      <c r="J13" s="186">
         <f>SUM(G13:I13)</f>
         <v/>
       </c>
-      <c r="K13" s="184">
+      <c r="K13" s="191">
         <f>J13-$L$3</f>
         <v/>
       </c>
@@ -4347,20 +4634,20 @@
       <c r="F14" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G14" s="180" t="n">
+      <c r="G14" s="187" t="n">
         <v>51</v>
       </c>
-      <c r="H14" s="181" t="n">
+      <c r="H14" s="188" t="n">
         <v>67.5</v>
       </c>
-      <c r="I14" s="178" t="n">
+      <c r="I14" s="185" t="n">
         <v>73.5</v>
       </c>
-      <c r="J14" s="179">
+      <c r="J14" s="186">
         <f>SUM(G14:I14)</f>
         <v/>
       </c>
-      <c r="K14" s="184">
+      <c r="K14" s="191">
         <f>J14-$L$3</f>
         <v/>
       </c>
@@ -4391,16 +4678,16 @@
       <c r="F15" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G15" s="180" t="n">
+      <c r="G15" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="181" t="n">
+      <c r="H15" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="178" t="n">
+      <c r="I15" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="186">
         <f>SUM(G15:I15)</f>
         <v/>
       </c>
@@ -4429,16 +4716,16 @@
       <c r="F16" s="26" t="n">
         <v>46143</v>
       </c>
-      <c r="G16" s="180" t="n">
+      <c r="G16" s="187" t="n">
         <v>44</v>
       </c>
-      <c r="H16" s="181" t="n">
+      <c r="H16" s="188" t="n">
         <v>38</v>
       </c>
-      <c r="I16" s="178" t="n">
+      <c r="I16" s="185" t="n">
         <v>23</v>
       </c>
-      <c r="J16" s="179">
+      <c r="J16" s="186">
         <f>SUM(G16:I16)</f>
         <v/>
       </c>
@@ -4470,16 +4757,16 @@
       <c r="F17" s="23" t="n">
         <v>44805</v>
       </c>
-      <c r="G17" s="176" t="n">
+      <c r="G17" s="183" t="n">
         <v>36</v>
       </c>
-      <c r="H17" s="177" t="n">
+      <c r="H17" s="184" t="n">
         <v>39</v>
       </c>
-      <c r="I17" s="178" t="n">
+      <c r="I17" s="185" t="n">
         <v>41</v>
       </c>
-      <c r="J17" s="179">
+      <c r="J17" s="186">
         <f>SUM(G17:I17)</f>
         <v/>
       </c>
@@ -4511,16 +4798,16 @@
       <c r="F18" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G18" s="180" t="n">
+      <c r="G18" s="187" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="181" t="n">
+      <c r="H18" s="188" t="n">
         <v>16</v>
       </c>
-      <c r="I18" s="178" t="n">
+      <c r="I18" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="179">
+      <c r="J18" s="186">
         <f>SUM(G18:I18)</f>
         <v/>
       </c>
@@ -4552,16 +4839,16 @@
       <c r="F19" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G19" s="180" t="n">
+      <c r="G19" s="187" t="n">
         <v>46.5</v>
       </c>
-      <c r="H19" s="181" t="n">
+      <c r="H19" s="188" t="n">
         <v>33</v>
       </c>
-      <c r="I19" s="178" t="n">
+      <c r="I19" s="185" t="n">
         <v>38.5</v>
       </c>
-      <c r="J19" s="179">
+      <c r="J19" s="186">
         <f>SUM(G19:I19)</f>
         <v/>
       </c>
@@ -4595,16 +4882,16 @@
       <c r="F20" s="23" t="n">
         <v>44652</v>
       </c>
-      <c r="G20" s="176" t="n">
+      <c r="G20" s="183" t="n">
         <v>9.5</v>
       </c>
-      <c r="H20" s="177" t="n">
+      <c r="H20" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I20" s="178" t="n">
+      <c r="I20" s="185" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="179">
+      <c r="J20" s="186">
         <f>SUM(G20:I20)</f>
         <v/>
       </c>
@@ -4636,16 +4923,16 @@
       <c r="F21" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G21" s="180" t="n">
+      <c r="G21" s="187" t="n">
         <v>14</v>
       </c>
-      <c r="H21" s="181" t="n">
+      <c r="H21" s="188" t="n">
         <v>9</v>
       </c>
-      <c r="I21" s="178" t="n">
+      <c r="I21" s="185" t="n">
         <v>12</v>
       </c>
-      <c r="J21" s="179">
+      <c r="J21" s="186">
         <f>SUM(G21:I21)</f>
         <v/>
       </c>
@@ -4677,20 +4964,20 @@
       <c r="F22" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G22" s="182" t="n">
+      <c r="G22" s="189" t="n">
         <v>66</v>
       </c>
-      <c r="H22" s="183" t="n">
+      <c r="H22" s="190" t="n">
         <v>62</v>
       </c>
-      <c r="I22" s="178" t="n">
+      <c r="I22" s="185" t="n">
         <v>59</v>
       </c>
-      <c r="J22" s="179">
+      <c r="J22" s="186">
         <f>SUM(G22:I22)</f>
         <v/>
       </c>
-      <c r="K22" s="184">
+      <c r="K22" s="191">
         <f>J22-$L$3</f>
         <v/>
       </c>
@@ -4721,16 +5008,16 @@
       <c r="F23" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G23" s="182" t="n">
+      <c r="G23" s="189" t="n">
         <v>30.5</v>
       </c>
-      <c r="H23" s="183" t="n">
+      <c r="H23" s="190" t="n">
         <v>32.5</v>
       </c>
-      <c r="I23" s="178" t="n">
+      <c r="I23" s="185" t="n">
         <v>22.5</v>
       </c>
-      <c r="J23" s="179">
+      <c r="J23" s="186">
         <f>SUM(G23:I23)</f>
         <v/>
       </c>
@@ -4762,16 +5049,16 @@
       <c r="F24" s="23" t="n">
         <v>45383</v>
       </c>
-      <c r="G24" s="182" t="n">
+      <c r="G24" s="189" t="n">
         <v>21.5</v>
       </c>
-      <c r="H24" s="183" t="n">
+      <c r="H24" s="190" t="n">
         <v>30.5</v>
       </c>
-      <c r="I24" s="178" t="n">
+      <c r="I24" s="185" t="n">
         <v>18</v>
       </c>
-      <c r="J24" s="179">
+      <c r="J24" s="186">
         <f>SUM(G24:I24)</f>
         <v/>
       </c>
@@ -4803,16 +5090,16 @@
       <c r="F25" s="23" t="n">
         <v>45068</v>
       </c>
-      <c r="G25" s="182" t="n">
+      <c r="G25" s="189" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="183" t="n">
+      <c r="H25" s="190" t="n">
         <v>27</v>
       </c>
-      <c r="I25" s="178" t="n">
+      <c r="I25" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="179">
+      <c r="J25" s="186">
         <f>SUM(G25:I25)</f>
         <v/>
       </c>
@@ -4844,16 +5131,16 @@
       <c r="F26" s="23" t="n">
         <v>44562</v>
       </c>
-      <c r="G26" s="182" t="n">
+      <c r="G26" s="189" t="n">
         <v>21</v>
       </c>
-      <c r="H26" s="183" t="n">
+      <c r="H26" s="190" t="n">
         <v>20.5</v>
       </c>
-      <c r="I26" s="178" t="n">
+      <c r="I26" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="179">
+      <c r="J26" s="186">
         <f>SUM(G26:I26)</f>
         <v/>
       </c>
@@ -4887,16 +5174,16 @@
       <c r="F27" s="23" t="n">
         <v>44896</v>
       </c>
-      <c r="G27" s="182" t="n">
+      <c r="G27" s="189" t="n">
         <v>18.5</v>
       </c>
-      <c r="H27" s="183" t="n">
+      <c r="H27" s="190" t="n">
         <v>23.5</v>
       </c>
-      <c r="I27" s="178" t="n">
+      <c r="I27" s="185" t="n">
         <v>16</v>
       </c>
-      <c r="J27" s="179">
+      <c r="J27" s="186">
         <f>SUM(G27:I27)</f>
         <v/>
       </c>
@@ -4928,20 +5215,20 @@
       <c r="F28" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G28" s="176" t="n">
+      <c r="G28" s="183" t="n">
         <v>49</v>
       </c>
-      <c r="H28" s="177" t="n">
+      <c r="H28" s="184" t="n">
         <v>71.5</v>
       </c>
-      <c r="I28" s="178" t="n">
+      <c r="I28" s="185" t="n">
         <v>39.5</v>
       </c>
-      <c r="J28" s="179">
+      <c r="J28" s="186">
         <f>SUM(G28:I28)</f>
         <v/>
       </c>
-      <c r="K28" s="184">
+      <c r="K28" s="191">
         <f>J28-$L$3</f>
         <v/>
       </c>
@@ -4972,16 +5259,16 @@
       <c r="F29" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G29" s="180" t="n">
+      <c r="G29" s="187" t="n">
         <v>25</v>
       </c>
-      <c r="H29" s="181" t="n">
+      <c r="H29" s="188" t="n">
         <v>18</v>
       </c>
-      <c r="I29" s="178" t="n">
+      <c r="I29" s="185" t="n">
         <v>26</v>
       </c>
-      <c r="J29" s="179">
+      <c r="J29" s="186">
         <f>SUM(G29:I29)</f>
         <v/>
       </c>
@@ -5013,16 +5300,16 @@
       <c r="F30" s="24" t="n">
         <v>45754</v>
       </c>
-      <c r="G30" s="180" t="n">
+      <c r="G30" s="187" t="n">
         <v>8</v>
       </c>
-      <c r="H30" s="181" t="n">
+      <c r="H30" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="178" t="n">
+      <c r="I30" s="185" t="n">
         <v>2.5</v>
       </c>
-      <c r="J30" s="179">
+      <c r="J30" s="186">
         <f>SUM(G30:I30)</f>
         <v/>
       </c>
@@ -5054,16 +5341,16 @@
       <c r="F31" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G31" s="180" t="n">
+      <c r="G31" s="187" t="n">
         <v>6</v>
       </c>
-      <c r="H31" s="181" t="n">
+      <c r="H31" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="178" t="n">
+      <c r="I31" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="179">
+      <c r="J31" s="186">
         <f>SUM(G31:I31)</f>
         <v/>
       </c>
@@ -5097,16 +5384,16 @@
       <c r="F32" s="24" t="n">
         <v>45200</v>
       </c>
-      <c r="G32" s="180" t="n">
+      <c r="G32" s="187" t="n">
         <v>42</v>
       </c>
-      <c r="H32" s="181" t="n">
+      <c r="H32" s="188" t="n">
         <v>32</v>
       </c>
-      <c r="I32" s="178" t="n">
+      <c r="I32" s="185" t="n">
         <v>38</v>
       </c>
-      <c r="J32" s="179">
+      <c r="J32" s="186">
         <f>SUM(G32:I32)</f>
         <v/>
       </c>
@@ -5138,20 +5425,20 @@
       <c r="F33" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G33" s="180" t="n">
+      <c r="G33" s="187" t="n">
         <v>91</v>
       </c>
-      <c r="H33" s="181" t="n">
+      <c r="H33" s="188" t="n">
         <v>90</v>
       </c>
-      <c r="I33" s="178" t="n">
+      <c r="I33" s="185" t="n">
         <v>108.5</v>
       </c>
-      <c r="J33" s="179">
+      <c r="J33" s="186">
         <f>SUM(G33:I33)</f>
         <v/>
       </c>
-      <c r="K33" s="184">
+      <c r="K33" s="191">
         <f>J33-$L$3</f>
         <v/>
       </c>
@@ -5182,20 +5469,20 @@
       <c r="F34" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G34" s="180" t="n">
+      <c r="G34" s="187" t="n">
         <v>56</v>
       </c>
-      <c r="H34" s="181" t="n">
+      <c r="H34" s="188" t="n">
         <v>60</v>
       </c>
-      <c r="I34" s="178" t="n">
+      <c r="I34" s="185" t="n">
         <v>61</v>
       </c>
-      <c r="J34" s="179">
+      <c r="J34" s="186">
         <f>SUM(G34:I34)</f>
         <v/>
       </c>
-      <c r="K34" s="184">
+      <c r="K34" s="191">
         <f>J34-$L$3</f>
         <v/>
       </c>
@@ -5224,16 +5511,16 @@
       <c r="F35" s="23" t="n">
         <v>45748</v>
       </c>
-      <c r="G35" s="180" t="n">
+      <c r="G35" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="181" t="n">
+      <c r="H35" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="178" t="n">
+      <c r="I35" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="179">
+      <c r="J35" s="186">
         <f>SUM(G35:I35)</f>
         <v/>
       </c>
@@ -5265,16 +5552,16 @@
       <c r="F36" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G36" s="180" t="n">
+      <c r="G36" s="187" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="181" t="n">
+      <c r="H36" s="188" t="n">
         <v>37</v>
       </c>
-      <c r="I36" s="178" t="n">
+      <c r="I36" s="185" t="n">
         <v>45</v>
       </c>
-      <c r="J36" s="179">
+      <c r="J36" s="186">
         <f>SUM(G36:I36)</f>
         <v/>
       </c>
@@ -5306,20 +5593,20 @@
       <c r="F37" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G37" s="180" t="n">
+      <c r="G37" s="187" t="n">
         <v>64</v>
       </c>
-      <c r="H37" s="181" t="n">
+      <c r="H37" s="188" t="n">
         <v>68</v>
       </c>
-      <c r="I37" s="178" t="n">
+      <c r="I37" s="185" t="n">
         <v>72</v>
       </c>
-      <c r="J37" s="179">
+      <c r="J37" s="186">
         <f>SUM(G37:I37)</f>
         <v/>
       </c>
-      <c r="K37" s="184">
+      <c r="K37" s="191">
         <f>J37-$L$3</f>
         <v/>
       </c>
@@ -5350,20 +5637,20 @@
       <c r="F38" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G38" s="180" t="n">
+      <c r="G38" s="187" t="n">
         <v>73.5</v>
       </c>
-      <c r="H38" s="181" t="n">
+      <c r="H38" s="188" t="n">
         <v>69.5</v>
       </c>
-      <c r="I38" s="178" t="n">
+      <c r="I38" s="185" t="n">
         <v>63</v>
       </c>
-      <c r="J38" s="179">
+      <c r="J38" s="186">
         <f>SUM(G38:I38)</f>
         <v/>
       </c>
-      <c r="K38" s="184">
+      <c r="K38" s="191">
         <f>J38-$L$3</f>
         <v/>
       </c>
@@ -5394,16 +5681,16 @@
       <c r="F39" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G39" s="180" t="n">
+      <c r="G39" s="187" t="n">
         <v>61</v>
       </c>
-      <c r="H39" s="181" t="n">
+      <c r="H39" s="188" t="n">
         <v>53</v>
       </c>
-      <c r="I39" s="178" t="n">
+      <c r="I39" s="185" t="n">
         <v>40</v>
       </c>
-      <c r="J39" s="179">
+      <c r="J39" s="186">
         <f>SUM(G39:I39)</f>
         <v/>
       </c>
@@ -5435,20 +5722,20 @@
       <c r="F40" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G40" s="180" t="n">
+      <c r="G40" s="187" t="n">
         <v>60</v>
       </c>
-      <c r="H40" s="181" t="n">
+      <c r="H40" s="188" t="n">
         <v>73</v>
       </c>
-      <c r="I40" s="178" t="n">
+      <c r="I40" s="185" t="n">
         <v>56.5</v>
       </c>
-      <c r="J40" s="179">
+      <c r="J40" s="186">
         <f>SUM(G40:I40)</f>
         <v/>
       </c>
-      <c r="K40" s="184">
+      <c r="K40" s="191">
         <f>J40-$L$3</f>
         <v/>
       </c>
@@ -5481,16 +5768,16 @@
       <c r="F41" s="23" t="n">
         <v>45962</v>
       </c>
-      <c r="G41" s="180" t="n">
+      <c r="G41" s="187" t="n">
         <v>25</v>
       </c>
-      <c r="H41" s="181" t="n">
+      <c r="H41" s="188" t="n">
         <v>36</v>
       </c>
-      <c r="I41" s="178" t="n">
+      <c r="I41" s="185" t="n">
         <v>25</v>
       </c>
-      <c r="J41" s="179">
+      <c r="J41" s="186">
         <f>SUM(G41:I41)</f>
         <v/>
       </c>
@@ -5522,16 +5809,16 @@
       <c r="F42" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G42" s="180" t="n">
+      <c r="G42" s="187" t="n">
         <v>46.5</v>
       </c>
-      <c r="H42" s="181" t="n">
+      <c r="H42" s="188" t="n">
         <v>40.5</v>
       </c>
-      <c r="I42" s="178" t="n">
+      <c r="I42" s="185" t="n">
         <v>42</v>
       </c>
-      <c r="J42" s="179">
+      <c r="J42" s="186">
         <f>SUM(G42:I42)</f>
         <v/>
       </c>
@@ -5563,16 +5850,16 @@
       <c r="F43" s="23" t="n">
         <v>44991</v>
       </c>
-      <c r="G43" s="180" t="n">
+      <c r="G43" s="187" t="n">
         <v>0.5</v>
       </c>
-      <c r="H43" s="181" t="n">
+      <c r="H43" s="188" t="n">
         <v>25.5</v>
       </c>
-      <c r="I43" s="178" t="n">
+      <c r="I43" s="185" t="n">
         <v>14.5</v>
       </c>
-      <c r="J43" s="179">
+      <c r="J43" s="186">
         <f>SUM(G43:I43)</f>
         <v/>
       </c>
@@ -5604,16 +5891,16 @@
       <c r="F44" s="23" t="n">
         <v>44229</v>
       </c>
-      <c r="G44" s="176" t="n">
+      <c r="G44" s="183" t="n">
         <v>9.5</v>
       </c>
-      <c r="H44" s="177" t="n">
+      <c r="H44" s="184" t="n">
         <v>15.5</v>
       </c>
-      <c r="I44" s="178" t="n">
+      <c r="I44" s="185" t="n">
         <v>6.5</v>
       </c>
-      <c r="J44" s="179">
+      <c r="J44" s="186">
         <f>SUM(G44:I44)</f>
         <v/>
       </c>
@@ -5645,16 +5932,16 @@
       <c r="F45" s="21" t="n">
         <v>44621</v>
       </c>
-      <c r="G45" s="176" t="n">
+      <c r="G45" s="183" t="n">
         <v>8</v>
       </c>
-      <c r="H45" s="177" t="n">
+      <c r="H45" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="178" t="n">
+      <c r="I45" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="179">
+      <c r="J45" s="186">
         <f>SUM(G45:I45)</f>
         <v/>
       </c>
@@ -5675,16 +5962,16 @@
       <c r="F46" s="21" t="n">
         <v>46235</v>
       </c>
-      <c r="G46" s="176" t="n">
+      <c r="G46" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="177" t="n">
+      <c r="H46" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="178" t="n">
+      <c r="I46" s="185" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="179">
+      <c r="J46" s="186">
         <f>SUM(G46:I46)</f>
         <v/>
       </c>
@@ -5716,16 +6003,16 @@
       <c r="F47" s="21" t="n">
         <v>44348</v>
       </c>
-      <c r="G47" s="176" t="n">
+      <c r="G47" s="183" t="n">
         <v>36</v>
       </c>
-      <c r="H47" s="177" t="n">
+      <c r="H47" s="184" t="n">
         <v>39</v>
       </c>
-      <c r="I47" s="178" t="n">
+      <c r="I47" s="185" t="n">
         <v>41</v>
       </c>
-      <c r="J47" s="179">
+      <c r="J47" s="186">
         <f>SUM(G47:I47)</f>
         <v/>
       </c>
@@ -5757,16 +6044,16 @@
       <c r="F48" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G48" s="180" t="n">
+      <c r="G48" s="187" t="n">
         <v>16.5</v>
       </c>
-      <c r="H48" s="181" t="n">
+      <c r="H48" s="188" t="n">
         <v>16</v>
       </c>
-      <c r="I48" s="178" t="n">
+      <c r="I48" s="185" t="n">
         <v>24</v>
       </c>
-      <c r="J48" s="179">
+      <c r="J48" s="186">
         <f>SUM(G48:I48)</f>
         <v/>
       </c>
@@ -5800,16 +6087,16 @@
       <c r="F49" s="21" t="n">
         <v>44927</v>
       </c>
-      <c r="G49" s="176" t="n">
+      <c r="G49" s="183" t="n">
         <v>20.5</v>
       </c>
-      <c r="H49" s="177" t="n">
+      <c r="H49" s="184" t="n">
         <v>33</v>
       </c>
-      <c r="I49" s="178" t="n">
+      <c r="I49" s="185" t="n">
         <v>20</v>
       </c>
-      <c r="J49" s="179">
+      <c r="J49" s="186">
         <f>SUM(G49:I49)</f>
         <v/>
       </c>
@@ -5839,16 +6126,16 @@
       <c r="F50" s="21" t="n">
         <v>45677</v>
       </c>
-      <c r="G50" s="176" t="n">
+      <c r="G50" s="183" t="n">
         <v>36</v>
       </c>
-      <c r="H50" s="177" t="n">
+      <c r="H50" s="184" t="n">
         <v>29</v>
       </c>
-      <c r="I50" s="178" t="n">
+      <c r="I50" s="185" t="n">
         <v>40</v>
       </c>
-      <c r="J50" s="179">
+      <c r="J50" s="186">
         <f>SUM(G50:I50)</f>
         <v/>
       </c>
@@ -5880,16 +6167,16 @@
       <c r="F51" s="21" t="n">
         <v>46214</v>
       </c>
-      <c r="G51" s="176" t="n">
+      <c r="G51" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="177" t="n">
+      <c r="H51" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="178" t="n">
+      <c r="I51" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="179">
+      <c r="J51" s="186">
         <f>SUM(G51:I51)</f>
         <v/>
       </c>
@@ -5921,20 +6208,20 @@
       <c r="F52" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G52" s="180" t="n">
+      <c r="G52" s="187" t="n">
         <v>61.5</v>
       </c>
-      <c r="H52" s="181" t="n">
+      <c r="H52" s="188" t="n">
         <v>42</v>
       </c>
-      <c r="I52" s="178" t="n">
+      <c r="I52" s="185" t="n">
         <v>53.5</v>
       </c>
-      <c r="J52" s="179">
+      <c r="J52" s="186">
         <f>SUM(G52:I52)</f>
         <v/>
       </c>
-      <c r="K52" s="184">
+      <c r="K52" s="191">
         <f>J52-$L$3</f>
         <v/>
       </c>
@@ -5965,16 +6252,16 @@
       <c r="F53" s="21" t="n">
         <v>44197</v>
       </c>
-      <c r="G53" s="180" t="n">
+      <c r="G53" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="181" t="n">
+      <c r="H53" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="178" t="n">
+      <c r="I53" s="185" t="n">
         <v>17</v>
       </c>
-      <c r="J53" s="179">
+      <c r="J53" s="186">
         <f>SUM(G53:I53)</f>
         <v/>
       </c>
@@ -6002,16 +6289,16 @@
       <c r="F54" s="21" t="n">
         <v>46062</v>
       </c>
-      <c r="G54" s="180" t="n">
+      <c r="G54" s="187" t="n">
         <v>39.5</v>
       </c>
-      <c r="H54" s="181" t="n">
+      <c r="H54" s="188" t="n">
         <v>32</v>
       </c>
-      <c r="I54" s="178" t="n">
+      <c r="I54" s="185" t="n">
         <v>33</v>
       </c>
-      <c r="J54" s="179">
+      <c r="J54" s="186">
         <f>SUM(G54:I54)</f>
         <v/>
       </c>
@@ -6045,20 +6332,20 @@
       <c r="F55" s="24" t="n">
         <v>45139</v>
       </c>
-      <c r="G55" s="180" t="n">
+      <c r="G55" s="187" t="n">
         <v>76</v>
       </c>
-      <c r="H55" s="181" t="n">
+      <c r="H55" s="188" t="n">
         <v>81</v>
       </c>
-      <c r="I55" s="178" t="n">
+      <c r="I55" s="185" t="n">
         <v>92</v>
       </c>
-      <c r="J55" s="179">
+      <c r="J55" s="186">
         <f>SUM(G55:I55)</f>
         <v/>
       </c>
-      <c r="K55" s="184">
+      <c r="K55" s="191">
         <f>J55-$L$3</f>
         <v/>
       </c>
@@ -6089,16 +6376,16 @@
       <c r="F56" s="24" t="n">
         <v>45817</v>
       </c>
-      <c r="G56" s="180" t="n">
+      <c r="G56" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="181" t="n">
+      <c r="H56" s="188" t="n">
         <v>8</v>
       </c>
-      <c r="I56" s="178" t="n">
+      <c r="I56" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J56" s="179">
+      <c r="J56" s="186">
         <f>SUM(G56:I56)</f>
         <v/>
       </c>
@@ -6130,16 +6417,16 @@
       <c r="F57" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G57" s="180" t="n">
+      <c r="G57" s="187" t="n">
         <v>42</v>
       </c>
-      <c r="H57" s="181" t="n">
+      <c r="H57" s="188" t="n">
         <v>47</v>
       </c>
-      <c r="I57" s="178" t="n">
+      <c r="I57" s="185" t="n">
         <v>43</v>
       </c>
-      <c r="J57" s="179">
+      <c r="J57" s="186">
         <f>SUM(G57:I57)</f>
         <v/>
       </c>
@@ -6173,16 +6460,16 @@
       <c r="F58" s="24" t="n">
         <v>46023</v>
       </c>
-      <c r="G58" s="176" t="n">
+      <c r="G58" s="183" t="n">
         <v>33</v>
       </c>
-      <c r="H58" s="177" t="n">
+      <c r="H58" s="184" t="n">
         <v>37</v>
       </c>
-      <c r="I58" s="178" t="n">
+      <c r="I58" s="185" t="n">
         <v>41</v>
       </c>
-      <c r="J58" s="179">
+      <c r="J58" s="186">
         <f>SUM(G58:I58)</f>
         <v/>
       </c>
@@ -6216,16 +6503,16 @@
       <c r="F59" s="23" t="n">
         <v>44562</v>
       </c>
-      <c r="G59" s="176" t="n">
+      <c r="G59" s="183" t="n">
         <v>19</v>
       </c>
-      <c r="H59" s="177" t="n">
+      <c r="H59" s="184" t="n">
         <v>12</v>
       </c>
-      <c r="I59" s="178" t="n">
+      <c r="I59" s="185" t="n">
         <v>11</v>
       </c>
-      <c r="J59" s="179">
+      <c r="J59" s="186">
         <f>SUM(G59:I59)</f>
         <v/>
       </c>
@@ -6259,16 +6546,16 @@
       <c r="F60" s="23" t="n">
         <v>45231</v>
       </c>
-      <c r="G60" s="180" t="n">
+      <c r="G60" s="187" t="n">
         <v>57.5</v>
       </c>
-      <c r="H60" s="181" t="n">
+      <c r="H60" s="188" t="n">
         <v>36</v>
       </c>
-      <c r="I60" s="178" t="n">
+      <c r="I60" s="185" t="n">
         <v>44.5</v>
       </c>
-      <c r="J60" s="179">
+      <c r="J60" s="186">
         <f>SUM(G60:I60)</f>
         <v/>
       </c>
@@ -6300,20 +6587,20 @@
       <c r="F61" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G61" s="180" t="n">
+      <c r="G61" s="187" t="n">
         <v>64.5</v>
       </c>
-      <c r="H61" s="181" t="n">
+      <c r="H61" s="188" t="n">
         <v>55</v>
       </c>
-      <c r="I61" s="178" t="n">
+      <c r="I61" s="185" t="n">
         <v>71</v>
       </c>
-      <c r="J61" s="179">
+      <c r="J61" s="186">
         <f>SUM(G61:I61)</f>
         <v/>
       </c>
-      <c r="K61" s="184">
+      <c r="K61" s="191">
         <f>J61-$L$3</f>
         <v/>
       </c>
@@ -6346,20 +6633,20 @@
       <c r="F62" s="23" t="n">
         <v>45992</v>
       </c>
-      <c r="G62" s="180" t="n">
+      <c r="G62" s="187" t="n">
         <v>43</v>
       </c>
-      <c r="H62" s="181" t="n">
+      <c r="H62" s="188" t="n">
         <v>58</v>
       </c>
-      <c r="I62" s="178" t="n">
+      <c r="I62" s="185" t="n">
         <v>72</v>
       </c>
-      <c r="J62" s="179">
+      <c r="J62" s="186">
         <f>SUM(G62:I62)</f>
         <v/>
       </c>
-      <c r="K62" s="184">
+      <c r="K62" s="191">
         <f>J62-$L$3</f>
         <v/>
       </c>
@@ -6386,16 +6673,16 @@
       <c r="F63" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G63" s="180" t="n">
+      <c r="G63" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="181" t="n">
+      <c r="H63" s="188" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="178" t="n">
+      <c r="I63" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="179">
+      <c r="J63" s="186">
         <f>SUM(G63:I63)</f>
         <v/>
       </c>
@@ -6427,16 +6714,16 @@
       <c r="F64" s="23" t="n">
         <v>44879</v>
       </c>
-      <c r="G64" s="180" t="n">
+      <c r="G64" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="181" t="n">
+      <c r="H64" s="188" t="n">
         <v>8</v>
       </c>
-      <c r="I64" s="178" t="n">
+      <c r="I64" s="185" t="n">
         <v>8</v>
       </c>
-      <c r="J64" s="179">
+      <c r="J64" s="186">
         <f>SUM(G64:I64)</f>
         <v/>
       </c>
@@ -6468,16 +6755,16 @@
       <c r="F65" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G65" s="180" t="n">
+      <c r="G65" s="187" t="n">
         <v>18.5</v>
       </c>
-      <c r="H65" s="181" t="n">
+      <c r="H65" s="188" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="178" t="n">
+      <c r="I65" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="179">
+      <c r="J65" s="186">
         <f>SUM(G65:I65)</f>
         <v/>
       </c>
@@ -6511,16 +6798,16 @@
       <c r="F66" s="24" t="n">
         <v>44652</v>
       </c>
-      <c r="G66" s="180" t="n">
+      <c r="G66" s="187" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="181" t="n">
+      <c r="H66" s="188" t="n">
         <v>26</v>
       </c>
-      <c r="I66" s="178" t="n">
+      <c r="I66" s="185" t="n">
         <v>14</v>
       </c>
-      <c r="J66" s="179">
+      <c r="J66" s="186">
         <f>SUM(G66:I66)</f>
         <v/>
       </c>
@@ -6552,20 +6839,20 @@
       <c r="F67" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G67" s="180" t="n">
+      <c r="G67" s="187" t="n">
         <v>48</v>
       </c>
-      <c r="H67" s="181" t="n">
+      <c r="H67" s="188" t="n">
         <v>54.5</v>
       </c>
-      <c r="I67" s="178" t="n">
+      <c r="I67" s="185" t="n">
         <v>58</v>
       </c>
-      <c r="J67" s="179">
+      <c r="J67" s="186">
         <f>SUM(G67:I67)</f>
         <v/>
       </c>
-      <c r="K67" s="184">
+      <c r="K67" s="191">
         <f>J67-$L$3</f>
         <v/>
       </c>
@@ -6587,16 +6874,16 @@
           <t>2026-07-0</t>
         </is>
       </c>
-      <c r="G68" s="176" t="n">
+      <c r="G68" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="181" t="n">
+      <c r="H68" s="188" t="n">
         <v>11</v>
       </c>
-      <c r="I68" s="178" t="n">
+      <c r="I68" s="185" t="n">
         <v>9</v>
       </c>
-      <c r="J68" s="179">
+      <c r="J68" s="186">
         <f>SUM(G68:I68)</f>
         <v/>
       </c>
@@ -6628,16 +6915,16 @@
       <c r="F69" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G69" s="180" t="n">
+      <c r="G69" s="187" t="n">
         <v>44.5</v>
       </c>
-      <c r="H69" s="181" t="n">
+      <c r="H69" s="188" t="n">
         <v>51</v>
       </c>
-      <c r="I69" s="178" t="n">
+      <c r="I69" s="185" t="n">
         <v>59.5</v>
       </c>
-      <c r="J69" s="179">
+      <c r="J69" s="186">
         <f>SUM(G69:I69)</f>
         <v/>
       </c>
@@ -6671,20 +6958,20 @@
       <c r="F70" s="24" t="n">
         <v>45047</v>
       </c>
-      <c r="G70" s="180" t="n">
+      <c r="G70" s="187" t="n">
         <v>87</v>
       </c>
-      <c r="H70" s="181" t="n">
+      <c r="H70" s="188" t="n">
         <v>69</v>
       </c>
-      <c r="I70" s="178" t="n">
+      <c r="I70" s="185" t="n">
         <v>61</v>
       </c>
-      <c r="J70" s="179">
+      <c r="J70" s="186">
         <f>SUM(G70:I70)</f>
         <v/>
       </c>
-      <c r="K70" s="184">
+      <c r="K70" s="191">
         <f>J70-$L$3</f>
         <v/>
       </c>
@@ -6715,16 +7002,16 @@
       <c r="F71" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G71" s="180" t="n">
+      <c r="G71" s="187" t="n">
         <v>10.5</v>
       </c>
-      <c r="H71" s="181" t="n">
+      <c r="H71" s="188" t="n">
         <v>16.5</v>
       </c>
-      <c r="I71" s="178" t="n">
+      <c r="I71" s="185" t="n">
         <v>15.5</v>
       </c>
-      <c r="J71" s="179">
+      <c r="J71" s="186">
         <f>SUM(G71:I71)</f>
         <v/>
       </c>
@@ -6756,16 +7043,16 @@
       <c r="F72" s="21" t="n">
         <v>44200</v>
       </c>
-      <c r="G72" s="176" t="n">
+      <c r="G72" s="183" t="n">
         <v>47</v>
       </c>
-      <c r="H72" s="177" t="n">
+      <c r="H72" s="184" t="n">
         <v>37.5</v>
       </c>
-      <c r="I72" s="178" t="n">
+      <c r="I72" s="185" t="n">
         <v>7</v>
       </c>
-      <c r="J72" s="179">
+      <c r="J72" s="186">
         <f>SUM(G72:I72)</f>
         <v/>
       </c>
@@ -6797,16 +7084,16 @@
       <c r="F73" s="29" t="n">
         <v>44197</v>
       </c>
-      <c r="G73" s="176" t="n">
+      <c r="G73" s="183" t="n">
         <v>18.5</v>
       </c>
-      <c r="H73" s="177" t="n">
+      <c r="H73" s="184" t="n">
         <v>25</v>
       </c>
-      <c r="I73" s="185" t="n">
+      <c r="I73" s="192" t="n">
         <v>25</v>
       </c>
-      <c r="J73" s="179">
+      <c r="J73" s="186">
         <f>SUM(G73:I73)</f>
         <v/>
       </c>
@@ -6827,16 +7114,16 @@
       <c r="F74" s="29" t="n">
         <v>46204</v>
       </c>
-      <c r="G74" s="176" t="n">
+      <c r="G74" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="177" t="n">
+      <c r="H74" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I74" s="178" t="n">
+      <c r="I74" s="185" t="n">
         <v>28</v>
       </c>
-      <c r="J74" s="179">
+      <c r="J74" s="186">
         <f>SUM(G74:I74)</f>
         <v/>
       </c>
@@ -6857,16 +7144,16 @@
       <c r="F75" s="29" t="n">
         <v>46204</v>
       </c>
-      <c r="G75" s="176" t="n">
+      <c r="G75" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="177" t="n">
+      <c r="H75" s="184" t="n">
         <v>47</v>
       </c>
-      <c r="I75" s="178" t="n">
+      <c r="I75" s="185" t="n">
         <v>53</v>
       </c>
-      <c r="J75" s="179">
+      <c r="J75" s="186">
         <f>SUM(G75:I75)</f>
         <v/>
       </c>
@@ -6898,16 +7185,16 @@
       <c r="F76" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G76" s="176" t="n">
+      <c r="G76" s="183" t="n">
         <v>34.5</v>
       </c>
-      <c r="H76" s="177" t="n">
+      <c r="H76" s="184" t="n">
         <v>41.5</v>
       </c>
-      <c r="I76" s="178" t="n">
+      <c r="I76" s="185" t="n">
         <v>47.5</v>
       </c>
-      <c r="J76" s="179">
+      <c r="J76" s="186">
         <f>SUM(G76:I76)</f>
         <v/>
       </c>
@@ -6939,16 +7226,16 @@
       <c r="F77" s="31" t="n">
         <v>44621</v>
       </c>
-      <c r="G77" s="176" t="n">
+      <c r="G77" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="177" t="n">
+      <c r="H77" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I77" s="174" t="n">
+      <c r="I77" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="179">
+      <c r="J77" s="186">
         <f>SUM(G77:I77)</f>
         <v/>
       </c>
@@ -6980,16 +7267,16 @@
       <c r="F78" s="23" t="n">
         <v>44621</v>
       </c>
-      <c r="G78" s="176" t="n">
+      <c r="G78" s="183" t="n">
         <v>8.5</v>
       </c>
-      <c r="H78" s="177" t="n">
+      <c r="H78" s="184" t="n">
         <v>8</v>
       </c>
-      <c r="I78" s="178" t="n">
+      <c r="I78" s="185" t="n">
         <v>24</v>
       </c>
-      <c r="J78" s="179">
+      <c r="J78" s="186">
         <f>SUM(G78:I78)</f>
         <v/>
       </c>
@@ -7023,16 +7310,16 @@
       <c r="F79" s="23" t="n">
         <v>45292</v>
       </c>
-      <c r="G79" s="176" t="n">
+      <c r="G79" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="177" t="n">
+      <c r="H79" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="178" t="n">
+      <c r="I79" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="179">
+      <c r="J79" s="186">
         <f>SUM(G79:I79)</f>
         <v/>
       </c>
@@ -7064,16 +7351,16 @@
       <c r="F80" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G80" s="176" t="n">
+      <c r="G80" s="183" t="n">
         <v>9</v>
       </c>
-      <c r="H80" s="177" t="n">
+      <c r="H80" s="184" t="n">
         <v>26</v>
       </c>
-      <c r="I80" s="178" t="n">
+      <c r="I80" s="185" t="n">
         <v>39</v>
       </c>
-      <c r="J80" s="179">
+      <c r="J80" s="186">
         <f>SUM(G80:I80)</f>
         <v/>
       </c>
@@ -7105,16 +7392,16 @@
       <c r="F81" s="23" t="n">
         <v>45450</v>
       </c>
-      <c r="G81" s="176" t="n">
+      <c r="G81" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="177" t="n">
+      <c r="H81" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="178" t="n">
+      <c r="I81" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="179">
+      <c r="J81" s="186">
         <f>SUM(G81:I81)</f>
         <v/>
       </c>
@@ -7146,16 +7433,16 @@
       <c r="F82" s="23" t="n">
         <v>45536</v>
       </c>
-      <c r="G82" s="176" t="n">
+      <c r="G82" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="177" t="n">
+      <c r="H82" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="178" t="n">
+      <c r="I82" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="179">
+      <c r="J82" s="186">
         <f>SUM(G82:I82)</f>
         <v/>
       </c>
@@ -7184,16 +7471,16 @@
       <c r="F83" s="24" t="n">
         <v>46143</v>
       </c>
-      <c r="G83" s="176" t="n">
+      <c r="G83" s="183" t="n">
         <v>42</v>
       </c>
-      <c r="H83" s="177" t="n">
+      <c r="H83" s="184" t="n">
         <v>50</v>
       </c>
-      <c r="I83" s="178" t="n">
+      <c r="I83" s="185" t="n">
         <v>45</v>
       </c>
-      <c r="J83" s="179">
+      <c r="J83" s="186">
         <f>SUM(G83:I83)</f>
         <v/>
       </c>
@@ -7225,16 +7512,16 @@
       <c r="F84" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G84" s="176" t="n">
+      <c r="G84" s="183" t="n">
         <v>3</v>
       </c>
-      <c r="H84" s="177" t="n">
+      <c r="H84" s="184" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="178" t="n">
+      <c r="I84" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="179">
+      <c r="J84" s="186">
         <f>SUM(G84:I84)</f>
         <v/>
       </c>
@@ -7268,16 +7555,16 @@
       <c r="F85" s="24" t="n">
         <v>45108</v>
       </c>
-      <c r="G85" s="176" t="n">
+      <c r="G85" s="183" t="n">
         <v>20</v>
       </c>
-      <c r="H85" s="177" t="n">
+      <c r="H85" s="184" t="n">
         <v>16</v>
       </c>
-      <c r="I85" s="178" t="n">
+      <c r="I85" s="185" t="n">
         <v>25.5</v>
       </c>
-      <c r="J85" s="179">
+      <c r="J85" s="186">
         <f>SUM(G85:I85)</f>
         <v/>
       </c>
@@ -7309,16 +7596,16 @@
       <c r="F86" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G86" s="176" t="n">
+      <c r="G86" s="183" t="n">
         <v>36</v>
       </c>
-      <c r="H86" s="177" t="n">
+      <c r="H86" s="184" t="n">
         <v>39</v>
       </c>
-      <c r="I86" s="178" t="n">
+      <c r="I86" s="185" t="n">
         <v>41</v>
       </c>
-      <c r="J86" s="179">
+      <c r="J86" s="186">
         <f>SUM(G86:I86)</f>
         <v/>
       </c>
@@ -7350,16 +7637,16 @@
       <c r="F87" s="23" t="n">
         <v>45793</v>
       </c>
-      <c r="G87" s="176" t="n">
+      <c r="G87" s="183" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="177" t="n">
+      <c r="H87" s="184" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="178" t="n">
+      <c r="I87" s="185" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="179">
+      <c r="J87" s="186">
         <f>SUM(G87:I87)</f>
         <v/>
       </c>
@@ -7391,20 +7678,20 @@
       <c r="F88" s="23" t="n">
         <v>44197</v>
       </c>
-      <c r="G88" s="176" t="n">
+      <c r="G88" s="183" t="n">
         <v>70</v>
       </c>
-      <c r="H88" s="177" t="n">
+      <c r="H88" s="184" t="n">
         <v>75</v>
       </c>
-      <c r="I88" s="178" t="n">
+      <c r="I88" s="185" t="n">
         <v>80</v>
       </c>
-      <c r="J88" s="179">
+      <c r="J88" s="186">
         <f>SUM(G88:I88)</f>
         <v/>
       </c>
-      <c r="K88" s="184">
+      <c r="K88" s="191">
         <f>J88-$L$3</f>
         <v/>
       </c>
@@ -7435,16 +7722,16 @@
       <c r="F89" s="23" t="n">
         <v>45261</v>
       </c>
-      <c r="G89" s="176" t="n">
+      <c r="G89" s="183" t="n">
         <v>18</v>
       </c>
-      <c r="H89" s="177" t="n">
+      <c r="H89" s="184" t="n">
         <v>14</v>
       </c>
-      <c r="I89" s="178" t="n">
+      <c r="I89" s="185" t="n">
         <v>21.5</v>
       </c>
-      <c r="J89" s="179">
+      <c r="J89" s="186">
         <f>SUM(G89:I89)</f>
         <v/>
       </c>
@@ -7476,16 +7763,16 @@
       <c r="F90" s="33" t="n">
         <v>45261</v>
       </c>
-      <c r="G90" s="186" t="n">
+      <c r="G90" s="193" t="n">
         <v>21</v>
       </c>
-      <c r="H90" s="187" t="n">
+      <c r="H90" s="194" t="n">
         <v>28</v>
       </c>
-      <c r="I90" s="185" t="n">
+      <c r="I90" s="192" t="n">
         <v>29</v>
       </c>
-      <c r="J90" s="188">
+      <c r="J90" s="195">
         <f>SUM(G90:I90)</f>
         <v/>
       </c>
@@ -7510,10 +7797,10 @@
         <f>SUM(H3:H90)</f>
         <v/>
       </c>
-      <c r="I91" s="189" t="n">
+      <c r="I91" s="196" t="n">
         <v>2578</v>
       </c>
-      <c r="J91" s="190">
+      <c r="J91" s="197">
         <f>SUM(J3:J90)</f>
         <v/>
       </c>
@@ -7556,7 +7843,7 @@
     <col width="12.625" customWidth="1" style="71" min="9" max="9"/>
     <col width="11.375" customWidth="1" style="71" min="10" max="10"/>
     <col width="11.125" customWidth="1" style="70" min="11" max="14"/>
-    <col width="9.25" customWidth="1" style="191" min="15" max="16"/>
+    <col width="9.25" customWidth="1" style="198" min="15" max="16"/>
     <col width="8.75" customWidth="1" style="70" min="17" max="16384"/>
   </cols>
   <sheetData>
@@ -8602,13 +8889,13 @@
         <v>45887</v>
       </c>
       <c r="K19" s="81" t="n"/>
-      <c r="L19" s="192" t="n">
+      <c r="L19" s="199" t="n">
         <v>44</v>
       </c>
-      <c r="M19" s="193" t="n">
+      <c r="M19" s="200" t="n">
         <v>42</v>
       </c>
-      <c r="N19" s="192" t="n">
+      <c r="N19" s="199" t="n">
         <v>51</v>
       </c>
       <c r="O19" s="107">
@@ -8660,13 +8947,13 @@
         <v>45536</v>
       </c>
       <c r="K20" s="81" t="n"/>
-      <c r="L20" s="192" t="n">
+      <c r="L20" s="199" t="n">
         <v>28.5</v>
       </c>
-      <c r="M20" s="193" t="n">
+      <c r="M20" s="200" t="n">
         <v>20.5</v>
       </c>
-      <c r="N20" s="192" t="n">
+      <c r="N20" s="199" t="n">
         <v>41</v>
       </c>
       <c r="O20" s="107">
@@ -8718,13 +9005,13 @@
         <v>45536</v>
       </c>
       <c r="K21" s="81" t="n"/>
-      <c r="L21" s="192" t="n">
+      <c r="L21" s="199" t="n">
         <v>45</v>
       </c>
-      <c r="M21" s="193" t="n">
+      <c r="M21" s="200" t="n">
         <v>63</v>
       </c>
-      <c r="N21" s="192" t="n">
+      <c r="N21" s="199" t="n">
         <v>63</v>
       </c>
       <c r="O21" s="107">
@@ -8779,13 +9066,13 @@
         <v>45536</v>
       </c>
       <c r="K22" s="81" t="n"/>
-      <c r="L22" s="192" t="n">
+      <c r="L22" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M22" s="193" t="n">
+      <c r="M22" s="200" t="n">
         <v>47</v>
       </c>
-      <c r="N22" s="192" t="n">
+      <c r="N22" s="199" t="n">
         <v>63</v>
       </c>
       <c r="O22" s="107">
@@ -8840,13 +9127,13 @@
         <v>45536</v>
       </c>
       <c r="K23" s="81" t="n"/>
-      <c r="L23" s="192" t="n">
+      <c r="L23" s="199" t="n">
         <v>43</v>
       </c>
-      <c r="M23" s="193" t="n">
+      <c r="M23" s="200" t="n">
         <v>58</v>
       </c>
-      <c r="N23" s="192" t="n">
+      <c r="N23" s="199" t="n">
         <v>44</v>
       </c>
       <c r="O23" s="107">
@@ -8891,13 +9178,13 @@
         <v>44571</v>
       </c>
       <c r="K24" s="81" t="n"/>
-      <c r="L24" s="192" t="n">
+      <c r="L24" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="193" t="n">
+      <c r="M24" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="192" t="n">
+      <c r="N24" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="107">
@@ -8949,13 +9236,13 @@
         <v>45536</v>
       </c>
       <c r="K25" s="81" t="n"/>
-      <c r="L25" s="192" t="n">
+      <c r="L25" s="199" t="n">
         <v>32</v>
       </c>
-      <c r="M25" s="193" t="n">
+      <c r="M25" s="200" t="n">
         <v>10.5</v>
       </c>
-      <c r="N25" s="192" t="n">
+      <c r="N25" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="107">
@@ -9007,13 +9294,13 @@
         <v>45536</v>
       </c>
       <c r="K26" s="81" t="n"/>
-      <c r="L26" s="192" t="n">
+      <c r="L26" s="199" t="n">
         <v>65</v>
       </c>
-      <c r="M26" s="193" t="n">
+      <c r="M26" s="200" t="n">
         <v>71.5</v>
       </c>
-      <c r="N26" s="192" t="n">
+      <c r="N26" s="199" t="n">
         <v>54</v>
       </c>
       <c r="O26" s="107">
@@ -9068,13 +9355,13 @@
         <v>45536</v>
       </c>
       <c r="K27" s="81" t="n"/>
-      <c r="L27" s="192" t="n">
+      <c r="L27" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M27" s="193" t="n">
+      <c r="M27" s="200" t="n">
         <v>53</v>
       </c>
-      <c r="N27" s="192" t="n">
+      <c r="N27" s="199" t="n">
         <v>54</v>
       </c>
       <c r="O27" s="107">
@@ -9126,13 +9413,13 @@
         <v>45536</v>
       </c>
       <c r="K28" s="81" t="n"/>
-      <c r="L28" s="192" t="n">
+      <c r="L28" s="199" t="n">
         <v>44</v>
       </c>
-      <c r="M28" s="193" t="n">
+      <c r="M28" s="200" t="n">
         <v>52</v>
       </c>
-      <c r="N28" s="192" t="n">
+      <c r="N28" s="199" t="n">
         <v>41</v>
       </c>
       <c r="O28" s="107">
@@ -9184,13 +9471,13 @@
         <v>45536</v>
       </c>
       <c r="K29" s="81" t="n"/>
-      <c r="L29" s="192" t="n">
+      <c r="L29" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M29" s="193" t="n">
+      <c r="M29" s="200" t="n">
         <v>39</v>
       </c>
-      <c r="N29" s="192" t="n">
+      <c r="N29" s="199" t="n">
         <v>38</v>
       </c>
       <c r="O29" s="107">
@@ -9242,13 +9529,13 @@
         <v>45536</v>
       </c>
       <c r="K30" s="81" t="n"/>
-      <c r="L30" s="192" t="n">
+      <c r="L30" s="199" t="n">
         <v>44</v>
       </c>
-      <c r="M30" s="193" t="n">
+      <c r="M30" s="200" t="n">
         <v>44</v>
       </c>
-      <c r="N30" s="192" t="n">
+      <c r="N30" s="199" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="107">
@@ -9300,13 +9587,13 @@
         <v>45536</v>
       </c>
       <c r="K31" s="81" t="n"/>
-      <c r="L31" s="192" t="n">
+      <c r="L31" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M31" s="193" t="n">
+      <c r="M31" s="200" t="n">
         <v>38</v>
       </c>
-      <c r="N31" s="192" t="n">
+      <c r="N31" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O31" s="107">
@@ -9358,13 +9645,13 @@
         <v>45900</v>
       </c>
       <c r="K32" s="81" t="n"/>
-      <c r="L32" s="192" t="n">
+      <c r="L32" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M32" s="193" t="n">
+      <c r="M32" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N32" s="192" t="n">
+      <c r="N32" s="199" t="n">
         <v>36</v>
       </c>
       <c r="O32" s="107">
@@ -9416,13 +9703,13 @@
         <v>46030</v>
       </c>
       <c r="K33" s="81" t="n"/>
-      <c r="L33" s="192" t="n">
+      <c r="L33" s="199" t="n">
         <v>70</v>
       </c>
-      <c r="M33" s="193" t="n">
+      <c r="M33" s="200" t="n">
         <v>72</v>
       </c>
-      <c r="N33" s="192" t="n">
+      <c r="N33" s="199" t="n">
         <v>58</v>
       </c>
       <c r="O33" s="107">
@@ -9477,13 +9764,13 @@
         <v>46032</v>
       </c>
       <c r="K34" s="81" t="n"/>
-      <c r="L34" s="192" t="n">
+      <c r="L34" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="193" t="n">
+      <c r="M34" s="200" t="n">
         <v>25</v>
       </c>
-      <c r="N34" s="192" t="n">
+      <c r="N34" s="199" t="n">
         <v>28</v>
       </c>
       <c r="O34" s="107">
@@ -9535,13 +9822,13 @@
         <v>45536</v>
       </c>
       <c r="K35" s="81" t="n"/>
-      <c r="L35" s="192" t="n">
+      <c r="L35" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M35" s="193" t="n">
+      <c r="M35" s="200" t="n">
         <v>31</v>
       </c>
-      <c r="N35" s="192" t="n">
+      <c r="N35" s="199" t="n">
         <v>40</v>
       </c>
       <c r="O35" s="107">
@@ -9593,13 +9880,13 @@
         <v>45536</v>
       </c>
       <c r="K36" s="81" t="n"/>
-      <c r="L36" s="192" t="n">
+      <c r="L36" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M36" s="193" t="n">
+      <c r="M36" s="200" t="n">
         <v>63</v>
       </c>
-      <c r="N36" s="192" t="n">
+      <c r="N36" s="199" t="n">
         <v>57</v>
       </c>
       <c r="O36" s="107">
@@ -9651,13 +9938,13 @@
         <v>45536</v>
       </c>
       <c r="K37" s="81" t="n"/>
-      <c r="L37" s="192" t="n">
+      <c r="L37" s="199" t="n">
         <v>55</v>
       </c>
-      <c r="M37" s="193" t="n">
+      <c r="M37" s="200" t="n">
         <v>33</v>
       </c>
-      <c r="N37" s="192" t="n">
+      <c r="N37" s="199" t="n">
         <v>36</v>
       </c>
       <c r="O37" s="107">
@@ -9709,13 +9996,13 @@
         <v>45536</v>
       </c>
       <c r="K38" s="81" t="n"/>
-      <c r="L38" s="192" t="n">
+      <c r="L38" s="199" t="n">
         <v>30</v>
       </c>
-      <c r="M38" s="193" t="n">
+      <c r="M38" s="200" t="n">
         <v>17</v>
       </c>
-      <c r="N38" s="192" t="n">
+      <c r="N38" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O38" s="107">
@@ -9767,13 +10054,13 @@
         <v>45536</v>
       </c>
       <c r="K39" s="81" t="n"/>
-      <c r="L39" s="192" t="n">
+      <c r="L39" s="199" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="193" t="n">
+      <c r="M39" s="200" t="n">
         <v>32</v>
       </c>
-      <c r="N39" s="192" t="n">
+      <c r="N39" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O39" s="107">
@@ -9825,13 +10112,13 @@
         <v>45536</v>
       </c>
       <c r="K40" s="81" t="n"/>
-      <c r="L40" s="192" t="n">
+      <c r="L40" s="199" t="n">
         <v>25</v>
       </c>
-      <c r="M40" s="193" t="n">
+      <c r="M40" s="200" t="n">
         <v>22</v>
       </c>
-      <c r="N40" s="192" t="n">
+      <c r="N40" s="199" t="n">
         <v>22</v>
       </c>
       <c r="O40" s="107">
@@ -9883,13 +10170,13 @@
         <v>44197</v>
       </c>
       <c r="K41" s="81" t="n"/>
-      <c r="L41" s="192" t="n">
+      <c r="L41" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="193" t="n">
+      <c r="M41" s="200" t="n">
         <v>38</v>
       </c>
-      <c r="N41" s="192" t="n">
+      <c r="N41" s="199" t="n">
         <v>9</v>
       </c>
       <c r="O41" s="107">
@@ -9941,13 +10228,13 @@
         <v>45536</v>
       </c>
       <c r="K42" s="81" t="n"/>
-      <c r="L42" s="192" t="n">
+      <c r="L42" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M42" s="193" t="n">
+      <c r="M42" s="200" t="n">
         <v>47</v>
       </c>
-      <c r="N42" s="192" t="n">
+      <c r="N42" s="199" t="n">
         <v>33</v>
       </c>
       <c r="O42" s="107">
@@ -9999,13 +10286,13 @@
         <v>45536</v>
       </c>
       <c r="K43" s="81" t="n"/>
-      <c r="L43" s="192" t="n">
+      <c r="L43" s="199" t="n">
         <v>18</v>
       </c>
-      <c r="M43" s="193" t="n">
+      <c r="M43" s="200" t="n">
         <v>61</v>
       </c>
-      <c r="N43" s="192" t="n">
+      <c r="N43" s="199" t="n">
         <v>29</v>
       </c>
       <c r="O43" s="107">
@@ -10057,13 +10344,13 @@
         <v>45536</v>
       </c>
       <c r="K44" s="81" t="n"/>
-      <c r="L44" s="192" t="n">
+      <c r="L44" s="199" t="n">
         <v>46</v>
       </c>
-      <c r="M44" s="193" t="n">
+      <c r="M44" s="200" t="n">
         <v>69</v>
       </c>
-      <c r="N44" s="192" t="n">
+      <c r="N44" s="199" t="n">
         <v>63</v>
       </c>
       <c r="O44" s="107">
@@ -10118,13 +10405,13 @@
         <v>45536</v>
       </c>
       <c r="K45" s="81" t="n"/>
-      <c r="L45" s="192" t="n">
+      <c r="L45" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M45" s="193" t="n">
+      <c r="M45" s="200" t="n">
         <v>58</v>
       </c>
-      <c r="N45" s="192" t="n">
+      <c r="N45" s="199" t="n">
         <v>58.5</v>
       </c>
       <c r="O45" s="107">
@@ -10179,13 +10466,13 @@
         <v>45536</v>
       </c>
       <c r="K46" s="81" t="n"/>
-      <c r="L46" s="192" t="n">
+      <c r="L46" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M46" s="193" t="n">
+      <c r="M46" s="200" t="n">
         <v>58</v>
       </c>
-      <c r="N46" s="192" t="n">
+      <c r="N46" s="199" t="n">
         <v>75</v>
       </c>
       <c r="O46" s="107">
@@ -10240,13 +10527,13 @@
         <v>45536</v>
       </c>
       <c r="K47" s="81" t="n"/>
-      <c r="L47" s="192" t="n">
+      <c r="L47" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M47" s="193" t="n">
+      <c r="M47" s="200" t="n">
         <v>37</v>
       </c>
-      <c r="N47" s="192" t="n">
+      <c r="N47" s="199" t="n">
         <v>41</v>
       </c>
       <c r="O47" s="107">
@@ -10298,13 +10585,13 @@
         <v>45536</v>
       </c>
       <c r="K48" s="81" t="n"/>
-      <c r="L48" s="192" t="n">
+      <c r="L48" s="199" t="n">
         <v>42</v>
       </c>
-      <c r="M48" s="193" t="n">
+      <c r="M48" s="200" t="n">
         <v>66</v>
       </c>
-      <c r="N48" s="192" t="n">
+      <c r="N48" s="199" t="n">
         <v>61</v>
       </c>
       <c r="O48" s="107">
@@ -10359,13 +10646,13 @@
         <v>45809</v>
       </c>
       <c r="K49" s="81" t="n"/>
-      <c r="L49" s="192" t="n">
+      <c r="L49" s="199" t="n">
         <v>21</v>
       </c>
-      <c r="M49" s="193" t="n">
+      <c r="M49" s="200" t="n">
         <v>32</v>
       </c>
-      <c r="N49" s="192" t="n">
+      <c r="N49" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O49" s="107">
@@ -10417,13 +10704,13 @@
         <v>45536</v>
       </c>
       <c r="K50" s="81" t="n"/>
-      <c r="L50" s="192" t="n">
+      <c r="L50" s="199" t="n">
         <v>51</v>
       </c>
-      <c r="M50" s="193" t="n">
+      <c r="M50" s="200" t="n">
         <v>47</v>
       </c>
-      <c r="N50" s="192" t="n">
+      <c r="N50" s="199" t="n">
         <v>42</v>
       </c>
       <c r="O50" s="107">
@@ -10475,13 +10762,13 @@
         <v>45536</v>
       </c>
       <c r="K51" s="81" t="n"/>
-      <c r="L51" s="192" t="n">
+      <c r="L51" s="199" t="n">
         <v>87</v>
       </c>
-      <c r="M51" s="193" t="n">
+      <c r="M51" s="200" t="n">
         <v>85</v>
       </c>
-      <c r="N51" s="192" t="n">
+      <c r="N51" s="199" t="n">
         <v>92.5</v>
       </c>
       <c r="O51" s="107">
@@ -10536,13 +10823,13 @@
         <v>45536</v>
       </c>
       <c r="K52" s="81" t="n"/>
-      <c r="L52" s="192" t="n">
+      <c r="L52" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M52" s="193" t="n">
+      <c r="M52" s="200" t="n">
         <v>23</v>
       </c>
-      <c r="N52" s="192" t="n">
+      <c r="N52" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="107">
@@ -10594,13 +10881,13 @@
         <v>45536</v>
       </c>
       <c r="K53" s="81" t="n"/>
-      <c r="L53" s="192" t="n">
+      <c r="L53" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M53" s="193" t="n">
+      <c r="M53" s="200" t="n">
         <v>17</v>
       </c>
-      <c r="N53" s="192" t="n">
+      <c r="N53" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O53" s="107">
@@ -10652,13 +10939,13 @@
         <v>45536</v>
       </c>
       <c r="K54" s="81" t="n"/>
-      <c r="L54" s="192" t="n">
+      <c r="L54" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M54" s="193" t="n">
+      <c r="M54" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="N54" s="192" t="n">
+      <c r="N54" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="107">
@@ -10710,13 +10997,13 @@
         <v>45536</v>
       </c>
       <c r="K55" s="81" t="n"/>
-      <c r="L55" s="192" t="n">
+      <c r="L55" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M55" s="193" t="n">
+      <c r="M55" s="200" t="n">
         <v>29</v>
       </c>
-      <c r="N55" s="192" t="n">
+      <c r="N55" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O55" s="107">
@@ -10749,13 +11036,13 @@
         <v>46143</v>
       </c>
       <c r="K56" s="81" t="n"/>
-      <c r="L56" s="192" t="n">
+      <c r="L56" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M56" s="193" t="n">
+      <c r="M56" s="200" t="n">
         <v>46</v>
       </c>
-      <c r="N56" s="192" t="n">
+      <c r="N56" s="199" t="n">
         <v>32</v>
       </c>
       <c r="O56" s="107">
@@ -10807,13 +11094,13 @@
         <v>45536</v>
       </c>
       <c r="K57" s="81" t="n"/>
-      <c r="L57" s="192" t="n">
+      <c r="L57" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M57" s="193" t="n">
+      <c r="M57" s="200" t="n">
         <v>50</v>
       </c>
-      <c r="N57" s="192" t="n">
+      <c r="N57" s="199" t="n">
         <v>49</v>
       </c>
       <c r="O57" s="107">
@@ -10865,13 +11152,13 @@
         <v>45775</v>
       </c>
       <c r="K58" s="81" t="n"/>
-      <c r="L58" s="192" t="n">
+      <c r="L58" s="199" t="n">
         <v>23.5</v>
       </c>
-      <c r="M58" s="193" t="n">
+      <c r="M58" s="200" t="n">
         <v>5</v>
       </c>
-      <c r="N58" s="192" t="n">
+      <c r="N58" s="199" t="n">
         <v>9</v>
       </c>
       <c r="O58" s="107">
@@ -10923,13 +11210,13 @@
         <v>45536</v>
       </c>
       <c r="K59" s="81" t="n"/>
-      <c r="L59" s="192" t="n">
+      <c r="L59" s="199" t="n">
         <v>30</v>
       </c>
-      <c r="M59" s="193" t="n">
+      <c r="M59" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="N59" s="192" t="n">
+      <c r="N59" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O59" s="107">
@@ -10981,13 +11268,13 @@
         <v>45536</v>
       </c>
       <c r="K60" s="81" t="n"/>
-      <c r="L60" s="192" t="n">
+      <c r="L60" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M60" s="193" t="n">
+      <c r="M60" s="200" t="n">
         <v>31</v>
       </c>
-      <c r="N60" s="192" t="n">
+      <c r="N60" s="199" t="n">
         <v>32</v>
       </c>
       <c r="O60" s="107">
@@ -11039,13 +11326,13 @@
         <v>45536</v>
       </c>
       <c r="K61" s="81" t="n"/>
-      <c r="L61" s="192" t="n">
+      <c r="L61" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M61" s="193" t="n">
+      <c r="M61" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N61" s="192" t="n">
+      <c r="N61" s="199" t="n">
         <v>27</v>
       </c>
       <c r="O61" s="107">
@@ -11097,13 +11384,13 @@
         <v>45536</v>
       </c>
       <c r="K62" s="81" t="n"/>
-      <c r="L62" s="192" t="n">
+      <c r="L62" s="199" t="n">
         <v>29</v>
       </c>
-      <c r="M62" s="193" t="n">
+      <c r="M62" s="200" t="n">
         <v>16.5</v>
       </c>
-      <c r="N62" s="192" t="n">
+      <c r="N62" s="199" t="n">
         <v>12</v>
       </c>
       <c r="O62" s="107">
@@ -11155,13 +11442,13 @@
         <v>45536</v>
       </c>
       <c r="K63" s="81" t="n"/>
-      <c r="L63" s="192" t="n">
+      <c r="L63" s="199" t="n">
         <v>26</v>
       </c>
-      <c r="M63" s="193" t="n">
+      <c r="M63" s="200" t="n">
         <v>20</v>
       </c>
-      <c r="N63" s="192" t="n">
+      <c r="N63" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O63" s="107">
@@ -11213,13 +11500,13 @@
         <v>45536</v>
       </c>
       <c r="K64" s="81" t="n"/>
-      <c r="L64" s="192" t="n">
+      <c r="L64" s="199" t="n">
         <v>18</v>
       </c>
-      <c r="M64" s="193" t="n">
+      <c r="M64" s="200" t="n">
         <v>16</v>
       </c>
-      <c r="N64" s="192" t="n">
+      <c r="N64" s="199" t="n">
         <v>16</v>
       </c>
       <c r="O64" s="107">
@@ -11271,13 +11558,13 @@
         <v>45536</v>
       </c>
       <c r="K65" s="81" t="n"/>
-      <c r="L65" s="192" t="n">
+      <c r="L65" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M65" s="193" t="n">
+      <c r="M65" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N65" s="192" t="n">
+      <c r="N65" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O65" s="107">
@@ -11329,13 +11616,13 @@
         <v>45839</v>
       </c>
       <c r="K66" s="81" t="n"/>
-      <c r="L66" s="192" t="n">
+      <c r="L66" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M66" s="193" t="n">
+      <c r="M66" s="200" t="n">
         <v>32</v>
       </c>
-      <c r="N66" s="192" t="n">
+      <c r="N66" s="199" t="n">
         <v>32</v>
       </c>
       <c r="O66" s="107">
@@ -11387,13 +11674,13 @@
         <v>45536</v>
       </c>
       <c r="K67" s="81" t="n"/>
-      <c r="L67" s="192" t="n">
+      <c r="L67" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M67" s="193" t="n">
+      <c r="M67" s="200" t="n">
         <v>26</v>
       </c>
-      <c r="N67" s="192" t="n">
+      <c r="N67" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O67" s="107">
@@ -11422,13 +11709,13 @@
         <v>46226</v>
       </c>
       <c r="K68" s="81" t="n"/>
-      <c r="L68" s="192" t="n">
+      <c r="L68" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M68" s="193" t="n">
+      <c r="M68" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="192" t="n">
+      <c r="N68" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O68" s="107">
@@ -11480,13 +11767,13 @@
         <v>45536</v>
       </c>
       <c r="K69" s="81" t="n"/>
-      <c r="L69" s="192" t="n">
+      <c r="L69" s="199" t="n">
         <v>10</v>
       </c>
-      <c r="M69" s="193" t="n">
+      <c r="M69" s="200" t="n">
         <v>8</v>
       </c>
-      <c r="N69" s="192" t="n">
+      <c r="N69" s="199" t="n">
         <v>10</v>
       </c>
       <c r="O69" s="107">
@@ -11538,13 +11825,13 @@
         <v>45536</v>
       </c>
       <c r="K70" s="81" t="n"/>
-      <c r="L70" s="192" t="n">
+      <c r="L70" s="199" t="n">
         <v>45</v>
       </c>
-      <c r="M70" s="193" t="n">
+      <c r="M70" s="200" t="n">
         <v>49</v>
       </c>
-      <c r="N70" s="192" t="n">
+      <c r="N70" s="199" t="n">
         <v>33</v>
       </c>
       <c r="O70" s="107">
@@ -11596,13 +11883,13 @@
         <v>45536</v>
       </c>
       <c r="K71" s="81" t="n"/>
-      <c r="L71" s="192" t="n">
+      <c r="L71" s="199" t="n">
         <v>30</v>
       </c>
-      <c r="M71" s="193" t="n">
+      <c r="M71" s="200" t="n">
         <v>38</v>
       </c>
-      <c r="N71" s="192" t="n">
+      <c r="N71" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O71" s="107">
@@ -11654,13 +11941,13 @@
         <v>45536</v>
       </c>
       <c r="K72" s="81" t="n"/>
-      <c r="L72" s="192" t="n">
+      <c r="L72" s="199" t="n">
         <v>47</v>
       </c>
-      <c r="M72" s="193" t="n">
+      <c r="M72" s="200" t="n">
         <v>50</v>
       </c>
-      <c r="N72" s="192" t="n">
+      <c r="N72" s="199" t="n">
         <v>63</v>
       </c>
       <c r="O72" s="107">
@@ -11692,13 +11979,13 @@
         <v>46204</v>
       </c>
       <c r="K73" s="81" t="n"/>
-      <c r="L73" s="192" t="n">
+      <c r="L73" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="193" t="n">
+      <c r="M73" s="200" t="n">
         <v>18</v>
       </c>
-      <c r="N73" s="192" t="n">
+      <c r="N73" s="199" t="n">
         <v>27</v>
       </c>
       <c r="O73" s="107">
@@ -11750,13 +12037,13 @@
         <v>45536</v>
       </c>
       <c r="K74" s="81" t="n"/>
-      <c r="L74" s="192" t="n">
+      <c r="L74" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M74" s="193" t="n">
+      <c r="M74" s="200" t="n">
         <v>41</v>
       </c>
-      <c r="N74" s="192" t="n">
+      <c r="N74" s="199" t="n">
         <v>45</v>
       </c>
       <c r="O74" s="107">
@@ -11801,13 +12088,13 @@
         <v>44652</v>
       </c>
       <c r="K75" s="81" t="n"/>
-      <c r="L75" s="192" t="n">
+      <c r="L75" s="199" t="n">
         <v>32</v>
       </c>
-      <c r="M75" s="193" t="n">
+      <c r="M75" s="200" t="n">
         <v>54</v>
       </c>
-      <c r="N75" s="192" t="n">
+      <c r="N75" s="199" t="n">
         <v>21</v>
       </c>
       <c r="O75" s="107">
@@ -11840,13 +12127,13 @@
         <v>46143</v>
       </c>
       <c r="K76" s="81" t="n"/>
-      <c r="L76" s="192" t="n">
+      <c r="L76" s="199" t="n">
         <v>34</v>
       </c>
-      <c r="M76" s="193" t="n">
+      <c r="M76" s="200" t="n">
         <v>39</v>
       </c>
-      <c r="N76" s="192" t="n">
+      <c r="N76" s="199" t="n">
         <v>39</v>
       </c>
       <c r="O76" s="107">
@@ -11898,13 +12185,13 @@
         <v>46206</v>
       </c>
       <c r="K77" s="81" t="n"/>
-      <c r="L77" s="192" t="n">
+      <c r="L77" s="199" t="n">
         <v>63</v>
       </c>
-      <c r="M77" s="193" t="n">
+      <c r="M77" s="200" t="n">
         <v>3</v>
       </c>
-      <c r="N77" s="192" t="n">
+      <c r="N77" s="199" t="n">
         <v>42</v>
       </c>
       <c r="O77" s="107">
@@ -11956,13 +12243,13 @@
         <v>45536</v>
       </c>
       <c r="K78" s="81" t="n"/>
-      <c r="L78" s="192" t="n">
+      <c r="L78" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M78" s="193" t="n">
+      <c r="M78" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N78" s="192" t="n">
+      <c r="N78" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="107">
@@ -12014,13 +12301,13 @@
         <v>45536</v>
       </c>
       <c r="K79" s="81" t="n"/>
-      <c r="L79" s="192" t="n">
+      <c r="L79" s="199" t="n">
         <v>34</v>
       </c>
-      <c r="M79" s="193" t="n">
+      <c r="M79" s="200" t="n">
         <v>42</v>
       </c>
-      <c r="N79" s="192" t="n">
+      <c r="N79" s="199" t="n">
         <v>34</v>
       </c>
       <c r="O79" s="107">
@@ -12072,13 +12359,13 @@
         <v>45809</v>
       </c>
       <c r="K80" s="81" t="n"/>
-      <c r="L80" s="192" t="n">
+      <c r="L80" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M80" s="193" t="n">
+      <c r="M80" s="200" t="n">
         <v>38</v>
       </c>
-      <c r="N80" s="192" t="n">
+      <c r="N80" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O80" s="107">
@@ -12130,13 +12417,13 @@
         <v>45536</v>
       </c>
       <c r="K81" s="81" t="n"/>
-      <c r="L81" s="192" t="n">
+      <c r="L81" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="193" t="n">
+      <c r="M81" s="200" t="n">
         <v>8</v>
       </c>
-      <c r="N81" s="192" t="n">
+      <c r="N81" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="107">
@@ -12188,13 +12475,13 @@
         <v>45536</v>
       </c>
       <c r="K82" s="81" t="n"/>
-      <c r="L82" s="192" t="n">
+      <c r="L82" s="199" t="n">
         <v>31</v>
       </c>
-      <c r="M82" s="193" t="n">
+      <c r="M82" s="200" t="n">
         <v>57</v>
       </c>
-      <c r="N82" s="192" t="n">
+      <c r="N82" s="199" t="n">
         <v>28</v>
       </c>
       <c r="O82" s="107">
@@ -12246,13 +12533,13 @@
         <v>45536</v>
       </c>
       <c r="K83" s="81" t="n"/>
-      <c r="L83" s="192" t="n">
+      <c r="L83" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M83" s="193" t="n">
+      <c r="M83" s="200" t="n">
         <v>52</v>
       </c>
-      <c r="N83" s="192" t="n">
+      <c r="N83" s="199" t="n">
         <v>28</v>
       </c>
       <c r="O83" s="107">
@@ -12304,13 +12591,13 @@
         <v>45536</v>
       </c>
       <c r="K84" s="81" t="n"/>
-      <c r="L84" s="192" t="n">
+      <c r="L84" s="199" t="n">
         <v>40</v>
       </c>
-      <c r="M84" s="193" t="n">
+      <c r="M84" s="200" t="n">
         <v>52</v>
       </c>
-      <c r="N84" s="192" t="n">
+      <c r="N84" s="199" t="n">
         <v>20</v>
       </c>
       <c r="O84" s="107">
@@ -12362,13 +12649,13 @@
         <v>45536</v>
       </c>
       <c r="K85" s="81" t="n"/>
-      <c r="L85" s="192" t="n">
+      <c r="L85" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M85" s="193" t="n">
+      <c r="M85" s="200" t="n">
         <v>41</v>
       </c>
-      <c r="N85" s="192" t="n">
+      <c r="N85" s="199" t="n">
         <v>26</v>
       </c>
       <c r="O85" s="107">
@@ -12420,13 +12707,13 @@
         <v>45536</v>
       </c>
       <c r="K86" s="81" t="n"/>
-      <c r="L86" s="192" t="n">
+      <c r="L86" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M86" s="193" t="n">
+      <c r="M86" s="200" t="n">
         <v>52</v>
       </c>
-      <c r="N86" s="192" t="n">
+      <c r="N86" s="199" t="n">
         <v>20</v>
       </c>
       <c r="O86" s="107">
@@ -12478,13 +12765,13 @@
         <v>45536</v>
       </c>
       <c r="K87" s="81" t="n"/>
-      <c r="L87" s="192" t="n">
+      <c r="L87" s="199" t="n">
         <v>42</v>
       </c>
-      <c r="M87" s="193" t="n">
+      <c r="M87" s="200" t="n">
         <v>30</v>
       </c>
-      <c r="N87" s="192" t="n">
+      <c r="N87" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O87" s="107">
@@ -12536,13 +12823,13 @@
         <v>45536</v>
       </c>
       <c r="K88" s="81" t="n"/>
-      <c r="L88" s="192" t="n">
+      <c r="L88" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M88" s="193" t="n">
+      <c r="M88" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N88" s="192" t="n">
+      <c r="N88" s="199" t="n">
         <v>9</v>
       </c>
       <c r="O88" s="107">
@@ -12594,13 +12881,13 @@
         <v>45536</v>
       </c>
       <c r="K89" s="81" t="n"/>
-      <c r="L89" s="192" t="n">
+      <c r="L89" s="199" t="n">
         <v>21</v>
       </c>
-      <c r="M89" s="193" t="n">
+      <c r="M89" s="200" t="n">
         <v>34</v>
       </c>
-      <c r="N89" s="192" t="n">
+      <c r="N89" s="199" t="n">
         <v>18</v>
       </c>
       <c r="O89" s="107">
@@ -12652,13 +12939,13 @@
         <v>45139</v>
       </c>
       <c r="K90" s="81" t="n"/>
-      <c r="L90" s="192" t="n">
+      <c r="L90" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M90" s="193" t="n">
+      <c r="M90" s="200" t="n">
         <v>50</v>
       </c>
-      <c r="N90" s="192" t="n">
+      <c r="N90" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O90" s="107">
@@ -12710,13 +12997,13 @@
         <v>45536</v>
       </c>
       <c r="K91" s="81" t="n"/>
-      <c r="L91" s="192" t="n">
+      <c r="L91" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M91" s="193" t="n">
+      <c r="M91" s="200" t="n">
         <v>40</v>
       </c>
-      <c r="N91" s="192" t="n">
+      <c r="N91" s="199" t="n">
         <v>29</v>
       </c>
       <c r="O91" s="107">
@@ -12749,13 +13036,13 @@
         <v>46168</v>
       </c>
       <c r="K92" s="81" t="n"/>
-      <c r="L92" s="192" t="n">
+      <c r="L92" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M92" s="193" t="n">
+      <c r="M92" s="200" t="n">
         <v>33</v>
       </c>
-      <c r="N92" s="192" t="n">
+      <c r="N92" s="199" t="n">
         <v>30</v>
       </c>
       <c r="O92" s="107">
@@ -12788,13 +13075,13 @@
         <v>46143</v>
       </c>
       <c r="K93" s="81" t="n"/>
-      <c r="L93" s="192" t="n">
+      <c r="L93" s="199" t="n">
         <v>10</v>
       </c>
-      <c r="M93" s="193" t="n">
+      <c r="M93" s="200" t="n">
         <v>24</v>
       </c>
-      <c r="N93" s="192" t="n">
+      <c r="N93" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O93" s="107">
@@ -12846,13 +13133,13 @@
         <v>45536</v>
       </c>
       <c r="K94" s="81" t="n"/>
-      <c r="L94" s="192" t="n">
+      <c r="L94" s="199" t="n">
         <v>38</v>
       </c>
-      <c r="M94" s="193" t="n">
+      <c r="M94" s="200" t="n">
         <v>38</v>
       </c>
-      <c r="N94" s="192" t="n">
+      <c r="N94" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O94" s="107">
@@ -12904,13 +13191,13 @@
         <v>45778</v>
       </c>
       <c r="K95" s="81" t="n"/>
-      <c r="L95" s="192" t="n">
+      <c r="L95" s="199" t="n">
         <v>15</v>
       </c>
-      <c r="M95" s="193" t="n">
+      <c r="M95" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N95" s="192" t="n">
+      <c r="N95" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O95" s="107">
@@ -12962,13 +13249,13 @@
         <v>45536</v>
       </c>
       <c r="K96" s="81" t="n"/>
-      <c r="L96" s="192" t="n">
+      <c r="L96" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M96" s="193" t="n">
+      <c r="M96" s="200" t="n">
         <v>60</v>
       </c>
-      <c r="N96" s="192" t="n">
+      <c r="N96" s="199" t="n">
         <v>50</v>
       </c>
       <c r="O96" s="107">
@@ -13020,13 +13307,13 @@
         <v>45536</v>
       </c>
       <c r="K97" s="81" t="n"/>
-      <c r="L97" s="192" t="n">
+      <c r="L97" s="199" t="n">
         <v>24</v>
       </c>
-      <c r="M97" s="193" t="n">
+      <c r="M97" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="N97" s="192" t="n">
+      <c r="N97" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O97" s="107">
@@ -13078,13 +13365,13 @@
         <v>45536</v>
       </c>
       <c r="K98" s="81" t="n"/>
-      <c r="L98" s="192" t="n">
+      <c r="L98" s="199" t="n">
         <v>12</v>
       </c>
-      <c r="M98" s="193" t="n">
+      <c r="M98" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="192" t="n">
+      <c r="N98" s="199" t="n">
         <v>9</v>
       </c>
       <c r="O98" s="107">
@@ -13136,13 +13423,13 @@
         <v>45536</v>
       </c>
       <c r="K99" s="81" t="n"/>
-      <c r="L99" s="192" t="n">
+      <c r="L99" s="199" t="n">
         <v>15</v>
       </c>
-      <c r="M99" s="193" t="n">
+      <c r="M99" s="200" t="n">
         <v>28</v>
       </c>
-      <c r="N99" s="192" t="n">
+      <c r="N99" s="199" t="n">
         <v>13</v>
       </c>
       <c r="O99" s="107">
@@ -13194,13 +13481,13 @@
         <v>45536</v>
       </c>
       <c r="K100" s="81" t="n"/>
-      <c r="L100" s="192" t="n">
+      <c r="L100" s="199" t="n">
         <v>32</v>
       </c>
-      <c r="M100" s="193" t="n">
+      <c r="M100" s="200" t="n">
         <v>28</v>
       </c>
-      <c r="N100" s="192" t="n">
+      <c r="N100" s="199" t="n">
         <v>12</v>
       </c>
       <c r="O100" s="107">
@@ -13233,13 +13520,13 @@
         <v>46143</v>
       </c>
       <c r="K101" s="81" t="n"/>
-      <c r="L101" s="192" t="n">
+      <c r="L101" s="199" t="n">
         <v>9</v>
       </c>
-      <c r="M101" s="193" t="n">
+      <c r="M101" s="200" t="n">
         <v>23</v>
       </c>
-      <c r="N101" s="192" t="n">
+      <c r="N101" s="199" t="n">
         <v>22</v>
       </c>
       <c r="O101" s="107">
@@ -13291,13 +13578,13 @@
         <v>45536</v>
       </c>
       <c r="K102" s="81" t="n"/>
-      <c r="L102" s="192" t="n">
+      <c r="L102" s="199" t="n">
         <v>50</v>
       </c>
-      <c r="M102" s="193" t="n">
+      <c r="M102" s="200" t="n">
         <v>63</v>
       </c>
-      <c r="N102" s="192" t="n">
+      <c r="N102" s="199" t="n">
         <v>29</v>
       </c>
       <c r="O102" s="107">
@@ -13349,13 +13636,13 @@
         <v>45536</v>
       </c>
       <c r="K103" s="81" t="n"/>
-      <c r="L103" s="192" t="n">
+      <c r="L103" s="199" t="n">
         <v>24</v>
       </c>
-      <c r="M103" s="193" t="n">
+      <c r="M103" s="200" t="n">
         <v>35.5</v>
       </c>
-      <c r="N103" s="192" t="n">
+      <c r="N103" s="199" t="n">
         <v>23</v>
       </c>
       <c r="O103" s="107">
@@ -13407,13 +13694,13 @@
         <v>45536</v>
       </c>
       <c r="K104" s="81" t="n"/>
-      <c r="L104" s="192" t="n">
+      <c r="L104" s="199" t="n">
         <v>10</v>
       </c>
-      <c r="M104" s="193" t="n">
+      <c r="M104" s="200" t="n">
         <v>24</v>
       </c>
-      <c r="N104" s="192" t="n">
+      <c r="N104" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O104" s="107">
@@ -13465,13 +13752,13 @@
         <v>45536</v>
       </c>
       <c r="K105" s="81" t="n"/>
-      <c r="L105" s="192" t="n">
+      <c r="L105" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M105" s="193" t="n">
+      <c r="M105" s="200" t="n">
         <v>49</v>
       </c>
-      <c r="N105" s="192" t="n">
+      <c r="N105" s="199" t="n">
         <v>44</v>
       </c>
       <c r="O105" s="107">
@@ -13523,13 +13810,13 @@
         <v>45536</v>
       </c>
       <c r="K106" s="81" t="n"/>
-      <c r="L106" s="192" t="n">
+      <c r="L106" s="199" t="n">
         <v>18</v>
       </c>
-      <c r="M106" s="193" t="n">
+      <c r="M106" s="200" t="n">
         <v>16</v>
       </c>
-      <c r="N106" s="192" t="n">
+      <c r="N106" s="199" t="n">
         <v>16</v>
       </c>
       <c r="O106" s="107">
@@ -13581,13 +13868,13 @@
         <v>45536</v>
       </c>
       <c r="K107" s="81" t="n"/>
-      <c r="L107" s="192" t="n">
+      <c r="L107" s="199" t="n">
         <v>47</v>
       </c>
-      <c r="M107" s="193" t="n">
+      <c r="M107" s="200" t="n">
         <v>64</v>
       </c>
-      <c r="N107" s="192" t="n">
+      <c r="N107" s="199" t="n">
         <v>58</v>
       </c>
       <c r="O107" s="107">
@@ -13642,13 +13929,13 @@
         <v>45536</v>
       </c>
       <c r="K108" s="81" t="n"/>
-      <c r="L108" s="192" t="n">
+      <c r="L108" s="199" t="n">
         <v>47</v>
       </c>
-      <c r="M108" s="193" t="n">
+      <c r="M108" s="200" t="n">
         <v>32</v>
       </c>
-      <c r="N108" s="192" t="n">
+      <c r="N108" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O108" s="107">
@@ -13700,13 +13987,13 @@
         <v>45536</v>
       </c>
       <c r="K109" s="81" t="n"/>
-      <c r="L109" s="192" t="n">
+      <c r="L109" s="199" t="n">
         <v>24</v>
       </c>
-      <c r="M109" s="193" t="n">
+      <c r="M109" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="N109" s="192" t="n">
+      <c r="N109" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O109" s="107">
@@ -13758,13 +14045,13 @@
         <v>45536</v>
       </c>
       <c r="K110" s="81" t="n"/>
-      <c r="L110" s="192" t="n">
+      <c r="L110" s="199" t="n">
         <v>3</v>
       </c>
-      <c r="M110" s="193" t="n">
+      <c r="M110" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N110" s="192" t="n">
+      <c r="N110" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="107">
@@ -13816,13 +14103,13 @@
         <v>45536</v>
       </c>
       <c r="K111" s="81" t="n"/>
-      <c r="L111" s="192" t="n">
+      <c r="L111" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M111" s="193" t="n">
+      <c r="M111" s="200" t="n">
         <v>18</v>
       </c>
-      <c r="N111" s="192" t="n">
+      <c r="N111" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O111" s="107">
@@ -13874,13 +14161,13 @@
         <v>45536</v>
       </c>
       <c r="K112" s="81" t="n"/>
-      <c r="L112" s="192" t="n">
+      <c r="L112" s="199" t="n">
         <v>36</v>
       </c>
-      <c r="M112" s="193" t="n">
+      <c r="M112" s="200" t="n">
         <v>56</v>
       </c>
-      <c r="N112" s="192" t="n">
+      <c r="N112" s="199" t="n">
         <v>60</v>
       </c>
       <c r="O112" s="107">
@@ -13932,13 +14219,13 @@
         <v>45536</v>
       </c>
       <c r="K113" s="81" t="n"/>
-      <c r="L113" s="192" t="n">
+      <c r="L113" s="199" t="n">
         <v>53</v>
       </c>
-      <c r="M113" s="193" t="n">
+      <c r="M113" s="200" t="n">
         <v>52</v>
       </c>
-      <c r="N113" s="192" t="n">
+      <c r="N113" s="199" t="n">
         <v>63</v>
       </c>
       <c r="O113" s="107">
@@ -13993,13 +14280,13 @@
         <v>45536</v>
       </c>
       <c r="K114" s="81" t="n"/>
-      <c r="L114" s="192" t="n">
+      <c r="L114" s="199" t="n">
         <v>18</v>
       </c>
-      <c r="M114" s="193" t="n">
+      <c r="M114" s="200" t="n">
         <v>24</v>
       </c>
-      <c r="N114" s="192" t="n">
+      <c r="N114" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O114" s="107">
@@ -14051,13 +14338,13 @@
         <v>45536</v>
       </c>
       <c r="K115" s="81" t="n"/>
-      <c r="L115" s="192" t="n">
+      <c r="L115" s="199" t="n">
         <v>26</v>
       </c>
-      <c r="M115" s="193" t="n">
+      <c r="M115" s="200" t="n">
         <v>39</v>
       </c>
-      <c r="N115" s="192" t="n">
+      <c r="N115" s="199" t="n">
         <v>22</v>
       </c>
       <c r="O115" s="107">
@@ -14090,13 +14377,13 @@
         <v>46143</v>
       </c>
       <c r="K116" s="81" t="n"/>
-      <c r="L116" s="192" t="n">
+      <c r="L116" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M116" s="193" t="n">
+      <c r="M116" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N116" s="192" t="n">
+      <c r="N116" s="199" t="n">
         <v>32</v>
       </c>
       <c r="O116" s="107">
@@ -14148,13 +14435,13 @@
         <v>45536</v>
       </c>
       <c r="K117" s="81" t="n"/>
-      <c r="L117" s="192" t="n">
+      <c r="L117" s="199" t="n">
         <v>39</v>
       </c>
-      <c r="M117" s="193" t="n">
+      <c r="M117" s="200" t="n">
         <v>66</v>
       </c>
-      <c r="N117" s="192" t="n">
+      <c r="N117" s="199" t="n">
         <v>49</v>
       </c>
       <c r="O117" s="107">
@@ -14208,13 +14495,13 @@
         <v>45870</v>
       </c>
       <c r="K118" s="81" t="n"/>
-      <c r="L118" s="192" t="n">
+      <c r="L118" s="199" t="n">
         <v>32</v>
       </c>
-      <c r="M118" s="193" t="n">
+      <c r="M118" s="200" t="n">
         <v>20.5</v>
       </c>
-      <c r="N118" s="192" t="n">
+      <c r="N118" s="199" t="n">
         <v>33</v>
       </c>
       <c r="O118" s="107">
@@ -14266,13 +14553,13 @@
         <v>45536</v>
       </c>
       <c r="K119" s="81" t="n"/>
-      <c r="L119" s="192" t="n">
+      <c r="L119" s="199" t="n">
         <v>3</v>
       </c>
-      <c r="M119" s="193" t="n">
+      <c r="M119" s="200" t="n">
         <v>33</v>
       </c>
-      <c r="N119" s="192" t="n">
+      <c r="N119" s="199" t="n">
         <v>12</v>
       </c>
       <c r="O119" s="107">
@@ -14324,13 +14611,13 @@
         <v>45536</v>
       </c>
       <c r="K120" s="81" t="n"/>
-      <c r="L120" s="192" t="n">
+      <c r="L120" s="199" t="n">
         <v>56</v>
       </c>
-      <c r="M120" s="193" t="n">
+      <c r="M120" s="200" t="n">
         <v>41</v>
       </c>
-      <c r="N120" s="192" t="n">
+      <c r="N120" s="199" t="n">
         <v>49</v>
       </c>
       <c r="O120" s="107">
@@ -14359,13 +14646,13 @@
         <v>46235</v>
       </c>
       <c r="K121" s="81" t="n"/>
-      <c r="L121" s="192" t="n">
+      <c r="L121" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M121" s="193" t="n">
+      <c r="M121" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N121" s="192" t="n">
+      <c r="N121" s="199" t="n">
         <v>21</v>
       </c>
       <c r="O121" s="107">
@@ -14417,13 +14704,13 @@
         <v>45536</v>
       </c>
       <c r="K122" s="81" t="n"/>
-      <c r="L122" s="192" t="n">
+      <c r="L122" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M122" s="193" t="n">
+      <c r="M122" s="200" t="n">
         <v>41</v>
       </c>
-      <c r="N122" s="192" t="n">
+      <c r="N122" s="199" t="n">
         <v>13</v>
       </c>
       <c r="O122" s="107">
@@ -14475,13 +14762,13 @@
         <v>45536</v>
       </c>
       <c r="K123" s="81" t="n"/>
-      <c r="L123" s="192" t="n">
+      <c r="L123" s="199" t="n">
         <v>30</v>
       </c>
-      <c r="M123" s="193" t="n">
+      <c r="M123" s="200" t="n">
         <v>17</v>
       </c>
-      <c r="N123" s="192" t="n">
+      <c r="N123" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O123" s="107">
@@ -14510,13 +14797,13 @@
         <v>46235</v>
       </c>
       <c r="K124" s="81" t="n"/>
-      <c r="L124" s="192" t="n">
+      <c r="L124" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M124" s="193" t="n">
+      <c r="M124" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N124" s="192" t="n">
+      <c r="N124" s="199" t="n">
         <v>15</v>
       </c>
       <c r="O124" s="107">
@@ -14568,13 +14855,13 @@
         <v>45809</v>
       </c>
       <c r="K125" s="81" t="n"/>
-      <c r="L125" s="192" t="n">
+      <c r="L125" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M125" s="193" t="n">
+      <c r="M125" s="200" t="n">
         <v>33</v>
       </c>
-      <c r="N125" s="192" t="n">
+      <c r="N125" s="199" t="n">
         <v>32</v>
       </c>
       <c r="O125" s="107">
@@ -14626,13 +14913,13 @@
         <v>45536</v>
       </c>
       <c r="K126" s="81" t="n"/>
-      <c r="L126" s="192" t="n">
+      <c r="L126" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M126" s="193" t="n">
+      <c r="M126" s="200" t="n">
         <v>40</v>
       </c>
-      <c r="N126" s="192" t="n">
+      <c r="N126" s="199" t="n">
         <v>45</v>
       </c>
       <c r="O126" s="107">
@@ -14684,13 +14971,13 @@
         <v>45536</v>
       </c>
       <c r="K127" s="81" t="n"/>
-      <c r="L127" s="192" t="n">
+      <c r="L127" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M127" s="193" t="n">
+      <c r="M127" s="200" t="n">
         <v>32</v>
       </c>
-      <c r="N127" s="192" t="n">
+      <c r="N127" s="199" t="n">
         <v>6</v>
       </c>
       <c r="O127" s="107">
@@ -14742,13 +15029,13 @@
         <v>46222</v>
       </c>
       <c r="K128" s="81" t="n"/>
-      <c r="L128" s="192" t="n">
+      <c r="L128" s="199" t="n">
         <v>15</v>
       </c>
-      <c r="M128" s="193" t="n">
+      <c r="M128" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N128" s="192" t="n">
+      <c r="N128" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="107">
@@ -14800,13 +15087,13 @@
         <v>45536</v>
       </c>
       <c r="K129" s="81" t="n"/>
-      <c r="L129" s="192" t="n">
+      <c r="L129" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M129" s="193" t="n">
+      <c r="M129" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N129" s="192" t="n">
+      <c r="N129" s="199" t="n">
         <v>9</v>
       </c>
       <c r="O129" s="107">
@@ -14835,13 +15122,13 @@
         <v>46235</v>
       </c>
       <c r="K130" s="81" t="n"/>
-      <c r="L130" s="192" t="n">
+      <c r="L130" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="M130" s="193" t="n">
+      <c r="M130" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N130" s="192" t="n">
+      <c r="N130" s="199" t="n">
         <v>18</v>
       </c>
       <c r="O130" s="107">
@@ -14893,13 +15180,13 @@
         <v>45536</v>
       </c>
       <c r="K131" s="81" t="n"/>
-      <c r="L131" s="192" t="n">
+      <c r="L131" s="199" t="n">
         <v>35</v>
       </c>
-      <c r="M131" s="193" t="n">
+      <c r="M131" s="200" t="n">
         <v>23</v>
       </c>
-      <c r="N131" s="192" t="n">
+      <c r="N131" s="199" t="n">
         <v>24</v>
       </c>
       <c r="O131" s="107">
@@ -14951,13 +15238,13 @@
         <v>45959</v>
       </c>
       <c r="K132" s="81" t="n"/>
-      <c r="L132" s="192" t="n">
+      <c r="L132" s="199" t="n">
         <v>55.5</v>
       </c>
-      <c r="M132" s="193" t="n">
+      <c r="M132" s="200" t="n">
         <v>55</v>
       </c>
-      <c r="N132" s="192" t="n">
+      <c r="N132" s="199" t="n">
         <v>47</v>
       </c>
       <c r="O132" s="107">
@@ -15012,13 +15299,13 @@
         <v>45536</v>
       </c>
       <c r="K133" s="81" t="n"/>
-      <c r="L133" s="192" t="n">
+      <c r="L133" s="199" t="n">
         <v>62</v>
       </c>
-      <c r="M133" s="193" t="n">
+      <c r="M133" s="200" t="n">
         <v>58</v>
       </c>
-      <c r="N133" s="192" t="n">
+      <c r="N133" s="199" t="n">
         <v>71</v>
       </c>
       <c r="O133" s="107">
@@ -15073,13 +15360,13 @@
         <v>45536</v>
       </c>
       <c r="K134" s="81" t="n"/>
-      <c r="L134" s="192" t="n">
+      <c r="L134" s="199" t="n">
         <v>17</v>
       </c>
-      <c r="M134" s="193" t="n">
+      <c r="M134" s="200" t="n">
         <v>24</v>
       </c>
-      <c r="N134" s="192" t="n">
+      <c r="N134" s="199" t="n">
         <v>8</v>
       </c>
       <c r="O134" s="107">
@@ -15131,13 +15418,13 @@
         <v>45536</v>
       </c>
       <c r="K135" s="81" t="n"/>
-      <c r="L135" s="192" t="n">
+      <c r="L135" s="199" t="n">
         <v>25</v>
       </c>
-      <c r="M135" s="193" t="n">
+      <c r="M135" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N135" s="192" t="n">
+      <c r="N135" s="199" t="n">
         <v>18</v>
       </c>
       <c r="O135" s="107">
@@ -15189,13 +15476,13 @@
         <v>45536</v>
       </c>
       <c r="K136" s="81" t="n"/>
-      <c r="L136" s="192" t="n">
+      <c r="L136" s="199" t="n">
         <v>75</v>
       </c>
-      <c r="M136" s="193" t="n">
+      <c r="M136" s="200" t="n">
         <v>72.5</v>
       </c>
-      <c r="N136" s="192" t="n">
+      <c r="N136" s="199" t="n">
         <v>77</v>
       </c>
       <c r="O136" s="107">
@@ -15250,13 +15537,13 @@
         <v>45536</v>
       </c>
       <c r="K137" s="81" t="n"/>
-      <c r="L137" s="192" t="n">
+      <c r="L137" s="199" t="n">
         <v>51</v>
       </c>
-      <c r="M137" s="193" t="n">
+      <c r="M137" s="200" t="n">
         <v>49</v>
       </c>
-      <c r="N137" s="192" t="n">
+      <c r="N137" s="199" t="n">
         <v>50</v>
       </c>
       <c r="O137" s="107">
@@ -15308,13 +15595,13 @@
         <v>45536</v>
       </c>
       <c r="K138" s="81" t="n"/>
-      <c r="L138" s="192" t="n">
+      <c r="L138" s="199" t="n">
         <v>37</v>
       </c>
-      <c r="M138" s="193" t="n">
+      <c r="M138" s="200" t="n">
         <v>60</v>
       </c>
-      <c r="N138" s="192" t="n">
+      <c r="N138" s="199" t="n">
         <v>20</v>
       </c>
       <c r="O138" s="107">
@@ -15366,13 +15653,13 @@
         <v>45536</v>
       </c>
       <c r="K139" s="81" t="n"/>
-      <c r="L139" s="192" t="n">
+      <c r="L139" s="199" t="n">
         <v>34</v>
       </c>
-      <c r="M139" s="193" t="n">
+      <c r="M139" s="200" t="n">
         <v>39</v>
       </c>
-      <c r="N139" s="192" t="n">
+      <c r="N139" s="199" t="n">
         <v>38</v>
       </c>
       <c r="O139" s="107">
@@ -15424,13 +15711,13 @@
         <v>45536</v>
       </c>
       <c r="K140" s="81" t="n"/>
-      <c r="L140" s="192" t="n">
+      <c r="L140" s="199" t="n">
         <v>56</v>
       </c>
-      <c r="M140" s="193" t="n">
+      <c r="M140" s="200" t="n">
         <v>58</v>
       </c>
-      <c r="N140" s="192" t="n">
+      <c r="N140" s="199" t="n">
         <v>71</v>
       </c>
       <c r="O140" s="107">
@@ -15485,13 +15772,13 @@
         <v>45536</v>
       </c>
       <c r="K141" s="81" t="n"/>
-      <c r="L141" s="192" t="n">
+      <c r="L141" s="199" t="n">
         <v>56.5</v>
       </c>
-      <c r="M141" s="193" t="n">
+      <c r="M141" s="200" t="n">
         <v>69</v>
       </c>
-      <c r="N141" s="192" t="n">
+      <c r="N141" s="199" t="n">
         <v>66</v>
       </c>
       <c r="O141" s="107">
@@ -15546,13 +15833,13 @@
         <v>45536</v>
       </c>
       <c r="K142" s="81" t="n"/>
-      <c r="L142" s="192" t="n">
+      <c r="L142" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M142" s="193" t="n">
+      <c r="M142" s="200" t="n">
         <v>17</v>
       </c>
-      <c r="N142" s="192" t="n">
+      <c r="N142" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="107">
@@ -15604,13 +15891,13 @@
         <v>45536</v>
       </c>
       <c r="K143" s="81" t="n"/>
-      <c r="L143" s="192" t="n">
+      <c r="L143" s="199" t="n">
         <v>28</v>
       </c>
-      <c r="M143" s="193" t="n">
+      <c r="M143" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N143" s="192" t="n">
+      <c r="N143" s="199" t="n">
         <v>33</v>
       </c>
       <c r="O143" s="107">
@@ -15662,13 +15949,13 @@
         <v>45536</v>
       </c>
       <c r="K144" s="81" t="n"/>
-      <c r="L144" s="192" t="n">
+      <c r="L144" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M144" s="193" t="n">
+      <c r="M144" s="200" t="n">
         <v>35</v>
       </c>
-      <c r="N144" s="192" t="n">
+      <c r="N144" s="199" t="n">
         <v>12</v>
       </c>
       <c r="O144" s="107">
@@ -15720,13 +16007,13 @@
         <v>45839</v>
       </c>
       <c r="K145" s="81" t="n"/>
-      <c r="L145" s="192" t="n">
+      <c r="L145" s="199" t="n">
         <v>18</v>
       </c>
-      <c r="M145" s="193" t="n">
+      <c r="M145" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N145" s="192" t="n">
+      <c r="N145" s="199" t="n">
         <v>20</v>
       </c>
       <c r="O145" s="107">
@@ -15778,13 +16065,13 @@
         <v>45536</v>
       </c>
       <c r="K146" s="81" t="n"/>
-      <c r="L146" s="192" t="n">
+      <c r="L146" s="199" t="n">
         <v>27</v>
       </c>
-      <c r="M146" s="193" t="n">
+      <c r="M146" s="200" t="n">
         <v>0</v>
       </c>
-      <c r="N146" s="192" t="n">
+      <c r="N146" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O146" s="107">
@@ -15836,13 +16123,13 @@
         <v>45778</v>
       </c>
       <c r="K147" s="81" t="n"/>
-      <c r="L147" s="192" t="n">
+      <c r="L147" s="199" t="n">
         <v>9</v>
       </c>
-      <c r="M147" s="193" t="n">
+      <c r="M147" s="200" t="n">
         <v>1.5</v>
       </c>
-      <c r="N147" s="192" t="n">
+      <c r="N147" s="199" t="n">
         <v>3</v>
       </c>
       <c r="O147" s="107">
@@ -15894,13 +16181,13 @@
         <v>46018</v>
       </c>
       <c r="K148" s="81" t="n"/>
-      <c r="L148" s="192" t="n">
+      <c r="L148" s="199" t="n">
         <v>45</v>
       </c>
-      <c r="M148" s="193" t="n">
+      <c r="M148" s="200" t="n">
         <v>55</v>
       </c>
-      <c r="N148" s="192" t="n">
+      <c r="N148" s="199" t="n">
         <v>47</v>
       </c>
       <c r="O148" s="107">
@@ -15952,13 +16239,13 @@
         <v>45536</v>
       </c>
       <c r="K149" s="81" t="n"/>
-      <c r="L149" s="192" t="n">
+      <c r="L149" s="199" t="n">
         <v>33</v>
       </c>
-      <c r="M149" s="193" t="n">
+      <c r="M149" s="200" t="n">
         <v>39</v>
       </c>
-      <c r="N149" s="192" t="n">
+      <c r="N149" s="199" t="n">
         <v>35</v>
       </c>
       <c r="O149" s="107">
@@ -16010,13 +16297,13 @@
         <v>45536</v>
       </c>
       <c r="K150" s="81" t="n"/>
-      <c r="L150" s="192" t="n">
+      <c r="L150" s="199" t="n">
         <v>10</v>
       </c>
-      <c r="M150" s="193" t="n">
+      <c r="M150" s="200" t="n">
         <v>8</v>
       </c>
-      <c r="N150" s="192" t="n">
+      <c r="N150" s="199" t="n">
         <v>8</v>
       </c>
       <c r="O150" s="107">
@@ -16068,13 +16355,13 @@
         <v>45536</v>
       </c>
       <c r="K151" s="81" t="n"/>
-      <c r="L151" s="192" t="n">
+      <c r="L151" s="199" t="n">
         <v>26</v>
       </c>
-      <c r="M151" s="193" t="n">
+      <c r="M151" s="200" t="n">
         <v>24</v>
       </c>
-      <c r="N151" s="192" t="n">
+      <c r="N151" s="199" t="n">
         <v>18</v>
       </c>
       <c r="O151" s="107">
@@ -16126,13 +16413,13 @@
         <v>45536</v>
       </c>
       <c r="K152" s="99" t="n"/>
-      <c r="L152" s="194" t="n">
+      <c r="L152" s="201" t="n">
         <v>26</v>
       </c>
-      <c r="M152" s="195" t="n">
+      <c r="M152" s="202" t="n">
         <v>0</v>
       </c>
-      <c r="N152" s="192" t="n">
+      <c r="N152" s="199" t="n">
         <v>0</v>
       </c>
       <c r="O152" s="107">
@@ -16184,13 +16471,13 @@
         <v>45536</v>
       </c>
       <c r="K153" s="99" t="n"/>
-      <c r="L153" s="194" t="n">
+      <c r="L153" s="201" t="n">
         <v>36</v>
       </c>
-      <c r="M153" s="195" t="n">
+      <c r="M153" s="202" t="n">
         <v>49</v>
       </c>
-      <c r="N153" s="192" t="n">
+      <c r="N153" s="199" t="n">
         <v>49</v>
       </c>
       <c r="O153" s="107">
@@ -16227,11 +16514,11 @@
         <f>SUM(N3:N153)</f>
         <v/>
       </c>
-      <c r="O154" s="196">
+      <c r="O154" s="203">
         <f>SUM(O3:O153)</f>
         <v/>
       </c>
-      <c r="P154" s="196">
+      <c r="P154" s="203">
         <f>SUM(P3:P153)</f>
         <v/>
       </c>

--- a/주52시간_3개월_현황_요약_0902.xlsx
+++ b/주52시간_3개월_현황_요약_0902.xlsx
@@ -7,13 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="0.요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="아모레 업무" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="아모레 생산" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1.10월예측" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="아모레 업무" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="아모레 생산" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0.요약'!$A$1:$R$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1.10월예측'!$A$1:$R$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -232,8 +234,13 @@
       <color rgb="00C00000"/>
       <sz val="7.5"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -285,6 +292,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -890,7 +902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1484,6 +1496,69 @@
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1984,23 +2059,6 @@
           <t>3개월 탄력근로 단위기간(7·8·9월) 연장근로 현황 — 요약</t>
         </is>
       </c>
-      <c r="B1" s="132" t="n"/>
-      <c r="C1" s="132" t="n"/>
-      <c r="D1" s="132" t="n"/>
-      <c r="E1" s="132" t="n"/>
-      <c r="F1" s="132" t="n"/>
-      <c r="G1" s="132" t="n"/>
-      <c r="H1" s="132" t="n"/>
-      <c r="I1" s="132" t="n"/>
-      <c r="J1" s="132" t="n"/>
-      <c r="K1" s="132" t="n"/>
-      <c r="L1" s="132" t="n"/>
-      <c r="M1" s="132" t="n"/>
-      <c r="N1" s="132" t="n"/>
-      <c r="O1" s="132" t="n"/>
-      <c r="P1" s="132" t="n"/>
-      <c r="Q1" s="132" t="n"/>
-      <c r="R1" s="132" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1" s="130">
       <c r="A2" s="133" t="inlineStr">
@@ -2008,23 +2066,23 @@
           <t>단위기간 4·5·6월 / 7·8·9월 / 10·11·12월  ·  기간 한도 156H(12H/주 × 13주)  ·  9월 잔여 = 156H − (7월+8월)  |  6월은 직전 단위기간이므로 현 구간 계산 제외  |  원본 2개 시트 미수정  ·  2026.09.02</t>
         </is>
       </c>
-      <c r="B2" s="134" t="n"/>
-      <c r="C2" s="134" t="n"/>
-      <c r="D2" s="134" t="n"/>
-      <c r="E2" s="134" t="n"/>
-      <c r="F2" s="134" t="n"/>
-      <c r="G2" s="134" t="n"/>
-      <c r="H2" s="134" t="n"/>
-      <c r="I2" s="134" t="n"/>
-      <c r="J2" s="134" t="n"/>
-      <c r="K2" s="134" t="n"/>
-      <c r="L2" s="134" t="n"/>
-      <c r="M2" s="134" t="n"/>
-      <c r="N2" s="134" t="n"/>
-      <c r="O2" s="134" t="n"/>
-      <c r="P2" s="134" t="n"/>
-      <c r="Q2" s="134" t="n"/>
-      <c r="R2" s="134" t="n"/>
+      <c r="B2" s="204" t="n"/>
+      <c r="C2" s="204" t="n"/>
+      <c r="D2" s="204" t="n"/>
+      <c r="E2" s="204" t="n"/>
+      <c r="F2" s="204" t="n"/>
+      <c r="G2" s="204" t="n"/>
+      <c r="H2" s="204" t="n"/>
+      <c r="I2" s="204" t="n"/>
+      <c r="J2" s="204" t="n"/>
+      <c r="K2" s="204" t="n"/>
+      <c r="L2" s="204" t="n"/>
+      <c r="M2" s="204" t="n"/>
+      <c r="N2" s="204" t="n"/>
+      <c r="O2" s="204" t="n"/>
+      <c r="P2" s="204" t="n"/>
+      <c r="Q2" s="204" t="n"/>
+      <c r="R2" s="205" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1" s="130">
       <c r="A3" s="135" t="inlineStr">
@@ -2032,23 +2090,6 @@
           <t>① 전체 현황</t>
         </is>
       </c>
-      <c r="B3" s="136" t="n"/>
-      <c r="C3" s="136" t="n"/>
-      <c r="D3" s="136" t="n"/>
-      <c r="E3" s="136" t="n"/>
-      <c r="F3" s="136" t="n"/>
-      <c r="G3" s="136" t="n"/>
-      <c r="H3" s="136" t="n"/>
-      <c r="I3" s="136" t="n"/>
-      <c r="J3" s="136" t="n"/>
-      <c r="K3" s="136" t="n"/>
-      <c r="L3" s="136" t="n"/>
-      <c r="M3" s="136" t="n"/>
-      <c r="N3" s="136" t="n"/>
-      <c r="O3" s="136" t="n"/>
-      <c r="P3" s="136" t="n"/>
-      <c r="Q3" s="136" t="n"/>
-      <c r="R3" s="136" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1" s="130">
       <c r="A4" s="137" t="inlineStr">
@@ -2101,14 +2142,14 @@
           <t>판정</t>
         </is>
       </c>
-      <c r="K4" s="139" t="n"/>
-      <c r="L4" s="139" t="n"/>
-      <c r="M4" s="139" t="n"/>
-      <c r="N4" s="139" t="n"/>
-      <c r="O4" s="139" t="n"/>
-      <c r="P4" s="139" t="n"/>
-      <c r="Q4" s="139" t="n"/>
-      <c r="R4" s="139" t="n"/>
+      <c r="K4" s="204" t="n"/>
+      <c r="L4" s="204" t="n"/>
+      <c r="M4" s="204" t="n"/>
+      <c r="N4" s="204" t="n"/>
+      <c r="O4" s="204" t="n"/>
+      <c r="P4" s="204" t="n"/>
+      <c r="Q4" s="204" t="n"/>
+      <c r="R4" s="205" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1" s="130">
       <c r="A5" s="140" t="inlineStr">
@@ -2145,14 +2186,14 @@
           <t>현 단위기간(7·8·9월) 7·8월 소진 14,354H · 인당 60H (한도 156H의 39%)</t>
         </is>
       </c>
-      <c r="K5" s="146" t="n"/>
-      <c r="L5" s="146" t="n"/>
-      <c r="M5" s="146" t="n"/>
-      <c r="N5" s="146" t="n"/>
-      <c r="O5" s="146" t="n"/>
-      <c r="P5" s="146" t="n"/>
-      <c r="Q5" s="146" t="n"/>
-      <c r="R5" s="146" t="n"/>
+      <c r="K5" s="204" t="n"/>
+      <c r="L5" s="204" t="n"/>
+      <c r="M5" s="204" t="n"/>
+      <c r="N5" s="204" t="n"/>
+      <c r="O5" s="204" t="n"/>
+      <c r="P5" s="204" t="n"/>
+      <c r="Q5" s="204" t="n"/>
+      <c r="R5" s="205" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1" s="130">
       <c r="A6" s="140" t="inlineStr">
@@ -2189,14 +2230,14 @@
           <t>9월 잔여 연장 전사 23,032H · 인당 96H — 9월 잔업·특근의 상한</t>
         </is>
       </c>
-      <c r="K6" s="148" t="n"/>
-      <c r="L6" s="148" t="n"/>
-      <c r="M6" s="148" t="n"/>
-      <c r="N6" s="148" t="n"/>
-      <c r="O6" s="148" t="n"/>
-      <c r="P6" s="148" t="n"/>
-      <c r="Q6" s="148" t="n"/>
-      <c r="R6" s="148" t="n"/>
+      <c r="K6" s="204" t="n"/>
+      <c r="L6" s="204" t="n"/>
+      <c r="M6" s="204" t="n"/>
+      <c r="N6" s="204" t="n"/>
+      <c r="O6" s="204" t="n"/>
+      <c r="P6" s="204" t="n"/>
+      <c r="Q6" s="204" t="n"/>
+      <c r="R6" s="205" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1" s="130">
       <c r="A7" s="140" t="inlineStr">
@@ -2233,14 +2274,14 @@
           <t>잔여 0H 4명 · 30H 미만 19명  |  10월부터 새 단위기간 → 156H 리셋</t>
         </is>
       </c>
-      <c r="K7" s="148" t="n"/>
-      <c r="L7" s="148" t="n"/>
-      <c r="M7" s="148" t="n"/>
-      <c r="N7" s="148" t="n"/>
-      <c r="O7" s="148" t="n"/>
-      <c r="P7" s="148" t="n"/>
-      <c r="Q7" s="148" t="n"/>
-      <c r="R7" s="148" t="n"/>
+      <c r="K7" s="204" t="n"/>
+      <c r="L7" s="204" t="n"/>
+      <c r="M7" s="204" t="n"/>
+      <c r="N7" s="204" t="n"/>
+      <c r="O7" s="204" t="n"/>
+      <c r="P7" s="204" t="n"/>
+      <c r="Q7" s="204" t="n"/>
+      <c r="R7" s="205" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1" s="130">
       <c r="A8" s="135" t="inlineStr">
@@ -2248,23 +2289,6 @@
           <t>② 공정 · 라인별 현황 및 9월 여력</t>
         </is>
       </c>
-      <c r="B8" s="136" t="n"/>
-      <c r="C8" s="136" t="n"/>
-      <c r="D8" s="136" t="n"/>
-      <c r="E8" s="136" t="n"/>
-      <c r="F8" s="136" t="n"/>
-      <c r="G8" s="136" t="n"/>
-      <c r="H8" s="136" t="n"/>
-      <c r="I8" s="136" t="n"/>
-      <c r="J8" s="136" t="n"/>
-      <c r="K8" s="136" t="n"/>
-      <c r="L8" s="136" t="n"/>
-      <c r="M8" s="136" t="n"/>
-      <c r="N8" s="136" t="n"/>
-      <c r="O8" s="136" t="n"/>
-      <c r="P8" s="136" t="n"/>
-      <c r="Q8" s="136" t="n"/>
-      <c r="R8" s="136" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1" s="130">
       <c r="A9" s="137" t="inlineStr">
@@ -2901,23 +2925,6 @@
           <t>③ 9월 잔여 연장시간 하위 30명 — 잔업·특근 편성 시 우선 배제 (진한 음영 = 잔여 0H)</t>
         </is>
       </c>
-      <c r="B18" s="136" t="n"/>
-      <c r="C18" s="136" t="n"/>
-      <c r="D18" s="136" t="n"/>
-      <c r="E18" s="136" t="n"/>
-      <c r="F18" s="136" t="n"/>
-      <c r="G18" s="136" t="n"/>
-      <c r="H18" s="136" t="n"/>
-      <c r="I18" s="136" t="n"/>
-      <c r="J18" s="136" t="n"/>
-      <c r="K18" s="136" t="n"/>
-      <c r="L18" s="136" t="n"/>
-      <c r="M18" s="136" t="n"/>
-      <c r="N18" s="136" t="n"/>
-      <c r="O18" s="136" t="n"/>
-      <c r="P18" s="136" t="n"/>
-      <c r="Q18" s="136" t="n"/>
-      <c r="R18" s="136" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1" s="130">
       <c r="A19" s="137" t="inlineStr">
@@ -3357,23 +3364,6 @@
           <t>④ 38주 대응전략 연계 판정</t>
         </is>
       </c>
-      <c r="B25" s="136" t="n"/>
-      <c r="C25" s="136" t="n"/>
-      <c r="D25" s="136" t="n"/>
-      <c r="E25" s="136" t="n"/>
-      <c r="F25" s="136" t="n"/>
-      <c r="G25" s="136" t="n"/>
-      <c r="H25" s="136" t="n"/>
-      <c r="I25" s="136" t="n"/>
-      <c r="J25" s="136" t="n"/>
-      <c r="K25" s="136" t="n"/>
-      <c r="L25" s="136" t="n"/>
-      <c r="M25" s="136" t="n"/>
-      <c r="N25" s="136" t="n"/>
-      <c r="O25" s="136" t="n"/>
-      <c r="P25" s="136" t="n"/>
-      <c r="Q25" s="136" t="n"/>
-      <c r="R25" s="136" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1" s="130">
       <c r="A26" s="138" t="inlineStr">
@@ -3381,31 +3371,31 @@
           <t>38주 대안</t>
         </is>
       </c>
-      <c r="B26" s="139" t="n"/>
-      <c r="C26" s="139" t="n"/>
-      <c r="D26" s="139" t="n"/>
+      <c r="B26" s="204" t="n"/>
+      <c r="C26" s="204" t="n"/>
+      <c r="D26" s="205" t="n"/>
       <c r="E26" s="138" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="F26" s="139" t="n"/>
+      <c r="F26" s="205" t="n"/>
       <c r="G26" s="138" t="inlineStr">
         <is>
           <t>근거 (근로시간)</t>
         </is>
       </c>
-      <c r="H26" s="139" t="n"/>
-      <c r="I26" s="139" t="n"/>
-      <c r="J26" s="139" t="n"/>
-      <c r="K26" s="139" t="n"/>
-      <c r="L26" s="139" t="n"/>
-      <c r="M26" s="139" t="n"/>
-      <c r="N26" s="139" t="n"/>
-      <c r="O26" s="139" t="n"/>
-      <c r="P26" s="139" t="n"/>
-      <c r="Q26" s="139" t="n"/>
-      <c r="R26" s="139" t="n"/>
+      <c r="H26" s="204" t="n"/>
+      <c r="I26" s="204" t="n"/>
+      <c r="J26" s="204" t="n"/>
+      <c r="K26" s="204" t="n"/>
+      <c r="L26" s="204" t="n"/>
+      <c r="M26" s="204" t="n"/>
+      <c r="N26" s="204" t="n"/>
+      <c r="O26" s="204" t="n"/>
+      <c r="P26" s="204" t="n"/>
+      <c r="Q26" s="204" t="n"/>
+      <c r="R26" s="205" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1" s="130">
       <c r="A27" s="168" t="inlineStr">
@@ -3413,31 +3403,31 @@
           <t>[전제] 야간 편성과 근로시간의 관계</t>
         </is>
       </c>
-      <c r="B27" s="146" t="n"/>
-      <c r="C27" s="146" t="n"/>
-      <c r="D27" s="146" t="n"/>
+      <c r="B27" s="204" t="n"/>
+      <c r="C27" s="204" t="n"/>
+      <c r="D27" s="205" t="n"/>
       <c r="E27" s="157" t="inlineStr">
         <is>
           <t>구분 필요</t>
         </is>
       </c>
-      <c r="F27" s="169" t="n"/>
+      <c r="F27" s="205" t="n"/>
       <c r="G27" s="170" t="inlineStr">
         <is>
           <t>주야 2조를 각 8H 소정근로로 편성하면 연장근로는 발생하지 않음 — 156H 한도와 무관. 야간은 가산수당 50% · 여성 야간근로 동의(근기법 §70②) · 특수건강진단이 제약. 한도가 걸리는 것은 기존 인원에게 잔업으로 야간을 얹는 경우</t>
         </is>
       </c>
-      <c r="H27" s="134" t="n"/>
-      <c r="I27" s="134" t="n"/>
-      <c r="J27" s="134" t="n"/>
-      <c r="K27" s="134" t="n"/>
-      <c r="L27" s="134" t="n"/>
-      <c r="M27" s="134" t="n"/>
-      <c r="N27" s="134" t="n"/>
-      <c r="O27" s="134" t="n"/>
-      <c r="P27" s="134" t="n"/>
-      <c r="Q27" s="134" t="n"/>
-      <c r="R27" s="134" t="n"/>
+      <c r="H27" s="204" t="n"/>
+      <c r="I27" s="204" t="n"/>
+      <c r="J27" s="204" t="n"/>
+      <c r="K27" s="204" t="n"/>
+      <c r="L27" s="204" t="n"/>
+      <c r="M27" s="204" t="n"/>
+      <c r="N27" s="204" t="n"/>
+      <c r="O27" s="204" t="n"/>
+      <c r="P27" s="204" t="n"/>
+      <c r="Q27" s="204" t="n"/>
+      <c r="R27" s="205" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1" s="130">
       <c r="A28" s="168" t="inlineStr">
@@ -3445,31 +3435,31 @@
           <t>세정 1안) 2대 주야 맞교대</t>
         </is>
       </c>
-      <c r="B28" s="146" t="n"/>
-      <c r="C28" s="146" t="n"/>
-      <c r="D28" s="146" t="n"/>
+      <c r="B28" s="204" t="n"/>
+      <c r="C28" s="204" t="n"/>
+      <c r="D28" s="205" t="n"/>
       <c r="E28" s="157" t="inlineStr">
         <is>
           <t>인원 문제</t>
         </is>
       </c>
-      <c r="F28" s="169" t="n"/>
+      <c r="F28" s="205" t="n"/>
       <c r="G28" s="170" t="inlineStr">
         <is>
           <t>별도 조 편성이면 근로시간 한도 아님. 지원 7명 차출 시 원 소속 공백을 잔업으로 메우면 그때 한도가 걸림 — 창고 100H·로봇 101H·내용물 69H는 여유, 세척 59H가 병목</t>
         </is>
       </c>
-      <c r="H28" s="134" t="n"/>
-      <c r="I28" s="134" t="n"/>
-      <c r="J28" s="134" t="n"/>
-      <c r="K28" s="134" t="n"/>
-      <c r="L28" s="134" t="n"/>
-      <c r="M28" s="134" t="n"/>
-      <c r="N28" s="134" t="n"/>
-      <c r="O28" s="134" t="n"/>
-      <c r="P28" s="134" t="n"/>
-      <c r="Q28" s="134" t="n"/>
-      <c r="R28" s="134" t="n"/>
+      <c r="H28" s="204" t="n"/>
+      <c r="I28" s="204" t="n"/>
+      <c r="J28" s="204" t="n"/>
+      <c r="K28" s="204" t="n"/>
+      <c r="L28" s="204" t="n"/>
+      <c r="M28" s="204" t="n"/>
+      <c r="N28" s="204" t="n"/>
+      <c r="O28" s="204" t="n"/>
+      <c r="P28" s="204" t="n"/>
+      <c r="Q28" s="204" t="n"/>
+      <c r="R28" s="205" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1" s="130">
       <c r="A29" s="168" t="inlineStr">
@@ -3477,31 +3467,31 @@
           <t>세정 2안) 직선 1대 Full 잔특</t>
         </is>
       </c>
-      <c r="B29" s="146" t="n"/>
-      <c r="C29" s="146" t="n"/>
-      <c r="D29" s="146" t="n"/>
+      <c r="B29" s="204" t="n"/>
+      <c r="C29" s="204" t="n"/>
+      <c r="D29" s="205" t="n"/>
       <c r="E29" s="158" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
-      <c r="F29" s="171" t="n"/>
+      <c r="F29" s="205" t="n"/>
       <c r="G29" s="170" t="inlineStr">
         <is>
           <t>순수 잔업·특근이라 잔여 직결. 직선 24명 1,902H(인당 79H) · 염모 27명 3,712H(인당 138H) — 염모 전용이 유리</t>
         </is>
       </c>
-      <c r="H29" s="134" t="n"/>
-      <c r="I29" s="134" t="n"/>
-      <c r="J29" s="134" t="n"/>
-      <c r="K29" s="134" t="n"/>
-      <c r="L29" s="134" t="n"/>
-      <c r="M29" s="134" t="n"/>
-      <c r="N29" s="134" t="n"/>
-      <c r="O29" s="134" t="n"/>
-      <c r="P29" s="134" t="n"/>
-      <c r="Q29" s="134" t="n"/>
-      <c r="R29" s="134" t="n"/>
+      <c r="H29" s="204" t="n"/>
+      <c r="I29" s="204" t="n"/>
+      <c r="J29" s="204" t="n"/>
+      <c r="K29" s="204" t="n"/>
+      <c r="L29" s="204" t="n"/>
+      <c r="M29" s="204" t="n"/>
+      <c r="N29" s="204" t="n"/>
+      <c r="O29" s="204" t="n"/>
+      <c r="P29" s="204" t="n"/>
+      <c r="Q29" s="204" t="n"/>
+      <c r="R29" s="205" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1" s="130">
       <c r="A30" s="168" t="inlineStr">
@@ -3509,31 +3499,31 @@
           <t>멀티 2안) 7·8호기 주야</t>
         </is>
       </c>
-      <c r="B30" s="146" t="n"/>
-      <c r="C30" s="146" t="n"/>
-      <c r="D30" s="146" t="n"/>
+      <c r="B30" s="204" t="n"/>
+      <c r="C30" s="204" t="n"/>
+      <c r="D30" s="205" t="n"/>
       <c r="E30" s="157" t="inlineStr">
         <is>
           <t>인원 문제</t>
         </is>
       </c>
-      <c r="F30" s="169" t="n"/>
+      <c r="F30" s="205" t="n"/>
       <c r="G30" s="170" t="inlineStr">
         <is>
           <t>세정 1안과 동일 구조. 잔업 부가 시 멀티 20명 1,631H(인당 82H), 잔여 50H 미만 4명 제외 편성</t>
         </is>
       </c>
-      <c r="H30" s="134" t="n"/>
-      <c r="I30" s="134" t="n"/>
-      <c r="J30" s="134" t="n"/>
-      <c r="K30" s="134" t="n"/>
-      <c r="L30" s="134" t="n"/>
-      <c r="M30" s="134" t="n"/>
-      <c r="N30" s="134" t="n"/>
-      <c r="O30" s="134" t="n"/>
-      <c r="P30" s="134" t="n"/>
-      <c r="Q30" s="134" t="n"/>
-      <c r="R30" s="134" t="n"/>
+      <c r="H30" s="204" t="n"/>
+      <c r="I30" s="204" t="n"/>
+      <c r="J30" s="204" t="n"/>
+      <c r="K30" s="204" t="n"/>
+      <c r="L30" s="204" t="n"/>
+      <c r="M30" s="204" t="n"/>
+      <c r="N30" s="204" t="n"/>
+      <c r="O30" s="204" t="n"/>
+      <c r="P30" s="204" t="n"/>
+      <c r="Q30" s="204" t="n"/>
+      <c r="R30" s="205" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1" s="130">
       <c r="A31" s="168" t="inlineStr">
@@ -3541,31 +3531,31 @@
           <t>튜브) 9/14 2Shift 1대 추가</t>
         </is>
       </c>
-      <c r="B31" s="146" t="n"/>
-      <c r="C31" s="146" t="n"/>
-      <c r="D31" s="146" t="n"/>
+      <c r="B31" s="204" t="n"/>
+      <c r="C31" s="204" t="n"/>
+      <c r="D31" s="205" t="n"/>
       <c r="E31" s="158" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
-      <c r="F31" s="171" t="n"/>
+      <c r="F31" s="205" t="n"/>
       <c r="G31" s="170" t="inlineStr">
         <is>
           <t>튜브 17명 1,287H(인당 76H) · 잔여 부족 2명(최명필 21H·김진만 24H) 제외 시 여력 있음</t>
         </is>
       </c>
-      <c r="H31" s="134" t="n"/>
-      <c r="I31" s="134" t="n"/>
-      <c r="J31" s="134" t="n"/>
-      <c r="K31" s="134" t="n"/>
-      <c r="L31" s="134" t="n"/>
-      <c r="M31" s="134" t="n"/>
-      <c r="N31" s="134" t="n"/>
-      <c r="O31" s="134" t="n"/>
-      <c r="P31" s="134" t="n"/>
-      <c r="Q31" s="134" t="n"/>
-      <c r="R31" s="134" t="n"/>
+      <c r="H31" s="204" t="n"/>
+      <c r="I31" s="204" t="n"/>
+      <c r="J31" s="204" t="n"/>
+      <c r="K31" s="204" t="n"/>
+      <c r="L31" s="204" t="n"/>
+      <c r="M31" s="204" t="n"/>
+      <c r="N31" s="204" t="n"/>
+      <c r="O31" s="204" t="n"/>
+      <c r="P31" s="204" t="n"/>
+      <c r="Q31" s="204" t="n"/>
+      <c r="R31" s="205" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1" s="130">
       <c r="A32" s="168" t="inlineStr">
@@ -3573,31 +3563,31 @@
           <t>튜브) 간접(주임) → 직접화</t>
         </is>
       </c>
-      <c r="B32" s="146" t="n"/>
-      <c r="C32" s="146" t="n"/>
-      <c r="D32" s="146" t="n"/>
+      <c r="B32" s="204" t="n"/>
+      <c r="C32" s="204" t="n"/>
+      <c r="D32" s="205" t="n"/>
       <c r="E32" s="155" t="inlineStr">
         <is>
           <t>불가</t>
         </is>
       </c>
-      <c r="F32" s="148" t="n"/>
+      <c r="F32" s="205" t="n"/>
       <c r="G32" s="170" t="inlineStr">
         <is>
           <t>관리업무에 직접작업을 더하는 구조라 연장 발생 불가피. 주임 3명 잔여 74H(인당 25H) 전 직책 최저</t>
         </is>
       </c>
-      <c r="H32" s="134" t="n"/>
-      <c r="I32" s="134" t="n"/>
-      <c r="J32" s="134" t="n"/>
-      <c r="K32" s="134" t="n"/>
-      <c r="L32" s="134" t="n"/>
-      <c r="M32" s="134" t="n"/>
-      <c r="N32" s="134" t="n"/>
-      <c r="O32" s="134" t="n"/>
-      <c r="P32" s="134" t="n"/>
-      <c r="Q32" s="134" t="n"/>
-      <c r="R32" s="134" t="n"/>
+      <c r="H32" s="204" t="n"/>
+      <c r="I32" s="204" t="n"/>
+      <c r="J32" s="204" t="n"/>
+      <c r="K32" s="204" t="n"/>
+      <c r="L32" s="204" t="n"/>
+      <c r="M32" s="204" t="n"/>
+      <c r="N32" s="204" t="n"/>
+      <c r="O32" s="204" t="n"/>
+      <c r="P32" s="204" t="n"/>
+      <c r="Q32" s="204" t="n"/>
+      <c r="R32" s="205" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1" s="130">
       <c r="A33" s="168" t="inlineStr">
@@ -3605,31 +3595,31 @@
           <t>10월 1·2주 연속 특근</t>
         </is>
       </c>
-      <c r="B33" s="146" t="n"/>
-      <c r="C33" s="146" t="n"/>
-      <c r="D33" s="146" t="n"/>
+      <c r="B33" s="204" t="n"/>
+      <c r="C33" s="204" t="n"/>
+      <c r="D33" s="205" t="n"/>
       <c r="E33" s="158" t="inlineStr">
         <is>
           <t>한도 여유</t>
         </is>
       </c>
-      <c r="F33" s="171" t="n"/>
+      <c r="F33" s="205" t="n"/>
       <c r="G33" s="170" t="inlineStr">
         <is>
           <t>10월부터 새 단위기간(10·11·12월) → 156H 리셋되어 근로시간 한도로는 막히지 않음. 남는 제약은 휴일근로 동의 · 가산수당 · 추석 직후 3주 연속 무휴 피로도 → 3안(9/23) 권고</t>
         </is>
       </c>
-      <c r="H33" s="134" t="n"/>
-      <c r="I33" s="134" t="n"/>
-      <c r="J33" s="134" t="n"/>
-      <c r="K33" s="134" t="n"/>
-      <c r="L33" s="134" t="n"/>
-      <c r="M33" s="134" t="n"/>
-      <c r="N33" s="134" t="n"/>
-      <c r="O33" s="134" t="n"/>
-      <c r="P33" s="134" t="n"/>
-      <c r="Q33" s="134" t="n"/>
-      <c r="R33" s="134" t="n"/>
+      <c r="H33" s="204" t="n"/>
+      <c r="I33" s="204" t="n"/>
+      <c r="J33" s="204" t="n"/>
+      <c r="K33" s="204" t="n"/>
+      <c r="L33" s="204" t="n"/>
+      <c r="M33" s="204" t="n"/>
+      <c r="N33" s="204" t="n"/>
+      <c r="O33" s="204" t="n"/>
+      <c r="P33" s="204" t="n"/>
+      <c r="Q33" s="204" t="n"/>
+      <c r="R33" s="205" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1" s="130">
       <c r="A34" s="135" t="inlineStr">
@@ -3637,23 +3627,6 @@
           <t>⑤ 9월 토요 특근 시나리오 — 잔여 대비 소요</t>
         </is>
       </c>
-      <c r="B34" s="136" t="n"/>
-      <c r="C34" s="136" t="n"/>
-      <c r="D34" s="136" t="n"/>
-      <c r="E34" s="136" t="n"/>
-      <c r="F34" s="136" t="n"/>
-      <c r="G34" s="136" t="n"/>
-      <c r="H34" s="136" t="n"/>
-      <c r="I34" s="136" t="n"/>
-      <c r="J34" s="136" t="n"/>
-      <c r="K34" s="136" t="n"/>
-      <c r="L34" s="136" t="n"/>
-      <c r="M34" s="136" t="n"/>
-      <c r="N34" s="136" t="n"/>
-      <c r="O34" s="136" t="n"/>
-      <c r="P34" s="136" t="n"/>
-      <c r="Q34" s="136" t="n"/>
-      <c r="R34" s="136" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="130">
       <c r="A35" s="138" t="inlineStr">
@@ -3661,15 +3634,15 @@
           <t>특근 횟수</t>
         </is>
       </c>
-      <c r="B35" s="139" t="n"/>
-      <c r="C35" s="139" t="n"/>
+      <c r="B35" s="204" t="n"/>
+      <c r="C35" s="205" t="n"/>
       <c r="D35" s="138" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="E35" s="139" t="n"/>
-      <c r="F35" s="139" t="n"/>
+      <c r="E35" s="204" t="n"/>
+      <c r="F35" s="205" t="n"/>
       <c r="G35" s="138" t="inlineStr">
         <is>
           <t>인당 소요</t>
@@ -3680,7 +3653,7 @@
           <t>전사 소요(H)</t>
         </is>
       </c>
-      <c r="I35" s="139" t="n"/>
+      <c r="I35" s="205" t="n"/>
       <c r="J35" s="138" t="inlineStr">
         <is>
           <t>잔여 대비</t>
@@ -3691,17 +3664,17 @@
           <t>편성 불가</t>
         </is>
       </c>
-      <c r="L35" s="139" t="n"/>
+      <c r="L35" s="205" t="n"/>
       <c r="M35" s="138" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="N35" s="139" t="n"/>
-      <c r="O35" s="139" t="n"/>
-      <c r="P35" s="139" t="n"/>
-      <c r="Q35" s="139" t="n"/>
-      <c r="R35" s="139" t="n"/>
+      <c r="N35" s="204" t="n"/>
+      <c r="O35" s="204" t="n"/>
+      <c r="P35" s="204" t="n"/>
+      <c r="Q35" s="204" t="n"/>
+      <c r="R35" s="205" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1" s="130">
       <c r="A36" s="140" t="inlineStr">
@@ -3709,15 +3682,15 @@
           <t>1회</t>
         </is>
       </c>
-      <c r="B36" s="146" t="n"/>
-      <c r="C36" s="146" t="n"/>
+      <c r="B36" s="204" t="n"/>
+      <c r="C36" s="205" t="n"/>
       <c r="D36" s="172" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
-      <c r="E36" s="134" t="n"/>
-      <c r="F36" s="134" t="n"/>
+      <c r="E36" s="204" t="n"/>
+      <c r="F36" s="205" t="n"/>
       <c r="G36" s="172" t="inlineStr">
         <is>
           <t>8H</t>
@@ -3726,7 +3699,7 @@
       <c r="H36" s="141" t="n">
         <v>1912</v>
       </c>
-      <c r="I36" s="134" t="n"/>
+      <c r="I36" s="205" t="n"/>
       <c r="J36" s="173" t="inlineStr">
         <is>
           <t>8%</t>
@@ -3737,17 +3710,17 @@
           <t>6명</t>
         </is>
       </c>
-      <c r="L36" s="134" t="n"/>
+      <c r="L36" s="205" t="n"/>
       <c r="M36" s="175" t="inlineStr">
         <is>
           <t>여유</t>
         </is>
       </c>
-      <c r="N36" s="171" t="n"/>
-      <c r="O36" s="171" t="n"/>
-      <c r="P36" s="171" t="n"/>
-      <c r="Q36" s="171" t="n"/>
-      <c r="R36" s="171" t="n"/>
+      <c r="N36" s="204" t="n"/>
+      <c r="O36" s="204" t="n"/>
+      <c r="P36" s="204" t="n"/>
+      <c r="Q36" s="204" t="n"/>
+      <c r="R36" s="205" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1" s="130">
       <c r="A37" s="140" t="inlineStr">
@@ -3755,15 +3728,15 @@
           <t>2회</t>
         </is>
       </c>
-      <c r="B37" s="146" t="n"/>
-      <c r="C37" s="146" t="n"/>
+      <c r="B37" s="204" t="n"/>
+      <c r="C37" s="205" t="n"/>
       <c r="D37" s="172" t="inlineStr">
         <is>
           <t>9/5 · 12</t>
         </is>
       </c>
-      <c r="E37" s="134" t="n"/>
-      <c r="F37" s="134" t="n"/>
+      <c r="E37" s="204" t="n"/>
+      <c r="F37" s="205" t="n"/>
       <c r="G37" s="172" t="inlineStr">
         <is>
           <t>16H</t>
@@ -3772,7 +3745,7 @@
       <c r="H37" s="141" t="n">
         <v>3824</v>
       </c>
-      <c r="I37" s="134" t="n"/>
+      <c r="I37" s="205" t="n"/>
       <c r="J37" s="173" t="inlineStr">
         <is>
           <t>17%</t>
@@ -3783,17 +3756,17 @@
           <t>7명</t>
         </is>
       </c>
-      <c r="L37" s="134" t="n"/>
+      <c r="L37" s="205" t="n"/>
       <c r="M37" s="175" t="inlineStr">
         <is>
           <t>여유</t>
         </is>
       </c>
-      <c r="N37" s="171" t="n"/>
-      <c r="O37" s="171" t="n"/>
-      <c r="P37" s="171" t="n"/>
-      <c r="Q37" s="171" t="n"/>
-      <c r="R37" s="171" t="n"/>
+      <c r="N37" s="204" t="n"/>
+      <c r="O37" s="204" t="n"/>
+      <c r="P37" s="204" t="n"/>
+      <c r="Q37" s="204" t="n"/>
+      <c r="R37" s="205" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1" s="130">
       <c r="A38" s="140" t="inlineStr">
@@ -3801,15 +3774,15 @@
           <t>3회</t>
         </is>
       </c>
-      <c r="B38" s="146" t="n"/>
-      <c r="C38" s="146" t="n"/>
+      <c r="B38" s="204" t="n"/>
+      <c r="C38" s="205" t="n"/>
       <c r="D38" s="172" t="inlineStr">
         <is>
           <t>9/5 · 12 · 19</t>
         </is>
       </c>
-      <c r="E38" s="134" t="n"/>
-      <c r="F38" s="134" t="n"/>
+      <c r="E38" s="204" t="n"/>
+      <c r="F38" s="205" t="n"/>
       <c r="G38" s="172" t="inlineStr">
         <is>
           <t>24H</t>
@@ -3818,7 +3791,7 @@
       <c r="H38" s="141" t="n">
         <v>5736</v>
       </c>
-      <c r="I38" s="134" t="n"/>
+      <c r="I38" s="205" t="n"/>
       <c r="J38" s="173" t="inlineStr">
         <is>
           <t>25%</t>
@@ -3829,17 +3802,17 @@
           <t>11명</t>
         </is>
       </c>
-      <c r="L38" s="134" t="n"/>
+      <c r="L38" s="205" t="n"/>
       <c r="M38" s="175" t="inlineStr">
         <is>
           <t>권장 상한 — 세척실 5명(김영두·박태근·이세호·한인수·선우찬) 제외 편성</t>
         </is>
       </c>
-      <c r="N38" s="171" t="n"/>
-      <c r="O38" s="171" t="n"/>
-      <c r="P38" s="171" t="n"/>
-      <c r="Q38" s="171" t="n"/>
-      <c r="R38" s="171" t="n"/>
+      <c r="N38" s="204" t="n"/>
+      <c r="O38" s="204" t="n"/>
+      <c r="P38" s="204" t="n"/>
+      <c r="Q38" s="204" t="n"/>
+      <c r="R38" s="205" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1" s="130">
       <c r="A39" s="140" t="inlineStr">
@@ -3847,15 +3820,15 @@
           <t>4회</t>
         </is>
       </c>
-      <c r="B39" s="146" t="n"/>
-      <c r="C39" s="146" t="n"/>
+      <c r="B39" s="204" t="n"/>
+      <c r="C39" s="205" t="n"/>
       <c r="D39" s="172" t="inlineStr">
         <is>
           <t>+ 9/26 (추석 연휴)</t>
         </is>
       </c>
-      <c r="E39" s="134" t="n"/>
-      <c r="F39" s="134" t="n"/>
+      <c r="E39" s="204" t="n"/>
+      <c r="F39" s="205" t="n"/>
       <c r="G39" s="172" t="inlineStr">
         <is>
           <t>32H</t>
@@ -3864,7 +3837,7 @@
       <c r="H39" s="141" t="n">
         <v>7648</v>
       </c>
-      <c r="I39" s="134" t="n"/>
+      <c r="I39" s="205" t="n"/>
       <c r="J39" s="173" t="inlineStr">
         <is>
           <t>33%</t>
@@ -3875,17 +3848,17 @@
           <t>22명</t>
         </is>
       </c>
-      <c r="L39" s="134" t="n"/>
+      <c r="L39" s="205" t="n"/>
       <c r="M39" s="176" t="inlineStr">
         <is>
           <t>9/26은 추석 연휴 중 토요일 — 휴일근로 가산·연휴 근무 동의 별도 필요</t>
         </is>
       </c>
-      <c r="N39" s="169" t="n"/>
-      <c r="O39" s="169" t="n"/>
-      <c r="P39" s="169" t="n"/>
-      <c r="Q39" s="169" t="n"/>
-      <c r="R39" s="169" t="n"/>
+      <c r="N39" s="204" t="n"/>
+      <c r="O39" s="204" t="n"/>
+      <c r="P39" s="204" t="n"/>
+      <c r="Q39" s="204" t="n"/>
+      <c r="R39" s="205" t="n"/>
     </row>
     <row r="40" ht="14" customHeight="1" s="130">
       <c r="A40" s="135" t="inlineStr">
@@ -3893,23 +3866,6 @@
           <t>⑥ 원본 수식 확인 필요</t>
         </is>
       </c>
-      <c r="B40" s="136" t="n"/>
-      <c r="C40" s="136" t="n"/>
-      <c r="D40" s="136" t="n"/>
-      <c r="E40" s="136" t="n"/>
-      <c r="F40" s="136" t="n"/>
-      <c r="G40" s="136" t="n"/>
-      <c r="H40" s="136" t="n"/>
-      <c r="I40" s="136" t="n"/>
-      <c r="J40" s="136" t="n"/>
-      <c r="K40" s="136" t="n"/>
-      <c r="L40" s="136" t="n"/>
-      <c r="M40" s="136" t="n"/>
-      <c r="N40" s="136" t="n"/>
-      <c r="O40" s="136" t="n"/>
-      <c r="P40" s="136" t="n"/>
-      <c r="Q40" s="136" t="n"/>
-      <c r="R40" s="136" t="n"/>
     </row>
     <row r="41" ht="12" customHeight="1" s="130">
       <c r="A41" s="177" t="inlineStr">
@@ -3917,27 +3873,27 @@
           <t>업무 I91</t>
         </is>
       </c>
-      <c r="B41" s="146" t="n"/>
-      <c r="C41" s="146" t="n"/>
+      <c r="B41" s="204" t="n"/>
+      <c r="C41" s="205" t="n"/>
       <c r="D41" s="178" t="inlineStr">
         <is>
           <t>8월 합계가 수식이 아닌 값 2,578. 실제 합 2,569 (9H 차이) · J91(7,680)과 불일치 → =SUM(I3:I90)</t>
         </is>
       </c>
-      <c r="E41" s="134" t="n"/>
-      <c r="F41" s="134" t="n"/>
-      <c r="G41" s="134" t="n"/>
-      <c r="H41" s="134" t="n"/>
-      <c r="I41" s="134" t="n"/>
-      <c r="J41" s="134" t="n"/>
-      <c r="K41" s="134" t="n"/>
-      <c r="L41" s="134" t="n"/>
-      <c r="M41" s="134" t="n"/>
-      <c r="N41" s="134" t="n"/>
-      <c r="O41" s="134" t="n"/>
-      <c r="P41" s="134" t="n"/>
-      <c r="Q41" s="134" t="n"/>
-      <c r="R41" s="134" t="n"/>
+      <c r="E41" s="204" t="n"/>
+      <c r="F41" s="204" t="n"/>
+      <c r="G41" s="204" t="n"/>
+      <c r="H41" s="204" t="n"/>
+      <c r="I41" s="204" t="n"/>
+      <c r="J41" s="204" t="n"/>
+      <c r="K41" s="204" t="n"/>
+      <c r="L41" s="204" t="n"/>
+      <c r="M41" s="204" t="n"/>
+      <c r="N41" s="204" t="n"/>
+      <c r="O41" s="204" t="n"/>
+      <c r="P41" s="204" t="n"/>
+      <c r="Q41" s="204" t="n"/>
+      <c r="R41" s="205" t="n"/>
     </row>
     <row r="42" ht="12" customHeight="1" s="130">
       <c r="A42" s="177" t="inlineStr">
@@ -3945,26 +3901,26 @@
           <t>업무 M3</t>
         </is>
       </c>
-      <c r="B42" s="146" t="n"/>
-      <c r="C42" s="146" t="n"/>
+      <c r="B42" s="204" t="n"/>
+      <c r="C42" s="205" t="n"/>
       <c r="D42" s="178">
         <f>COUNTIF(J3:J153,"&gt;156") 범위에 합계행 J91(7,680) 포함되어 17명. 실제 16명 → 범위 J3:J90</f>
         <v/>
       </c>
-      <c r="E42" s="134" t="n"/>
-      <c r="F42" s="134" t="n"/>
-      <c r="G42" s="134" t="n"/>
-      <c r="H42" s="134" t="n"/>
-      <c r="I42" s="134" t="n"/>
-      <c r="J42" s="134" t="n"/>
-      <c r="K42" s="134" t="n"/>
-      <c r="L42" s="134" t="n"/>
-      <c r="M42" s="134" t="n"/>
-      <c r="N42" s="134" t="n"/>
-      <c r="O42" s="134" t="n"/>
-      <c r="P42" s="134" t="n"/>
-      <c r="Q42" s="134" t="n"/>
-      <c r="R42" s="134" t="n"/>
+      <c r="E42" s="204" t="n"/>
+      <c r="F42" s="204" t="n"/>
+      <c r="G42" s="204" t="n"/>
+      <c r="H42" s="204" t="n"/>
+      <c r="I42" s="204" t="n"/>
+      <c r="J42" s="204" t="n"/>
+      <c r="K42" s="204" t="n"/>
+      <c r="L42" s="204" t="n"/>
+      <c r="M42" s="204" t="n"/>
+      <c r="N42" s="204" t="n"/>
+      <c r="O42" s="204" t="n"/>
+      <c r="P42" s="204" t="n"/>
+      <c r="Q42" s="204" t="n"/>
+      <c r="R42" s="205" t="n"/>
     </row>
     <row r="43" ht="12" customHeight="1" s="130">
       <c r="A43" s="177" t="inlineStr">
@@ -3972,32 +3928,32 @@
           <t>업무 L3 / 생산 Q3</t>
         </is>
       </c>
-      <c r="B43" s="146" t="n"/>
-      <c r="C43" s="146" t="n"/>
+      <c r="B43" s="204" t="n"/>
+      <c r="C43" s="205" t="n"/>
       <c r="D43" s="178">
         <f>52*3. 값 156은 맞으나 연장 한도는 주 12H → =12*13이 정확한 근거 (생산 R3 COUNTIF는 정상)</f>
         <v/>
       </c>
-      <c r="E43" s="134" t="n"/>
-      <c r="F43" s="134" t="n"/>
-      <c r="G43" s="134" t="n"/>
-      <c r="H43" s="134" t="n"/>
-      <c r="I43" s="134" t="n"/>
-      <c r="J43" s="134" t="n"/>
-      <c r="K43" s="134" t="n"/>
-      <c r="L43" s="134" t="n"/>
-      <c r="M43" s="134" t="n"/>
-      <c r="N43" s="134" t="n"/>
-      <c r="O43" s="134" t="n"/>
-      <c r="P43" s="134" t="n"/>
-      <c r="Q43" s="134" t="n"/>
-      <c r="R43" s="134" t="n"/>
+      <c r="E43" s="204" t="n"/>
+      <c r="F43" s="204" t="n"/>
+      <c r="G43" s="204" t="n"/>
+      <c r="H43" s="204" t="n"/>
+      <c r="I43" s="204" t="n"/>
+      <c r="J43" s="204" t="n"/>
+      <c r="K43" s="204" t="n"/>
+      <c r="L43" s="204" t="n"/>
+      <c r="M43" s="204" t="n"/>
+      <c r="N43" s="204" t="n"/>
+      <c r="O43" s="204" t="n"/>
+      <c r="P43" s="204" t="n"/>
+      <c r="Q43" s="204" t="n"/>
+      <c r="R43" s="205" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="H35:I35"/>
     <mergeCell ref="J6:R6"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A25:R25"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="A37:C37"/>
@@ -4071,6 +4027,1051 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="130" min="1" max="1"/>
+    <col width="6.5" customWidth="1" style="130" min="2" max="2"/>
+    <col width="7.5" customWidth="1" style="130" min="3" max="3"/>
+    <col width="6.5" customWidth="1" style="130" min="4" max="4"/>
+    <col width="7.5" customWidth="1" style="130" min="5" max="5"/>
+    <col width="6.5" customWidth="1" style="130" min="6" max="6"/>
+    <col width="10" customWidth="1" style="130" min="7" max="7"/>
+    <col width="6.5" customWidth="1" style="130" min="8" max="8"/>
+    <col width="7.5" customWidth="1" style="130" min="9" max="9"/>
+    <col width="6.5" customWidth="1" style="130" min="10" max="10"/>
+    <col width="7.5" customWidth="1" style="130" min="11" max="11"/>
+    <col width="6.5" customWidth="1" style="130" min="12" max="12"/>
+    <col width="10" customWidth="1" style="130" min="13" max="13"/>
+    <col width="6.5" customWidth="1" style="130" min="14" max="14"/>
+    <col width="7.5" customWidth="1" style="130" min="15" max="15"/>
+    <col width="6.5" customWidth="1" style="130" min="16" max="16"/>
+    <col width="7.5" customWidth="1" style="130" min="17" max="17"/>
+    <col width="6.5" customWidth="1" style="130" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="130">
+      <c r="A1" s="131" t="inlineStr">
+        <is>
+          <t>10월 연장근로 예측 — 신규 단위기간(10·11·12월)</t>
+        </is>
+      </c>
+      <c r="B1" s="132" t="n"/>
+      <c r="C1" s="132" t="n"/>
+      <c r="D1" s="132" t="n"/>
+      <c r="E1" s="132" t="n"/>
+      <c r="F1" s="132" t="n"/>
+      <c r="G1" s="132" t="n"/>
+      <c r="H1" s="132" t="n"/>
+      <c r="I1" s="132" t="n"/>
+      <c r="J1" s="132" t="n"/>
+      <c r="K1" s="132" t="n"/>
+      <c r="L1" s="132" t="n"/>
+      <c r="M1" s="132" t="n"/>
+      <c r="N1" s="132" t="n"/>
+      <c r="O1" s="132" t="n"/>
+      <c r="P1" s="132" t="n"/>
+      <c r="Q1" s="132" t="n"/>
+      <c r="R1" s="132" t="n"/>
+    </row>
+    <row r="2" ht="12" customHeight="1" s="130">
+      <c r="A2" s="206" t="inlineStr">
+        <is>
+          <t>10월부터 3개월 탄력근로 단위기간이 새로 시작되어 개인당 156H가 리셋됨  ·  9월 잔여와 무관하게 신규 한도 적용  |  2026.09.02</t>
+        </is>
+      </c>
+      <c r="B2" s="134" t="n"/>
+      <c r="C2" s="134" t="n"/>
+      <c r="D2" s="134" t="n"/>
+      <c r="E2" s="134" t="n"/>
+      <c r="F2" s="134" t="n"/>
+      <c r="G2" s="134" t="n"/>
+      <c r="H2" s="134" t="n"/>
+      <c r="I2" s="134" t="n"/>
+      <c r="J2" s="134" t="n"/>
+      <c r="K2" s="134" t="n"/>
+      <c r="L2" s="134" t="n"/>
+      <c r="M2" s="134" t="n"/>
+      <c r="N2" s="134" t="n"/>
+      <c r="O2" s="134" t="n"/>
+      <c r="P2" s="134" t="n"/>
+      <c r="Q2" s="134" t="n"/>
+      <c r="R2" s="134" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1" s="130">
+      <c r="A3" s="135" t="inlineStr">
+        <is>
+          <t>① 10월 근무일 요건</t>
+        </is>
+      </c>
+      <c r="B3" s="136" t="n"/>
+      <c r="C3" s="136" t="n"/>
+      <c r="D3" s="136" t="n"/>
+      <c r="E3" s="136" t="n"/>
+      <c r="F3" s="136" t="n"/>
+      <c r="G3" s="136" t="n"/>
+      <c r="H3" s="136" t="n"/>
+      <c r="I3" s="136" t="n"/>
+      <c r="J3" s="136" t="n"/>
+      <c r="K3" s="136" t="n"/>
+      <c r="L3" s="136" t="n"/>
+      <c r="M3" s="136" t="n"/>
+      <c r="N3" s="136" t="n"/>
+      <c r="O3" s="136" t="n"/>
+      <c r="P3" s="136" t="n"/>
+      <c r="Q3" s="136" t="n"/>
+      <c r="R3" s="136" t="n"/>
+    </row>
+    <row r="4" ht="13" customHeight="1" s="130">
+      <c r="A4" s="207" t="inlineStr">
+        <is>
+          <t>실근무 평일</t>
+        </is>
+      </c>
+      <c r="B4" s="146" t="n"/>
+      <c r="C4" s="146" t="n"/>
+      <c r="D4" s="208" t="inlineStr">
+        <is>
+          <t>20일</t>
+        </is>
+      </c>
+      <c r="E4" s="134" t="n"/>
+      <c r="F4" s="134" t="n"/>
+      <c r="G4" s="134" t="n"/>
+      <c r="H4" s="134" t="n"/>
+      <c r="I4" s="134" t="n"/>
+      <c r="J4" s="207" t="inlineStr">
+        <is>
+          <t>토요일</t>
+        </is>
+      </c>
+      <c r="K4" s="146" t="n"/>
+      <c r="L4" s="146" t="n"/>
+      <c r="M4" s="208" t="inlineStr">
+        <is>
+          <t>5회 (3·10·17·24·31)</t>
+        </is>
+      </c>
+      <c r="N4" s="134" t="n"/>
+      <c r="O4" s="134" t="n"/>
+      <c r="P4" s="134" t="n"/>
+      <c r="Q4" s="134" t="n"/>
+      <c r="R4" s="134" t="n"/>
+    </row>
+    <row r="5" ht="13" customHeight="1" s="130">
+      <c r="A5" s="207" t="inlineStr">
+        <is>
+          <t>일요일</t>
+        </is>
+      </c>
+      <c r="B5" s="146" t="n"/>
+      <c r="C5" s="146" t="n"/>
+      <c r="D5" s="208" t="inlineStr">
+        <is>
+          <t>4일 (4·11·18·25)</t>
+        </is>
+      </c>
+      <c r="E5" s="134" t="n"/>
+      <c r="F5" s="134" t="n"/>
+      <c r="G5" s="134" t="n"/>
+      <c r="H5" s="134" t="n"/>
+      <c r="I5" s="134" t="n"/>
+      <c r="J5" s="207" t="inlineStr">
+        <is>
+          <t>공휴일</t>
+        </is>
+      </c>
+      <c r="K5" s="146" t="n"/>
+      <c r="L5" s="146" t="n"/>
+      <c r="M5" s="208" t="inlineStr">
+        <is>
+          <t>3일 — 10/3 개천절(토) · 10/5 대체공휴일(월) · 10/9 한글날(금)</t>
+        </is>
+      </c>
+      <c r="N5" s="134" t="n"/>
+      <c r="O5" s="134" t="n"/>
+      <c r="P5" s="134" t="n"/>
+      <c r="Q5" s="134" t="n"/>
+      <c r="R5" s="134" t="n"/>
+    </row>
+    <row r="6" ht="12" customHeight="1" s="130">
+      <c r="A6" s="206" t="inlineStr">
+        <is>
+          <t>※ 개천절이 토요일이라 10/5(월)이 대체공휴일. 10월은 유급휴일이 3일이라 평일 근무일이 20일로 줄어든다.</t>
+        </is>
+      </c>
+      <c r="B6" s="134" t="n"/>
+      <c r="C6" s="134" t="n"/>
+      <c r="D6" s="134" t="n"/>
+      <c r="E6" s="134" t="n"/>
+      <c r="F6" s="134" t="n"/>
+      <c r="G6" s="134" t="n"/>
+      <c r="H6" s="134" t="n"/>
+      <c r="I6" s="134" t="n"/>
+      <c r="J6" s="134" t="n"/>
+      <c r="K6" s="134" t="n"/>
+      <c r="L6" s="134" t="n"/>
+      <c r="M6" s="134" t="n"/>
+      <c r="N6" s="134" t="n"/>
+      <c r="O6" s="134" t="n"/>
+      <c r="P6" s="134" t="n"/>
+      <c r="Q6" s="134" t="n"/>
+      <c r="R6" s="134" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1" s="130">
+      <c r="A8" s="135" t="inlineStr">
+        <is>
+          <t>② 10월 연장근로 시나리오 — 단위기간 한도 156H 대비</t>
+        </is>
+      </c>
+      <c r="B8" s="136" t="n"/>
+      <c r="C8" s="136" t="n"/>
+      <c r="D8" s="136" t="n"/>
+      <c r="E8" s="136" t="n"/>
+      <c r="F8" s="136" t="n"/>
+      <c r="G8" s="136" t="n"/>
+      <c r="H8" s="136" t="n"/>
+      <c r="I8" s="136" t="n"/>
+      <c r="J8" s="136" t="n"/>
+      <c r="K8" s="136" t="n"/>
+      <c r="L8" s="136" t="n"/>
+      <c r="M8" s="136" t="n"/>
+      <c r="N8" s="136" t="n"/>
+      <c r="O8" s="136" t="n"/>
+      <c r="P8" s="136" t="n"/>
+      <c r="Q8" s="136" t="n"/>
+      <c r="R8" s="136" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="130">
+      <c r="A9" s="209" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B9" s="139" t="n"/>
+      <c r="C9" s="209" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="D9" s="139" t="n"/>
+      <c r="E9" s="139" t="n"/>
+      <c r="F9" s="139" t="n"/>
+      <c r="G9" s="139" t="n"/>
+      <c r="H9" s="139" t="n"/>
+      <c r="I9" s="209" t="inlineStr">
+        <is>
+          <t>인당(H)</t>
+        </is>
+      </c>
+      <c r="J9" s="139" t="n"/>
+      <c r="K9" s="209" t="inlineStr">
+        <is>
+          <t>전사(H)</t>
+        </is>
+      </c>
+      <c r="L9" s="139" t="n"/>
+      <c r="M9" s="209" t="inlineStr">
+        <is>
+          <t>156H 소진</t>
+        </is>
+      </c>
+      <c r="N9" s="139" t="n"/>
+      <c r="O9" s="209" t="inlineStr">
+        <is>
+          <t>11·12월 잔여</t>
+        </is>
+      </c>
+      <c r="P9" s="139" t="n"/>
+      <c r="Q9" s="209" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="R9" s="139" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1" s="130">
+      <c r="A10" s="207" t="inlineStr">
+        <is>
+          <t>A 보수</t>
+        </is>
+      </c>
+      <c r="B10" s="146" t="n"/>
+      <c r="C10" s="208" t="inlineStr">
+        <is>
+          <t>평일 잔업 없음 + 토특근 3회</t>
+        </is>
+      </c>
+      <c r="D10" s="134" t="n"/>
+      <c r="E10" s="134" t="n"/>
+      <c r="F10" s="134" t="n"/>
+      <c r="G10" s="134" t="n"/>
+      <c r="H10" s="134" t="n"/>
+      <c r="I10" s="210" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="134" t="n"/>
+      <c r="K10" s="211" t="n">
+        <v>5736</v>
+      </c>
+      <c r="L10" s="134" t="n"/>
+      <c r="M10" s="212" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="N10" s="134" t="n"/>
+      <c r="O10" s="213" t="n">
+        <v>132</v>
+      </c>
+      <c r="P10" s="134" t="n"/>
+      <c r="Q10" s="214" t="inlineStr">
+        <is>
+          <t>여유</t>
+        </is>
+      </c>
+      <c r="R10" s="171" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1" s="130">
+      <c r="A11" s="207" t="inlineStr">
+        <is>
+          <t>B 표준</t>
+        </is>
+      </c>
+      <c r="B11" s="146" t="n"/>
+      <c r="C11" s="208" t="inlineStr">
+        <is>
+          <t>평일 2H × 20일 + 토특근 3회</t>
+        </is>
+      </c>
+      <c r="D11" s="134" t="n"/>
+      <c r="E11" s="134" t="n"/>
+      <c r="F11" s="134" t="n"/>
+      <c r="G11" s="134" t="n"/>
+      <c r="H11" s="134" t="n"/>
+      <c r="I11" s="210" t="n">
+        <v>64</v>
+      </c>
+      <c r="J11" s="134" t="n"/>
+      <c r="K11" s="211" t="n">
+        <v>15296</v>
+      </c>
+      <c r="L11" s="134" t="n"/>
+      <c r="M11" s="212" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="N11" s="134" t="n"/>
+      <c r="O11" s="213" t="n">
+        <v>92</v>
+      </c>
+      <c r="P11" s="134" t="n"/>
+      <c r="Q11" s="214" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="R11" s="171" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1" s="130">
+      <c r="A12" s="207" t="inlineStr">
+        <is>
+          <t>C 확대</t>
+        </is>
+      </c>
+      <c r="B12" s="146" t="n"/>
+      <c r="C12" s="208" t="inlineStr">
+        <is>
+          <t>평일 3H × 20일 + 토특근 4회 + 공휴일 1회</t>
+        </is>
+      </c>
+      <c r="D12" s="134" t="n"/>
+      <c r="E12" s="134" t="n"/>
+      <c r="F12" s="134" t="n"/>
+      <c r="G12" s="134" t="n"/>
+      <c r="H12" s="134" t="n"/>
+      <c r="I12" s="210" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="134" t="n"/>
+      <c r="K12" s="211" t="n">
+        <v>23900</v>
+      </c>
+      <c r="L12" s="134" t="n"/>
+      <c r="M12" s="212" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="N12" s="134" t="n"/>
+      <c r="O12" s="215" t="n">
+        <v>56</v>
+      </c>
+      <c r="P12" s="134" t="n"/>
+      <c r="Q12" s="216" t="inlineStr">
+        <is>
+          <t>11·12월 압박</t>
+        </is>
+      </c>
+      <c r="R12" s="169" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1" s="130">
+      <c r="A13" s="207" t="inlineStr">
+        <is>
+          <t>D 최대</t>
+        </is>
+      </c>
+      <c r="B13" s="146" t="n"/>
+      <c r="C13" s="208" t="inlineStr">
+        <is>
+          <t>평일 4H × 20일 + 토특근 5회 + 공휴일 2회</t>
+        </is>
+      </c>
+      <c r="D13" s="134" t="n"/>
+      <c r="E13" s="134" t="n"/>
+      <c r="F13" s="134" t="n"/>
+      <c r="G13" s="134" t="n"/>
+      <c r="H13" s="134" t="n"/>
+      <c r="I13" s="210" t="n">
+        <v>136</v>
+      </c>
+      <c r="J13" s="134" t="n"/>
+      <c r="K13" s="211" t="n">
+        <v>32504</v>
+      </c>
+      <c r="L13" s="134" t="n"/>
+      <c r="M13" s="212" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="N13" s="134" t="n"/>
+      <c r="O13" s="215" t="n">
+        <v>20</v>
+      </c>
+      <c r="P13" s="134" t="n"/>
+      <c r="Q13" s="217" t="inlineStr">
+        <is>
+          <t>11·12월 20H — 사실상 불가</t>
+        </is>
+      </c>
+      <c r="R13" s="148" t="n"/>
+    </row>
+    <row r="14" ht="12" customHeight="1" s="130">
+      <c r="A14" s="206" t="inlineStr">
+        <is>
+          <t>※ 1일 연장 4H = 소정 8H + 연장 4H(1일 12H 한도). 전사 = 239명 기준. 10월을 100H 이상 쓰면 11·12월에 쓸 수 있는 시간이 56H 이하로 떨어진다.</t>
+        </is>
+      </c>
+      <c r="B14" s="134" t="n"/>
+      <c r="C14" s="134" t="n"/>
+      <c r="D14" s="134" t="n"/>
+      <c r="E14" s="134" t="n"/>
+      <c r="F14" s="134" t="n"/>
+      <c r="G14" s="134" t="n"/>
+      <c r="H14" s="134" t="n"/>
+      <c r="I14" s="134" t="n"/>
+      <c r="J14" s="134" t="n"/>
+      <c r="K14" s="134" t="n"/>
+      <c r="L14" s="134" t="n"/>
+      <c r="M14" s="134" t="n"/>
+      <c r="N14" s="134" t="n"/>
+      <c r="O14" s="134" t="n"/>
+      <c r="P14" s="134" t="n"/>
+      <c r="Q14" s="134" t="n"/>
+      <c r="R14" s="134" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" s="130">
+      <c r="A16" s="218" t="inlineStr">
+        <is>
+          <t>③ MES 시스템 확보안 × 10월 1·2주 연속 특근 — 상충 검토</t>
+        </is>
+      </c>
+      <c r="B16" s="219" t="n"/>
+      <c r="C16" s="219" t="n"/>
+      <c r="D16" s="219" t="n"/>
+      <c r="E16" s="219" t="n"/>
+      <c r="F16" s="219" t="n"/>
+      <c r="G16" s="219" t="n"/>
+      <c r="H16" s="219" t="n"/>
+      <c r="I16" s="219" t="n"/>
+      <c r="J16" s="219" t="n"/>
+      <c r="K16" s="219" t="n"/>
+      <c r="L16" s="219" t="n"/>
+      <c r="M16" s="219" t="n"/>
+      <c r="N16" s="219" t="n"/>
+      <c r="O16" s="219" t="n"/>
+      <c r="P16" s="219" t="n"/>
+      <c r="Q16" s="219" t="n"/>
+      <c r="R16" s="219" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="130">
+      <c r="A17" s="209" t="inlineStr">
+        <is>
+          <t>MES 안</t>
+        </is>
+      </c>
+      <c r="B17" s="139" t="n"/>
+      <c r="C17" s="209" t="inlineStr">
+        <is>
+          <t>일정</t>
+        </is>
+      </c>
+      <c r="D17" s="139" t="n"/>
+      <c r="E17" s="139" t="n"/>
+      <c r="F17" s="139" t="n"/>
+      <c r="G17" s="139" t="n"/>
+      <c r="H17" s="209" t="inlineStr">
+        <is>
+          <t>잠기는 토요일</t>
+        </is>
+      </c>
+      <c r="I17" s="139" t="n"/>
+      <c r="J17" s="139" t="n"/>
+      <c r="K17" s="209" t="inlineStr">
+        <is>
+          <t>10월 1·2주 연속 특근과의 관계</t>
+        </is>
+      </c>
+      <c r="L17" s="139" t="n"/>
+      <c r="M17" s="139" t="n"/>
+      <c r="N17" s="139" t="n"/>
+      <c r="O17" s="139" t="n"/>
+      <c r="P17" s="139" t="n"/>
+      <c r="Q17" s="139" t="n"/>
+      <c r="R17" s="139" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1" s="130">
+      <c r="A18" s="207" t="inlineStr">
+        <is>
+          <t>1안</t>
+        </is>
+      </c>
+      <c r="B18" s="146" t="n"/>
+      <c r="C18" s="208" t="inlineStr">
+        <is>
+          <t>10/2 근무 → 10/3~5 휴식 → 10/6 오픈</t>
+        </is>
+      </c>
+      <c r="D18" s="134" t="n"/>
+      <c r="E18" s="134" t="n"/>
+      <c r="F18" s="134" t="n"/>
+      <c r="G18" s="134" t="n"/>
+      <c r="H18" s="220" t="inlineStr">
+        <is>
+          <t>10/3</t>
+        </is>
+      </c>
+      <c r="I18" s="134" t="n"/>
+      <c r="J18" s="134" t="n"/>
+      <c r="K18" s="221" t="inlineStr">
+        <is>
+          <t>10월 1주차 특근(10/3) 불가 — AP가 요청한 '10월 1·2주 연속 특근'과 정면 충돌</t>
+        </is>
+      </c>
+      <c r="L18" s="148" t="n"/>
+      <c r="M18" s="148" t="n"/>
+      <c r="N18" s="148" t="n"/>
+      <c r="O18" s="148" t="n"/>
+      <c r="P18" s="148" t="n"/>
+      <c r="Q18" s="148" t="n"/>
+      <c r="R18" s="148" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1" s="130">
+      <c r="A19" s="207" t="inlineStr">
+        <is>
+          <t>2안</t>
+        </is>
+      </c>
+      <c r="B19" s="146" t="n"/>
+      <c r="C19" s="208" t="inlineStr">
+        <is>
+          <t>10/8 근무 → 10/9~11 휴식 → 10/12 오픈</t>
+        </is>
+      </c>
+      <c r="D19" s="134" t="n"/>
+      <c r="E19" s="134" t="n"/>
+      <c r="F19" s="134" t="n"/>
+      <c r="G19" s="134" t="n"/>
+      <c r="H19" s="220" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="I19" s="134" t="n"/>
+      <c r="J19" s="134" t="n"/>
+      <c r="K19" s="221" t="inlineStr">
+        <is>
+          <t>10월 2주차 특근(10/10) 불가 — 동일하게 충돌</t>
+        </is>
+      </c>
+      <c r="L19" s="148" t="n"/>
+      <c r="M19" s="148" t="n"/>
+      <c r="N19" s="148" t="n"/>
+      <c r="O19" s="148" t="n"/>
+      <c r="P19" s="148" t="n"/>
+      <c r="Q19" s="148" t="n"/>
+      <c r="R19" s="148" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" s="130">
+      <c r="A20" s="207" t="inlineStr">
+        <is>
+          <t>3안</t>
+        </is>
+      </c>
+      <c r="B20" s="146" t="n"/>
+      <c r="C20" s="208" t="inlineStr">
+        <is>
+          <t>9/23 근무 → 9/24~26 휴식 (추석 연휴)</t>
+        </is>
+      </c>
+      <c r="D20" s="134" t="n"/>
+      <c r="E20" s="134" t="n"/>
+      <c r="F20" s="134" t="n"/>
+      <c r="G20" s="134" t="n"/>
+      <c r="H20" s="222" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="I20" s="134" t="n"/>
+      <c r="J20" s="134" t="n"/>
+      <c r="K20" s="223" t="inlineStr">
+        <is>
+          <t>10월 토요일을 하나도 잠그지 않음 — 연속 특근과 양립하는 유일한 안</t>
+        </is>
+      </c>
+      <c r="L20" s="171" t="n"/>
+      <c r="M20" s="171" t="n"/>
+      <c r="N20" s="171" t="n"/>
+      <c r="O20" s="171" t="n"/>
+      <c r="P20" s="171" t="n"/>
+      <c r="Q20" s="171" t="n"/>
+      <c r="R20" s="171" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" s="130">
+      <c r="A21" s="224" t="inlineStr">
+        <is>
+          <t>▶ AP가 같은 회의에서 '10월 1·2주 연속 특근'과 'MES 확보를 위한 10월 초 3일 휴식'을 함께 요청했으나, 1안·2안은 그 특근일을 직접 잠근다. 두 요구를 모두 만족하는 것은 3안(9/23)뿐이다. 회의에서 확정 요청.</t>
+        </is>
+      </c>
+      <c r="B21" s="148" t="n"/>
+      <c r="C21" s="148" t="n"/>
+      <c r="D21" s="148" t="n"/>
+      <c r="E21" s="148" t="n"/>
+      <c r="F21" s="148" t="n"/>
+      <c r="G21" s="148" t="n"/>
+      <c r="H21" s="148" t="n"/>
+      <c r="I21" s="148" t="n"/>
+      <c r="J21" s="148" t="n"/>
+      <c r="K21" s="148" t="n"/>
+      <c r="L21" s="148" t="n"/>
+      <c r="M21" s="148" t="n"/>
+      <c r="N21" s="148" t="n"/>
+      <c r="O21" s="148" t="n"/>
+      <c r="P21" s="148" t="n"/>
+      <c r="Q21" s="148" t="n"/>
+      <c r="R21" s="148" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1" s="130">
+      <c r="A23" s="135" t="inlineStr">
+        <is>
+          <t>④ 9월과의 연계</t>
+        </is>
+      </c>
+      <c r="B23" s="136" t="n"/>
+      <c r="C23" s="136" t="n"/>
+      <c r="D23" s="136" t="n"/>
+      <c r="E23" s="136" t="n"/>
+      <c r="F23" s="136" t="n"/>
+      <c r="G23" s="136" t="n"/>
+      <c r="H23" s="136" t="n"/>
+      <c r="I23" s="136" t="n"/>
+      <c r="J23" s="136" t="n"/>
+      <c r="K23" s="136" t="n"/>
+      <c r="L23" s="136" t="n"/>
+      <c r="M23" s="136" t="n"/>
+      <c r="N23" s="136" t="n"/>
+      <c r="O23" s="136" t="n"/>
+      <c r="P23" s="136" t="n"/>
+      <c r="Q23" s="136" t="n"/>
+      <c r="R23" s="136" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="130">
+      <c r="A24" s="209" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B24" s="139" t="n"/>
+      <c r="C24" s="139" t="n"/>
+      <c r="D24" s="139" t="n"/>
+      <c r="E24" s="209" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F24" s="139" t="n"/>
+      <c r="G24" s="139" t="n"/>
+      <c r="H24" s="209" t="inlineStr">
+        <is>
+          <t>의미</t>
+        </is>
+      </c>
+      <c r="I24" s="139" t="n"/>
+      <c r="J24" s="139" t="n"/>
+      <c r="K24" s="139" t="n"/>
+      <c r="L24" s="139" t="n"/>
+      <c r="M24" s="139" t="n"/>
+      <c r="N24" s="139" t="n"/>
+      <c r="O24" s="139" t="n"/>
+      <c r="P24" s="139" t="n"/>
+      <c r="Q24" s="139" t="n"/>
+      <c r="R24" s="139" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1" s="130">
+      <c r="A25" s="225" t="inlineStr">
+        <is>
+          <t>9월 잔여 (현 단위기간)</t>
+        </is>
+      </c>
+      <c r="B25" s="146" t="n"/>
+      <c r="C25" s="146" t="n"/>
+      <c r="D25" s="146" t="n"/>
+      <c r="E25" s="222" t="inlineStr">
+        <is>
+          <t>23,032H</t>
+        </is>
+      </c>
+      <c r="F25" s="134" t="n"/>
+      <c r="G25" s="134" t="n"/>
+      <c r="H25" s="208" t="inlineStr">
+        <is>
+          <t>인당 96H. 9월에 얼마를 쓰든 10월 한도에는 영향 없음 — 단위기간이 다름</t>
+        </is>
+      </c>
+      <c r="I25" s="134" t="n"/>
+      <c r="J25" s="134" t="n"/>
+      <c r="K25" s="134" t="n"/>
+      <c r="L25" s="134" t="n"/>
+      <c r="M25" s="134" t="n"/>
+      <c r="N25" s="134" t="n"/>
+      <c r="O25" s="134" t="n"/>
+      <c r="P25" s="134" t="n"/>
+      <c r="Q25" s="134" t="n"/>
+      <c r="R25" s="134" t="n"/>
+    </row>
+    <row r="26" ht="13" customHeight="1" s="130">
+      <c r="A26" s="225" t="inlineStr">
+        <is>
+          <t>9월 편성 불가 인원</t>
+        </is>
+      </c>
+      <c r="B26" s="146" t="n"/>
+      <c r="C26" s="146" t="n"/>
+      <c r="D26" s="146" t="n"/>
+      <c r="E26" s="222" t="inlineStr">
+        <is>
+          <t>4명</t>
+        </is>
+      </c>
+      <c r="F26" s="134" t="n"/>
+      <c r="G26" s="134" t="n"/>
+      <c r="H26" s="208" t="inlineStr">
+        <is>
+          <t>김영두·박태근·이세호·문석. 10월에는 리셋되어 전원 편성 가능</t>
+        </is>
+      </c>
+      <c r="I26" s="134" t="n"/>
+      <c r="J26" s="134" t="n"/>
+      <c r="K26" s="134" t="n"/>
+      <c r="L26" s="134" t="n"/>
+      <c r="M26" s="134" t="n"/>
+      <c r="N26" s="134" t="n"/>
+      <c r="O26" s="134" t="n"/>
+      <c r="P26" s="134" t="n"/>
+      <c r="Q26" s="134" t="n"/>
+      <c r="R26" s="134" t="n"/>
+    </row>
+    <row r="27" ht="13" customHeight="1" s="130">
+      <c r="A27" s="225" t="inlineStr">
+        <is>
+          <t>10월 권장(B안) 인당</t>
+        </is>
+      </c>
+      <c r="B27" s="146" t="n"/>
+      <c r="C27" s="146" t="n"/>
+      <c r="D27" s="146" t="n"/>
+      <c r="E27" s="222" t="inlineStr">
+        <is>
+          <t>64H</t>
+        </is>
+      </c>
+      <c r="F27" s="134" t="n"/>
+      <c r="G27" s="134" t="n"/>
+      <c r="H27" s="208" t="inlineStr">
+        <is>
+          <t>전사 15,296H. 9월 잔여(23,032H)와 합치면 9~10월 2개월 확보량 38,328H</t>
+        </is>
+      </c>
+      <c r="I27" s="134" t="n"/>
+      <c r="J27" s="134" t="n"/>
+      <c r="K27" s="134" t="n"/>
+      <c r="L27" s="134" t="n"/>
+      <c r="M27" s="134" t="n"/>
+      <c r="N27" s="134" t="n"/>
+      <c r="O27" s="134" t="n"/>
+      <c r="P27" s="134" t="n"/>
+      <c r="Q27" s="134" t="n"/>
+      <c r="R27" s="134" t="n"/>
+    </row>
+    <row r="28" ht="13" customHeight="1" s="130">
+      <c r="A28" s="225" t="inlineStr">
+        <is>
+          <t>11·12월 여유</t>
+        </is>
+      </c>
+      <c r="B28" s="146" t="n"/>
+      <c r="C28" s="146" t="n"/>
+      <c r="D28" s="146" t="n"/>
+      <c r="E28" s="222" t="inlineStr">
+        <is>
+          <t>92H</t>
+        </is>
+      </c>
+      <c r="F28" s="134" t="n"/>
+      <c r="G28" s="134" t="n"/>
+      <c r="H28" s="208" t="inlineStr">
+        <is>
+          <t>B안 기준. 연말 물량 대응 여지를 남기는 수준</t>
+        </is>
+      </c>
+      <c r="I28" s="134" t="n"/>
+      <c r="J28" s="134" t="n"/>
+      <c r="K28" s="134" t="n"/>
+      <c r="L28" s="134" t="n"/>
+      <c r="M28" s="134" t="n"/>
+      <c r="N28" s="134" t="n"/>
+      <c r="O28" s="134" t="n"/>
+      <c r="P28" s="134" t="n"/>
+      <c r="Q28" s="134" t="n"/>
+      <c r="R28" s="134" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" s="130">
+      <c r="A30" s="135" t="inlineStr">
+        <is>
+          <t>⑤ 10월 편성 시 유의</t>
+        </is>
+      </c>
+      <c r="B30" s="136" t="n"/>
+      <c r="C30" s="136" t="n"/>
+      <c r="D30" s="136" t="n"/>
+      <c r="E30" s="136" t="n"/>
+      <c r="F30" s="136" t="n"/>
+      <c r="G30" s="136" t="n"/>
+      <c r="H30" s="136" t="n"/>
+      <c r="I30" s="136" t="n"/>
+      <c r="J30" s="136" t="n"/>
+      <c r="K30" s="136" t="n"/>
+      <c r="L30" s="136" t="n"/>
+      <c r="M30" s="136" t="n"/>
+      <c r="N30" s="136" t="n"/>
+      <c r="O30" s="136" t="n"/>
+      <c r="P30" s="136" t="n"/>
+      <c r="Q30" s="136" t="n"/>
+      <c r="R30" s="136" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="130">
+      <c r="A31" s="226" t="inlineStr">
+        <is>
+          <t>10월 특근일 3곳이 유급휴일 — 10/3(개천절·토) · 10/5(대체공휴일·월) · 10/9(한글날·금). 휴일근로 가산(8H 이내 50% · 초과 100%)이 붙고 여성 근로자는 휴일근로에도 개별 동의가 필요하다.</t>
+        </is>
+      </c>
+      <c r="B31" s="134" t="n"/>
+      <c r="C31" s="134" t="n"/>
+      <c r="D31" s="134" t="n"/>
+      <c r="E31" s="134" t="n"/>
+      <c r="F31" s="134" t="n"/>
+      <c r="G31" s="134" t="n"/>
+      <c r="H31" s="134" t="n"/>
+      <c r="I31" s="134" t="n"/>
+      <c r="J31" s="134" t="n"/>
+      <c r="K31" s="134" t="n"/>
+      <c r="L31" s="134" t="n"/>
+      <c r="M31" s="134" t="n"/>
+      <c r="N31" s="134" t="n"/>
+      <c r="O31" s="134" t="n"/>
+      <c r="P31" s="134" t="n"/>
+      <c r="Q31" s="134" t="n"/>
+      <c r="R31" s="134" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="130">
+      <c r="A32" s="226" t="inlineStr">
+        <is>
+          <t>추석 연휴(9/24~26) 직후 10월 1·2주까지 연속 특근을 얹으면 3주 연속 무휴가 된다. 안전·품질 리스크 상승.</t>
+        </is>
+      </c>
+      <c r="B32" s="134" t="n"/>
+      <c r="C32" s="134" t="n"/>
+      <c r="D32" s="134" t="n"/>
+      <c r="E32" s="134" t="n"/>
+      <c r="F32" s="134" t="n"/>
+      <c r="G32" s="134" t="n"/>
+      <c r="H32" s="134" t="n"/>
+      <c r="I32" s="134" t="n"/>
+      <c r="J32" s="134" t="n"/>
+      <c r="K32" s="134" t="n"/>
+      <c r="L32" s="134" t="n"/>
+      <c r="M32" s="134" t="n"/>
+      <c r="N32" s="134" t="n"/>
+      <c r="O32" s="134" t="n"/>
+      <c r="P32" s="134" t="n"/>
+      <c r="Q32" s="134" t="n"/>
+      <c r="R32" s="134" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="130">
+      <c r="A33" s="226" t="inlineStr">
+        <is>
+          <t>야간 편성은 별도 조를 8H 소정근로로 짜면 연장이 발생하지 않아 156H 한도와 무관하다. 제약은 가산수당 50% · 여성 야간근로 동의 · 야간작업 특수건강진단이다.</t>
+        </is>
+      </c>
+      <c r="B33" s="134" t="n"/>
+      <c r="C33" s="134" t="n"/>
+      <c r="D33" s="134" t="n"/>
+      <c r="E33" s="134" t="n"/>
+      <c r="F33" s="134" t="n"/>
+      <c r="G33" s="134" t="n"/>
+      <c r="H33" s="134" t="n"/>
+      <c r="I33" s="134" t="n"/>
+      <c r="J33" s="134" t="n"/>
+      <c r="K33" s="134" t="n"/>
+      <c r="L33" s="134" t="n"/>
+      <c r="M33" s="134" t="n"/>
+      <c r="N33" s="134" t="n"/>
+      <c r="O33" s="134" t="n"/>
+      <c r="P33" s="134" t="n"/>
+      <c r="Q33" s="134" t="n"/>
+      <c r="R33" s="134" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1" s="130">
+      <c r="A34" s="226" t="inlineStr">
+        <is>
+          <t>본 예측은 근로시간 공급 측면만 산출한 값이다. 10월 오더 확정 후 소요 공수와 대조해 시나리오를 확정해야 한다.</t>
+        </is>
+      </c>
+      <c r="B34" s="134" t="n"/>
+      <c r="C34" s="134" t="n"/>
+      <c r="D34" s="134" t="n"/>
+      <c r="E34" s="134" t="n"/>
+      <c r="F34" s="134" t="n"/>
+      <c r="G34" s="134" t="n"/>
+      <c r="H34" s="134" t="n"/>
+      <c r="I34" s="134" t="n"/>
+      <c r="J34" s="134" t="n"/>
+      <c r="K34" s="134" t="n"/>
+      <c r="L34" s="134" t="n"/>
+      <c r="M34" s="134" t="n"/>
+      <c r="N34" s="134" t="n"/>
+      <c r="O34" s="134" t="n"/>
+      <c r="P34" s="134" t="n"/>
+      <c r="Q34" s="134" t="n"/>
+      <c r="R34" s="134" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="H26:R26"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A33:R33"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A30:R30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H25:R25"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="H28:R28"/>
+    <mergeCell ref="A34:R34"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="A21:R21"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A32:R32"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A23:R23"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A31:R31"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="H27:R27"/>
+    <mergeCell ref="H24:R24"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="O13:P13"/>
+  </mergeCells>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7822,7 +8823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="8" tint="0.5999938962981048"/>

--- a/주52시간_3개월_현황_요약_0902.xlsx
+++ b/주52시간_3개월_현황_요약_0902.xlsx
@@ -7,15 +7,17 @@
   </bookViews>
   <sheets>
     <sheet name="0.요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1.10월예측" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="아모레 업무" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="아모레 생산" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1.9월풀특근" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.10월예측" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="아모레 업무" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="아모레 생산" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0.요약'!$A$1:$R$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'1.10월예측'!$A$1:$R$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1.9월풀특근'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2.10월예측'!$A$1:$R$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'아모레 업무'!$A$2:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'아모레 생산'!$A$2:$P$154</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -238,6 +240,12 @@
       <name val="맑은 고딕"/>
       <color rgb="00C00000"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8.5"/>
     </font>
   </fonts>
   <fills count="12">
@@ -902,7 +910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1559,6 +1567,222 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2061,7 +2285,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1" s="130">
-      <c r="A2" s="133" t="inlineStr">
+      <c r="A2" s="227" t="inlineStr">
         <is>
           <t>단위기간 4·5·6월 / 7·8·9월 / 10·11·12월  ·  기간 한도 156H(12H/주 × 13주)  ·  9월 잔여 = 156H − (7월+8월)  |  6월은 직전 단위기간이므로 현 구간 계산 제외  |  원본 2개 시트 미수정  ·  2026.09.02</t>
         </is>
@@ -2137,7 +2361,7 @@
           <t>잔여 0H</t>
         </is>
       </c>
-      <c r="J4" s="138" t="inlineStr">
+      <c r="J4" s="235" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
@@ -2152,18 +2376,18 @@
       <c r="R4" s="205" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1" s="130">
-      <c r="A5" s="140" t="inlineStr">
+      <c r="A5" s="228" t="inlineStr">
         <is>
           <t>업무도급</t>
         </is>
       </c>
-      <c r="B5" s="141" t="n">
+      <c r="B5" s="240" t="n">
         <v>88</v>
       </c>
-      <c r="C5" s="141" t="n">
+      <c r="C5" s="240" t="n">
         <v>2664.5</v>
       </c>
-      <c r="D5" s="141" t="n">
+      <c r="D5" s="240" t="n">
         <v>2569</v>
       </c>
       <c r="E5" s="142" t="n">
@@ -2196,18 +2420,18 @@
       <c r="R5" s="205" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1" s="130">
-      <c r="A6" s="140" t="inlineStr">
+      <c r="A6" s="228" t="inlineStr">
         <is>
           <t>생산도급</t>
         </is>
       </c>
-      <c r="B6" s="141" t="n">
+      <c r="B6" s="240" t="n">
         <v>151</v>
       </c>
-      <c r="C6" s="141" t="n">
+      <c r="C6" s="240" t="n">
         <v>4983</v>
       </c>
-      <c r="D6" s="141" t="n">
+      <c r="D6" s="240" t="n">
         <v>4138</v>
       </c>
       <c r="E6" s="142" t="n">
@@ -2240,7 +2464,7 @@
       <c r="R6" s="205" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1" s="130">
-      <c r="A7" s="140" t="inlineStr">
+      <c r="A7" s="228" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -2269,7 +2493,7 @@
       <c r="I7" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="151" t="inlineStr">
+      <c r="J7" s="221" t="inlineStr">
         <is>
           <t>잔여 0H 4명 · 30H 미만 19명  |  10월부터 새 단위기간 → 156H 리셋</t>
         </is>
@@ -2392,12 +2616,12 @@
       </c>
     </row>
     <row r="10" ht="12" customHeight="1" s="130">
-      <c r="A10" s="152" t="inlineStr">
+      <c r="A10" s="259" t="inlineStr">
         <is>
           <t>주임 (생)</t>
         </is>
       </c>
-      <c r="B10" s="141" t="n">
+      <c r="B10" s="240" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="153" t="n">
@@ -2409,7 +2633,7 @@
       <c r="E10" s="142" t="n">
         <v>74.5</v>
       </c>
-      <c r="F10" s="155" t="inlineStr">
+      <c r="F10" s="249" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -2419,19 +2643,19 @@
           <t>원료 창고 (업)</t>
         </is>
       </c>
-      <c r="H10" s="141" t="n">
+      <c r="H10" s="240" t="n">
         <v>6</v>
       </c>
       <c r="I10" s="143" t="n">
         <v>74.25</v>
       </c>
-      <c r="J10" s="141" t="n">
+      <c r="J10" s="240" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="142" t="n">
         <v>490.5</v>
       </c>
-      <c r="L10" s="157" t="inlineStr">
+      <c r="L10" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2441,31 +2665,31 @@
           <t>PM장 (생)</t>
         </is>
       </c>
-      <c r="N10" s="141" t="n">
+      <c r="N10" s="240" t="n">
         <v>1</v>
       </c>
       <c r="O10" s="143" t="n">
         <v>41</v>
       </c>
-      <c r="P10" s="141" t="n">
+      <c r="P10" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="142" t="n">
         <v>115</v>
       </c>
-      <c r="R10" s="158" t="inlineStr">
+      <c r="R10" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" s="130">
-      <c r="A11" s="152" t="inlineStr">
+      <c r="A11" s="259" t="inlineStr">
         <is>
           <t>HnB (생)</t>
         </is>
       </c>
-      <c r="B11" s="141" t="n">
+      <c r="B11" s="240" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="153" t="n">
@@ -2477,7 +2701,7 @@
       <c r="E11" s="142" t="n">
         <v>210</v>
       </c>
-      <c r="F11" s="155" t="inlineStr">
+      <c r="F11" s="249" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -2487,19 +2711,19 @@
           <t>행정 (생)</t>
         </is>
       </c>
-      <c r="H11" s="141" t="n">
+      <c r="H11" s="240" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="143" t="n">
         <v>74</v>
       </c>
-      <c r="J11" s="141" t="n">
+      <c r="J11" s="240" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="142" t="n">
         <v>82</v>
       </c>
-      <c r="L11" s="157" t="inlineStr">
+      <c r="L11" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2509,31 +2733,31 @@
           <t>(미기재) (업)</t>
         </is>
       </c>
-      <c r="N11" s="141" t="n">
+      <c r="N11" s="240" t="n">
         <v>4</v>
       </c>
       <c r="O11" s="143" t="n">
         <v>39.75</v>
       </c>
-      <c r="P11" s="141" t="n">
+      <c r="P11" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="142" t="n">
         <v>465</v>
       </c>
-      <c r="R11" s="158" t="inlineStr">
+      <c r="R11" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1" s="130">
-      <c r="A12" s="152" t="inlineStr">
+      <c r="A12" s="259" t="inlineStr">
         <is>
           <t>세척실 (업)</t>
         </is>
       </c>
-      <c r="B12" s="141" t="n">
+      <c r="B12" s="240" t="n">
         <v>14</v>
       </c>
       <c r="C12" s="153" t="n">
@@ -2545,7 +2769,7 @@
       <c r="E12" s="142" t="n">
         <v>825.5</v>
       </c>
-      <c r="F12" s="155" t="inlineStr">
+      <c r="F12" s="249" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -2555,19 +2779,19 @@
           <t>계획자 (생)</t>
         </is>
       </c>
-      <c r="H12" s="141" t="n">
+      <c r="H12" s="240" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="143" t="n">
         <v>72.5</v>
       </c>
-      <c r="J12" s="141" t="n">
+      <c r="J12" s="240" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="142" t="n">
         <v>250.5</v>
       </c>
-      <c r="L12" s="157" t="inlineStr">
+      <c r="L12" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2577,7 +2801,7 @@
           <t>공작/미화 (업)</t>
         </is>
       </c>
-      <c r="N12" s="141" t="n">
+      <c r="N12" s="240" t="n">
         <v>15</v>
       </c>
       <c r="O12" s="143" t="n">
@@ -2589,7 +2813,7 @@
       <c r="Q12" s="142" t="n">
         <v>1911.5</v>
       </c>
-      <c r="R12" s="158" t="inlineStr">
+      <c r="R12" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2601,7 +2825,7 @@
           <t>내용물 관리 (업)</t>
         </is>
       </c>
-      <c r="B13" s="141" t="n">
+      <c r="B13" s="240" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="143" t="n">
@@ -2613,7 +2837,7 @@
       <c r="E13" s="142" t="n">
         <v>343.5</v>
       </c>
-      <c r="F13" s="157" t="inlineStr">
+      <c r="F13" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2623,7 +2847,7 @@
           <t>초격차 (생)</t>
         </is>
       </c>
-      <c r="H13" s="141" t="n">
+      <c r="H13" s="240" t="n">
         <v>19</v>
       </c>
       <c r="I13" s="143" t="n">
@@ -2635,7 +2859,7 @@
       <c r="K13" s="142" t="n">
         <v>1896</v>
       </c>
-      <c r="L13" s="157" t="inlineStr">
+      <c r="L13" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2645,19 +2869,19 @@
           <t>염모 (생)</t>
         </is>
       </c>
-      <c r="N13" s="141" t="n">
+      <c r="N13" s="240" t="n">
         <v>27</v>
       </c>
       <c r="O13" s="143" t="n">
         <v>18.5</v>
       </c>
-      <c r="P13" s="141" t="n">
+      <c r="P13" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="142" t="n">
         <v>3712.5</v>
       </c>
-      <c r="R13" s="158" t="inlineStr">
+      <c r="R13" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2669,7 +2893,7 @@
           <t>튜브 (생)</t>
         </is>
       </c>
-      <c r="B14" s="141" t="n">
+      <c r="B14" s="240" t="n">
         <v>17</v>
       </c>
       <c r="C14" s="143" t="n">
@@ -2681,7 +2905,7 @@
       <c r="E14" s="142" t="n">
         <v>1287</v>
       </c>
-      <c r="F14" s="157" t="inlineStr">
+      <c r="F14" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2691,19 +2915,19 @@
           <t>실적/순회 (생)</t>
         </is>
       </c>
-      <c r="H14" s="141" t="n">
+      <c r="H14" s="240" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="143" t="n">
         <v>55.875</v>
       </c>
-      <c r="J14" s="141" t="n">
+      <c r="J14" s="240" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="142" t="n">
         <v>400.5</v>
       </c>
-      <c r="L14" s="158" t="inlineStr">
+      <c r="L14" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2713,19 +2937,19 @@
           <t>(미기재) (생)</t>
         </is>
       </c>
-      <c r="N14" s="141" t="n">
+      <c r="N14" s="240" t="n">
         <v>6</v>
       </c>
       <c r="O14" s="143" t="n">
         <v>17</v>
       </c>
-      <c r="P14" s="141" t="n">
+      <c r="P14" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="142" t="n">
         <v>834</v>
       </c>
-      <c r="R14" s="158" t="inlineStr">
+      <c r="R14" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2737,7 +2961,7 @@
           <t>PM (생)</t>
         </is>
       </c>
-      <c r="B15" s="141" t="n">
+      <c r="B15" s="240" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="143" t="n">
@@ -2749,7 +2973,7 @@
       <c r="E15" s="142" t="n">
         <v>682.5</v>
       </c>
-      <c r="F15" s="157" t="inlineStr">
+      <c r="F15" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2759,7 +2983,7 @@
           <t>포장재 창고 (업)</t>
         </is>
       </c>
-      <c r="H15" s="141" t="n">
+      <c r="H15" s="240" t="n">
         <v>25</v>
       </c>
       <c r="I15" s="143" t="n">
@@ -2771,7 +2995,7 @@
       <c r="K15" s="142" t="n">
         <v>2508</v>
       </c>
-      <c r="L15" s="158" t="inlineStr">
+      <c r="L15" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2781,19 +3005,19 @@
           <t>관리자 (업)</t>
         </is>
       </c>
-      <c r="N15" s="141" t="n">
+      <c r="N15" s="240" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="143" t="n">
         <v>2.5</v>
       </c>
-      <c r="P15" s="141" t="n">
+      <c r="P15" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="142" t="n">
         <v>153.5</v>
       </c>
-      <c r="R15" s="158" t="inlineStr">
+      <c r="R15" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2805,19 +3029,19 @@
           <t>직선 (생)</t>
         </is>
       </c>
-      <c r="B16" s="141" t="n">
+      <c r="B16" s="240" t="n">
         <v>24</v>
       </c>
       <c r="C16" s="143" t="n">
         <v>76.75</v>
       </c>
-      <c r="D16" s="141" t="n">
+      <c r="D16" s="240" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="142" t="n">
         <v>1902</v>
       </c>
-      <c r="F16" s="157" t="inlineStr">
+      <c r="F16" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2827,7 +3051,7 @@
           <t>적재실 (업)</t>
         </is>
       </c>
-      <c r="H16" s="141" t="n">
+      <c r="H16" s="240" t="n">
         <v>17</v>
       </c>
       <c r="I16" s="143" t="n">
@@ -2839,7 +3063,7 @@
       <c r="K16" s="142" t="n">
         <v>1722.5</v>
       </c>
-      <c r="L16" s="158" t="inlineStr">
+      <c r="L16" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2849,19 +3073,19 @@
           <t>작업지휘자 (업)</t>
         </is>
       </c>
-      <c r="N16" s="141" t="n">
+      <c r="N16" s="240" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="141" t="n">
+      <c r="P16" s="240" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="142" t="n">
         <v>156</v>
       </c>
-      <c r="R16" s="158" t="inlineStr">
+      <c r="R16" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -2873,7 +3097,7 @@
           <t>멀티 (생)</t>
         </is>
       </c>
-      <c r="B17" s="141" t="n">
+      <c r="B17" s="240" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="143" t="n">
@@ -2885,7 +3109,7 @@
       <c r="E17" s="142" t="n">
         <v>1631</v>
       </c>
-      <c r="F17" s="157" t="inlineStr">
+      <c r="F17" s="250" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -2895,19 +3119,19 @@
           <t>O/C (생)</t>
         </is>
       </c>
-      <c r="H17" s="141" t="n">
+      <c r="H17" s="240" t="n">
         <v>12</v>
       </c>
       <c r="I17" s="143" t="n">
         <v>41.08333333333334</v>
       </c>
-      <c r="J17" s="141" t="n">
+      <c r="J17" s="240" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="142" t="n">
         <v>1379</v>
       </c>
-      <c r="L17" s="158" t="inlineStr">
+      <c r="L17" s="248" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -3366,7 +3590,7 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="130">
-      <c r="A26" s="138" t="inlineStr">
+      <c r="A26" s="235" t="inlineStr">
         <is>
           <t>38주 대안</t>
         </is>
@@ -3374,13 +3598,13 @@
       <c r="B26" s="204" t="n"/>
       <c r="C26" s="204" t="n"/>
       <c r="D26" s="205" t="n"/>
-      <c r="E26" s="138" t="inlineStr">
+      <c r="E26" s="235" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
       <c r="F26" s="205" t="n"/>
-      <c r="G26" s="138" t="inlineStr">
+      <c r="G26" s="235" t="inlineStr">
         <is>
           <t>근거 (근로시간)</t>
         </is>
@@ -3406,13 +3630,13 @@
       <c r="B27" s="204" t="n"/>
       <c r="C27" s="204" t="n"/>
       <c r="D27" s="205" t="n"/>
-      <c r="E27" s="157" t="inlineStr">
+      <c r="E27" s="250" t="inlineStr">
         <is>
           <t>구분 필요</t>
         </is>
       </c>
       <c r="F27" s="205" t="n"/>
-      <c r="G27" s="170" t="inlineStr">
+      <c r="G27" s="255" t="inlineStr">
         <is>
           <t>주야 2조를 각 8H 소정근로로 편성하면 연장근로는 발생하지 않음 — 156H 한도와 무관. 야간은 가산수당 50% · 여성 야간근로 동의(근기법 §70②) · 특수건강진단이 제약. 한도가 걸리는 것은 기존 인원에게 잔업으로 야간을 얹는 경우</t>
         </is>
@@ -3438,13 +3662,13 @@
       <c r="B28" s="204" t="n"/>
       <c r="C28" s="204" t="n"/>
       <c r="D28" s="205" t="n"/>
-      <c r="E28" s="157" t="inlineStr">
+      <c r="E28" s="250" t="inlineStr">
         <is>
           <t>인원 문제</t>
         </is>
       </c>
       <c r="F28" s="205" t="n"/>
-      <c r="G28" s="170" t="inlineStr">
+      <c r="G28" s="255" t="inlineStr">
         <is>
           <t>별도 조 편성이면 근로시간 한도 아님. 지원 7명 차출 시 원 소속 공백을 잔업으로 메우면 그때 한도가 걸림 — 창고 100H·로봇 101H·내용물 69H는 여유, 세척 59H가 병목</t>
         </is>
@@ -3470,13 +3694,13 @@
       <c r="B29" s="204" t="n"/>
       <c r="C29" s="204" t="n"/>
       <c r="D29" s="205" t="n"/>
-      <c r="E29" s="158" t="inlineStr">
+      <c r="E29" s="248" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
       <c r="F29" s="205" t="n"/>
-      <c r="G29" s="170" t="inlineStr">
+      <c r="G29" s="255" t="inlineStr">
         <is>
           <t>순수 잔업·특근이라 잔여 직결. 직선 24명 1,902H(인당 79H) · 염모 27명 3,712H(인당 138H) — 염모 전용이 유리</t>
         </is>
@@ -3502,13 +3726,13 @@
       <c r="B30" s="204" t="n"/>
       <c r="C30" s="204" t="n"/>
       <c r="D30" s="205" t="n"/>
-      <c r="E30" s="157" t="inlineStr">
+      <c r="E30" s="250" t="inlineStr">
         <is>
           <t>인원 문제</t>
         </is>
       </c>
       <c r="F30" s="205" t="n"/>
-      <c r="G30" s="170" t="inlineStr">
+      <c r="G30" s="255" t="inlineStr">
         <is>
           <t>세정 1안과 동일 구조. 잔업 부가 시 멀티 20명 1,631H(인당 82H), 잔여 50H 미만 4명 제외 편성</t>
         </is>
@@ -3534,13 +3758,13 @@
       <c r="B31" s="204" t="n"/>
       <c r="C31" s="204" t="n"/>
       <c r="D31" s="205" t="n"/>
-      <c r="E31" s="158" t="inlineStr">
+      <c r="E31" s="248" t="inlineStr">
         <is>
           <t>가능</t>
         </is>
       </c>
       <c r="F31" s="205" t="n"/>
-      <c r="G31" s="170" t="inlineStr">
+      <c r="G31" s="255" t="inlineStr">
         <is>
           <t>튜브 17명 1,287H(인당 76H) · 잔여 부족 2명(최명필 21H·김진만 24H) 제외 시 여력 있음</t>
         </is>
@@ -3566,13 +3790,13 @@
       <c r="B32" s="204" t="n"/>
       <c r="C32" s="204" t="n"/>
       <c r="D32" s="205" t="n"/>
-      <c r="E32" s="155" t="inlineStr">
+      <c r="E32" s="249" t="inlineStr">
         <is>
           <t>불가</t>
         </is>
       </c>
       <c r="F32" s="205" t="n"/>
-      <c r="G32" s="170" t="inlineStr">
+      <c r="G32" s="255" t="inlineStr">
         <is>
           <t>관리업무에 직접작업을 더하는 구조라 연장 발생 불가피. 주임 3명 잔여 74H(인당 25H) 전 직책 최저</t>
         </is>
@@ -3598,13 +3822,13 @@
       <c r="B33" s="204" t="n"/>
       <c r="C33" s="204" t="n"/>
       <c r="D33" s="205" t="n"/>
-      <c r="E33" s="158" t="inlineStr">
+      <c r="E33" s="248" t="inlineStr">
         <is>
           <t>한도 여유</t>
         </is>
       </c>
       <c r="F33" s="205" t="n"/>
-      <c r="G33" s="170" t="inlineStr">
+      <c r="G33" s="255" t="inlineStr">
         <is>
           <t>10월부터 새 단위기간(10·11·12월) → 156H 리셋되어 근로시간 한도로는 막히지 않음. 남는 제약은 휴일근로 동의 · 가산수당 · 추석 직후 3주 연속 무휴 피로도 → 3안(9/23) 권고</t>
         </is>
@@ -3629,43 +3853,43 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="130">
-      <c r="A35" s="138" t="inlineStr">
+      <c r="A35" s="235" t="inlineStr">
         <is>
           <t>특근 횟수</t>
         </is>
       </c>
       <c r="B35" s="204" t="n"/>
       <c r="C35" s="205" t="n"/>
-      <c r="D35" s="138" t="inlineStr">
+      <c r="D35" s="235" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
       <c r="E35" s="204" t="n"/>
       <c r="F35" s="205" t="n"/>
-      <c r="G35" s="138" t="inlineStr">
+      <c r="G35" s="235" t="inlineStr">
         <is>
           <t>인당 소요</t>
         </is>
       </c>
-      <c r="H35" s="138" t="inlineStr">
+      <c r="H35" s="235" t="inlineStr">
         <is>
           <t>전사 소요(H)</t>
         </is>
       </c>
       <c r="I35" s="205" t="n"/>
-      <c r="J35" s="138" t="inlineStr">
+      <c r="J35" s="235" t="inlineStr">
         <is>
           <t>잔여 대비</t>
         </is>
       </c>
-      <c r="K35" s="138" t="inlineStr">
+      <c r="K35" s="235" t="inlineStr">
         <is>
           <t>편성 불가</t>
         </is>
       </c>
       <c r="L35" s="205" t="n"/>
-      <c r="M35" s="138" t="inlineStr">
+      <c r="M35" s="235" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3677,41 +3901,41 @@
       <c r="R35" s="205" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1" s="130">
-      <c r="A36" s="140" t="inlineStr">
+      <c r="A36" s="228" t="inlineStr">
         <is>
           <t>1회</t>
         </is>
       </c>
       <c r="B36" s="204" t="n"/>
       <c r="C36" s="205" t="n"/>
-      <c r="D36" s="172" t="inlineStr">
+      <c r="D36" s="251" t="inlineStr">
         <is>
           <t>9/5</t>
         </is>
       </c>
       <c r="E36" s="204" t="n"/>
       <c r="F36" s="205" t="n"/>
-      <c r="G36" s="172" t="inlineStr">
+      <c r="G36" s="251" t="inlineStr">
         <is>
           <t>8H</t>
         </is>
       </c>
-      <c r="H36" s="141" t="n">
+      <c r="H36" s="240" t="n">
         <v>1912</v>
       </c>
       <c r="I36" s="205" t="n"/>
-      <c r="J36" s="173" t="inlineStr">
+      <c r="J36" s="262" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="K36" s="174" t="inlineStr">
+      <c r="K36" s="220" t="inlineStr">
         <is>
           <t>6명</t>
         </is>
       </c>
       <c r="L36" s="205" t="n"/>
-      <c r="M36" s="175" t="inlineStr">
+      <c r="M36" s="243" t="inlineStr">
         <is>
           <t>여유</t>
         </is>
@@ -3723,41 +3947,41 @@
       <c r="R36" s="205" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1" s="130">
-      <c r="A37" s="140" t="inlineStr">
+      <c r="A37" s="228" t="inlineStr">
         <is>
           <t>2회</t>
         </is>
       </c>
       <c r="B37" s="204" t="n"/>
       <c r="C37" s="205" t="n"/>
-      <c r="D37" s="172" t="inlineStr">
+      <c r="D37" s="251" t="inlineStr">
         <is>
           <t>9/5 · 12</t>
         </is>
       </c>
       <c r="E37" s="204" t="n"/>
       <c r="F37" s="205" t="n"/>
-      <c r="G37" s="172" t="inlineStr">
+      <c r="G37" s="251" t="inlineStr">
         <is>
           <t>16H</t>
         </is>
       </c>
-      <c r="H37" s="141" t="n">
+      <c r="H37" s="240" t="n">
         <v>3824</v>
       </c>
       <c r="I37" s="205" t="n"/>
-      <c r="J37" s="173" t="inlineStr">
+      <c r="J37" s="262" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="K37" s="174" t="inlineStr">
+      <c r="K37" s="220" t="inlineStr">
         <is>
           <t>7명</t>
         </is>
       </c>
       <c r="L37" s="205" t="n"/>
-      <c r="M37" s="175" t="inlineStr">
+      <c r="M37" s="243" t="inlineStr">
         <is>
           <t>여유</t>
         </is>
@@ -3769,41 +3993,41 @@
       <c r="R37" s="205" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1" s="130">
-      <c r="A38" s="140" t="inlineStr">
+      <c r="A38" s="228" t="inlineStr">
         <is>
           <t>3회</t>
         </is>
       </c>
       <c r="B38" s="204" t="n"/>
       <c r="C38" s="205" t="n"/>
-      <c r="D38" s="172" t="inlineStr">
+      <c r="D38" s="251" t="inlineStr">
         <is>
           <t>9/5 · 12 · 19</t>
         </is>
       </c>
       <c r="E38" s="204" t="n"/>
       <c r="F38" s="205" t="n"/>
-      <c r="G38" s="172" t="inlineStr">
+      <c r="G38" s="251" t="inlineStr">
         <is>
           <t>24H</t>
         </is>
       </c>
-      <c r="H38" s="141" t="n">
+      <c r="H38" s="240" t="n">
         <v>5736</v>
       </c>
       <c r="I38" s="205" t="n"/>
-      <c r="J38" s="173" t="inlineStr">
+      <c r="J38" s="262" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="K38" s="174" t="inlineStr">
+      <c r="K38" s="220" t="inlineStr">
         <is>
           <t>11명</t>
         </is>
       </c>
       <c r="L38" s="205" t="n"/>
-      <c r="M38" s="175" t="inlineStr">
+      <c r="M38" s="243" t="inlineStr">
         <is>
           <t>권장 상한 — 세척실 5명(김영두·박태근·이세호·한인수·선우찬) 제외 편성</t>
         </is>
@@ -3815,41 +4039,41 @@
       <c r="R38" s="205" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1" s="130">
-      <c r="A39" s="140" t="inlineStr">
+      <c r="A39" s="228" t="inlineStr">
         <is>
           <t>4회</t>
         </is>
       </c>
       <c r="B39" s="204" t="n"/>
       <c r="C39" s="205" t="n"/>
-      <c r="D39" s="172" t="inlineStr">
+      <c r="D39" s="251" t="inlineStr">
         <is>
           <t>+ 9/26 (추석 연휴)</t>
         </is>
       </c>
       <c r="E39" s="204" t="n"/>
       <c r="F39" s="205" t="n"/>
-      <c r="G39" s="172" t="inlineStr">
+      <c r="G39" s="251" t="inlineStr">
         <is>
           <t>32H</t>
         </is>
       </c>
-      <c r="H39" s="141" t="n">
+      <c r="H39" s="240" t="n">
         <v>7648</v>
       </c>
       <c r="I39" s="205" t="n"/>
-      <c r="J39" s="173" t="inlineStr">
+      <c r="J39" s="262" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="K39" s="174" t="inlineStr">
+      <c r="K39" s="220" t="inlineStr">
         <is>
           <t>22명</t>
         </is>
       </c>
       <c r="L39" s="205" t="n"/>
-      <c r="M39" s="176" t="inlineStr">
+      <c r="M39" s="242" t="inlineStr">
         <is>
           <t>9/26은 추석 연휴 중 토요일 — 휴일근로 가산·연휴 근무 동의 별도 필요</t>
         </is>
@@ -3951,8 +4175,8 @@
     </row>
   </sheetData>
   <mergeCells count="67">
+    <mergeCell ref="H35:I35"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H35:I35"/>
     <mergeCell ref="J6:R6"/>
     <mergeCell ref="A25:R25"/>
     <mergeCell ref="H38:I38"/>
@@ -4030,7 +4254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="130" min="1" max="1"/>
@@ -4056,7 +4280,7 @@
     <row r="1" ht="22" customHeight="1" s="130">
       <c r="A1" s="131" t="inlineStr">
         <is>
-          <t>10월 연장근로 예측 — 신규 단위기간(10·11·12월)</t>
+          <t>9월 풀 특근(8월 수준 재현) 검증 — 단위기간 7·8·9월</t>
         </is>
       </c>
       <c r="B1" s="132" t="n"/>
@@ -4078,9 +4302,9 @@
       <c r="R1" s="132" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1" s="130">
-      <c r="A2" s="206" t="inlineStr">
-        <is>
-          <t>10월부터 3개월 탄력근로 단위기간이 새로 시작되어 개인당 156H가 리셋됨  ·  9월 잔여와 무관하게 신규 한도 적용  |  2026.09.02</t>
+      <c r="A2" s="264" t="inlineStr">
+        <is>
+          <t>가정: 9월 시간외를 개인별 8월 실적 그대로 재현  ·  한도 156H(연장 12H/주 × 13주)  ·  대상 239명(업무 88 / 생산 151)  |  2026.09.02</t>
         </is>
       </c>
       <c r="B2" s="134" t="n"/>
@@ -4104,7 +4328,7 @@
     <row r="3" ht="14" customHeight="1" s="130">
       <c r="A3" s="135" t="inlineStr">
         <is>
-          <t>① 10월 근무일 요건</t>
+          <t>① 결론</t>
         </is>
       </c>
       <c r="B3" s="136" t="n"/>
@@ -4125,106 +4349,147 @@
       <c r="Q3" s="136" t="n"/>
       <c r="R3" s="136" t="n"/>
     </row>
-    <row r="4" ht="13" customHeight="1" s="130">
-      <c r="A4" s="207" t="inlineStr">
-        <is>
-          <t>실근무 평일</t>
+    <row r="4" ht="14" customHeight="1" s="130">
+      <c r="A4" s="265" t="inlineStr">
+        <is>
+          <t>7·8월 소진</t>
         </is>
       </c>
       <c r="B4" s="146" t="n"/>
-      <c r="C4" s="146" t="n"/>
-      <c r="D4" s="208" t="inlineStr">
-        <is>
-          <t>20일</t>
-        </is>
-      </c>
-      <c r="E4" s="134" t="n"/>
+      <c r="C4" s="266" t="inlineStr">
+        <is>
+          <t>14,354H</t>
+        </is>
+      </c>
+      <c r="D4" s="171" t="n"/>
+      <c r="E4" s="267" t="inlineStr">
+        <is>
+          <t>인당 60H (한도의 39%)</t>
+        </is>
+      </c>
       <c r="F4" s="134" t="n"/>
-      <c r="G4" s="134" t="n"/>
-      <c r="H4" s="134" t="n"/>
-      <c r="I4" s="134" t="n"/>
-      <c r="J4" s="207" t="inlineStr">
-        <is>
-          <t>토요일</t>
-        </is>
-      </c>
-      <c r="K4" s="146" t="n"/>
-      <c r="L4" s="146" t="n"/>
-      <c r="M4" s="208" t="inlineStr">
-        <is>
-          <t>5회 (3·10·17·24·31)</t>
-        </is>
-      </c>
-      <c r="N4" s="134" t="n"/>
-      <c r="O4" s="134" t="n"/>
-      <c r="P4" s="134" t="n"/>
-      <c r="Q4" s="134" t="n"/>
+      <c r="G4" s="265" t="inlineStr">
+        <is>
+          <t>9월 잔여</t>
+        </is>
+      </c>
+      <c r="H4" s="146" t="n"/>
+      <c r="I4" s="266" t="inlineStr">
+        <is>
+          <t>23,032H</t>
+        </is>
+      </c>
+      <c r="J4" s="171" t="n"/>
+      <c r="K4" s="267" t="inlineStr">
+        <is>
+          <t>인당 96H</t>
+        </is>
+      </c>
+      <c r="L4" s="134" t="n"/>
+      <c r="M4" s="265" t="inlineStr">
+        <is>
+          <t>8월 수준 요구</t>
+        </is>
+      </c>
+      <c r="N4" s="146" t="n"/>
+      <c r="O4" s="268" t="inlineStr">
+        <is>
+          <t>6,707H</t>
+        </is>
+      </c>
+      <c r="P4" s="146" t="n"/>
+      <c r="Q4" s="267" t="inlineStr">
+        <is>
+          <t>인당 28H</t>
+        </is>
+      </c>
       <c r="R4" s="134" t="n"/>
     </row>
-    <row r="5" ht="13" customHeight="1" s="130">
-      <c r="A5" s="207" t="inlineStr">
-        <is>
-          <t>일요일</t>
+    <row r="5" ht="14" customHeight="1" s="130">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>한도 내 편성 가능</t>
         </is>
       </c>
       <c r="B5" s="146" t="n"/>
-      <c r="C5" s="146" t="n"/>
-      <c r="D5" s="208" t="inlineStr">
-        <is>
-          <t>4일 (4·11·18·25)</t>
-        </is>
-      </c>
-      <c r="E5" s="134" t="n"/>
+      <c r="C5" s="269" t="inlineStr">
+        <is>
+          <t>5,268H</t>
+        </is>
+      </c>
+      <c r="D5" s="169" t="n"/>
+      <c r="E5" s="267" t="inlineStr">
+        <is>
+          <t>요구의 79%</t>
+        </is>
+      </c>
       <c r="F5" s="134" t="n"/>
-      <c r="G5" s="134" t="n"/>
-      <c r="H5" s="134" t="n"/>
-      <c r="I5" s="134" t="n"/>
-      <c r="J5" s="207" t="inlineStr">
-        <is>
-          <t>공휴일</t>
-        </is>
-      </c>
-      <c r="K5" s="146" t="n"/>
-      <c r="L5" s="146" t="n"/>
-      <c r="M5" s="208" t="inlineStr">
-        <is>
-          <t>3일 — 10/3 개천절(토) · 10/5 대체공휴일(월) · 10/9 한글날(금)</t>
-        </is>
-      </c>
-      <c r="N5" s="134" t="n"/>
-      <c r="O5" s="134" t="n"/>
-      <c r="P5" s="134" t="n"/>
-      <c r="Q5" s="134" t="n"/>
+      <c r="G5" s="265" t="inlineStr">
+        <is>
+          <t>편성 불가(부족)</t>
+        </is>
+      </c>
+      <c r="H5" s="146" t="n"/>
+      <c r="I5" s="270" t="inlineStr">
+        <is>
+          <t>1,438H</t>
+        </is>
+      </c>
+      <c r="J5" s="148" t="n"/>
+      <c r="K5" s="267" t="inlineStr">
+        <is>
+          <t>요구의 21%</t>
+        </is>
+      </c>
+      <c r="L5" s="134" t="n"/>
+      <c r="M5" s="265" t="inlineStr">
+        <is>
+          <t>한도 초과 인원</t>
+        </is>
+      </c>
+      <c r="N5" s="146" t="n"/>
+      <c r="O5" s="270" t="inlineStr">
+        <is>
+          <t>38명</t>
+        </is>
+      </c>
+      <c r="P5" s="148" t="n"/>
+      <c r="Q5" s="267" t="inlineStr">
+        <is>
+          <t>전체의 16%</t>
+        </is>
+      </c>
       <c r="R5" s="134" t="n"/>
     </row>
-    <row r="6" ht="12" customHeight="1" s="130">
-      <c r="A6" s="206" t="inlineStr">
-        <is>
-          <t>※ 개천절이 토요일이라 10/5(월)이 대체공휴일. 10월은 유급휴일이 3일이라 평일 근무일이 20일로 줄어든다.</t>
-        </is>
-      </c>
-      <c r="B6" s="134" t="n"/>
-      <c r="C6" s="134" t="n"/>
-      <c r="D6" s="134" t="n"/>
-      <c r="E6" s="134" t="n"/>
-      <c r="F6" s="134" t="n"/>
-      <c r="G6" s="134" t="n"/>
-      <c r="H6" s="134" t="n"/>
-      <c r="I6" s="134" t="n"/>
-      <c r="J6" s="134" t="n"/>
-      <c r="K6" s="134" t="n"/>
-      <c r="L6" s="134" t="n"/>
-      <c r="M6" s="134" t="n"/>
-      <c r="N6" s="134" t="n"/>
-      <c r="O6" s="134" t="n"/>
-      <c r="P6" s="134" t="n"/>
-      <c r="Q6" s="134" t="n"/>
-      <c r="R6" s="134" t="n"/>
-    </row>
+    <row r="6" ht="26" customHeight="1" s="130">
+      <c r="A6" s="234" t="inlineStr">
+        <is>
+          <t>▶ 9월을 8월처럼 풀 특근으로 돌리면 38명이 3개월 한도 156H를 넘는다. 전사로는 1,438H(21%)를 편성할 수 없어, 그만큼을 여유 인원으로 대체하거나 축소해야 한다. 9월 잔여 총량(23,032H) 자체는 충분하므로, 문제는 총량이 아니라 특정 인원·공정에 쏠린 편중이다.</t>
+        </is>
+      </c>
+      <c r="B6" s="148" t="n"/>
+      <c r="C6" s="148" t="n"/>
+      <c r="D6" s="148" t="n"/>
+      <c r="E6" s="148" t="n"/>
+      <c r="F6" s="148" t="n"/>
+      <c r="G6" s="148" t="n"/>
+      <c r="H6" s="148" t="n"/>
+      <c r="I6" s="148" t="n"/>
+      <c r="J6" s="148" t="n"/>
+      <c r="K6" s="148" t="n"/>
+      <c r="L6" s="148" t="n"/>
+      <c r="M6" s="148" t="n"/>
+      <c r="N6" s="148" t="n"/>
+      <c r="O6" s="148" t="n"/>
+      <c r="P6" s="148" t="n"/>
+      <c r="Q6" s="148" t="n"/>
+      <c r="R6" s="148" t="n"/>
+    </row>
+    <row r="7" s="130"/>
     <row r="8" ht="14" customHeight="1" s="130">
       <c r="A8" s="135" t="inlineStr">
         <is>
-          <t>② 10월 연장근로 시나리오 — 단위기간 한도 156H 대비</t>
+          <t>② 공정별 — 8월 재현 시 한도 초과 현황 (초과 인원 많은 순)</t>
         </is>
       </c>
       <c r="B8" s="136" t="n"/>
@@ -4246,506 +4511,636 @@
       <c r="R8" s="136" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="130">
-      <c r="A9" s="209" t="inlineStr">
-        <is>
-          <t>시나리오</t>
+      <c r="A9" s="271" t="inlineStr">
+        <is>
+          <t>공정</t>
         </is>
       </c>
       <c r="B9" s="139" t="n"/>
-      <c r="C9" s="209" t="inlineStr">
-        <is>
-          <t>구성</t>
-        </is>
-      </c>
-      <c r="D9" s="139" t="n"/>
+      <c r="C9" s="139" t="n"/>
+      <c r="D9" s="271" t="inlineStr">
+        <is>
+          <t>총원</t>
+        </is>
+      </c>
       <c r="E9" s="139" t="n"/>
-      <c r="F9" s="139" t="n"/>
+      <c r="F9" s="271" t="inlineStr">
+        <is>
+          <t>초과</t>
+        </is>
+      </c>
       <c r="G9" s="139" t="n"/>
-      <c r="H9" s="139" t="n"/>
-      <c r="I9" s="209" t="inlineStr">
-        <is>
-          <t>인당(H)</t>
-        </is>
-      </c>
-      <c r="J9" s="139" t="n"/>
-      <c r="K9" s="209" t="inlineStr">
-        <is>
-          <t>전사(H)</t>
-        </is>
-      </c>
-      <c r="L9" s="139" t="n"/>
-      <c r="M9" s="209" t="inlineStr">
-        <is>
-          <t>156H 소진</t>
-        </is>
-      </c>
-      <c r="N9" s="139" t="n"/>
-      <c r="O9" s="209" t="inlineStr">
-        <is>
-          <t>11·12월 잔여</t>
-        </is>
-      </c>
+      <c r="H9" s="271" t="inlineStr">
+        <is>
+          <t>비중</t>
+        </is>
+      </c>
+      <c r="I9" s="139" t="n"/>
+      <c r="J9" s="271" t="inlineStr">
+        <is>
+          <t>초과량</t>
+        </is>
+      </c>
+      <c r="K9" s="139" t="n"/>
+      <c r="L9" s="271" t="inlineStr">
+        <is>
+          <t>공정 잔여</t>
+        </is>
+      </c>
+      <c r="M9" s="139" t="n"/>
+      <c r="N9" s="271" t="inlineStr">
+        <is>
+          <t>판정 / 조치</t>
+        </is>
+      </c>
+      <c r="O9" s="139" t="n"/>
       <c r="P9" s="139" t="n"/>
-      <c r="Q9" s="209" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
+      <c r="Q9" s="139" t="n"/>
       <c r="R9" s="139" t="n"/>
     </row>
-    <row r="10" ht="13" customHeight="1" s="130">
-      <c r="A10" s="207" t="inlineStr">
-        <is>
-          <t>A 보수</t>
+    <row r="10" ht="12.5" customHeight="1" s="130">
+      <c r="A10" s="272" t="inlineStr">
+        <is>
+          <t>세척실</t>
         </is>
       </c>
       <c r="B10" s="146" t="n"/>
-      <c r="C10" s="208" t="inlineStr">
-        <is>
-          <t>평일 잔업 없음 + 토특근 3회</t>
-        </is>
-      </c>
-      <c r="D10" s="134" t="n"/>
+      <c r="C10" s="146" t="n"/>
+      <c r="D10" s="273" t="n">
+        <v>14</v>
+      </c>
       <c r="E10" s="134" t="n"/>
-      <c r="F10" s="134" t="n"/>
+      <c r="F10" s="274" t="n">
+        <v>6</v>
+      </c>
       <c r="G10" s="134" t="n"/>
-      <c r="H10" s="134" t="n"/>
-      <c r="I10" s="210" t="n">
+      <c r="H10" s="275" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="I10" s="134" t="n"/>
+      <c r="J10" s="276" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="K10" s="134" t="n"/>
+      <c r="L10" s="276" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="M10" s="134" t="n"/>
+      <c r="N10" s="277" t="inlineStr">
+        <is>
+          <t>최대 병목 — 초과 6명·518H. 세정 증설(1안) 투입원과 동일 공정. 잔여 826H로는 대체 불가 → 충원 없이는 9월 풀 특근 불가</t>
+        </is>
+      </c>
+      <c r="O10" s="148" t="n"/>
+      <c r="P10" s="148" t="n"/>
+      <c r="Q10" s="148" t="n"/>
+      <c r="R10" s="148" t="n"/>
+    </row>
+    <row r="11" ht="12.5" customHeight="1" s="130">
+      <c r="A11" s="272" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="B11" s="146" t="n"/>
+      <c r="C11" s="146" t="n"/>
+      <c r="D11" s="273" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="134" t="n"/>
+      <c r="F11" s="274" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="134" t="n"/>
+      <c r="H11" s="275" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="I11" s="134" t="n"/>
+      <c r="J11" s="276" t="n">
+        <v>133</v>
+      </c>
+      <c r="K11" s="134" t="n"/>
+      <c r="L11" s="276" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="M11" s="134" t="n"/>
+      <c r="N11" s="278" t="inlineStr">
+        <is>
+          <t>2명 초과 133H. 설비 대응 공백 시 라인 정지 직결 — 우선 완화 대상</t>
+        </is>
+      </c>
+      <c r="O11" s="169" t="n"/>
+      <c r="P11" s="169" t="n"/>
+      <c r="Q11" s="169" t="n"/>
+      <c r="R11" s="169" t="n"/>
+    </row>
+    <row r="12" ht="12.5" customHeight="1" s="130">
+      <c r="A12" s="272" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+      <c r="B12" s="146" t="n"/>
+      <c r="C12" s="146" t="n"/>
+      <c r="D12" s="273" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="134" t="n"/>
+      <c r="F12" s="274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="134" t="n"/>
+      <c r="H12" s="275" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="134" t="n"/>
+      <c r="J12" s="276" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="K12" s="134" t="n"/>
+      <c r="L12" s="276" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M12" s="134" t="n"/>
+      <c r="N12" s="277" t="inlineStr">
+        <is>
+          <t>3명 전원 초과 · 잔여 74H로 전 직책 최저. '주임 직접화' 요구는 근로시간으로도 불가</t>
+        </is>
+      </c>
+      <c r="O12" s="148" t="n"/>
+      <c r="P12" s="148" t="n"/>
+      <c r="Q12" s="148" t="n"/>
+      <c r="R12" s="148" t="n"/>
+    </row>
+    <row r="13" ht="12.5" customHeight="1" s="130">
+      <c r="A13" s="272" t="inlineStr">
+        <is>
+          <t>포장재 창고</t>
+        </is>
+      </c>
+      <c r="B13" s="146" t="n"/>
+      <c r="C13" s="146" t="n"/>
+      <c r="D13" s="273" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="134" t="n"/>
+      <c r="F13" s="274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="134" t="n"/>
+      <c r="H13" s="275" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I13" s="134" t="n"/>
+      <c r="J13" s="276" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="K13" s="134" t="n"/>
+      <c r="L13" s="276" t="n">
+        <v>2508</v>
+      </c>
+      <c r="M13" s="134" t="n"/>
+      <c r="N13" s="279" t="inlineStr">
+        <is>
+          <t>잔여 2,508H로 공정 내 재배분 가능. 3명 축소 후 여유 인원 이관</t>
+        </is>
+      </c>
+      <c r="O13" s="171" t="n"/>
+      <c r="P13" s="171" t="n"/>
+      <c r="Q13" s="171" t="n"/>
+      <c r="R13" s="171" t="n"/>
+    </row>
+    <row r="14" ht="12.5" customHeight="1" s="130">
+      <c r="A14" s="272" t="inlineStr">
+        <is>
+          <t>HnB</t>
+        </is>
+      </c>
+      <c r="B14" s="146" t="n"/>
+      <c r="C14" s="146" t="n"/>
+      <c r="D14" s="273" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="134" t="n"/>
+      <c r="F14" s="274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="134" t="n"/>
+      <c r="H14" s="275" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="134" t="n"/>
+      <c r="J14" s="276" t="n">
+        <v>97</v>
+      </c>
+      <c r="K14" s="134" t="n"/>
+      <c r="L14" s="276" t="n">
+        <v>210</v>
+      </c>
+      <c r="M14" s="134" t="n"/>
+      <c r="N14" s="277" t="inlineStr">
+        <is>
+          <t>5명 중 3명 초과(60%) · 잔여 210H. 인원 절대 부족 — 타 공정 지원 필요</t>
+        </is>
+      </c>
+      <c r="O14" s="148" t="n"/>
+      <c r="P14" s="148" t="n"/>
+      <c r="Q14" s="148" t="n"/>
+      <c r="R14" s="148" t="n"/>
+    </row>
+    <row r="15" ht="12.5" customHeight="1" s="130">
+      <c r="A15" s="272" t="inlineStr">
+        <is>
+          <t>멀티</t>
+        </is>
+      </c>
+      <c r="B15" s="146" t="n"/>
+      <c r="C15" s="146" t="n"/>
+      <c r="D15" s="273" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" s="134" t="n"/>
+      <c r="F15" s="274" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="134" t="n"/>
+      <c r="H15" s="275" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="134" t="n"/>
+      <c r="J15" s="276" t="n">
+        <v>96</v>
+      </c>
+      <c r="K15" s="134" t="n"/>
+      <c r="L15" s="276" t="n">
+        <v>1631</v>
+      </c>
+      <c r="M15" s="134" t="n"/>
+      <c r="N15" s="278" t="inlineStr">
+        <is>
+          <t>잔여 1,631H. 공정 내 재배분 가능하나 4명은 편성 제외</t>
+        </is>
+      </c>
+      <c r="O15" s="169" t="n"/>
+      <c r="P15" s="169" t="n"/>
+      <c r="Q15" s="169" t="n"/>
+      <c r="R15" s="169" t="n"/>
+    </row>
+    <row r="16" ht="12.5" customHeight="1" s="130">
+      <c r="A16" s="272" t="inlineStr">
+        <is>
+          <t>직선</t>
+        </is>
+      </c>
+      <c r="B16" s="146" t="n"/>
+      <c r="C16" s="146" t="n"/>
+      <c r="D16" s="273" t="n">
         <v>24</v>
       </c>
-      <c r="J10" s="134" t="n"/>
-      <c r="K10" s="211" t="n">
-        <v>5736</v>
-      </c>
-      <c r="L10" s="134" t="n"/>
-      <c r="M10" s="212" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="N10" s="134" t="n"/>
-      <c r="O10" s="213" t="n">
-        <v>132</v>
-      </c>
-      <c r="P10" s="134" t="n"/>
-      <c r="Q10" s="214" t="inlineStr">
-        <is>
-          <t>여유</t>
-        </is>
-      </c>
-      <c r="R10" s="171" t="n"/>
-    </row>
-    <row r="11" ht="13" customHeight="1" s="130">
-      <c r="A11" s="207" t="inlineStr">
-        <is>
-          <t>B 표준</t>
-        </is>
-      </c>
-      <c r="B11" s="146" t="n"/>
-      <c r="C11" s="208" t="inlineStr">
-        <is>
-          <t>평일 2H × 20일 + 토특근 3회</t>
-        </is>
-      </c>
-      <c r="D11" s="134" t="n"/>
-      <c r="E11" s="134" t="n"/>
-      <c r="F11" s="134" t="n"/>
-      <c r="G11" s="134" t="n"/>
-      <c r="H11" s="134" t="n"/>
-      <c r="I11" s="210" t="n">
-        <v>64</v>
-      </c>
-      <c r="J11" s="134" t="n"/>
-      <c r="K11" s="211" t="n">
-        <v>15296</v>
-      </c>
-      <c r="L11" s="134" t="n"/>
-      <c r="M11" s="212" t="n">
-        <v>0.4102564102564102</v>
-      </c>
-      <c r="N11" s="134" t="n"/>
-      <c r="O11" s="213" t="n">
-        <v>92</v>
-      </c>
-      <c r="P11" s="134" t="n"/>
-      <c r="Q11" s="214" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="R11" s="171" t="n"/>
-    </row>
-    <row r="12" ht="13" customHeight="1" s="130">
-      <c r="A12" s="207" t="inlineStr">
-        <is>
-          <t>C 확대</t>
-        </is>
-      </c>
-      <c r="B12" s="146" t="n"/>
-      <c r="C12" s="208" t="inlineStr">
-        <is>
-          <t>평일 3H × 20일 + 토특근 4회 + 공휴일 1회</t>
-        </is>
-      </c>
-      <c r="D12" s="134" t="n"/>
-      <c r="E12" s="134" t="n"/>
-      <c r="F12" s="134" t="n"/>
-      <c r="G12" s="134" t="n"/>
-      <c r="H12" s="134" t="n"/>
-      <c r="I12" s="210" t="n">
-        <v>100</v>
-      </c>
-      <c r="J12" s="134" t="n"/>
-      <c r="K12" s="211" t="n">
-        <v>23900</v>
-      </c>
-      <c r="L12" s="134" t="n"/>
-      <c r="M12" s="212" t="n">
-        <v>0.6410256410256411</v>
-      </c>
-      <c r="N12" s="134" t="n"/>
-      <c r="O12" s="215" t="n">
-        <v>56</v>
-      </c>
-      <c r="P12" s="134" t="n"/>
-      <c r="Q12" s="216" t="inlineStr">
-        <is>
-          <t>11·12월 압박</t>
-        </is>
-      </c>
-      <c r="R12" s="169" t="n"/>
-    </row>
-    <row r="13" ht="13" customHeight="1" s="130">
-      <c r="A13" s="207" t="inlineStr">
-        <is>
-          <t>D 최대</t>
-        </is>
-      </c>
-      <c r="B13" s="146" t="n"/>
-      <c r="C13" s="208" t="inlineStr">
-        <is>
-          <t>평일 4H × 20일 + 토특근 5회 + 공휴일 2회</t>
-        </is>
-      </c>
-      <c r="D13" s="134" t="n"/>
-      <c r="E13" s="134" t="n"/>
-      <c r="F13" s="134" t="n"/>
-      <c r="G13" s="134" t="n"/>
-      <c r="H13" s="134" t="n"/>
-      <c r="I13" s="210" t="n">
-        <v>136</v>
-      </c>
-      <c r="J13" s="134" t="n"/>
-      <c r="K13" s="211" t="n">
-        <v>32504</v>
-      </c>
-      <c r="L13" s="134" t="n"/>
-      <c r="M13" s="212" t="n">
-        <v>0.8717948717948718</v>
-      </c>
-      <c r="N13" s="134" t="n"/>
-      <c r="O13" s="215" t="n">
-        <v>20</v>
-      </c>
-      <c r="P13" s="134" t="n"/>
-      <c r="Q13" s="217" t="inlineStr">
-        <is>
-          <t>11·12월 20H — 사실상 불가</t>
-        </is>
-      </c>
-      <c r="R13" s="148" t="n"/>
-    </row>
-    <row r="14" ht="12" customHeight="1" s="130">
-      <c r="A14" s="206" t="inlineStr">
-        <is>
-          <t>※ 1일 연장 4H = 소정 8H + 연장 4H(1일 12H 한도). 전사 = 239명 기준. 10월을 100H 이상 쓰면 11·12월에 쓸 수 있는 시간이 56H 이하로 떨어진다.</t>
-        </is>
-      </c>
-      <c r="B14" s="134" t="n"/>
-      <c r="C14" s="134" t="n"/>
-      <c r="D14" s="134" t="n"/>
-      <c r="E14" s="134" t="n"/>
-      <c r="F14" s="134" t="n"/>
-      <c r="G14" s="134" t="n"/>
-      <c r="H14" s="134" t="n"/>
-      <c r="I14" s="134" t="n"/>
-      <c r="J14" s="134" t="n"/>
-      <c r="K14" s="134" t="n"/>
-      <c r="L14" s="134" t="n"/>
-      <c r="M14" s="134" t="n"/>
-      <c r="N14" s="134" t="n"/>
-      <c r="O14" s="134" t="n"/>
-      <c r="P14" s="134" t="n"/>
-      <c r="Q14" s="134" t="n"/>
-      <c r="R14" s="134" t="n"/>
-    </row>
-    <row r="16" ht="14" customHeight="1" s="130">
-      <c r="A16" s="218" t="inlineStr">
-        <is>
-          <t>③ MES 시스템 확보안 × 10월 1·2주 연속 특근 — 상충 검토</t>
-        </is>
-      </c>
-      <c r="B16" s="219" t="n"/>
-      <c r="C16" s="219" t="n"/>
-      <c r="D16" s="219" t="n"/>
-      <c r="E16" s="219" t="n"/>
-      <c r="F16" s="219" t="n"/>
-      <c r="G16" s="219" t="n"/>
-      <c r="H16" s="219" t="n"/>
-      <c r="I16" s="219" t="n"/>
-      <c r="J16" s="219" t="n"/>
-      <c r="K16" s="219" t="n"/>
-      <c r="L16" s="219" t="n"/>
-      <c r="M16" s="219" t="n"/>
-      <c r="N16" s="219" t="n"/>
-      <c r="O16" s="219" t="n"/>
-      <c r="P16" s="219" t="n"/>
-      <c r="Q16" s="219" t="n"/>
-      <c r="R16" s="219" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="130">
-      <c r="A17" s="209" t="inlineStr">
-        <is>
-          <t>MES 안</t>
-        </is>
-      </c>
-      <c r="B17" s="139" t="n"/>
-      <c r="C17" s="209" t="inlineStr">
-        <is>
-          <t>일정</t>
-        </is>
-      </c>
-      <c r="D17" s="139" t="n"/>
-      <c r="E17" s="139" t="n"/>
-      <c r="F17" s="139" t="n"/>
-      <c r="G17" s="139" t="n"/>
-      <c r="H17" s="209" t="inlineStr">
-        <is>
-          <t>잠기는 토요일</t>
-        </is>
-      </c>
-      <c r="I17" s="139" t="n"/>
-      <c r="J17" s="139" t="n"/>
-      <c r="K17" s="209" t="inlineStr">
-        <is>
-          <t>10월 1·2주 연속 특근과의 관계</t>
-        </is>
-      </c>
-      <c r="L17" s="139" t="n"/>
-      <c r="M17" s="139" t="n"/>
-      <c r="N17" s="139" t="n"/>
-      <c r="O17" s="139" t="n"/>
-      <c r="P17" s="139" t="n"/>
-      <c r="Q17" s="139" t="n"/>
-      <c r="R17" s="139" t="n"/>
-    </row>
-    <row r="18" ht="14" customHeight="1" s="130">
-      <c r="A18" s="207" t="inlineStr">
-        <is>
-          <t>1안</t>
+      <c r="E16" s="134" t="n"/>
+      <c r="F16" s="274" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="134" t="n"/>
+      <c r="H16" s="275" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="I16" s="134" t="n"/>
+      <c r="J16" s="276" t="n">
+        <v>89</v>
+      </c>
+      <c r="K16" s="134" t="n"/>
+      <c r="L16" s="276" t="n">
+        <v>1902</v>
+      </c>
+      <c r="M16" s="134" t="n"/>
+      <c r="N16" s="278" t="inlineStr">
+        <is>
+          <t>잔여 1,902H로 최대 여유. 재배분으로 흡수 가능</t>
+        </is>
+      </c>
+      <c r="O16" s="169" t="n"/>
+      <c r="P16" s="169" t="n"/>
+      <c r="Q16" s="169" t="n"/>
+      <c r="R16" s="169" t="n"/>
+    </row>
+    <row r="17" ht="12.5" customHeight="1" s="130">
+      <c r="A17" s="272" t="inlineStr">
+        <is>
+          <t>튜브</t>
+        </is>
+      </c>
+      <c r="B17" s="146" t="n"/>
+      <c r="C17" s="146" t="n"/>
+      <c r="D17" s="273" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="134" t="n"/>
+      <c r="F17" s="274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="134" t="n"/>
+      <c r="H17" s="275" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="I17" s="134" t="n"/>
+      <c r="J17" s="276" t="n">
+        <v>89</v>
+      </c>
+      <c r="K17" s="134" t="n"/>
+      <c r="L17" s="276" t="n">
+        <v>1287</v>
+      </c>
+      <c r="M17" s="134" t="n"/>
+      <c r="N17" s="279" t="inlineStr">
+        <is>
+          <t>잔여 1,287H. 3명 제외 후 나머지 14명으로 6대 교대 유지 여부 재확인 필요</t>
+        </is>
+      </c>
+      <c r="O17" s="171" t="n"/>
+      <c r="P17" s="171" t="n"/>
+      <c r="Q17" s="171" t="n"/>
+      <c r="R17" s="171" t="n"/>
+    </row>
+    <row r="18" ht="12.5" customHeight="1" s="130">
+      <c r="A18" s="272" t="inlineStr">
+        <is>
+          <t>적재실</t>
         </is>
       </c>
       <c r="B18" s="146" t="n"/>
-      <c r="C18" s="208" t="inlineStr">
-        <is>
-          <t>10/2 근무 → 10/3~5 휴식 → 10/6 오픈</t>
-        </is>
-      </c>
-      <c r="D18" s="134" t="n"/>
+      <c r="C18" s="146" t="n"/>
+      <c r="D18" s="273" t="n">
+        <v>17</v>
+      </c>
       <c r="E18" s="134" t="n"/>
-      <c r="F18" s="134" t="n"/>
+      <c r="F18" s="274" t="n">
+        <v>2</v>
+      </c>
       <c r="G18" s="134" t="n"/>
-      <c r="H18" s="220" t="inlineStr">
-        <is>
-          <t>10/3</t>
-        </is>
+      <c r="H18" s="275" t="n">
+        <v>0.1176470588235294</v>
       </c>
       <c r="I18" s="134" t="n"/>
-      <c r="J18" s="134" t="n"/>
-      <c r="K18" s="221" t="inlineStr">
-        <is>
-          <t>10월 1주차 특근(10/3) 불가 — AP가 요청한 '10월 1·2주 연속 특근'과 정면 충돌</t>
-        </is>
-      </c>
-      <c r="L18" s="148" t="n"/>
-      <c r="M18" s="148" t="n"/>
-      <c r="N18" s="148" t="n"/>
-      <c r="O18" s="148" t="n"/>
-      <c r="P18" s="148" t="n"/>
-      <c r="Q18" s="148" t="n"/>
-      <c r="R18" s="148" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1" s="130">
-      <c r="A19" s="207" t="inlineStr">
-        <is>
-          <t>2안</t>
+      <c r="J18" s="276" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="K18" s="134" t="n"/>
+      <c r="L18" s="276" t="n">
+        <v>1722.5</v>
+      </c>
+      <c r="M18" s="134" t="n"/>
+      <c r="N18" s="279" t="inlineStr">
+        <is>
+          <t>잔여 1,722H. 재배분 가능</t>
+        </is>
+      </c>
+      <c r="O18" s="171" t="n"/>
+      <c r="P18" s="171" t="n"/>
+      <c r="Q18" s="171" t="n"/>
+      <c r="R18" s="171" t="n"/>
+    </row>
+    <row r="19" ht="12.5" customHeight="1" s="130">
+      <c r="A19" s="272" t="inlineStr">
+        <is>
+          <t>내용물 관리</t>
         </is>
       </c>
       <c r="B19" s="146" t="n"/>
-      <c r="C19" s="208" t="inlineStr">
-        <is>
-          <t>10/8 근무 → 10/9~11 휴식 → 10/12 오픈</t>
-        </is>
-      </c>
-      <c r="D19" s="134" t="n"/>
+      <c r="C19" s="146" t="n"/>
+      <c r="D19" s="273" t="n">
+        <v>5</v>
+      </c>
       <c r="E19" s="134" t="n"/>
-      <c r="F19" s="134" t="n"/>
+      <c r="F19" s="274" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" s="134" t="n"/>
-      <c r="H19" s="220" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
+      <c r="H19" s="275" t="n">
+        <v>0.4</v>
       </c>
       <c r="I19" s="134" t="n"/>
-      <c r="J19" s="134" t="n"/>
-      <c r="K19" s="221" t="inlineStr">
-        <is>
-          <t>10월 2주차 특근(10/10) 불가 — 동일하게 충돌</t>
-        </is>
-      </c>
-      <c r="L19" s="148" t="n"/>
-      <c r="M19" s="148" t="n"/>
-      <c r="N19" s="148" t="n"/>
+      <c r="J19" s="276" t="n">
+        <v>61</v>
+      </c>
+      <c r="K19" s="134" t="n"/>
+      <c r="L19" s="276" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="M19" s="134" t="n"/>
+      <c r="N19" s="277" t="inlineStr">
+        <is>
+          <t>5명 중 2명 초과 · 잔여 344H. 소수 공정 — 대체 인력 사전 지정 필요</t>
+        </is>
+      </c>
       <c r="O19" s="148" t="n"/>
       <c r="P19" s="148" t="n"/>
       <c r="Q19" s="148" t="n"/>
       <c r="R19" s="148" t="n"/>
     </row>
-    <row r="20" ht="14" customHeight="1" s="130">
-      <c r="A20" s="207" t="inlineStr">
-        <is>
-          <t>3안</t>
+    <row r="20" ht="12.5" customHeight="1" s="130">
+      <c r="A20" s="272" t="inlineStr">
+        <is>
+          <t>원료 창고</t>
         </is>
       </c>
       <c r="B20" s="146" t="n"/>
-      <c r="C20" s="208" t="inlineStr">
-        <is>
-          <t>9/23 근무 → 9/24~26 휴식 (추석 연휴)</t>
-        </is>
-      </c>
-      <c r="D20" s="134" t="n"/>
+      <c r="C20" s="146" t="n"/>
+      <c r="D20" s="273" t="n">
+        <v>6</v>
+      </c>
       <c r="E20" s="134" t="n"/>
-      <c r="F20" s="134" t="n"/>
+      <c r="F20" s="274" t="n">
+        <v>1</v>
+      </c>
       <c r="G20" s="134" t="n"/>
-      <c r="H20" s="222" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
+      <c r="H20" s="275" t="n">
+        <v>0.1666666666666667</v>
       </c>
       <c r="I20" s="134" t="n"/>
-      <c r="J20" s="134" t="n"/>
-      <c r="K20" s="223" t="inlineStr">
-        <is>
-          <t>10월 토요일을 하나도 잠그지 않음 — 연속 특근과 양립하는 유일한 안</t>
-        </is>
-      </c>
-      <c r="L20" s="171" t="n"/>
-      <c r="M20" s="171" t="n"/>
-      <c r="N20" s="171" t="n"/>
+      <c r="J20" s="276" t="n">
+        <v>41</v>
+      </c>
+      <c r="K20" s="134" t="n"/>
+      <c r="L20" s="276" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="M20" s="134" t="n"/>
+      <c r="N20" s="279" t="inlineStr">
+        <is>
+          <t>잔여 490H. 재배분 가능</t>
+        </is>
+      </c>
       <c r="O20" s="171" t="n"/>
       <c r="P20" s="171" t="n"/>
       <c r="Q20" s="171" t="n"/>
       <c r="R20" s="171" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1" s="130">
-      <c r="A21" s="224" t="inlineStr">
-        <is>
-          <t>▶ AP가 같은 회의에서 '10월 1·2주 연속 특근'과 'MES 확보를 위한 10월 초 3일 휴식'을 함께 요청했으나, 1안·2안은 그 특근일을 직접 잠근다. 두 요구를 모두 만족하는 것은 3안(9/23)뿐이다. 회의에서 확정 요청.</t>
-        </is>
-      </c>
-      <c r="B21" s="148" t="n"/>
-      <c r="C21" s="148" t="n"/>
-      <c r="D21" s="148" t="n"/>
-      <c r="E21" s="148" t="n"/>
-      <c r="F21" s="148" t="n"/>
-      <c r="G21" s="148" t="n"/>
-      <c r="H21" s="148" t="n"/>
-      <c r="I21" s="148" t="n"/>
-      <c r="J21" s="148" t="n"/>
-      <c r="K21" s="148" t="n"/>
-      <c r="L21" s="148" t="n"/>
-      <c r="M21" s="148" t="n"/>
-      <c r="N21" s="148" t="n"/>
-      <c r="O21" s="148" t="n"/>
-      <c r="P21" s="148" t="n"/>
-      <c r="Q21" s="148" t="n"/>
-      <c r="R21" s="148" t="n"/>
-    </row>
-    <row r="23" ht="14" customHeight="1" s="130">
-      <c r="A23" s="135" t="inlineStr">
-        <is>
-          <t>④ 9월과의 연계</t>
-        </is>
-      </c>
-      <c r="B23" s="136" t="n"/>
-      <c r="C23" s="136" t="n"/>
-      <c r="D23" s="136" t="n"/>
-      <c r="E23" s="136" t="n"/>
-      <c r="F23" s="136" t="n"/>
-      <c r="G23" s="136" t="n"/>
-      <c r="H23" s="136" t="n"/>
-      <c r="I23" s="136" t="n"/>
-      <c r="J23" s="136" t="n"/>
-      <c r="K23" s="136" t="n"/>
-      <c r="L23" s="136" t="n"/>
-      <c r="M23" s="136" t="n"/>
-      <c r="N23" s="136" t="n"/>
-      <c r="O23" s="136" t="n"/>
-      <c r="P23" s="136" t="n"/>
-      <c r="Q23" s="136" t="n"/>
-      <c r="R23" s="136" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="130">
-      <c r="A24" s="209" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B24" s="139" t="n"/>
-      <c r="C24" s="139" t="n"/>
-      <c r="D24" s="139" t="n"/>
-      <c r="E24" s="209" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="F24" s="139" t="n"/>
-      <c r="G24" s="139" t="n"/>
-      <c r="H24" s="209" t="inlineStr">
-        <is>
-          <t>의미</t>
-        </is>
-      </c>
-      <c r="I24" s="139" t="n"/>
-      <c r="J24" s="139" t="n"/>
-      <c r="K24" s="139" t="n"/>
-      <c r="L24" s="139" t="n"/>
-      <c r="M24" s="139" t="n"/>
-      <c r="N24" s="139" t="n"/>
-      <c r="O24" s="139" t="n"/>
-      <c r="P24" s="139" t="n"/>
-      <c r="Q24" s="139" t="n"/>
-      <c r="R24" s="139" t="n"/>
-    </row>
-    <row r="25" ht="13" customHeight="1" s="130">
-      <c r="A25" s="225" t="inlineStr">
-        <is>
-          <t>9월 잔여 (현 단위기간)</t>
-        </is>
-      </c>
-      <c r="B25" s="146" t="n"/>
-      <c r="C25" s="146" t="n"/>
-      <c r="D25" s="146" t="n"/>
-      <c r="E25" s="222" t="inlineStr">
-        <is>
-          <t>23,032H</t>
-        </is>
-      </c>
+    <row r="21" ht="12.5" customHeight="1" s="130">
+      <c r="A21" s="272" t="inlineStr">
+        <is>
+          <t>초격차</t>
+        </is>
+      </c>
+      <c r="B21" s="146" t="n"/>
+      <c r="C21" s="146" t="n"/>
+      <c r="D21" s="273" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" s="134" t="n"/>
+      <c r="F21" s="274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="134" t="n"/>
+      <c r="H21" s="275" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="I21" s="134" t="n"/>
+      <c r="J21" s="276" t="n">
+        <v>32</v>
+      </c>
+      <c r="K21" s="134" t="n"/>
+      <c r="L21" s="276" t="n">
+        <v>1896</v>
+      </c>
+      <c r="M21" s="134" t="n"/>
+      <c r="N21" s="279" t="inlineStr">
+        <is>
+          <t>1명만 초과 · 잔여 1,896H. 영향 없음</t>
+        </is>
+      </c>
+      <c r="O21" s="171" t="n"/>
+      <c r="P21" s="171" t="n"/>
+      <c r="Q21" s="171" t="n"/>
+      <c r="R21" s="171" t="n"/>
+    </row>
+    <row r="22" ht="12.5" customHeight="1" s="130">
+      <c r="A22" s="272" t="inlineStr">
+        <is>
+          <t>공작/미화</t>
+        </is>
+      </c>
+      <c r="B22" s="146" t="n"/>
+      <c r="C22" s="146" t="n"/>
+      <c r="D22" s="273" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="134" t="n"/>
+      <c r="F22" s="274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="134" t="n"/>
+      <c r="H22" s="275" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I22" s="134" t="n"/>
+      <c r="J22" s="276" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" s="134" t="n"/>
+      <c r="L22" s="276" t="n">
+        <v>1911.5</v>
+      </c>
+      <c r="M22" s="134" t="n"/>
+      <c r="N22" s="279" t="inlineStr">
+        <is>
+          <t>1명만 초과 · 잔여 1,912H. 영향 없음</t>
+        </is>
+      </c>
+      <c r="O22" s="171" t="n"/>
+      <c r="P22" s="171" t="n"/>
+      <c r="Q22" s="171" t="n"/>
+      <c r="R22" s="171" t="n"/>
+    </row>
+    <row r="23" ht="12.5" customHeight="1" s="130">
+      <c r="A23" s="272" t="inlineStr">
+        <is>
+          <t>계획자</t>
+        </is>
+      </c>
+      <c r="B23" s="146" t="n"/>
+      <c r="C23" s="146" t="n"/>
+      <c r="D23" s="273" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="134" t="n"/>
+      <c r="F23" s="274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="134" t="n"/>
+      <c r="H23" s="275" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I23" s="134" t="n"/>
+      <c r="J23" s="276" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K23" s="134" t="n"/>
+      <c r="L23" s="276" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="M23" s="134" t="n"/>
+      <c r="N23" s="278" t="inlineStr">
+        <is>
+          <t>3명 중 1명 초과 · 잔여 250H. 영향 제한적</t>
+        </is>
+      </c>
+      <c r="O23" s="169" t="n"/>
+      <c r="P23" s="169" t="n"/>
+      <c r="Q23" s="169" t="n"/>
+      <c r="R23" s="169" t="n"/>
+    </row>
+    <row r="24" ht="12.5" customHeight="1" s="130">
+      <c r="A24" s="272" t="inlineStr">
+        <is>
+          <t>실적/순회</t>
+        </is>
+      </c>
+      <c r="B24" s="146" t="n"/>
+      <c r="C24" s="146" t="n"/>
+      <c r="D24" s="273" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="134" t="n"/>
+      <c r="F24" s="274" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="134" t="n"/>
+      <c r="H24" s="275" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I24" s="134" t="n"/>
+      <c r="J24" s="276" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" s="134" t="n"/>
+      <c r="L24" s="276" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="M24" s="134" t="n"/>
+      <c r="N24" s="278" t="inlineStr">
+        <is>
+          <t>4명 중 1명 초과 · 잔여 400H. 영향 제한적</t>
+        </is>
+      </c>
+      <c r="O24" s="169" t="n"/>
+      <c r="P24" s="169" t="n"/>
+      <c r="Q24" s="169" t="n"/>
+      <c r="R24" s="169" t="n"/>
+    </row>
+    <row r="25" ht="12" customHeight="1" s="130">
+      <c r="A25" s="264" t="inlineStr">
+        <is>
+          <t>※ 초과량 = Σ(7월 + 8월×2 − 156).  공정 잔여 = Σmax(0, 156 − 7월 − 8월).  잔여가 초과량의 2배 미만이거나 초과 비중 40% 이상이면 공정 내 재배분 불가로 본다.</t>
+        </is>
+      </c>
+      <c r="B25" s="134" t="n"/>
+      <c r="C25" s="134" t="n"/>
+      <c r="D25" s="134" t="n"/>
+      <c r="E25" s="134" t="n"/>
       <c r="F25" s="134" t="n"/>
       <c r="G25" s="134" t="n"/>
-      <c r="H25" s="208" t="inlineStr">
-        <is>
-          <t>인당 96H. 9월에 얼마를 쓰든 10월 한도에는 영향 없음 — 단위기간이 다름</t>
-        </is>
-      </c>
+      <c r="H25" s="134" t="n"/>
       <c r="I25" s="134" t="n"/>
       <c r="J25" s="134" t="n"/>
       <c r="K25" s="134" t="n"/>
@@ -4757,25 +5152,1559 @@
       <c r="Q25" s="134" t="n"/>
       <c r="R25" s="134" t="n"/>
     </row>
-    <row r="26" ht="13" customHeight="1" s="130">
-      <c r="A26" s="225" t="inlineStr">
-        <is>
-          <t>9월 편성 불가 인원</t>
+    <row r="26" s="130"/>
+    <row r="27" ht="14" customHeight="1" s="130">
+      <c r="A27" s="135" t="inlineStr">
+        <is>
+          <t>③ 9월 편성 상위 제약 인원 (8월 재현 시 초과 큰 순)</t>
+        </is>
+      </c>
+      <c r="B27" s="136" t="n"/>
+      <c r="C27" s="136" t="n"/>
+      <c r="D27" s="136" t="n"/>
+      <c r="E27" s="136" t="n"/>
+      <c r="F27" s="136" t="n"/>
+      <c r="G27" s="136" t="n"/>
+      <c r="H27" s="136" t="n"/>
+      <c r="I27" s="136" t="n"/>
+      <c r="J27" s="136" t="n"/>
+      <c r="K27" s="136" t="n"/>
+      <c r="L27" s="136" t="n"/>
+      <c r="M27" s="136" t="n"/>
+      <c r="N27" s="136" t="n"/>
+      <c r="O27" s="136" t="n"/>
+      <c r="P27" s="136" t="n"/>
+      <c r="Q27" s="136" t="n"/>
+      <c r="R27" s="136" t="n"/>
+    </row>
+    <row r="28" ht="12.5" customHeight="1" s="130">
+      <c r="A28" s="265" t="inlineStr">
+        <is>
+          <t>박태근</t>
+        </is>
+      </c>
+      <c r="B28" s="146" t="n"/>
+      <c r="C28" s="267" t="inlineStr">
+        <is>
+          <t>세척실</t>
+        </is>
+      </c>
+      <c r="D28" s="134" t="n"/>
+      <c r="E28" s="280" t="inlineStr">
+        <is>
+          <t>초과 151H</t>
+        </is>
+      </c>
+      <c r="F28" s="148" t="n"/>
+      <c r="G28" s="265" t="inlineStr">
+        <is>
+          <t>김영두</t>
+        </is>
+      </c>
+      <c r="H28" s="146" t="n"/>
+      <c r="I28" s="267" t="inlineStr">
+        <is>
+          <t>세척실</t>
+        </is>
+      </c>
+      <c r="J28" s="134" t="n"/>
+      <c r="K28" s="280" t="inlineStr">
+        <is>
+          <t>초과 116H</t>
+        </is>
+      </c>
+      <c r="L28" s="148" t="n"/>
+      <c r="M28" s="265" t="inlineStr">
+        <is>
+          <t>문석</t>
+        </is>
+      </c>
+      <c r="N28" s="146" t="n"/>
+      <c r="O28" s="267" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="P28" s="134" t="n"/>
+      <c r="Q28" s="280" t="inlineStr">
+        <is>
+          <t>초과 114H</t>
+        </is>
+      </c>
+      <c r="R28" s="148" t="n"/>
+    </row>
+    <row r="29" ht="12.5" customHeight="1" s="130">
+      <c r="A29" s="265" t="inlineStr">
+        <is>
+          <t>이세호</t>
+        </is>
+      </c>
+      <c r="B29" s="146" t="n"/>
+      <c r="C29" s="267" t="inlineStr">
+        <is>
+          <t>세척실</t>
+        </is>
+      </c>
+      <c r="D29" s="134" t="n"/>
+      <c r="E29" s="280" t="inlineStr">
+        <is>
+          <t>초과 109H</t>
+        </is>
+      </c>
+      <c r="F29" s="148" t="n"/>
+      <c r="G29" s="265" t="inlineStr">
+        <is>
+          <t>한인수</t>
+        </is>
+      </c>
+      <c r="H29" s="146" t="n"/>
+      <c r="I29" s="267" t="inlineStr">
+        <is>
+          <t>세척실</t>
+        </is>
+      </c>
+      <c r="J29" s="134" t="n"/>
+      <c r="K29" s="280" t="inlineStr">
+        <is>
+          <t>초과 79H</t>
+        </is>
+      </c>
+      <c r="L29" s="148" t="n"/>
+      <c r="M29" s="265" t="inlineStr">
+        <is>
+          <t>조영순</t>
+        </is>
+      </c>
+      <c r="N29" s="146" t="n"/>
+      <c r="O29" s="267" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+      <c r="P29" s="134" t="n"/>
+      <c r="Q29" s="280" t="inlineStr">
+        <is>
+          <t>초과 70H</t>
+        </is>
+      </c>
+      <c r="R29" s="148" t="n"/>
+    </row>
+    <row r="30" ht="12.5" customHeight="1" s="130">
+      <c r="A30" s="265" t="inlineStr">
+        <is>
+          <t>김영준</t>
+        </is>
+      </c>
+      <c r="B30" s="146" t="n"/>
+      <c r="C30" s="267" t="inlineStr">
+        <is>
+          <t>적재실</t>
+        </is>
+      </c>
+      <c r="D30" s="134" t="n"/>
+      <c r="E30" s="280" t="inlineStr">
+        <is>
+          <t>초과 58H</t>
+        </is>
+      </c>
+      <c r="F30" s="148" t="n"/>
+      <c r="G30" s="265" t="inlineStr">
+        <is>
+          <t>서재권</t>
+        </is>
+      </c>
+      <c r="H30" s="146" t="n"/>
+      <c r="I30" s="267" t="inlineStr">
+        <is>
+          <t>포장재 창고</t>
+        </is>
+      </c>
+      <c r="J30" s="134" t="n"/>
+      <c r="K30" s="280" t="inlineStr">
+        <is>
+          <t>초과 56H</t>
+        </is>
+      </c>
+      <c r="L30" s="148" t="n"/>
+      <c r="M30" s="265" t="inlineStr">
+        <is>
+          <t>김해경</t>
+        </is>
+      </c>
+      <c r="N30" s="146" t="n"/>
+      <c r="O30" s="267" t="inlineStr">
+        <is>
+          <t>멀티</t>
+        </is>
+      </c>
+      <c r="P30" s="134" t="n"/>
+      <c r="Q30" s="280" t="inlineStr">
+        <is>
+          <t>초과 52H</t>
+        </is>
+      </c>
+      <c r="R30" s="148" t="n"/>
+    </row>
+    <row r="31" ht="12.5" customHeight="1" s="130">
+      <c r="A31" s="265" t="inlineStr">
+        <is>
+          <t>이준엽</t>
+        </is>
+      </c>
+      <c r="B31" s="146" t="n"/>
+      <c r="C31" s="267" t="inlineStr">
+        <is>
+          <t>포장재 창고</t>
+        </is>
+      </c>
+      <c r="D31" s="134" t="n"/>
+      <c r="E31" s="281" t="inlineStr">
+        <is>
+          <t>초과 46H</t>
+        </is>
+      </c>
+      <c r="F31" s="169" t="n"/>
+      <c r="G31" s="265" t="inlineStr">
+        <is>
+          <t>최명필</t>
+        </is>
+      </c>
+      <c r="H31" s="146" t="n"/>
+      <c r="I31" s="267" t="inlineStr">
+        <is>
+          <t>튜브</t>
+        </is>
+      </c>
+      <c r="J31" s="134" t="n"/>
+      <c r="K31" s="281" t="inlineStr">
+        <is>
+          <t>초과 45H</t>
+        </is>
+      </c>
+      <c r="L31" s="169" t="n"/>
+      <c r="M31" s="265" t="inlineStr">
+        <is>
+          <t>정혜숙</t>
+        </is>
+      </c>
+      <c r="N31" s="146" t="n"/>
+      <c r="O31" s="267" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+      <c r="P31" s="134" t="n"/>
+      <c r="Q31" s="281" t="inlineStr">
+        <is>
+          <t>초과 44H</t>
+        </is>
+      </c>
+      <c r="R31" s="169" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1" s="130">
+      <c r="A32" s="264" t="inlineStr">
+        <is>
+          <t>전체 38명 명단은 '아모레 업무' · '아모레 생산' 시트 원본에서 7월+8월×2 &gt; 156 조건으로 확인. 위 12명은 8월 실적이 이미 월 51.4H(주 12H 환산)를 크게 넘긴 인원으로, 9월 재현 자체가 불가하다.</t>
+        </is>
+      </c>
+      <c r="B32" s="134" t="n"/>
+      <c r="C32" s="134" t="n"/>
+      <c r="D32" s="134" t="n"/>
+      <c r="E32" s="134" t="n"/>
+      <c r="F32" s="134" t="n"/>
+      <c r="G32" s="134" t="n"/>
+      <c r="H32" s="134" t="n"/>
+      <c r="I32" s="134" t="n"/>
+      <c r="J32" s="134" t="n"/>
+      <c r="K32" s="134" t="n"/>
+      <c r="L32" s="134" t="n"/>
+      <c r="M32" s="134" t="n"/>
+      <c r="N32" s="134" t="n"/>
+      <c r="O32" s="134" t="n"/>
+      <c r="P32" s="134" t="n"/>
+      <c r="Q32" s="134" t="n"/>
+      <c r="R32" s="134" t="n"/>
+    </row>
+    <row r="33" s="130"/>
+    <row r="34" ht="14" customHeight="1" s="130">
+      <c r="A34" s="135" t="inlineStr">
+        <is>
+          <t>④ 대응안</t>
+        </is>
+      </c>
+      <c r="B34" s="136" t="n"/>
+      <c r="C34" s="136" t="n"/>
+      <c r="D34" s="136" t="n"/>
+      <c r="E34" s="136" t="n"/>
+      <c r="F34" s="136" t="n"/>
+      <c r="G34" s="136" t="n"/>
+      <c r="H34" s="136" t="n"/>
+      <c r="I34" s="136" t="n"/>
+      <c r="J34" s="136" t="n"/>
+      <c r="K34" s="136" t="n"/>
+      <c r="L34" s="136" t="n"/>
+      <c r="M34" s="136" t="n"/>
+      <c r="N34" s="136" t="n"/>
+      <c r="O34" s="136" t="n"/>
+      <c r="P34" s="136" t="n"/>
+      <c r="Q34" s="136" t="n"/>
+      <c r="R34" s="136" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="130">
+      <c r="A35" s="282" t="inlineStr"/>
+      <c r="B35" s="271" t="inlineStr">
+        <is>
+          <t>대응</t>
+        </is>
+      </c>
+      <c r="C35" s="139" t="n"/>
+      <c r="D35" s="139" t="n"/>
+      <c r="E35" s="271" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="F35" s="139" t="n"/>
+      <c r="G35" s="139" t="n"/>
+      <c r="H35" s="139" t="n"/>
+      <c r="I35" s="139" t="n"/>
+      <c r="J35" s="139" t="n"/>
+      <c r="K35" s="139" t="n"/>
+      <c r="L35" s="139" t="n"/>
+      <c r="M35" s="139" t="n"/>
+      <c r="N35" s="271" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
+      <c r="O35" s="139" t="n"/>
+      <c r="P35" s="139" t="n"/>
+      <c r="Q35" s="139" t="n"/>
+      <c r="R35" s="139" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1" s="130">
+      <c r="A36" s="271" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B36" s="272" t="inlineStr">
+        <is>
+          <t>초과 38명 9월 편성 축소</t>
+        </is>
+      </c>
+      <c r="C36" s="146" t="n"/>
+      <c r="D36" s="146" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>초과분 1,438H를 개인별로 삭감. 잔여 0H 4명(박태근·김영두·문석·이세호)은 9월 시간외 전면 제외</t>
+        </is>
+      </c>
+      <c r="F36" s="134" t="n"/>
+      <c r="G36" s="134" t="n"/>
+      <c r="H36" s="134" t="n"/>
+      <c r="I36" s="134" t="n"/>
+      <c r="J36" s="134" t="n"/>
+      <c r="K36" s="134" t="n"/>
+      <c r="L36" s="134" t="n"/>
+      <c r="M36" s="134" t="n"/>
+      <c r="N36" s="284" t="inlineStr">
+        <is>
+          <t>즉시 / 비용 0</t>
+        </is>
+      </c>
+      <c r="O36" s="171" t="n"/>
+      <c r="P36" s="171" t="n"/>
+      <c r="Q36" s="171" t="n"/>
+      <c r="R36" s="171" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1" s="130">
+      <c r="A37" s="271" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="272" t="inlineStr">
+        <is>
+          <t>공정 내 재배분</t>
+        </is>
+      </c>
+      <c r="C37" s="146" t="n"/>
+      <c r="D37" s="146" t="n"/>
+      <c r="E37" s="283" t="inlineStr">
+        <is>
+          <t>직선·초격차·공작미화·적재실·포장재창고는 잔여 충분 — 여유 인원으로 대체 편성</t>
+        </is>
+      </c>
+      <c r="F37" s="134" t="n"/>
+      <c r="G37" s="134" t="n"/>
+      <c r="H37" s="134" t="n"/>
+      <c r="I37" s="134" t="n"/>
+      <c r="J37" s="134" t="n"/>
+      <c r="K37" s="134" t="n"/>
+      <c r="L37" s="134" t="n"/>
+      <c r="M37" s="134" t="n"/>
+      <c r="N37" s="284" t="inlineStr">
+        <is>
+          <t>즉시 / 다능공 확인 필요</t>
+        </is>
+      </c>
+      <c r="O37" s="171" t="n"/>
+      <c r="P37" s="171" t="n"/>
+      <c r="Q37" s="171" t="n"/>
+      <c r="R37" s="171" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1" s="130">
+      <c r="A38" s="271" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="272" t="inlineStr">
+        <is>
+          <t>세척실·주임·HnB 충원</t>
+        </is>
+      </c>
+      <c r="C38" s="146" t="n"/>
+      <c r="D38" s="146" t="n"/>
+      <c r="E38" s="283" t="inlineStr">
+        <is>
+          <t>이 3개 공정은 잔여가 초과량을 못 덮음. 9월 물량을 8월 수준으로 유지하려면 충원이 전제</t>
+        </is>
+      </c>
+      <c r="F38" s="134" t="n"/>
+      <c r="G38" s="134" t="n"/>
+      <c r="H38" s="134" t="n"/>
+      <c r="I38" s="134" t="n"/>
+      <c r="J38" s="134" t="n"/>
+      <c r="K38" s="134" t="n"/>
+      <c r="L38" s="134" t="n"/>
+      <c r="M38" s="134" t="n"/>
+      <c r="N38" s="285" t="inlineStr">
+        <is>
+          <t>충원 없이는 불가</t>
+        </is>
+      </c>
+      <c r="O38" s="148" t="n"/>
+      <c r="P38" s="148" t="n"/>
+      <c r="Q38" s="148" t="n"/>
+      <c r="R38" s="148" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1" s="130">
+      <c r="A39" s="271" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="272" t="inlineStr">
+        <is>
+          <t>9월 토요특근 3회로 제한</t>
+        </is>
+      </c>
+      <c r="C39" s="146" t="n"/>
+      <c r="D39" s="146" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>9/5·12·19 (9/26은 추석연휴). 인당 24H = 9월 잔여의 25% 수준으로 관리</t>
+        </is>
+      </c>
+      <c r="F39" s="134" t="n"/>
+      <c r="G39" s="134" t="n"/>
+      <c r="H39" s="134" t="n"/>
+      <c r="I39" s="134" t="n"/>
+      <c r="J39" s="134" t="n"/>
+      <c r="K39" s="134" t="n"/>
+      <c r="L39" s="134" t="n"/>
+      <c r="M39" s="134" t="n"/>
+      <c r="N39" s="286" t="inlineStr">
+        <is>
+          <t>권장 상한</t>
+        </is>
+      </c>
+      <c r="O39" s="169" t="n"/>
+      <c r="P39" s="169" t="n"/>
+      <c r="Q39" s="169" t="n"/>
+      <c r="R39" s="169" t="n"/>
+    </row>
+    <row r="40" s="130"/>
+    <row r="41" ht="24" customHeight="1" s="130">
+      <c r="A41" s="224" t="inlineStr">
+        <is>
+          <t>※ 8월 개인 최대 실적은 108.5H(박태근·세척실)로 월 환산 주 25H 수준이다. 주 12H 한도를 전제하면 8월 실적 자체에 이미 초과 소지가 있어, 9월 '8월 수준 재현'을 그대로 약속하기 어렵다. 8월 실적의 시간외 구성(연장 / 휴일근로 / 소정 재편)을 먼저 확정해야 한다.</t>
+        </is>
+      </c>
+      <c r="B41" s="148" t="n"/>
+      <c r="C41" s="148" t="n"/>
+      <c r="D41" s="148" t="n"/>
+      <c r="E41" s="148" t="n"/>
+      <c r="F41" s="148" t="n"/>
+      <c r="G41" s="148" t="n"/>
+      <c r="H41" s="148" t="n"/>
+      <c r="I41" s="148" t="n"/>
+      <c r="J41" s="148" t="n"/>
+      <c r="K41" s="148" t="n"/>
+      <c r="L41" s="148" t="n"/>
+      <c r="M41" s="148" t="n"/>
+      <c r="N41" s="148" t="n"/>
+      <c r="O41" s="148" t="n"/>
+      <c r="P41" s="148" t="n"/>
+      <c r="Q41" s="148" t="n"/>
+      <c r="R41" s="148" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="196">
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A41:R41"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="N16:R16"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A27:R27"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E38:M38"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A38"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="N18:R18"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="N17:R17"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="N19:R19"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A34:R34"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="N9:R9"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="E39:M39"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="N36:R36"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="N20:R20"/>
+    <mergeCell ref="A35"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="N22:R22"/>
+    <mergeCell ref="N37:R37"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="N12:R12"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="A32:R32"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N14:R14"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="N23:R23"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="N35:R35"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A25:R25"/>
+    <mergeCell ref="N11:R11"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A39"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A36"/>
+    <mergeCell ref="N39:R39"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="N38:R38"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="N13:R13"/>
+    <mergeCell ref="A37"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="N15:R15"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="J17:K17"/>
+  </mergeCells>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="130" min="1" max="1"/>
+    <col width="6.5" customWidth="1" style="130" min="2" max="2"/>
+    <col width="7.5" customWidth="1" style="130" min="3" max="3"/>
+    <col width="6.5" customWidth="1" style="130" min="4" max="4"/>
+    <col width="7.5" customWidth="1" style="130" min="5" max="5"/>
+    <col width="6.5" customWidth="1" style="130" min="6" max="6"/>
+    <col width="10" customWidth="1" style="130" min="7" max="7"/>
+    <col width="6.5" customWidth="1" style="130" min="8" max="8"/>
+    <col width="7.5" customWidth="1" style="130" min="9" max="9"/>
+    <col width="6.5" customWidth="1" style="130" min="10" max="10"/>
+    <col width="7.5" customWidth="1" style="130" min="11" max="11"/>
+    <col width="6.5" customWidth="1" style="130" min="12" max="12"/>
+    <col width="10" customWidth="1" style="130" min="13" max="13"/>
+    <col width="6.5" customWidth="1" style="130" min="14" max="14"/>
+    <col width="7.5" customWidth="1" style="130" min="15" max="15"/>
+    <col width="6.5" customWidth="1" style="130" min="16" max="16"/>
+    <col width="7.5" customWidth="1" style="130" min="17" max="17"/>
+    <col width="6.5" customWidth="1" style="130" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" s="130">
+      <c r="A1" s="131" t="inlineStr">
+        <is>
+          <t>10월 예측 — '주 12시간 연장 + 토요특근 8시간' 요구 검증</t>
+        </is>
+      </c>
+      <c r="B1" s="132" t="n"/>
+      <c r="C1" s="132" t="n"/>
+      <c r="D1" s="132" t="n"/>
+      <c r="E1" s="132" t="n"/>
+      <c r="F1" s="132" t="n"/>
+      <c r="G1" s="132" t="n"/>
+      <c r="H1" s="132" t="n"/>
+      <c r="I1" s="132" t="n"/>
+      <c r="J1" s="132" t="n"/>
+      <c r="K1" s="132" t="n"/>
+      <c r="L1" s="132" t="n"/>
+      <c r="M1" s="132" t="n"/>
+      <c r="N1" s="132" t="n"/>
+      <c r="O1" s="132" t="n"/>
+      <c r="P1" s="132" t="n"/>
+      <c r="Q1" s="132" t="n"/>
+      <c r="R1" s="132" t="n"/>
+    </row>
+    <row r="2" ht="12" customHeight="1" s="130">
+      <c r="A2" s="264" t="inlineStr">
+        <is>
+          <t>신규 단위기간 10·11·12월(13.14주) · 연장 한도 156H(12H/주) · 소정근로 한도 525.7H(평균 주 40H)  |  2026.09.02</t>
+        </is>
+      </c>
+      <c r="B2" s="134" t="n"/>
+      <c r="C2" s="134" t="n"/>
+      <c r="D2" s="134" t="n"/>
+      <c r="E2" s="134" t="n"/>
+      <c r="F2" s="134" t="n"/>
+      <c r="G2" s="134" t="n"/>
+      <c r="H2" s="134" t="n"/>
+      <c r="I2" s="134" t="n"/>
+      <c r="J2" s="134" t="n"/>
+      <c r="K2" s="134" t="n"/>
+      <c r="L2" s="134" t="n"/>
+      <c r="M2" s="134" t="n"/>
+      <c r="N2" s="134" t="n"/>
+      <c r="O2" s="134" t="n"/>
+      <c r="P2" s="134" t="n"/>
+      <c r="Q2" s="134" t="n"/>
+      <c r="R2" s="134" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1" s="130">
+      <c r="A3" s="135" t="inlineStr">
+        <is>
+          <t>① 10월 근무일 구조 — 유급휴일 3일로 1·2주 평일이 2일·3일뿐</t>
+        </is>
+      </c>
+      <c r="B3" s="136" t="n"/>
+      <c r="C3" s="136" t="n"/>
+      <c r="D3" s="136" t="n"/>
+      <c r="E3" s="136" t="n"/>
+      <c r="F3" s="136" t="n"/>
+      <c r="G3" s="136" t="n"/>
+      <c r="H3" s="136" t="n"/>
+      <c r="I3" s="136" t="n"/>
+      <c r="J3" s="136" t="n"/>
+      <c r="K3" s="136" t="n"/>
+      <c r="L3" s="136" t="n"/>
+      <c r="M3" s="136" t="n"/>
+      <c r="N3" s="136" t="n"/>
+      <c r="O3" s="136" t="n"/>
+      <c r="P3" s="136" t="n"/>
+      <c r="Q3" s="136" t="n"/>
+      <c r="R3" s="136" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="130">
+      <c r="A4" s="271" t="inlineStr">
+        <is>
+          <t>주차</t>
+        </is>
+      </c>
+      <c r="B4" s="139" t="n"/>
+      <c r="C4" s="271" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D4" s="139" t="n"/>
+      <c r="E4" s="139" t="n"/>
+      <c r="F4" s="139" t="n"/>
+      <c r="G4" s="271" t="inlineStr">
+        <is>
+          <t>실근무 평일</t>
+        </is>
+      </c>
+      <c r="H4" s="139" t="n"/>
+      <c r="I4" s="271" t="inlineStr">
+        <is>
+          <t>토요일</t>
+        </is>
+      </c>
+      <c r="J4" s="139" t="n"/>
+      <c r="K4" s="271" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="L4" s="139" t="n"/>
+      <c r="M4" s="139" t="n"/>
+      <c r="N4" s="139" t="n"/>
+      <c r="O4" s="139" t="n"/>
+      <c r="P4" s="139" t="n"/>
+      <c r="Q4" s="139" t="n"/>
+      <c r="R4" s="139" t="n"/>
+    </row>
+    <row r="5" ht="12.5" customHeight="1" s="130">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>1주</t>
+        </is>
+      </c>
+      <c r="B5" s="146" t="n"/>
+      <c r="C5" s="283" t="inlineStr">
+        <is>
+          <t>10/1(목)~10/4(일)</t>
+        </is>
+      </c>
+      <c r="D5" s="134" t="n"/>
+      <c r="E5" s="134" t="n"/>
+      <c r="F5" s="134" t="n"/>
+      <c r="G5" s="274" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="134" t="n"/>
+      <c r="I5" s="287" t="inlineStr">
+        <is>
+          <t>10/3</t>
+        </is>
+      </c>
+      <c r="J5" s="134" t="n"/>
+      <c r="K5" s="288" t="inlineStr">
+        <is>
+          <t>10/3 개천절(토) — 유급휴일. 평일 2일뿐이라 잔업 최대 8H</t>
+        </is>
+      </c>
+      <c r="L5" s="169" t="n"/>
+      <c r="M5" s="169" t="n"/>
+      <c r="N5" s="169" t="n"/>
+      <c r="O5" s="169" t="n"/>
+      <c r="P5" s="169" t="n"/>
+      <c r="Q5" s="169" t="n"/>
+      <c r="R5" s="169" t="n"/>
+    </row>
+    <row r="6" ht="12.5" customHeight="1" s="130">
+      <c r="A6" s="265" t="inlineStr">
+        <is>
+          <t>2주</t>
+        </is>
+      </c>
+      <c r="B6" s="146" t="n"/>
+      <c r="C6" s="283" t="inlineStr">
+        <is>
+          <t>10/5(월)~10/11(일)</t>
+        </is>
+      </c>
+      <c r="D6" s="134" t="n"/>
+      <c r="E6" s="134" t="n"/>
+      <c r="F6" s="134" t="n"/>
+      <c r="G6" s="274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="134" t="n"/>
+      <c r="I6" s="287" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J6" s="134" t="n"/>
+      <c r="K6" s="288" t="inlineStr">
+        <is>
+          <t>10/5 대체공휴일 · 10/9 한글날 — 평일 3일</t>
+        </is>
+      </c>
+      <c r="L6" s="169" t="n"/>
+      <c r="M6" s="169" t="n"/>
+      <c r="N6" s="169" t="n"/>
+      <c r="O6" s="169" t="n"/>
+      <c r="P6" s="169" t="n"/>
+      <c r="Q6" s="169" t="n"/>
+      <c r="R6" s="169" t="n"/>
+    </row>
+    <row r="7" ht="12.5" customHeight="1" s="130">
+      <c r="A7" s="265" t="inlineStr">
+        <is>
+          <t>3주</t>
+        </is>
+      </c>
+      <c r="B7" s="146" t="n"/>
+      <c r="C7" s="283" t="inlineStr">
+        <is>
+          <t>10/12~10/18</t>
+        </is>
+      </c>
+      <c r="D7" s="134" t="n"/>
+      <c r="E7" s="134" t="n"/>
+      <c r="F7" s="134" t="n"/>
+      <c r="G7" s="289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="134" t="n"/>
+      <c r="I7" s="287" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+      <c r="J7" s="134" t="n"/>
+      <c r="K7" s="283" t="inlineStr"/>
+      <c r="L7" s="134" t="n"/>
+      <c r="M7" s="134" t="n"/>
+      <c r="N7" s="134" t="n"/>
+      <c r="O7" s="134" t="n"/>
+      <c r="P7" s="134" t="n"/>
+      <c r="Q7" s="134" t="n"/>
+      <c r="R7" s="134" t="n"/>
+    </row>
+    <row r="8" ht="12.5" customHeight="1" s="130">
+      <c r="A8" s="265" t="inlineStr">
+        <is>
+          <t>4주</t>
+        </is>
+      </c>
+      <c r="B8" s="146" t="n"/>
+      <c r="C8" s="283" t="inlineStr">
+        <is>
+          <t>10/19~10/25</t>
+        </is>
+      </c>
+      <c r="D8" s="134" t="n"/>
+      <c r="E8" s="134" t="n"/>
+      <c r="F8" s="134" t="n"/>
+      <c r="G8" s="289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="134" t="n"/>
+      <c r="I8" s="287" t="inlineStr">
+        <is>
+          <t>10/24</t>
+        </is>
+      </c>
+      <c r="J8" s="134" t="n"/>
+      <c r="K8" s="283" t="inlineStr"/>
+      <c r="L8" s="134" t="n"/>
+      <c r="M8" s="134" t="n"/>
+      <c r="N8" s="134" t="n"/>
+      <c r="O8" s="134" t="n"/>
+      <c r="P8" s="134" t="n"/>
+      <c r="Q8" s="134" t="n"/>
+      <c r="R8" s="134" t="n"/>
+    </row>
+    <row r="9" ht="12.5" customHeight="1" s="130">
+      <c r="A9" s="265" t="inlineStr">
+        <is>
+          <t>5주</t>
+        </is>
+      </c>
+      <c r="B9" s="146" t="n"/>
+      <c r="C9" s="283" t="inlineStr">
+        <is>
+          <t>10/26~10/31</t>
+        </is>
+      </c>
+      <c r="D9" s="134" t="n"/>
+      <c r="E9" s="134" t="n"/>
+      <c r="F9" s="134" t="n"/>
+      <c r="G9" s="289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="134" t="n"/>
+      <c r="I9" s="287" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+      <c r="J9" s="134" t="n"/>
+      <c r="K9" s="283" t="inlineStr"/>
+      <c r="L9" s="134" t="n"/>
+      <c r="M9" s="134" t="n"/>
+      <c r="N9" s="134" t="n"/>
+      <c r="O9" s="134" t="n"/>
+      <c r="P9" s="134" t="n"/>
+      <c r="Q9" s="134" t="n"/>
+      <c r="R9" s="134" t="n"/>
+    </row>
+    <row r="10" ht="13" customHeight="1" s="130">
+      <c r="A10" s="271" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="B10" s="139" t="n"/>
+      <c r="C10" s="272" t="inlineStr">
+        <is>
+          <t>10/1~10/31 (5개 주)</t>
+        </is>
+      </c>
+      <c r="D10" s="146" t="n"/>
+      <c r="E10" s="146" t="n"/>
+      <c r="F10" s="146" t="n"/>
+      <c r="G10" s="290" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="146" t="n"/>
+      <c r="I10" s="265" t="inlineStr">
+        <is>
+          <t>5회</t>
+        </is>
+      </c>
+      <c r="J10" s="146" t="n"/>
+      <c r="K10" s="272" t="inlineStr">
+        <is>
+          <t>평일 소정 20일 = 160H. 1일 연장 상한 4H(소정 8 + 연장 4 = 1일 12H)</t>
+        </is>
+      </c>
+      <c r="L10" s="146" t="n"/>
+      <c r="M10" s="146" t="n"/>
+      <c r="N10" s="146" t="n"/>
+      <c r="O10" s="146" t="n"/>
+      <c r="P10" s="146" t="n"/>
+      <c r="Q10" s="146" t="n"/>
+      <c r="R10" s="146" t="n"/>
+    </row>
+    <row r="11" s="130"/>
+    <row r="12" ht="14" customHeight="1" s="130">
+      <c r="A12" s="218" t="inlineStr">
+        <is>
+          <t>② 해석별 검증 — 근로기준법 §53의 주 12H 연장 한도에는 휴일근로(토요특근)가 포함된다</t>
+        </is>
+      </c>
+      <c r="B12" s="219" t="n"/>
+      <c r="C12" s="219" t="n"/>
+      <c r="D12" s="219" t="n"/>
+      <c r="E12" s="219" t="n"/>
+      <c r="F12" s="219" t="n"/>
+      <c r="G12" s="219" t="n"/>
+      <c r="H12" s="219" t="n"/>
+      <c r="I12" s="219" t="n"/>
+      <c r="J12" s="219" t="n"/>
+      <c r="K12" s="219" t="n"/>
+      <c r="L12" s="219" t="n"/>
+      <c r="M12" s="219" t="n"/>
+      <c r="N12" s="219" t="n"/>
+      <c r="O12" s="219" t="n"/>
+      <c r="P12" s="219" t="n"/>
+      <c r="Q12" s="219" t="n"/>
+      <c r="R12" s="219" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="130">
+      <c r="A13" s="282" t="inlineStr"/>
+      <c r="B13" s="271" t="inlineStr">
+        <is>
+          <t>안</t>
+        </is>
+      </c>
+      <c r="C13" s="139" t="n"/>
+      <c r="D13" s="139" t="n"/>
+      <c r="E13" s="271" t="inlineStr">
+        <is>
+          <t>편성 방식</t>
+        </is>
+      </c>
+      <c r="F13" s="139" t="n"/>
+      <c r="G13" s="139" t="n"/>
+      <c r="H13" s="139" t="n"/>
+      <c r="I13" s="271" t="inlineStr">
+        <is>
+          <t>연장H</t>
+        </is>
+      </c>
+      <c r="J13" s="271" t="inlineStr">
+        <is>
+          <t>소정편입</t>
+        </is>
+      </c>
+      <c r="K13" s="271" t="inlineStr">
+        <is>
+          <t>인당 총</t>
+        </is>
+      </c>
+      <c r="L13" s="271" t="inlineStr">
+        <is>
+          <t>전사 총(H)</t>
+        </is>
+      </c>
+      <c r="M13" s="139" t="n"/>
+      <c r="N13" s="271" t="inlineStr">
+        <is>
+          <t>156H 소진</t>
+        </is>
+      </c>
+      <c r="O13" s="271" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="P13" s="139" t="n"/>
+      <c r="Q13" s="139" t="n"/>
+      <c r="R13" s="139" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1" s="130">
+      <c r="A14" s="291" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B14" s="272" t="inlineStr">
+        <is>
+          <t>AP 요구 그대로</t>
+        </is>
+      </c>
+      <c r="C14" s="146" t="n"/>
+      <c r="D14" s="146" t="n"/>
+      <c r="E14" s="292" t="inlineStr">
+        <is>
+          <t>평일 연장 12H/주 + 토특근 8H/주 = 주 20H</t>
+        </is>
+      </c>
+      <c r="F14" s="134" t="n"/>
+      <c r="G14" s="134" t="n"/>
+      <c r="H14" s="134" t="n"/>
+      <c r="I14" s="289" t="n">
+        <v>96</v>
+      </c>
+      <c r="J14" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="293" t="n">
+        <v>256</v>
+      </c>
+      <c r="L14" s="276" t="n">
+        <v>61184</v>
+      </c>
+      <c r="M14" s="134" t="n"/>
+      <c r="N14" s="275" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="O14" s="294" t="inlineStr">
+        <is>
+          <t>위법 — 주 20H는 §53 한도를 8H 초과. 어떤 절차로도 이 형태로는 불가</t>
+        </is>
+      </c>
+      <c r="P14" s="148" t="n"/>
+      <c r="Q14" s="148" t="n"/>
+      <c r="R14" s="148" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" s="130">
+      <c r="A15" s="271" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B15" s="272" t="inlineStr">
+        <is>
+          <t>특근을 12H 안에 포함</t>
+        </is>
+      </c>
+      <c r="C15" s="146" t="n"/>
+      <c r="D15" s="146" t="n"/>
+      <c r="E15" s="292" t="inlineStr">
+        <is>
+          <t>토특근 8H + 평일 연장 4H = 주 12H (5주)</t>
+        </is>
+      </c>
+      <c r="F15" s="134" t="n"/>
+      <c r="G15" s="134" t="n"/>
+      <c r="H15" s="134" t="n"/>
+      <c r="I15" s="289" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="295" t="n">
+        <v>220</v>
+      </c>
+      <c r="L15" s="276" t="n">
+        <v>52580</v>
+      </c>
+      <c r="M15" s="134" t="n"/>
+      <c r="N15" s="275" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O15" s="296" t="inlineStr">
+        <is>
+          <t>적법 · 즉시 가능 — 절차 없음. 11·12월도 주 12H 그대로 유지 가능</t>
+        </is>
+      </c>
+      <c r="P15" s="171" t="n"/>
+      <c r="Q15" s="171" t="n"/>
+      <c r="R15" s="171" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" s="130">
+      <c r="A16" s="271" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B16" s="272" t="inlineStr">
+        <is>
+          <t>토 2회 소정근로일 편입</t>
+        </is>
+      </c>
+      <c r="C16" s="146" t="n"/>
+      <c r="D16" s="146" t="n"/>
+      <c r="E16" s="292" t="inlineStr">
+        <is>
+          <t>토 2회 소정화 + 연장 12H/주 = 주 최대 60H</t>
+        </is>
+      </c>
+      <c r="F16" s="134" t="n"/>
+      <c r="G16" s="134" t="n"/>
+      <c r="H16" s="134" t="n"/>
+      <c r="I16" s="289" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="273" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" s="297" t="n">
+        <v>236</v>
+      </c>
+      <c r="L16" s="276" t="n">
+        <v>56404</v>
+      </c>
+      <c r="M16" s="134" t="n"/>
+      <c r="N16" s="275" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O16" s="298" t="inlineStr">
+        <is>
+          <t>적법 · 서면합의 필요 — 소정 여유 21.7H 범위 내. 11·12월 영향 없음</t>
+        </is>
+      </c>
+      <c r="P16" s="169" t="n"/>
+      <c r="Q16" s="169" t="n"/>
+      <c r="R16" s="169" t="n"/>
+    </row>
+    <row r="17" ht="14" customHeight="1" s="130">
+      <c r="A17" s="271" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B17" s="272" t="inlineStr">
+        <is>
+          <t>토 5회 전부 소정화</t>
+        </is>
+      </c>
+      <c r="C17" s="146" t="n"/>
+      <c r="D17" s="146" t="n"/>
+      <c r="E17" s="292" t="inlineStr">
+        <is>
+          <t>토 5회 소정화 + 평일 연장 12H/주(1·2주는 8·12H)</t>
+        </is>
+      </c>
+      <c r="F17" s="134" t="n"/>
+      <c r="G17" s="134" t="n"/>
+      <c r="H17" s="134" t="n"/>
+      <c r="I17" s="289" t="n">
+        <v>56</v>
+      </c>
+      <c r="J17" s="273" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="297" t="n">
+        <v>256</v>
+      </c>
+      <c r="L17" s="276" t="n">
+        <v>61184</v>
+      </c>
+      <c r="M17" s="134" t="n"/>
+      <c r="N17" s="275" t="n">
+        <v>0.358974358974359</v>
+      </c>
+      <c r="O17" s="298" t="inlineStr">
+        <is>
+          <t>적법 · ②와 총량 동일 — 단 소정 18.3H 초과분만큼 11·12월 평일 2~3일을 비근무일로 지정해야 함</t>
+        </is>
+      </c>
+      <c r="P17" s="169" t="n"/>
+      <c r="Q17" s="169" t="n"/>
+      <c r="R17" s="169" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="130">
+      <c r="A18" s="261" t="inlineStr">
+        <is>
+          <t>※ '인당 총' = 10월 한 달 총 근무시간(평일 소정 160H 포함). 요구 물량 기준선은 ②의 256H다. ①은 36H(14%) 부족, ③은 20H(8%) 부족, ④만 256H로 요구를 정확히 충족한다. 연장H가 156H 한도를 압박하지 않는 이유는 주 12H 한도가 이미 매주를 묶고 있기 때문이며, 따라서 10월의 제약은 156H가 아니라 '주 12H'와 '10월 유급휴일 3일'이다.</t>
+        </is>
+      </c>
+      <c r="B18" s="134" t="n"/>
+      <c r="C18" s="134" t="n"/>
+      <c r="D18" s="134" t="n"/>
+      <c r="E18" s="134" t="n"/>
+      <c r="F18" s="134" t="n"/>
+      <c r="G18" s="134" t="n"/>
+      <c r="H18" s="134" t="n"/>
+      <c r="I18" s="134" t="n"/>
+      <c r="J18" s="134" t="n"/>
+      <c r="K18" s="134" t="n"/>
+      <c r="L18" s="134" t="n"/>
+      <c r="M18" s="134" t="n"/>
+      <c r="N18" s="134" t="n"/>
+      <c r="O18" s="134" t="n"/>
+      <c r="P18" s="134" t="n"/>
+      <c r="Q18" s="134" t="n"/>
+      <c r="R18" s="134" t="n"/>
+    </row>
+    <row r="19" s="130"/>
+    <row r="20" ht="14" customHeight="1" s="130">
+      <c r="A20" s="135" t="inlineStr">
+        <is>
+          <t>③ ④안 성립 조건 — 소정근로 총량 검증</t>
+        </is>
+      </c>
+      <c r="B20" s="136" t="n"/>
+      <c r="C20" s="136" t="n"/>
+      <c r="D20" s="136" t="n"/>
+      <c r="E20" s="136" t="n"/>
+      <c r="F20" s="136" t="n"/>
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="136" t="n"/>
+      <c r="I20" s="136" t="n"/>
+      <c r="J20" s="136" t="n"/>
+      <c r="K20" s="136" t="n"/>
+      <c r="L20" s="136" t="n"/>
+      <c r="M20" s="136" t="n"/>
+      <c r="N20" s="136" t="n"/>
+      <c r="O20" s="136" t="n"/>
+      <c r="P20" s="136" t="n"/>
+      <c r="Q20" s="136" t="n"/>
+      <c r="R20" s="136" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="130">
+      <c r="A21" s="271" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B21" s="139" t="n"/>
+      <c r="C21" s="139" t="n"/>
+      <c r="D21" s="139" t="n"/>
+      <c r="E21" s="271" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F21" s="139" t="n"/>
+      <c r="G21" s="139" t="n"/>
+      <c r="H21" s="271" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="I21" s="139" t="n"/>
+      <c r="J21" s="139" t="n"/>
+      <c r="K21" s="139" t="n"/>
+      <c r="L21" s="139" t="n"/>
+      <c r="M21" s="139" t="n"/>
+      <c r="N21" s="139" t="n"/>
+      <c r="O21" s="139" t="n"/>
+      <c r="P21" s="139" t="n"/>
+      <c r="Q21" s="139" t="n"/>
+      <c r="R21" s="139" t="n"/>
+    </row>
+    <row r="22" ht="12.5" customHeight="1" s="130">
+      <c r="A22" s="272" t="inlineStr">
+        <is>
+          <t>단위기간 소정 한도</t>
+        </is>
+      </c>
+      <c r="B22" s="146" t="n"/>
+      <c r="C22" s="146" t="n"/>
+      <c r="D22" s="146" t="n"/>
+      <c r="E22" s="265" t="inlineStr">
+        <is>
+          <t>525.7H</t>
+        </is>
+      </c>
+      <c r="F22" s="146" t="n"/>
+      <c r="G22" s="146" t="n"/>
+      <c r="H22" s="283" t="inlineStr">
+        <is>
+          <t>주 40H × 13.14주 (10/1~12/31, 92일)</t>
+        </is>
+      </c>
+      <c r="I22" s="134" t="n"/>
+      <c r="J22" s="134" t="n"/>
+      <c r="K22" s="134" t="n"/>
+      <c r="L22" s="134" t="n"/>
+      <c r="M22" s="134" t="n"/>
+      <c r="N22" s="134" t="n"/>
+      <c r="O22" s="134" t="n"/>
+      <c r="P22" s="134" t="n"/>
+      <c r="Q22" s="134" t="n"/>
+      <c r="R22" s="134" t="n"/>
+    </row>
+    <row r="23" ht="12.5" customHeight="1" s="130">
+      <c r="A23" s="272" t="inlineStr">
+        <is>
+          <t>평일 소정 소요</t>
+        </is>
+      </c>
+      <c r="B23" s="146" t="n"/>
+      <c r="C23" s="146" t="n"/>
+      <c r="D23" s="146" t="n"/>
+      <c r="E23" s="265" t="inlineStr">
+        <is>
+          <t>504H</t>
+        </is>
+      </c>
+      <c r="F23" s="146" t="n"/>
+      <c r="G23" s="146" t="n"/>
+      <c r="H23" s="283" t="inlineStr">
+        <is>
+          <t>10월 20일(160H) + 11월 21일(168H) + 12월 22일(176H, 12/25 제외)</t>
+        </is>
+      </c>
+      <c r="I23" s="134" t="n"/>
+      <c r="J23" s="134" t="n"/>
+      <c r="K23" s="134" t="n"/>
+      <c r="L23" s="134" t="n"/>
+      <c r="M23" s="134" t="n"/>
+      <c r="N23" s="134" t="n"/>
+      <c r="O23" s="134" t="n"/>
+      <c r="P23" s="134" t="n"/>
+      <c r="Q23" s="134" t="n"/>
+      <c r="R23" s="134" t="n"/>
+    </row>
+    <row r="24" ht="12.5" customHeight="1" s="130">
+      <c r="A24" s="272" t="inlineStr">
+        <is>
+          <t>소정 여유</t>
+        </is>
+      </c>
+      <c r="B24" s="146" t="n"/>
+      <c r="C24" s="146" t="n"/>
+      <c r="D24" s="146" t="n"/>
+      <c r="E24" s="284" t="inlineStr">
+        <is>
+          <t>21.7H</t>
+        </is>
+      </c>
+      <c r="F24" s="171" t="n"/>
+      <c r="G24" s="171" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>토요일 2회분(16H)까지는 무조건 편입 가능 → ③안</t>
+        </is>
+      </c>
+      <c r="I24" s="134" t="n"/>
+      <c r="J24" s="134" t="n"/>
+      <c r="K24" s="134" t="n"/>
+      <c r="L24" s="134" t="n"/>
+      <c r="M24" s="134" t="n"/>
+      <c r="N24" s="134" t="n"/>
+      <c r="O24" s="134" t="n"/>
+      <c r="P24" s="134" t="n"/>
+      <c r="Q24" s="134" t="n"/>
+      <c r="R24" s="134" t="n"/>
+    </row>
+    <row r="25" ht="12.5" customHeight="1" s="130">
+      <c r="A25" s="272" t="inlineStr">
+        <is>
+          <t>④안 소정 초과</t>
+        </is>
+      </c>
+      <c r="B25" s="146" t="n"/>
+      <c r="C25" s="146" t="n"/>
+      <c r="D25" s="146" t="n"/>
+      <c r="E25" s="286" t="inlineStr">
+        <is>
+          <t>18.3H</t>
+        </is>
+      </c>
+      <c r="F25" s="169" t="n"/>
+      <c r="G25" s="169" t="n"/>
+      <c r="H25" s="283" t="inlineStr">
+        <is>
+          <t>토 5회 편입 시 544H로 한도 초과 → 11·12월 평일 2~3일을 비근무일로 지정해 상쇄</t>
+        </is>
+      </c>
+      <c r="I25" s="134" t="n"/>
+      <c r="J25" s="134" t="n"/>
+      <c r="K25" s="134" t="n"/>
+      <c r="L25" s="134" t="n"/>
+      <c r="M25" s="134" t="n"/>
+      <c r="N25" s="134" t="n"/>
+      <c r="O25" s="134" t="n"/>
+      <c r="P25" s="134" t="n"/>
+      <c r="Q25" s="134" t="n"/>
+      <c r="R25" s="134" t="n"/>
+    </row>
+    <row r="26" ht="12.5" customHeight="1" s="130">
+      <c r="A26" s="272" t="inlineStr">
+        <is>
+          <t>주별 상한</t>
         </is>
       </c>
       <c r="B26" s="146" t="n"/>
       <c r="C26" s="146" t="n"/>
       <c r="D26" s="146" t="n"/>
-      <c r="E26" s="222" t="inlineStr">
-        <is>
-          <t>4명</t>
-        </is>
-      </c>
-      <c r="F26" s="134" t="n"/>
-      <c r="G26" s="134" t="n"/>
-      <c r="H26" s="208" t="inlineStr">
-        <is>
-          <t>김영두·박태근·이세호·문석. 10월에는 리셋되어 전원 편성 가능</t>
+      <c r="E26" s="284" t="inlineStr">
+        <is>
+          <t>60H ≤ 64H</t>
+        </is>
+      </c>
+      <c r="F26" s="171" t="n"/>
+      <c r="G26" s="171" t="n"/>
+      <c r="H26" s="283" t="inlineStr">
+        <is>
+          <t>소정 48H(평일 40 + 토 8) + 연장 12H. 탄력근로 주 최대 64H 이내</t>
         </is>
       </c>
       <c r="I26" s="134" t="n"/>
@@ -4789,25 +6718,25 @@
       <c r="Q26" s="134" t="n"/>
       <c r="R26" s="134" t="n"/>
     </row>
-    <row r="27" ht="13" customHeight="1" s="130">
-      <c r="A27" s="225" t="inlineStr">
-        <is>
-          <t>10월 권장(B안) 인당</t>
+    <row r="27" ht="12.5" customHeight="1" s="130">
+      <c r="A27" s="272" t="inlineStr">
+        <is>
+          <t>1일 상한</t>
         </is>
       </c>
       <c r="B27" s="146" t="n"/>
       <c r="C27" s="146" t="n"/>
       <c r="D27" s="146" t="n"/>
-      <c r="E27" s="222" t="inlineStr">
-        <is>
-          <t>64H</t>
-        </is>
-      </c>
-      <c r="F27" s="134" t="n"/>
-      <c r="G27" s="134" t="n"/>
-      <c r="H27" s="208" t="inlineStr">
-        <is>
-          <t>전사 15,296H. 9월 잔여(23,032H)와 합치면 9~10월 2개월 확보량 38,328H</t>
+      <c r="E27" s="284" t="inlineStr">
+        <is>
+          <t>10.4H ≤ 12H</t>
+        </is>
+      </c>
+      <c r="F27" s="171" t="n"/>
+      <c r="G27" s="171" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>평일 소정 8H + 연장 2.4H</t>
         </is>
       </c>
       <c r="I27" s="134" t="n"/>
@@ -4821,25 +6750,25 @@
       <c r="Q27" s="134" t="n"/>
       <c r="R27" s="134" t="n"/>
     </row>
-    <row r="28" ht="13" customHeight="1" s="130">
-      <c r="A28" s="225" t="inlineStr">
-        <is>
-          <t>11·12월 여유</t>
+    <row r="28" ht="12.5" customHeight="1" s="130">
+      <c r="A28" s="272" t="inlineStr">
+        <is>
+          <t>선행 절차</t>
         </is>
       </c>
       <c r="B28" s="146" t="n"/>
       <c r="C28" s="146" t="n"/>
       <c r="D28" s="146" t="n"/>
-      <c r="E28" s="222" t="inlineStr">
-        <is>
-          <t>92H</t>
-        </is>
-      </c>
-      <c r="F28" s="134" t="n"/>
-      <c r="G28" s="134" t="n"/>
-      <c r="H28" s="208" t="inlineStr">
-        <is>
-          <t>B안 기준. 연말 물량 대응 여지를 남기는 수준</t>
+      <c r="E28" s="285" t="inlineStr">
+        <is>
+          <t>9월 중</t>
+        </is>
+      </c>
+      <c r="F28" s="148" t="n"/>
+      <c r="G28" s="148" t="n"/>
+      <c r="H28" s="283" t="inlineStr">
+        <is>
+          <t>10·11·12월 단위기간은 10/1 전에 근로자대표 서면합의 및 근무표 사전 확정 필요(§51②)</t>
         </is>
       </c>
       <c r="I28" s="134" t="n"/>
@@ -4853,34 +6782,35 @@
       <c r="Q28" s="134" t="n"/>
       <c r="R28" s="134" t="n"/>
     </row>
+    <row r="29" s="130"/>
     <row r="30" ht="14" customHeight="1" s="130">
-      <c r="A30" s="135" t="inlineStr">
-        <is>
-          <t>⑤ 10월 편성 시 유의</t>
-        </is>
-      </c>
-      <c r="B30" s="136" t="n"/>
-      <c r="C30" s="136" t="n"/>
-      <c r="D30" s="136" t="n"/>
-      <c r="E30" s="136" t="n"/>
-      <c r="F30" s="136" t="n"/>
-      <c r="G30" s="136" t="n"/>
-      <c r="H30" s="136" t="n"/>
-      <c r="I30" s="136" t="n"/>
-      <c r="J30" s="136" t="n"/>
-      <c r="K30" s="136" t="n"/>
-      <c r="L30" s="136" t="n"/>
-      <c r="M30" s="136" t="n"/>
-      <c r="N30" s="136" t="n"/>
-      <c r="O30" s="136" t="n"/>
-      <c r="P30" s="136" t="n"/>
-      <c r="Q30" s="136" t="n"/>
-      <c r="R30" s="136" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="130">
+      <c r="A30" s="263" t="inlineStr">
+        <is>
+          <t>④ 회신안</t>
+        </is>
+      </c>
+      <c r="B30" s="132" t="n"/>
+      <c r="C30" s="132" t="n"/>
+      <c r="D30" s="132" t="n"/>
+      <c r="E30" s="132" t="n"/>
+      <c r="F30" s="132" t="n"/>
+      <c r="G30" s="132" t="n"/>
+      <c r="H30" s="132" t="n"/>
+      <c r="I30" s="132" t="n"/>
+      <c r="J30" s="132" t="n"/>
+      <c r="K30" s="132" t="n"/>
+      <c r="L30" s="132" t="n"/>
+      <c r="M30" s="132" t="n"/>
+      <c r="N30" s="132" t="n"/>
+      <c r="O30" s="132" t="n"/>
+      <c r="P30" s="132" t="n"/>
+      <c r="Q30" s="132" t="n"/>
+      <c r="R30" s="132" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="130">
       <c r="A31" s="226" t="inlineStr">
         <is>
-          <t>10월 특근일 3곳이 유급휴일 — 10/3(개천절·토) · 10/5(대체공휴일·월) · 10/9(한글날·금). 휴일근로 가산(8H 이내 50% · 초과 100%)이 붙고 여성 근로자는 휴일근로에도 개별 동의가 필요하다.</t>
+          <t>AP 요구를 문자 그대로(평일 연장 12H + 토특근 8H = 주 20H) 편성하는 것은 근로기준법 §53 위반이다. 휴일근로가 주 12H 연장 한도에 포함되므로, 특근을 하는 주의 평일 잔업은 4H가 상한이다.</t>
         </is>
       </c>
       <c r="B31" s="134" t="n"/>
@@ -4901,10 +6831,10 @@
       <c r="Q31" s="134" t="n"/>
       <c r="R31" s="134" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1" s="130">
+    <row r="32" ht="18" customHeight="1" s="130">
       <c r="A32" s="226" t="inlineStr">
         <is>
-          <t>추석 연휴(9/24~26) 직후 10월 1·2주까지 연속 특근을 얹으면 3주 연속 무휴가 된다. 안전·품질 리스크 상승.</t>
+          <t>같은 총량(인당 256H)을 적법하게 확보하는 방법은 ④안뿐이다. 토요일 5회를 3개월 탄력근로의 소정근로일로 편입하면 특근분이 연장 한도에서 빠져 평일 잔업 12H를 온전히 쓸 수 있다. 대가는 11·12월 평일 2~3일을 비근무일로 돌리는 것이며(임금 손실 없음), 10/1 이전 근로자대표 서면합의가 전제다.</t>
         </is>
       </c>
       <c r="B32" s="134" t="n"/>
@@ -4925,10 +6855,10 @@
       <c r="Q32" s="134" t="n"/>
       <c r="R32" s="134" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1" s="130">
+    <row r="33" ht="18" customHeight="1" s="130">
       <c r="A33" s="226" t="inlineStr">
         <is>
-          <t>야간 편성은 별도 조를 8H 소정근로로 짜면 연장이 발생하지 않아 156H 한도와 무관하다. 제약은 가산수당 50% · 여성 야간근로 동의 · 야간작업 특수건강진단이다.</t>
+          <t>절차 없이 즉시 가능한 것은 ①안(인당 220H)으로, 요구 대비 14% 부족하다. ③안(236H)은 8% 부족하되 11·12월에 영향을 주지 않는다. 어느 안을 택할지는 10~12월 확정 오더를 받아야 결정할 수 있다.</t>
         </is>
       </c>
       <c r="B33" s="134" t="n"/>
@@ -4949,10 +6879,10 @@
       <c r="Q33" s="134" t="n"/>
       <c r="R33" s="134" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1" s="130">
+    <row r="34" ht="18" customHeight="1" s="130">
       <c r="A34" s="226" t="inlineStr">
         <is>
-          <t>본 예측은 근로시간 공급 측면만 산출한 값이다. 10월 오더 확정 후 소요 공수와 대조해 시나리오를 확정해야 한다.</t>
+          <t>10/3·10/5·10/9는 유급휴일이다. 연장으로 처리하는 특근에는 휴일근로 가산(8H 이내 50% · 초과 100%)이 붙고 여성 근로자는 개별 동의가 필요하다. 소정근로일로 편입하면 가산은 없어지지만 근로자 동의가 더 무겁다.</t>
         </is>
       </c>
       <c r="B34" s="134" t="n"/>
@@ -4973,103 +6903,180 @@
       <c r="Q34" s="134" t="n"/>
       <c r="R34" s="134" t="n"/>
     </row>
+    <row r="35" ht="18" customHeight="1" s="130">
+      <c r="A35" s="226" t="inlineStr">
+        <is>
+          <t>'10월 1·2주 연속 특근'은 MES 확보 1안(10/3 잠금)·2안(10/10 잠금)과 양립 불가하며 3안(9/23)만 가능하다. 추석(9/24~26) 직후 10월 1·2주까지 연속 특근 시 3주 연속 무휴가 되는 점도 함께 확정 요청한다.</t>
+        </is>
+      </c>
+      <c r="B35" s="134" t="n"/>
+      <c r="C35" s="134" t="n"/>
+      <c r="D35" s="134" t="n"/>
+      <c r="E35" s="134" t="n"/>
+      <c r="F35" s="134" t="n"/>
+      <c r="G35" s="134" t="n"/>
+      <c r="H35" s="134" t="n"/>
+      <c r="I35" s="134" t="n"/>
+      <c r="J35" s="134" t="n"/>
+      <c r="K35" s="134" t="n"/>
+      <c r="L35" s="134" t="n"/>
+      <c r="M35" s="134" t="n"/>
+      <c r="N35" s="134" t="n"/>
+      <c r="O35" s="134" t="n"/>
+      <c r="P35" s="134" t="n"/>
+      <c r="Q35" s="134" t="n"/>
+      <c r="R35" s="134" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="130">
+      <c r="A36" s="226" t="inlineStr">
+        <is>
+          <t>본 예측은 근로시간 공급만 계산한 값이다. 세척실·주임·HnB의 인원 부족은 근로시간으로 해소되지 않으므로 충원 규모 합의가 병행되어야 한다.</t>
+        </is>
+      </c>
+      <c r="B36" s="134" t="n"/>
+      <c r="C36" s="134" t="n"/>
+      <c r="D36" s="134" t="n"/>
+      <c r="E36" s="134" t="n"/>
+      <c r="F36" s="134" t="n"/>
+      <c r="G36" s="134" t="n"/>
+      <c r="H36" s="134" t="n"/>
+      <c r="I36" s="134" t="n"/>
+      <c r="J36" s="134" t="n"/>
+      <c r="K36" s="134" t="n"/>
+      <c r="L36" s="134" t="n"/>
+      <c r="M36" s="134" t="n"/>
+      <c r="N36" s="134" t="n"/>
+      <c r="O36" s="134" t="n"/>
+      <c r="P36" s="134" t="n"/>
+      <c r="Q36" s="134" t="n"/>
+      <c r="R36" s="134" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="Q13:R13"/>
+  <mergeCells count="117">
+    <mergeCell ref="L17:M17"/>
     <mergeCell ref="H26:R26"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="O13:R13"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A33:R33"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K16"/>
+    <mergeCell ref="C6:F6"/>
     <mergeCell ref="E26:G26"/>
+    <mergeCell ref="J14"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="A35:R35"/>
+    <mergeCell ref="J13"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="J15"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="A30:R30"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="O16:R16"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="J16"/>
+    <mergeCell ref="I14"/>
+    <mergeCell ref="K14"/>
     <mergeCell ref="E28:G28"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A13"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="J17"/>
     <mergeCell ref="H25:R25"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="H28:R28"/>
     <mergeCell ref="A34:R34"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="J5:L5"/>
     <mergeCell ref="E24:G24"/>
+    <mergeCell ref="N14"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="A36:R36"/>
     <mergeCell ref="A1:R1"/>
+    <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="A21:R21"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="H23:R23"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="I13"/>
+    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="K13"/>
     <mergeCell ref="A32:R32"/>
-    <mergeCell ref="A14:R14"/>
-    <mergeCell ref="A23:R23"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="M5:R5"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="A6:R6"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I15"/>
+    <mergeCell ref="K15"/>
+    <mergeCell ref="N16"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="I16"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H22:R22"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="N13"/>
+    <mergeCell ref="I17"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A17"/>
+    <mergeCell ref="K17"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="K5:R5"/>
+    <mergeCell ref="N15"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="L13:M13"/>
     <mergeCell ref="A3:R3"/>
     <mergeCell ref="E27:G27"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="H21:R21"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="E25:G25"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="A20:R20"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A31:R31"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="H27:R27"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="N17"/>
     <mergeCell ref="H24:R24"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="A14"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -8823,7 +10830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="8" tint="0.5999938962981048"/>
